--- a/monthly.xlsx
+++ b/monthly.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K175"/>
+  <dimension ref="A1:L175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,40 +476,48 @@
           <t>Tencent</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SP500</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B2" t="n">
-        <v>20.63321495056152</v>
+        <v>17.27968597412109</v>
       </c>
       <c r="C2" t="n">
-        <v>29.19000053405762</v>
+        <v>23.01616859436035</v>
       </c>
       <c r="D2" t="n">
-        <v>14.53603553771973</v>
+        <v>14.39901924133301</v>
       </c>
       <c r="E2" t="n">
         <v>10.64550018310547</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3107500076293945</v>
+        <v>0.2842410802841187</v>
       </c>
       <c r="G2" t="n">
-        <v>29.60000038146973</v>
+        <v>29.31919097900391</v>
       </c>
       <c r="H2" t="n">
-        <v>24220</v>
+        <v>18010.4453125</v>
       </c>
       <c r="I2" t="n">
         <v>1.966667056083679</v>
       </c>
       <c r="J2" t="n">
-        <v>25.84000015258789</v>
+        <v>18.13143730163574</v>
       </c>
       <c r="K2" t="n">
-        <v>39.34483337402344</v>
+        <v>36.81422805786133</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1310.329956054688</v>
       </c>
     </row>
     <row r="3">
@@ -517,34 +525,37 @@
         <v>41061</v>
       </c>
       <c r="B3" t="n">
-        <v>20.85714340209961</v>
+        <v>17.46721839904785</v>
       </c>
       <c r="C3" t="n">
-        <v>30.59000015258789</v>
+        <v>24.12006759643555</v>
       </c>
       <c r="D3" t="n">
-        <v>14.51626586914062</v>
+        <v>14.37943363189697</v>
       </c>
       <c r="E3" t="n">
         <v>11.41749954223633</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3454999923706055</v>
+        <v>0.3160267770290375</v>
       </c>
       <c r="G3" t="n">
-        <v>31.10000038146973</v>
+        <v>30.80495834350586</v>
       </c>
       <c r="H3" t="n">
-        <v>24020</v>
+        <v>17869.375</v>
       </c>
       <c r="I3" t="n">
         <v>2.085999965667725</v>
       </c>
       <c r="J3" t="n">
-        <v>26.64999961853027</v>
+        <v>18.69979095458984</v>
       </c>
       <c r="K3" t="n">
-        <v>41.66791152954102</v>
+        <v>38.98789215087891</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1362.160034179688</v>
       </c>
     </row>
     <row r="4">
@@ -552,34 +563,37 @@
         <v>41091</v>
       </c>
       <c r="B4" t="n">
-        <v>21.81285667419434</v>
+        <v>18.26760482788086</v>
       </c>
       <c r="C4" t="n">
-        <v>29.46999931335449</v>
+        <v>23.23696136474609</v>
       </c>
       <c r="D4" t="n">
-        <v>15.84008979797363</v>
+        <v>15.69078254699707</v>
       </c>
       <c r="E4" t="n">
         <v>11.66499996185303</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3384999930858612</v>
+        <v>0.3096238970756531</v>
       </c>
       <c r="G4" t="n">
-        <v>21.70999908447266</v>
+        <v>21.50404167175293</v>
       </c>
       <c r="H4" t="n">
-        <v>26180</v>
+        <v>19476.28125</v>
       </c>
       <c r="I4" t="n">
         <v>1.827999949455261</v>
       </c>
       <c r="J4" t="n">
-        <v>25.70000076293945</v>
+        <v>18.03320121765137</v>
       </c>
       <c r="K4" t="n">
-        <v>42.73726272583008</v>
+        <v>39.98846435546875</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1379.319946289062</v>
       </c>
     </row>
     <row r="5">
@@ -587,34 +601,37 @@
         <v>41122</v>
       </c>
       <c r="B5" t="n">
-        <v>23.75857162475586</v>
+        <v>19.98251342773438</v>
       </c>
       <c r="C5" t="n">
-        <v>30.81999969482422</v>
+        <v>24.4624137878418</v>
       </c>
       <c r="D5" t="n">
-        <v>17.14439392089844</v>
+        <v>16.9827880859375</v>
       </c>
       <c r="E5" t="n">
         <v>12.41349983215332</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3507499992847443</v>
+        <v>0.3208290338516235</v>
       </c>
       <c r="G5" t="n">
-        <v>18.05999946594238</v>
+        <v>17.8886661529541</v>
       </c>
       <c r="H5" t="n">
-        <v>24660</v>
+        <v>18345.501953125</v>
       </c>
       <c r="I5" t="n">
         <v>1.901332974433899</v>
       </c>
       <c r="J5" t="n">
-        <v>24.82999992370605</v>
+        <v>17.57535934448242</v>
       </c>
       <c r="K5" t="n">
-        <v>43.69599533081055</v>
+        <v>40.88553237915039</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1406.579956054688</v>
       </c>
     </row>
     <row r="6">
@@ -622,34 +639,37 @@
         <v>41153</v>
       </c>
       <c r="B6" t="n">
-        <v>23.82500076293945</v>
+        <v>20.03837966918945</v>
       </c>
       <c r="C6" t="n">
-        <v>29.76000022888184</v>
+        <v>23.62107276916504</v>
       </c>
       <c r="D6" t="n">
-        <v>18.88138008117676</v>
+        <v>18.70340538024902</v>
       </c>
       <c r="E6" t="n">
         <v>12.71599960327148</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3334999978542328</v>
+        <v>0.3050504326820374</v>
       </c>
       <c r="G6" t="n">
-        <v>21.65999984741211</v>
+        <v>21.45451164245605</v>
       </c>
       <c r="H6" t="n">
-        <v>26920</v>
+        <v>20026.787109375</v>
       </c>
       <c r="I6" t="n">
         <v>1.952000021934509</v>
       </c>
       <c r="J6" t="n">
-        <v>22.65999984741211</v>
+        <v>16.03937339782715</v>
       </c>
       <c r="K6" t="n">
-        <v>48.71089553833008</v>
+        <v>45.57787322998047</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1440.670043945312</v>
       </c>
     </row>
     <row r="7">
@@ -657,34 +677,37 @@
         <v>41183</v>
       </c>
       <c r="B7" t="n">
-        <v>21.26142883300781</v>
+        <v>17.88224601745605</v>
       </c>
       <c r="C7" t="n">
-        <v>28.54000091552734</v>
+        <v>22.65273666381836</v>
       </c>
       <c r="D7" t="n">
-        <v>17.0245246887207</v>
+        <v>16.86404991149902</v>
       </c>
       <c r="E7" t="n">
         <v>11.64449977874756</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2994999885559082</v>
+        <v>0.2739509046077728</v>
       </c>
       <c r="G7" t="n">
-        <v>21.11000061035156</v>
+        <v>20.90973281860352</v>
       </c>
       <c r="H7" t="n">
-        <v>26200</v>
+        <v>19491.1640625</v>
       </c>
       <c r="I7" t="n">
         <v>1.875332951545715</v>
       </c>
       <c r="J7" t="n">
-        <v>21.6299991607666</v>
+        <v>15.31031131744385</v>
       </c>
       <c r="K7" t="n">
-        <v>50.51773452758789</v>
+        <v>47.26849746704102</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1412.160034179688</v>
       </c>
     </row>
     <row r="8">
@@ -692,34 +715,37 @@
         <v>41214</v>
       </c>
       <c r="B8" t="n">
-        <v>20.90285682678223</v>
+        <v>17.66096496582031</v>
       </c>
       <c r="C8" t="n">
-        <v>26.6200008392334</v>
+        <v>21.30241775512695</v>
       </c>
       <c r="D8" t="n">
-        <v>17.47672653198242</v>
+        <v>17.31199264526367</v>
       </c>
       <c r="E8" t="n">
         <v>12.60249996185303</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2992500066757202</v>
+        <v>0.2754881680011749</v>
       </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>27.73436737060547</v>
       </c>
       <c r="H8" t="n">
-        <v>28120</v>
+        <v>20919.51953125</v>
       </c>
       <c r="I8" t="n">
         <v>2.254667043685913</v>
       </c>
       <c r="J8" t="n">
-        <v>19.56999969482422</v>
+        <v>13.99492645263672</v>
       </c>
       <c r="K8" t="n">
-        <v>46.68281173706055</v>
+        <v>43.68023681640625</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1416.180053710938</v>
       </c>
     </row>
     <row r="9">
@@ -727,34 +753,37 @@
         <v>41244</v>
       </c>
       <c r="B9" t="n">
-        <v>19.00607109069824</v>
+        <v>16.05835914611816</v>
       </c>
       <c r="C9" t="n">
-        <v>26.70999908447266</v>
+        <v>21.37443351745605</v>
       </c>
       <c r="D9" t="n">
-        <v>17.70220184326172</v>
+        <v>17.53533935546875</v>
       </c>
       <c r="E9" t="n">
         <v>12.54349994659424</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3064999878406525</v>
+        <v>0.2821625173091888</v>
       </c>
       <c r="G9" t="n">
-        <v>26.6200008392334</v>
+        <v>26.36746406555176</v>
       </c>
       <c r="H9" t="n">
-        <v>30440</v>
+        <v>22761.583984375</v>
       </c>
       <c r="I9" t="n">
         <v>2.257999897003174</v>
       </c>
       <c r="J9" t="n">
-        <v>20.6200008392334</v>
+        <v>14.74580478668213</v>
       </c>
       <c r="K9" t="n">
-        <v>45.90845108032227</v>
+        <v>42.95568084716797</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1426.18994140625</v>
       </c>
     </row>
     <row r="10">
@@ -762,34 +791,37 @@
         <v>41275</v>
       </c>
       <c r="B10" t="n">
-        <v>16.26749992370605</v>
+        <v>13.7445240020752</v>
       </c>
       <c r="C10" t="n">
-        <v>27.45000076293945</v>
+        <v>21.96661949157715</v>
       </c>
       <c r="D10" t="n">
-        <v>18.91116142272949</v>
+        <v>18.73290824890137</v>
       </c>
       <c r="E10" t="n">
         <v>13.27499961853027</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3064999878406525</v>
+        <v>0.2821625173091888</v>
       </c>
       <c r="G10" t="n">
-        <v>30.97999954223633</v>
+        <v>30.68609619140625</v>
       </c>
       <c r="H10" t="n">
-        <v>28960</v>
+        <v>21654.91015625</v>
       </c>
       <c r="I10" t="n">
         <v>2.500667095184326</v>
       </c>
       <c r="J10" t="n">
-        <v>21.04000091552734</v>
+        <v>15.04615592956543</v>
       </c>
       <c r="K10" t="n">
-        <v>50.03836822509766</v>
+        <v>46.81996536254883</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1498.109985351562</v>
       </c>
     </row>
     <row r="11">
@@ -797,34 +829,37 @@
         <v>41306</v>
       </c>
       <c r="B11" t="n">
-        <v>15.76428604125977</v>
+        <v>13.39697551727295</v>
       </c>
       <c r="C11" t="n">
-        <v>27.79999923706055</v>
+        <v>22.43087768554688</v>
       </c>
       <c r="D11" t="n">
-        <v>20.05005073547363</v>
+        <v>19.86105537414551</v>
       </c>
       <c r="E11" t="n">
         <v>13.21350002288818</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3165000081062317</v>
+        <v>0.2931559681892395</v>
       </c>
       <c r="G11" t="n">
-        <v>27.25</v>
+        <v>26.99148368835449</v>
       </c>
       <c r="H11" t="n">
-        <v>30880</v>
+        <v>23090.59375</v>
       </c>
       <c r="I11" t="n">
         <v>2.322000026702881</v>
       </c>
       <c r="J11" t="n">
-        <v>20.8799991607666</v>
+        <v>15.09221458435059</v>
       </c>
       <c r="K11" t="n">
-        <v>49.44837951660156</v>
+        <v>46.26792144775391</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1514.680053710938</v>
       </c>
     </row>
     <row r="12">
@@ -832,34 +867,37 @@
         <v>41334</v>
       </c>
       <c r="B12" t="n">
-        <v>15.80928611755371</v>
+        <v>13.43521976470947</v>
       </c>
       <c r="C12" t="n">
-        <v>28.61000061035156</v>
+        <v>23.08444786071777</v>
       </c>
       <c r="D12" t="n">
-        <v>19.87462425231934</v>
+        <v>19.68729019165039</v>
       </c>
       <c r="E12" t="n">
         <v>13.32450008392334</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3207499980926514</v>
+        <v>0.2970924973487854</v>
       </c>
       <c r="G12" t="n">
-        <v>25.57999992370605</v>
+        <v>25.33732795715332</v>
       </c>
       <c r="H12" t="n">
-        <v>30540</v>
+        <v>22836.361328125</v>
       </c>
       <c r="I12" t="n">
         <v>2.526000022888184</v>
       </c>
       <c r="J12" t="n">
-        <v>21.84000015258789</v>
+        <v>15.78610801696777</v>
       </c>
       <c r="K12" t="n">
-        <v>45.50283432006836</v>
+        <v>42.57615661621094</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1569.18994140625</v>
       </c>
     </row>
     <row r="13">
@@ -867,34 +905,37 @@
         <v>41365</v>
       </c>
       <c r="B13" t="n">
-        <v>15.81357097625732</v>
+        <v>13.43886470794678</v>
       </c>
       <c r="C13" t="n">
-        <v>33.09999847412109</v>
+        <v>26.70727920532227</v>
       </c>
       <c r="D13" t="n">
-        <v>20.63488578796387</v>
+        <v>20.44038391113281</v>
       </c>
       <c r="E13" t="n">
         <v>12.69050025939941</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3442499935626984</v>
+        <v>0.318859189748764</v>
       </c>
       <c r="G13" t="n">
-        <v>27.77000045776367</v>
+        <v>27.50655555725098</v>
       </c>
       <c r="H13" t="n">
-        <v>30400</v>
+        <v>22731.6796875</v>
       </c>
       <c r="I13" t="n">
         <v>3.599333047866821</v>
       </c>
       <c r="J13" t="n">
-        <v>23.95000076293945</v>
+        <v>17.31123733520508</v>
       </c>
       <c r="K13" t="n">
-        <v>49.07963562011719</v>
+        <v>45.92290496826172</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1597.569946289062</v>
       </c>
     </row>
     <row r="14">
@@ -902,34 +943,37 @@
         <v>41395</v>
       </c>
       <c r="B14" t="n">
-        <v>16.06178665161133</v>
+        <v>13.74015426635742</v>
       </c>
       <c r="C14" t="n">
-        <v>34.90000152587891</v>
+        <v>28.35711288452148</v>
       </c>
       <c r="D14" t="n">
-        <v>21.80230140686035</v>
+        <v>21.59679222106934</v>
       </c>
       <c r="E14" t="n">
         <v>13.46000003814697</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3617500066757202</v>
+        <v>0.3367705047130585</v>
       </c>
       <c r="G14" t="n">
-        <v>24.35000038146973</v>
+        <v>24.11899757385254</v>
       </c>
       <c r="H14" t="n">
-        <v>30760</v>
+        <v>23000.865234375</v>
       </c>
       <c r="I14" t="n">
         <v>6.517333030700684</v>
       </c>
       <c r="J14" t="n">
-        <v>24.28000068664551</v>
+        <v>17.715087890625</v>
       </c>
       <c r="K14" t="n">
-        <v>56.74948120117188</v>
+        <v>53.29729461669922</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1630.739990234375</v>
       </c>
     </row>
     <row r="15">
@@ -937,34 +981,37 @@
         <v>41426</v>
       </c>
       <c r="B15" t="n">
-        <v>14.16178607940674</v>
+        <v>12.11478710174561</v>
       </c>
       <c r="C15" t="n">
-        <v>34.54000091552734</v>
+        <v>28.0645866394043</v>
       </c>
       <c r="D15" t="n">
-        <v>22.03128051757812</v>
+        <v>21.8236141204834</v>
       </c>
       <c r="E15" t="n">
         <v>13.88449954986572</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3510000109672546</v>
+        <v>0.3267627656459808</v>
       </c>
       <c r="G15" t="n">
-        <v>24.8799991607666</v>
+        <v>24.64397048950195</v>
       </c>
       <c r="H15" t="n">
-        <v>26840</v>
+        <v>20077.638671875</v>
       </c>
       <c r="I15" t="n">
         <v>7.157332897186279</v>
       </c>
       <c r="J15" t="n">
-        <v>24.22999954223633</v>
+        <v>17.67859840393066</v>
       </c>
       <c r="K15" t="n">
-        <v>56.08574676513672</v>
+        <v>52.67393493652344</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1606.280029296875</v>
       </c>
     </row>
     <row r="16">
@@ -972,34 +1019,37 @@
         <v>41456</v>
       </c>
       <c r="B16" t="n">
-        <v>16.16178512573242</v>
+        <v>13.82569789886475</v>
       </c>
       <c r="C16" t="n">
-        <v>31.84000015258789</v>
+        <v>25.87077331542969</v>
       </c>
       <c r="D16" t="n">
-        <v>22.21596527099609</v>
+        <v>22.00655746459961</v>
       </c>
       <c r="E16" t="n">
         <v>15.06099987030029</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3610000014305115</v>
+        <v>0.3360721468925476</v>
       </c>
       <c r="G16" t="n">
-        <v>36.79999923706055</v>
+        <v>36.45088195800781</v>
       </c>
       <c r="H16" t="n">
-        <v>25600</v>
+        <v>19150.052734375</v>
       </c>
       <c r="I16" t="n">
         <v>8.951999664306641</v>
       </c>
       <c r="J16" t="n">
-        <v>23.34000015258789</v>
+        <v>17.02923583984375</v>
       </c>
       <c r="K16" t="n">
-        <v>64.86181640625</v>
+        <v>60.91614151000977</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1685.72998046875</v>
       </c>
     </row>
     <row r="17">
@@ -1007,34 +1057,37 @@
         <v>41487</v>
       </c>
       <c r="B17" t="n">
-        <v>17.40071487426758</v>
+        <v>14.98383522033691</v>
       </c>
       <c r="C17" t="n">
-        <v>33.40000152587891</v>
+        <v>27.32954406738281</v>
       </c>
       <c r="D17" t="n">
-        <v>21.19369316101074</v>
+        <v>20.99392318725586</v>
       </c>
       <c r="E17" t="n">
         <v>14.04899978637695</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3687500059604645</v>
+        <v>0.3450179994106293</v>
       </c>
       <c r="G17" t="n">
-        <v>41.29000091552734</v>
+        <v>40.89828491210938</v>
       </c>
       <c r="H17" t="n">
-        <v>27360</v>
+        <v>20466.62109375</v>
       </c>
       <c r="I17" t="n">
         <v>11.26666736602783</v>
       </c>
       <c r="J17" t="n">
-        <v>21.97999954223633</v>
+        <v>16.19388198852539</v>
       </c>
       <c r="K17" t="n">
-        <v>67.03739929199219</v>
+        <v>62.95937347412109</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1632.969970703125</v>
       </c>
     </row>
     <row r="18">
@@ -1042,34 +1095,37 @@
         <v>41518</v>
       </c>
       <c r="B18" t="n">
-        <v>17.02678680419922</v>
+        <v>14.66183757781982</v>
       </c>
       <c r="C18" t="n">
-        <v>33.27999877929688</v>
+        <v>27.23135375976562</v>
       </c>
       <c r="D18" t="n">
-        <v>21.91967010498047</v>
+        <v>21.71305465698242</v>
       </c>
       <c r="E18" t="n">
         <v>15.63199996948242</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3889999985694885</v>
+        <v>0.3639646768569946</v>
       </c>
       <c r="G18" t="n">
-        <v>50.22999954223633</v>
+        <v>49.75347900390625</v>
       </c>
       <c r="H18" t="n">
-        <v>27340</v>
+        <v>20451.662109375</v>
       </c>
       <c r="I18" t="n">
         <v>12.89133262634277</v>
       </c>
       <c r="J18" t="n">
-        <v>22.92000007629395</v>
+        <v>16.88643455505371</v>
       </c>
       <c r="K18" t="n">
-        <v>75.00224304199219</v>
+        <v>70.43968963623047</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1681.550048828125</v>
       </c>
     </row>
     <row r="19">
@@ -1077,34 +1133,37 @@
         <v>41548</v>
       </c>
       <c r="B19" t="n">
-        <v>18.66785621643066</v>
+        <v>16.07497215270996</v>
       </c>
       <c r="C19" t="n">
-        <v>35.40999984741211</v>
+        <v>28.97423362731934</v>
       </c>
       <c r="D19" t="n">
-        <v>25.79029083251953</v>
+        <v>25.54719161987305</v>
       </c>
       <c r="E19" t="n">
         <v>18.20149993896484</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3797500133514404</v>
+        <v>0.355309933423996</v>
       </c>
       <c r="G19" t="n">
-        <v>50.20999908447266</v>
+        <v>49.73366165161133</v>
       </c>
       <c r="H19" t="n">
-        <v>29300</v>
+        <v>21917.8359375</v>
       </c>
       <c r="I19" t="n">
         <v>10.6626672744751</v>
       </c>
       <c r="J19" t="n">
-        <v>24.46999931335449</v>
+        <v>18.02840232849121</v>
       </c>
       <c r="K19" t="n">
-        <v>78.02593231201172</v>
+        <v>73.27944183349609</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1756.5400390625</v>
       </c>
     </row>
     <row r="20">
@@ -1112,34 +1171,37 @@
         <v>41579</v>
       </c>
       <c r="B20" t="n">
-        <v>19.85964393615723</v>
+        <v>17.20106887817383</v>
       </c>
       <c r="C20" t="n">
-        <v>38.13000106811523</v>
+        <v>31.43649482727051</v>
       </c>
       <c r="D20" t="n">
-        <v>26.51626586914062</v>
+        <v>26.26632308959961</v>
       </c>
       <c r="E20" t="n">
         <v>19.68099975585938</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3899999856948853</v>
+        <v>0.3668766021728516</v>
       </c>
       <c r="G20" t="n">
-        <v>47.0099983215332</v>
+        <v>46.56402206420898</v>
       </c>
       <c r="H20" t="n">
-        <v>29880</v>
+        <v>22351.70703125</v>
       </c>
       <c r="I20" t="n">
         <v>8.485333442687988</v>
       </c>
       <c r="J20" t="n">
-        <v>23.84000015258789</v>
+        <v>17.72867202758789</v>
       </c>
       <c r="K20" t="n">
-        <v>82.67208862304688</v>
+        <v>77.64295959472656</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1805.81005859375</v>
       </c>
     </row>
     <row r="21">
@@ -1147,34 +1209,37 @@
         <v>41609</v>
       </c>
       <c r="B21" t="n">
-        <v>20.03642845153809</v>
+        <v>17.35419082641602</v>
       </c>
       <c r="C21" t="n">
-        <v>37.40999984741211</v>
+        <v>30.84288024902344</v>
       </c>
       <c r="D21" t="n">
-        <v>28.04579544067383</v>
+        <v>27.78143501281738</v>
       </c>
       <c r="E21" t="n">
         <v>19.93950080871582</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4004999995231628</v>
+        <v>0.3767540156841278</v>
       </c>
       <c r="G21" t="n">
-        <v>54.65000152587891</v>
+        <v>54.13154983520508</v>
       </c>
       <c r="H21" t="n">
-        <v>27440</v>
+        <v>20729.638671875</v>
       </c>
       <c r="I21" t="n">
         <v>10.02866744995117</v>
       </c>
       <c r="J21" t="n">
-        <v>25.95999908447266</v>
+        <v>19.30521011352539</v>
       </c>
       <c r="K21" t="n">
-        <v>91.19004058837891</v>
+        <v>85.64276123046875</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1848.359985351562</v>
       </c>
     </row>
     <row r="22">
@@ -1182,34 +1247,37 @@
         <v>41640</v>
       </c>
       <c r="B22" t="n">
-        <v>17.87857055664062</v>
+        <v>15.48520088195801</v>
       </c>
       <c r="C22" t="n">
-        <v>37.84000015258789</v>
+        <v>31.1973991394043</v>
       </c>
       <c r="D22" t="n">
-        <v>29.55380439758301</v>
+        <v>29.27522659301758</v>
       </c>
       <c r="E22" t="n">
         <v>17.93449974060059</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3925000131130219</v>
+        <v>0.3692283928394318</v>
       </c>
       <c r="G22" t="n">
-        <v>62.56999969482422</v>
+        <v>61.97640991210938</v>
       </c>
       <c r="H22" t="n">
-        <v>25600</v>
+        <v>19339.603515625</v>
       </c>
       <c r="I22" t="n">
         <v>12.0939998626709</v>
       </c>
       <c r="J22" t="n">
-        <v>24.54000091552734</v>
+        <v>18.24922943115234</v>
       </c>
       <c r="K22" t="n">
-        <v>100.2057952880859</v>
+        <v>94.11006164550781</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1782.589965820312</v>
       </c>
     </row>
     <row r="23">
@@ -1217,34 +1285,37 @@
         <v>41671</v>
       </c>
       <c r="B23" t="n">
-        <v>18.79428672790527</v>
+        <v>16.37577247619629</v>
       </c>
       <c r="C23" t="n">
-        <v>38.31000137329102</v>
+        <v>31.82174110412598</v>
       </c>
       <c r="D23" t="n">
-        <v>30.42167282104492</v>
+        <v>30.13491439819336</v>
       </c>
       <c r="E23" t="n">
         <v>18.10499954223633</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4595000147819519</v>
+        <v>0.4342077076435089</v>
       </c>
       <c r="G23" t="n">
-        <v>68.45999908447266</v>
+        <v>67.81053924560547</v>
       </c>
       <c r="H23" t="n">
-        <v>26980</v>
+        <v>20382.12890625</v>
       </c>
       <c r="I23" t="n">
         <v>16.3206672668457</v>
       </c>
       <c r="J23" t="n">
-        <v>24.76000022888184</v>
+        <v>18.58841323852539</v>
       </c>
       <c r="K23" t="n">
-        <v>114.771125793457</v>
+        <v>107.7893600463867</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1859.449951171875</v>
       </c>
     </row>
     <row r="24">
@@ -1252,34 +1323,37 @@
         <v>41699</v>
       </c>
       <c r="B24" t="n">
-        <v>19.16928672790527</v>
+        <v>16.70251846313477</v>
       </c>
       <c r="C24" t="n">
-        <v>40.9900016784668</v>
+        <v>34.04784393310547</v>
       </c>
       <c r="D24" t="n">
-        <v>27.89064025878906</v>
+        <v>27.62774085998535</v>
       </c>
       <c r="E24" t="n">
         <v>16.81850051879883</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4477500021457672</v>
+        <v>0.4231044352054596</v>
       </c>
       <c r="G24" t="n">
-        <v>60.2400016784668</v>
+        <v>59.66851425170898</v>
       </c>
       <c r="H24" t="n">
-        <v>26860</v>
+        <v>20291.482421875</v>
       </c>
       <c r="I24" t="n">
         <v>13.89666652679443</v>
       </c>
       <c r="J24" t="n">
-        <v>25.80999946594238</v>
+        <v>19.3766975402832</v>
       </c>
       <c r="K24" t="n">
-        <v>99.46830749511719</v>
+        <v>93.41743469238281</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1872.339965820312</v>
       </c>
     </row>
     <row r="25">
@@ -1287,34 +1361,37 @@
         <v>41730</v>
       </c>
       <c r="B25" t="n">
-        <v>21.07464218139648</v>
+        <v>18.36268043518066</v>
       </c>
       <c r="C25" t="n">
-        <v>40.40000152587891</v>
+        <v>33.55776214599609</v>
       </c>
       <c r="D25" t="n">
-        <v>26.74399948120117</v>
+        <v>26.49190902709961</v>
       </c>
       <c r="E25" t="n">
         <v>15.20650005340576</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4617500007152557</v>
+        <v>0.4363337159156799</v>
       </c>
       <c r="G25" t="n">
-        <v>59.77999877929688</v>
+        <v>59.21287536621094</v>
       </c>
       <c r="H25" t="n">
-        <v>26860</v>
+        <v>20291.482421875</v>
       </c>
       <c r="I25" t="n">
         <v>13.85933303833008</v>
       </c>
       <c r="J25" t="n">
-        <v>26.69000053405762</v>
+        <v>20.03735160827637</v>
       </c>
       <c r="K25" t="n">
-        <v>89.08820343017578</v>
+        <v>83.66878509521484</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1883.949951171875</v>
       </c>
     </row>
     <row r="26">
@@ -1322,34 +1399,37 @@
         <v>41760</v>
       </c>
       <c r="B26" t="n">
-        <v>22.60714340209961</v>
+        <v>19.80799865722656</v>
       </c>
       <c r="C26" t="n">
-        <v>40.93999862670898</v>
+        <v>34.24623107910156</v>
       </c>
       <c r="D26" t="n">
-        <v>28.58250045776367</v>
+        <v>28.31308174133301</v>
       </c>
       <c r="E26" t="n">
         <v>15.6274995803833</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4749999940395355</v>
+        <v>0.4509217739105225</v>
       </c>
       <c r="G26" t="n">
-        <v>63.29999923706055</v>
+        <v>62.69948577880859</v>
       </c>
       <c r="H26" t="n">
-        <v>28860</v>
+        <v>21802.384765625</v>
       </c>
       <c r="I26" t="n">
         <v>13.85133266448975</v>
       </c>
       <c r="J26" t="n">
-        <v>27.31999969482422</v>
+        <v>20.68655967712402</v>
       </c>
       <c r="K26" t="n">
-        <v>100.7589111328125</v>
+        <v>94.85652160644531</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1923.569946289062</v>
       </c>
     </row>
     <row r="27">
@@ -1357,34 +1437,37 @@
         <v>41791</v>
       </c>
       <c r="B27" t="n">
-        <v>23.23250007629395</v>
+        <v>20.35593223571777</v>
       </c>
       <c r="C27" t="n">
-        <v>41.70000076293945</v>
+        <v>34.88195419311523</v>
       </c>
       <c r="D27" t="n">
-        <v>29.23349952697754</v>
+        <v>28.95794486999512</v>
       </c>
       <c r="E27" t="n">
         <v>16.23900032043457</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4634999930858612</v>
+        <v>0.4400046467781067</v>
       </c>
       <c r="G27" t="n">
-        <v>67.29000091552734</v>
+        <v>66.65163421630859</v>
       </c>
       <c r="H27" t="n">
-        <v>26440</v>
+        <v>19981.7265625</v>
       </c>
       <c r="I27" t="n">
         <v>16.00399971008301</v>
       </c>
       <c r="J27" t="n">
-        <v>30.89999961853027</v>
+        <v>23.39731788635254</v>
       </c>
       <c r="K27" t="n">
-        <v>108.9634323120117</v>
+        <v>102.5804214477539</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1960.22998046875</v>
       </c>
     </row>
     <row r="28">
@@ -1392,34 +1475,37 @@
         <v>41821</v>
       </c>
       <c r="B28" t="n">
-        <v>23.89999961853027</v>
+        <v>20.94077301025391</v>
       </c>
       <c r="C28" t="n">
-        <v>43.15999984741211</v>
+        <v>36.10324478149414</v>
       </c>
       <c r="D28" t="n">
-        <v>28.97750091552734</v>
+        <v>28.7043571472168</v>
       </c>
       <c r="E28" t="n">
         <v>15.64949989318848</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4375</v>
+        <v>0.4153226613998413</v>
       </c>
       <c r="G28" t="n">
-        <v>72.65000152587891</v>
+        <v>71.96078491210938</v>
       </c>
       <c r="H28" t="n">
-        <v>26860</v>
+        <v>20299.14453125</v>
       </c>
       <c r="I28" t="n">
         <v>14.88666725158691</v>
       </c>
       <c r="J28" t="n">
-        <v>33.88999938964844</v>
+        <v>25.66132545471191</v>
       </c>
       <c r="K28" t="n">
-        <v>118.3663711547852</v>
+        <v>111.4325561523438</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1930.670043945312</v>
       </c>
     </row>
     <row r="29">
@@ -1427,34 +1513,37 @@
         <v>41852</v>
       </c>
       <c r="B29" t="n">
-        <v>25.625</v>
+        <v>22.56387329101562</v>
       </c>
       <c r="C29" t="n">
-        <v>45.43000030517578</v>
+        <v>38.23944854736328</v>
       </c>
       <c r="D29" t="n">
-        <v>29.11800003051758</v>
+        <v>28.84353065490723</v>
       </c>
       <c r="E29" t="n">
         <v>16.95199966430664</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4862500131130219</v>
+        <v>0.463643491268158</v>
       </c>
       <c r="G29" t="n">
-        <v>74.81999969482422</v>
+        <v>74.11019134521484</v>
       </c>
       <c r="H29" t="n">
-        <v>24680</v>
+        <v>18651.623046875</v>
       </c>
       <c r="I29" t="n">
         <v>17.97999954223633</v>
       </c>
       <c r="J29" t="n">
-        <v>34.91999816894531</v>
+        <v>26.61711883544922</v>
       </c>
       <c r="K29" t="n">
-        <v>116.6148376464844</v>
+        <v>109.7836151123047</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2003.369995117188</v>
       </c>
     </row>
     <row r="30">
@@ -1462,34 +1551,37 @@
         <v>41883</v>
       </c>
       <c r="B30" t="n">
-        <v>25.1875</v>
+        <v>22.17863845825195</v>
       </c>
       <c r="C30" t="n">
-        <v>46.36000061035156</v>
+        <v>39.02223968505859</v>
       </c>
       <c r="D30" t="n">
-        <v>29.42049980163574</v>
+        <v>29.1431827545166</v>
       </c>
       <c r="E30" t="n">
         <v>16.12199974060059</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4612500071525574</v>
+        <v>0.4398057162761688</v>
       </c>
       <c r="G30" t="n">
-        <v>79.04000091552734</v>
+        <v>78.29016876220703</v>
       </c>
       <c r="H30" t="n">
-        <v>23680</v>
+        <v>17895.88671875</v>
       </c>
       <c r="I30" t="n">
         <v>16.17866706848145</v>
       </c>
       <c r="J30" t="n">
-        <v>34.81999969482422</v>
+        <v>26.54090118408203</v>
       </c>
       <c r="K30" t="n">
-        <v>106.4744186401367</v>
+        <v>100.2372207641602</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1972.2900390625</v>
       </c>
     </row>
     <row r="31">
@@ -1497,34 +1589,37 @@
         <v>41913</v>
       </c>
       <c r="B31" t="n">
-        <v>27</v>
+        <v>23.77461433410645</v>
       </c>
       <c r="C31" t="n">
-        <v>46.95000076293945</v>
+        <v>39.51885223388672</v>
       </c>
       <c r="D31" t="n">
-        <v>28.39349937438965</v>
+        <v>28.12586402893066</v>
       </c>
       <c r="E31" t="n">
         <v>15.27299976348877</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4884999990463257</v>
+        <v>0.4657888412475586</v>
       </c>
       <c r="G31" t="n">
-        <v>74.98999786376953</v>
+        <v>74.27860260009766</v>
       </c>
       <c r="H31" t="n">
-        <v>24880</v>
+        <v>18802.7734375</v>
       </c>
       <c r="I31" t="n">
         <v>16.11333274841309</v>
       </c>
       <c r="J31" t="n">
-        <v>34.0099983215332</v>
+        <v>25.92349243164062</v>
       </c>
       <c r="K31" t="n">
-        <v>113.9414596557617</v>
+        <v>107.2668380737305</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2018.050048828125</v>
       </c>
     </row>
     <row r="32">
@@ -1532,34 +1627,37 @@
         <v>41944</v>
       </c>
       <c r="B32" t="n">
-        <v>29.73250007629395</v>
+        <v>26.29422187805176</v>
       </c>
       <c r="C32" t="n">
-        <v>47.81000137329102</v>
+        <v>40.49655914306641</v>
       </c>
       <c r="D32" t="n">
-        <v>27.45400047302246</v>
+        <v>27.19521903991699</v>
       </c>
       <c r="E32" t="n">
         <v>16.93199920654297</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5242499709129333</v>
+        <v>0.5019922256469727</v>
       </c>
       <c r="G32" t="n">
-        <v>77.69999694824219</v>
+        <v>76.96286010742188</v>
       </c>
       <c r="H32" t="n">
-        <v>25740</v>
+        <v>19452.712890625</v>
       </c>
       <c r="I32" t="n">
         <v>16.30133247375488</v>
       </c>
       <c r="J32" t="n">
-        <v>37.25</v>
+        <v>28.57929039001465</v>
       </c>
       <c r="K32" t="n">
-        <v>114.3101959228516</v>
+        <v>107.6139755249023</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2067.56005859375</v>
       </c>
     </row>
     <row r="33">
@@ -1567,34 +1665,37 @@
         <v>41974</v>
       </c>
       <c r="B33" t="n">
-        <v>27.59499931335449</v>
+        <v>24.40389823913574</v>
       </c>
       <c r="C33" t="n">
-        <v>46.45000076293945</v>
+        <v>39.34459686279297</v>
       </c>
       <c r="D33" t="n">
-        <v>26.53300094604492</v>
+        <v>26.28290176391602</v>
       </c>
       <c r="E33" t="n">
         <v>15.51749992370605</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5012500286102295</v>
+        <v>0.479968786239624</v>
       </c>
       <c r="G33" t="n">
-        <v>78.01999664306641</v>
+        <v>77.27983856201172</v>
       </c>
       <c r="H33" t="n">
-        <v>26540</v>
+        <v>20350.82421875</v>
       </c>
       <c r="I33" t="n">
         <v>14.82733345031738</v>
       </c>
       <c r="J33" t="n">
-        <v>36.29000091552734</v>
+        <v>27.84275436401367</v>
       </c>
       <c r="K33" t="n">
-        <v>103.7088470458984</v>
+        <v>97.63363647460938</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2058.89990234375</v>
       </c>
     </row>
     <row r="34">
@@ -1602,34 +1703,37 @@
         <v>42005</v>
       </c>
       <c r="B34" t="n">
-        <v>29.29000091552734</v>
+        <v>25.90288734436035</v>
       </c>
       <c r="C34" t="n">
-        <v>40.40000152587891</v>
+        <v>34.22006225585938</v>
       </c>
       <c r="D34" t="n">
-        <v>26.87750053405762</v>
+        <v>26.6241512298584</v>
       </c>
       <c r="E34" t="n">
         <v>17.72649955749512</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4799999892711639</v>
+        <v>0.4596208333969116</v>
       </c>
       <c r="G34" t="n">
-        <v>75.91000366210938</v>
+        <v>75.18986511230469</v>
       </c>
       <c r="H34" t="n">
-        <v>27300</v>
+        <v>20933.587890625</v>
       </c>
       <c r="I34" t="n">
         <v>13.57333278656006</v>
       </c>
       <c r="J34" t="n">
-        <v>33.04000091552734</v>
+        <v>25.3492546081543</v>
       </c>
       <c r="K34" t="n">
-        <v>121.6850509643555</v>
+        <v>114.5568161010742</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1994.989990234375</v>
       </c>
     </row>
     <row r="35">
@@ -1637,34 +1741,37 @@
         <v>42036</v>
       </c>
       <c r="B35" t="n">
-        <v>32.1150016784668</v>
+        <v>28.5132942199707</v>
       </c>
       <c r="C35" t="n">
-        <v>43.84999847412109</v>
+        <v>37.40664672851562</v>
       </c>
       <c r="D35" t="n">
-        <v>28.13150024414062</v>
+        <v>27.8663330078125</v>
       </c>
       <c r="E35" t="n">
         <v>19.00799942016602</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5515000224113464</v>
+        <v>0.5301187038421631</v>
       </c>
       <c r="G35" t="n">
-        <v>78.97000122070312</v>
+        <v>78.2208251953125</v>
       </c>
       <c r="H35" t="n">
-        <v>27140</v>
+        <v>20810.900390625</v>
       </c>
       <c r="I35" t="n">
         <v>13.55599975585938</v>
       </c>
       <c r="J35" t="n">
-        <v>33.25</v>
+        <v>25.69334983825684</v>
       </c>
       <c r="K35" t="n">
-        <v>125.2802886962891</v>
+        <v>117.9414443969727</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2104.5</v>
       </c>
     </row>
     <row r="36">
@@ -1672,34 +1779,37 @@
         <v>42064</v>
       </c>
       <c r="B36" t="n">
-        <v>31.10750007629395</v>
+        <v>27.61878395080566</v>
       </c>
       <c r="C36" t="n">
-        <v>40.65999984741211</v>
+        <v>34.68539047241211</v>
       </c>
       <c r="D36" t="n">
-        <v>27.73500061035156</v>
+        <v>27.47357177734375</v>
       </c>
       <c r="E36" t="n">
         <v>18.60499954223633</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5232499837875366</v>
+        <v>0.5029637217521667</v>
       </c>
       <c r="G36" t="n">
-        <v>82.22000122070312</v>
+        <v>81.43999481201172</v>
       </c>
       <c r="H36" t="n">
-        <v>28820</v>
+        <v>22099.123046875</v>
       </c>
       <c r="I36" t="n">
         <v>12.58466720581055</v>
       </c>
       <c r="J36" t="n">
-        <v>31.27000045776367</v>
+        <v>24.16333961486816</v>
       </c>
       <c r="K36" t="n">
-        <v>135.697265625</v>
+        <v>127.7481994628906</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2067.889892578125</v>
       </c>
     </row>
     <row r="37">
@@ -1707,34 +1817,37 @@
         <v>42095</v>
       </c>
       <c r="B37" t="n">
-        <v>31.28750038146973</v>
+        <v>27.77860260009766</v>
       </c>
       <c r="C37" t="n">
-        <v>48.63999938964844</v>
+        <v>41.49279022216797</v>
       </c>
       <c r="D37" t="n">
-        <v>27.43849945068359</v>
+        <v>27.17986297607422</v>
       </c>
       <c r="E37" t="n">
         <v>21.0890007019043</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5550000071525574</v>
+        <v>0.5334829688072205</v>
       </c>
       <c r="G37" t="n">
-        <v>78.76999664306641</v>
+        <v>78.02271270751953</v>
       </c>
       <c r="H37" t="n">
-        <v>28200</v>
+        <v>21623.708984375</v>
       </c>
       <c r="I37" t="n">
         <v>15.06999969482422</v>
       </c>
       <c r="J37" t="n">
-        <v>32.54999923706055</v>
+        <v>25.15244293212891</v>
       </c>
       <c r="K37" t="n">
-        <v>148.3267059326172</v>
+        <v>139.6378173828125</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2085.510009765625</v>
       </c>
     </row>
     <row r="38">
@@ -1742,34 +1855,37 @@
         <v>42125</v>
       </c>
       <c r="B38" t="n">
-        <v>32.56999969482422</v>
+        <v>29.03806114196777</v>
       </c>
       <c r="C38" t="n">
-        <v>46.86000061035156</v>
+        <v>40.23413467407227</v>
       </c>
       <c r="D38" t="n">
-        <v>27.26600074768066</v>
+        <v>27.00899314880371</v>
       </c>
       <c r="E38" t="n">
         <v>21.46150016784668</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5532500147819519</v>
+        <v>0.534262478351593</v>
       </c>
       <c r="G38" t="n">
-        <v>79.19000244140625</v>
+        <v>78.43874359130859</v>
       </c>
       <c r="H38" t="n">
-        <v>26140</v>
+        <v>20044.1015625</v>
       </c>
       <c r="I38" t="n">
         <v>16.71999931335449</v>
       </c>
       <c r="J38" t="n">
-        <v>34.45999908447266</v>
+        <v>26.8209114074707</v>
       </c>
       <c r="K38" t="n">
-        <v>143.5330505371094</v>
+        <v>135.4529418945312</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2107.389892578125</v>
       </c>
     </row>
     <row r="39">
@@ -1777,34 +1893,37 @@
         <v>42156</v>
       </c>
       <c r="B39" t="n">
-        <v>31.35750007629395</v>
+        <v>27.95704078674316</v>
       </c>
       <c r="C39" t="n">
-        <v>44.15000152587891</v>
+        <v>37.90732955932617</v>
       </c>
       <c r="D39" t="n">
-        <v>27.00200080871582</v>
+        <v>26.74748039245605</v>
       </c>
       <c r="E39" t="n">
         <v>21.70450019836426</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5027499794960022</v>
+        <v>0.4854954779148102</v>
       </c>
       <c r="G39" t="n">
-        <v>85.76999664306641</v>
+        <v>84.95630645751953</v>
       </c>
       <c r="H39" t="n">
-        <v>25360</v>
+        <v>19461.2265625</v>
       </c>
       <c r="I39" t="n">
         <v>17.88400077819824</v>
       </c>
       <c r="J39" t="n">
-        <v>30.42000007629395</v>
+        <v>23.6764965057373</v>
       </c>
       <c r="K39" t="n">
-        <v>142.6111907958984</v>
+        <v>134.5829467773438</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2063.110107421875</v>
       </c>
     </row>
     <row r="40">
@@ -1812,34 +1931,37 @@
         <v>42186</v>
       </c>
       <c r="B40" t="n">
-        <v>30.32500076293945</v>
+        <v>27.03650856018066</v>
       </c>
       <c r="C40" t="n">
-        <v>46.70000076293945</v>
+        <v>40.09676742553711</v>
       </c>
       <c r="D40" t="n">
-        <v>32.875</v>
+        <v>32.56512069702148</v>
       </c>
       <c r="E40" t="n">
         <v>26.8075008392334</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4987500011920929</v>
+        <v>0.4816329479217529</v>
       </c>
       <c r="G40" t="n">
-        <v>94.01000213623047</v>
+        <v>93.11814880371094</v>
       </c>
       <c r="H40" t="n">
-        <v>23700</v>
+        <v>18187.3515625</v>
       </c>
       <c r="I40" t="n">
         <v>17.74333381652832</v>
       </c>
       <c r="J40" t="n">
-        <v>28.95000076293945</v>
+        <v>22.53237342834473</v>
       </c>
       <c r="K40" t="n">
-        <v>133.3926239013672</v>
+        <v>125.8833312988281</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2103.840087890625</v>
       </c>
     </row>
     <row r="41">
@@ -1847,34 +1969,37 @@
         <v>42217</v>
       </c>
       <c r="B41" t="n">
-        <v>28.19000053405762</v>
+        <v>25.24679946899414</v>
       </c>
       <c r="C41" t="n">
-        <v>43.52000045776367</v>
+        <v>37.61282348632812</v>
       </c>
       <c r="D41" t="n">
-        <v>32.39099884033203</v>
+        <v>32.08567428588867</v>
       </c>
       <c r="E41" t="n">
         <v>25.64450073242188</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5619999766349792</v>
+        <v>0.5449954867362976</v>
       </c>
       <c r="G41" t="n">
-        <v>89.43000030517578</v>
+        <v>88.58158111572266</v>
       </c>
       <c r="H41" t="n">
-        <v>21780</v>
+        <v>16713.943359375</v>
       </c>
       <c r="I41" t="n">
         <v>16.60400009155273</v>
       </c>
       <c r="J41" t="n">
-        <v>28.54000091552734</v>
+        <v>22.39779090881348</v>
       </c>
       <c r="K41" t="n">
-        <v>121.5006790161133</v>
+        <v>114.6608581542969</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1972.180053710938</v>
       </c>
     </row>
     <row r="42">
@@ -1882,34 +2007,37 @@
         <v>42248</v>
       </c>
       <c r="B42" t="n">
-        <v>27.57500076293945</v>
+        <v>24.69600486755371</v>
       </c>
       <c r="C42" t="n">
-        <v>44.2599983215332</v>
+        <v>38.25236892700195</v>
       </c>
       <c r="D42" t="n">
-        <v>31.91850090026855</v>
+        <v>31.61763572692871</v>
       </c>
       <c r="E42" t="n">
         <v>25.5944995880127</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6162499785423279</v>
+        <v>0.5976042747497559</v>
       </c>
       <c r="G42" t="n">
-        <v>89.90000152587891</v>
+        <v>89.04713439941406</v>
       </c>
       <c r="H42" t="n">
-        <v>22680</v>
+        <v>17404.59765625</v>
       </c>
       <c r="I42" t="n">
         <v>16.55999946594238</v>
       </c>
       <c r="J42" t="n">
-        <v>30.13999938964844</v>
+        <v>23.65345573425293</v>
       </c>
       <c r="K42" t="n">
-        <v>119.1960372924805</v>
+        <v>112.4859466552734</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1920.030029296875</v>
       </c>
     </row>
     <row r="43">
@@ -1917,34 +2045,37 @@
         <v>42278</v>
       </c>
       <c r="B43" t="n">
-        <v>29.875</v>
+        <v>26.75586700439453</v>
       </c>
       <c r="C43" t="n">
-        <v>52.63999938964844</v>
+        <v>45.49491500854492</v>
       </c>
       <c r="D43" t="n">
-        <v>36.86949920654297</v>
+        <v>36.52196502685547</v>
       </c>
       <c r="E43" t="n">
         <v>31.29500007629395</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7092499732971191</v>
+        <v>0.6877902746200562</v>
       </c>
       <c r="G43" t="n">
-        <v>101.9700012207031</v>
+        <v>101.0026321411133</v>
       </c>
       <c r="H43" t="n">
-        <v>27440</v>
+        <v>21057.412109375</v>
       </c>
       <c r="I43" t="n">
         <v>13.79533290863037</v>
       </c>
       <c r="J43" t="n">
-        <v>33.86000061035156</v>
+        <v>26.57285118103027</v>
       </c>
       <c r="K43" t="n">
-        <v>135.1441497802734</v>
+        <v>127.5362548828125</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2079.360107421875</v>
       </c>
     </row>
     <row r="44">
@@ -1952,34 +2083,37 @@
         <v>42309</v>
       </c>
       <c r="B44" t="n">
-        <v>29.57500076293945</v>
+        <v>26.6005687713623</v>
       </c>
       <c r="C44" t="n">
-        <v>54.34999847412109</v>
+        <v>47.28942108154297</v>
       </c>
       <c r="D44" t="n">
-        <v>38.14250183105469</v>
+        <v>37.7829704284668</v>
       </c>
       <c r="E44" t="n">
         <v>33.2400016784668</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7929999828338623</v>
+        <v>0.7719261050224304</v>
       </c>
       <c r="G44" t="n">
-        <v>104.2399978637695</v>
+        <v>103.251091003418</v>
       </c>
       <c r="H44" t="n">
-        <v>25680</v>
+        <v>19706.798828125</v>
       </c>
       <c r="I44" t="n">
         <v>15.35066699981689</v>
       </c>
       <c r="J44" t="n">
-        <v>34.77000045776367</v>
+        <v>27.47923469543457</v>
       </c>
       <c r="K44" t="n">
-        <v>142.2424468994141</v>
+        <v>134.2349548339844</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2080.409912109375</v>
       </c>
     </row>
     <row r="45">
@@ -1987,34 +2121,37 @@
         <v>42339</v>
       </c>
       <c r="B45" t="n">
-        <v>26.31500053405762</v>
+        <v>23.66843605041504</v>
       </c>
       <c r="C45" t="n">
-        <v>55.47999954223633</v>
+        <v>48.27262115478516</v>
       </c>
       <c r="D45" t="n">
-        <v>38.9005012512207</v>
+        <v>38.5338134765625</v>
       </c>
       <c r="E45" t="n">
         <v>33.79449844360352</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8240000009536743</v>
+        <v>0.8021023869514465</v>
       </c>
       <c r="G45" t="n">
-        <v>104.6600036621094</v>
+        <v>103.6671142578125</v>
       </c>
       <c r="H45" t="n">
-        <v>25200</v>
+        <v>19648.849609375</v>
       </c>
       <c r="I45" t="n">
         <v>16.00066757202148</v>
       </c>
       <c r="J45" t="n">
-        <v>34.45000076293945</v>
+        <v>27.22632026672363</v>
       </c>
       <c r="K45" t="n">
-        <v>140.5831146240234</v>
+        <v>132.6690368652344</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2043.93994140625</v>
       </c>
     </row>
     <row r="46">
@@ -2022,34 +2159,37 @@
         <v>42370</v>
       </c>
       <c r="B46" t="n">
-        <v>24.33499908447266</v>
+        <v>21.8875732421875</v>
       </c>
       <c r="C46" t="n">
-        <v>55.09000015258789</v>
+        <v>47.93328857421875</v>
       </c>
       <c r="D46" t="n">
-        <v>38.06750106811523</v>
+        <v>37.70867919921875</v>
       </c>
       <c r="E46" t="n">
         <v>29.35000038146973</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7322499752044678</v>
+        <v>0.7127906680107117</v>
       </c>
       <c r="G46" t="n">
-        <v>112.2099990844727</v>
+        <v>111.1454925537109</v>
       </c>
       <c r="H46" t="n">
-        <v>23000</v>
+        <v>17933.474609375</v>
       </c>
       <c r="I46" t="n">
         <v>12.74666690826416</v>
       </c>
       <c r="J46" t="n">
-        <v>31.02000045776367</v>
+        <v>24.51554489135742</v>
       </c>
       <c r="K46" t="n">
-        <v>133.5769958496094</v>
+        <v>126.0573425292969</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1940.239990234375</v>
       </c>
     </row>
     <row r="47">
@@ -2057,34 +2197,37 @@
         <v>42401</v>
       </c>
       <c r="B47" t="n">
-        <v>24.17250061035156</v>
+        <v>21.85938262939453</v>
       </c>
       <c r="C47" t="n">
-        <v>50.88000106811523</v>
+        <v>44.58805465698242</v>
       </c>
       <c r="D47" t="n">
-        <v>35.86100006103516</v>
+        <v>35.52297973632812</v>
       </c>
       <c r="E47" t="n">
         <v>27.62599945068359</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7839999794960022</v>
+        <v>0.7659457325935364</v>
       </c>
       <c r="G47" t="n">
-        <v>106.9199981689453</v>
+        <v>105.9056701660156</v>
       </c>
       <c r="H47" t="n">
-        <v>23560</v>
+        <v>18370.11328125</v>
       </c>
       <c r="I47" t="n">
         <v>12.79533290863037</v>
       </c>
       <c r="J47" t="n">
-        <v>29.59000015258789</v>
+        <v>23.59122657775879</v>
       </c>
       <c r="K47" t="n">
-        <v>130.8114318847656</v>
+        <v>123.4474716186523</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1932.22998046875</v>
       </c>
     </row>
     <row r="48">
@@ -2092,34 +2235,37 @@
         <v>42430</v>
       </c>
       <c r="B48" t="n">
-        <v>27.24749946594238</v>
+        <v>24.64013290405273</v>
       </c>
       <c r="C48" t="n">
-        <v>55.22999954223633</v>
+        <v>48.4001350402832</v>
       </c>
       <c r="D48" t="n">
-        <v>38.14500045776367</v>
+        <v>37.78544235229492</v>
       </c>
       <c r="E48" t="n">
         <v>29.68199920654297</v>
       </c>
       <c r="F48" t="n">
-        <v>0.890749990940094</v>
+        <v>0.8702376484870911</v>
       </c>
       <c r="G48" t="n">
-        <v>114.0999984741211</v>
+        <v>113.0175552368164</v>
       </c>
       <c r="H48" t="n">
-        <v>26240</v>
+        <v>20459.7578125</v>
       </c>
       <c r="I48" t="n">
         <v>15.31799983978271</v>
       </c>
       <c r="J48" t="n">
-        <v>32.34999847412109</v>
+        <v>25.79169273376465</v>
       </c>
       <c r="K48" t="n">
-        <v>146.0220642089844</v>
+        <v>137.8018188476562</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2059.739990234375</v>
       </c>
     </row>
     <row r="49">
@@ -2127,34 +2273,37 @@
         <v>42461</v>
       </c>
       <c r="B49" t="n">
-        <v>23.43499946594238</v>
+        <v>21.19246292114258</v>
       </c>
       <c r="C49" t="n">
-        <v>49.86999893188477</v>
+        <v>43.70295333862305</v>
       </c>
       <c r="D49" t="n">
-        <v>35.39400100708008</v>
+        <v>35.06037521362305</v>
       </c>
       <c r="E49" t="n">
         <v>32.97949981689453</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8882499933242798</v>
+        <v>0.8677952885627747</v>
       </c>
       <c r="G49" t="n">
-        <v>117.5800018310547</v>
+        <v>116.4645462036133</v>
       </c>
       <c r="H49" t="n">
-        <v>24900</v>
+        <v>19414.94140625</v>
       </c>
       <c r="I49" t="n">
         <v>16.05066680908203</v>
       </c>
       <c r="J49" t="n">
-        <v>30.28000068664551</v>
+        <v>24.14134407043457</v>
       </c>
       <c r="K49" t="n">
-        <v>146.4829864501953</v>
+        <v>138.2367706298828</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2065.300048828125</v>
       </c>
     </row>
     <row r="50">
@@ -2162,34 +2311,37 @@
         <v>42491</v>
       </c>
       <c r="B50" t="n">
-        <v>24.96500015258789</v>
+        <v>22.7135066986084</v>
       </c>
       <c r="C50" t="n">
-        <v>53</v>
+        <v>46.77076721191406</v>
       </c>
       <c r="D50" t="n">
-        <v>37.44250106811523</v>
+        <v>37.08957672119141</v>
       </c>
       <c r="E50" t="n">
         <v>36.13949966430664</v>
       </c>
       <c r="F50" t="n">
-        <v>1.167999982833862</v>
+        <v>1.144065976142883</v>
       </c>
       <c r="G50" t="n">
-        <v>118.8099975585938</v>
+        <v>117.6828765869141</v>
       </c>
       <c r="H50" t="n">
-        <v>25840</v>
+        <v>20147.87109375</v>
       </c>
       <c r="I50" t="n">
         <v>14.88199996948242</v>
       </c>
       <c r="J50" t="n">
-        <v>31.59000015258789</v>
+        <v>25.40331649780273</v>
       </c>
       <c r="K50" t="n">
-        <v>159.7577209472656</v>
+        <v>151.2547912597656</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2096.949951171875</v>
       </c>
     </row>
     <row r="51">
@@ -2197,34 +2349,37 @@
         <v>42522</v>
       </c>
       <c r="B51" t="n">
-        <v>23.89999961853027</v>
+        <v>21.74455642700195</v>
       </c>
       <c r="C51" t="n">
-        <v>51.16999816894531</v>
+        <v>45.15584564208984</v>
       </c>
       <c r="D51" t="n">
-        <v>35.17649841308594</v>
+        <v>34.84492492675781</v>
       </c>
       <c r="E51" t="n">
         <v>35.78099822998047</v>
       </c>
       <c r="F51" t="n">
-        <v>1.175250053405762</v>
+        <v>1.151167869567871</v>
       </c>
       <c r="G51" t="n">
-        <v>114.2799987792969</v>
+        <v>113.1958541870117</v>
       </c>
       <c r="H51" t="n">
-        <v>28500</v>
+        <v>22237.8125</v>
       </c>
       <c r="I51" t="n">
         <v>14.15200042724609</v>
       </c>
       <c r="J51" t="n">
-        <v>32.79999923706055</v>
+        <v>26.3763484954834</v>
       </c>
       <c r="K51" t="n">
-        <v>162.3389129638672</v>
+        <v>153.6986083984375</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2098.860107421875</v>
       </c>
     </row>
     <row r="52">
@@ -2232,34 +2387,37 @@
         <v>42552</v>
       </c>
       <c r="B52" t="n">
-        <v>26.05249977111816</v>
+        <v>23.70293045043945</v>
       </c>
       <c r="C52" t="n">
-        <v>56.68000030517578</v>
+        <v>50.01823806762695</v>
       </c>
       <c r="D52" t="n">
-        <v>39.56700134277344</v>
+        <v>39.19403839111328</v>
       </c>
       <c r="E52" t="n">
         <v>37.94049835205078</v>
       </c>
       <c r="F52" t="n">
-        <v>1.427500009536743</v>
+        <v>1.398248672485352</v>
       </c>
       <c r="G52" t="n">
-        <v>123.9400024414062</v>
+        <v>122.7642059326172</v>
       </c>
       <c r="H52" t="n">
-        <v>30780</v>
+        <v>24016.83984375</v>
       </c>
       <c r="I52" t="n">
         <v>15.65266704559326</v>
       </c>
       <c r="J52" t="n">
-        <v>34.86000061035156</v>
+        <v>28.03290939331055</v>
       </c>
       <c r="K52" t="n">
-        <v>171.9262237548828</v>
+        <v>162.7756195068359</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2173.60009765625</v>
       </c>
     </row>
     <row r="53">
@@ -2267,34 +2425,37 @@
         <v>42583</v>
       </c>
       <c r="B53" t="n">
-        <v>26.52499961853027</v>
+        <v>24.26354598999023</v>
       </c>
       <c r="C53" t="n">
-        <v>57.45999908447266</v>
+        <v>51.02260589599609</v>
       </c>
       <c r="D53" t="n">
-        <v>39.49250030517578</v>
+        <v>39.1202507019043</v>
       </c>
       <c r="E53" t="n">
         <v>38.45800018310547</v>
       </c>
       <c r="F53" t="n">
-        <v>1.533499956130981</v>
+        <v>1.504844903945923</v>
       </c>
       <c r="G53" t="n">
-        <v>126.120002746582</v>
+        <v>124.9235153198242</v>
       </c>
       <c r="H53" t="n">
-        <v>32400</v>
+        <v>25280.890625</v>
       </c>
       <c r="I53" t="n">
         <v>14.13399982452393</v>
       </c>
       <c r="J53" t="n">
-        <v>35.88999938964844</v>
+        <v>29.0799617767334</v>
       </c>
       <c r="K53" t="n">
-        <v>186.0306243896484</v>
+        <v>176.1293334960938</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2170.949951171875</v>
       </c>
     </row>
     <row r="54">
@@ -2302,34 +2463,37 @@
         <v>42614</v>
       </c>
       <c r="B54" t="n">
-        <v>28.26250076293945</v>
+        <v>25.85291290283203</v>
       </c>
       <c r="C54" t="n">
-        <v>57.59999847412109</v>
+        <v>51.14691925048828</v>
       </c>
       <c r="D54" t="n">
-        <v>40.20299911499023</v>
+        <v>39.82404708862305</v>
       </c>
       <c r="E54" t="n">
         <v>41.86550140380859</v>
       </c>
       <c r="F54" t="n">
-        <v>1.713000059127808</v>
+        <v>1.680990815162659</v>
       </c>
       <c r="G54" t="n">
-        <v>128.2700042724609</v>
+        <v>127.0531311035156</v>
       </c>
       <c r="H54" t="n">
-        <v>31960</v>
+        <v>24937.564453125</v>
       </c>
       <c r="I54" t="n">
         <v>13.60200023651123</v>
       </c>
       <c r="J54" t="n">
-        <v>37.75</v>
+        <v>30.58702659606934</v>
       </c>
       <c r="K54" t="n">
-        <v>196.3554229736328</v>
+        <v>185.9046325683594</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2168.27001953125</v>
       </c>
     </row>
     <row r="55">
@@ -2337,34 +2501,37 @@
         <v>42644</v>
       </c>
       <c r="B55" t="n">
-        <v>28.38500022888184</v>
+        <v>25.96496963500977</v>
       </c>
       <c r="C55" t="n">
-        <v>59.91999816894531</v>
+        <v>53.20698547363281</v>
       </c>
       <c r="D55" t="n">
-        <v>40.49499893188477</v>
+        <v>40.11328887939453</v>
       </c>
       <c r="E55" t="n">
         <v>39.49100112915039</v>
       </c>
       <c r="F55" t="n">
-        <v>1.779000043869019</v>
+        <v>1.745757460594177</v>
       </c>
       <c r="G55" t="n">
-        <v>130.9900054931641</v>
+        <v>129.747314453125</v>
       </c>
       <c r="H55" t="n">
-        <v>32780</v>
+        <v>25577.38671875</v>
       </c>
       <c r="I55" t="n">
         <v>13.18200016021729</v>
       </c>
       <c r="J55" t="n">
-        <v>34.86999893188477</v>
+        <v>28.25350379943848</v>
       </c>
       <c r="K55" t="n">
-        <v>189.7180633544922</v>
+        <v>179.6204986572266</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2126.14990234375</v>
       </c>
     </row>
     <row r="56">
@@ -2372,34 +2539,37 @@
         <v>42675</v>
       </c>
       <c r="B56" t="n">
-        <v>27.6299991607666</v>
+        <v>25.40410804748535</v>
       </c>
       <c r="C56" t="n">
-        <v>60.2599983215332</v>
+        <v>53.87038803100586</v>
       </c>
       <c r="D56" t="n">
-        <v>38.79399871826172</v>
+        <v>38.42832183837891</v>
       </c>
       <c r="E56" t="n">
         <v>37.52849960327148</v>
       </c>
       <c r="F56" t="n">
-        <v>2.305000066757202</v>
+        <v>2.265314817428589</v>
       </c>
       <c r="G56" t="n">
-        <v>118.4199981689453</v>
+        <v>117.2965621948242</v>
       </c>
       <c r="H56" t="n">
-        <v>34920</v>
+        <v>27247.16796875</v>
       </c>
       <c r="I56" t="n">
         <v>12.62666702270508</v>
       </c>
       <c r="J56" t="n">
-        <v>34.70000076293945</v>
+        <v>28.32864189147949</v>
       </c>
       <c r="K56" t="n">
-        <v>178.5635986328125</v>
+        <v>169.0597381591797</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2198.81005859375</v>
       </c>
     </row>
     <row r="57">
@@ -2407,34 +2577,37 @@
         <v>42705</v>
       </c>
       <c r="B57" t="n">
-        <v>28.95499992370605</v>
+        <v>26.62235450744629</v>
       </c>
       <c r="C57" t="n">
-        <v>62.13999938964844</v>
+        <v>55.55104064941406</v>
       </c>
       <c r="D57" t="n">
-        <v>39.62250137329102</v>
+        <v>39.24901962280273</v>
       </c>
       <c r="E57" t="n">
         <v>37.49349975585938</v>
       </c>
       <c r="F57" t="n">
-        <v>2.668499946594238</v>
+        <v>2.622556447982788</v>
       </c>
       <c r="G57" t="n">
-        <v>115.0500030517578</v>
+        <v>113.9585418701172</v>
       </c>
       <c r="H57" t="n">
-        <v>36040</v>
+        <v>28557.62109375</v>
       </c>
       <c r="I57" t="n">
         <v>14.24600028991699</v>
       </c>
       <c r="J57" t="n">
-        <v>36.27000045776367</v>
+        <v>29.61037063598633</v>
       </c>
       <c r="K57" t="n">
-        <v>174.8761749267578</v>
+        <v>165.5685729980469</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2238.830078125</v>
       </c>
     </row>
     <row r="58">
@@ -2442,34 +2615,37 @@
         <v>42736</v>
       </c>
       <c r="B58" t="n">
-        <v>30.33749961853027</v>
+        <v>27.89347839355469</v>
       </c>
       <c r="C58" t="n">
-        <v>64.65000152587891</v>
+        <v>57.7949104309082</v>
       </c>
       <c r="D58" t="n">
-        <v>41.00949859619141</v>
+        <v>40.62295150756836</v>
       </c>
       <c r="E58" t="n">
         <v>41.17399978637695</v>
       </c>
       <c r="F58" t="n">
-        <v>2.72950005531311</v>
+        <v>2.68250560760498</v>
       </c>
       <c r="G58" t="n">
-        <v>130.3200073242188</v>
+        <v>129.0836944580078</v>
       </c>
       <c r="H58" t="n">
-        <v>39460</v>
+        <v>31267.580078125</v>
       </c>
       <c r="I58" t="n">
         <v>16.79533386230469</v>
       </c>
       <c r="J58" t="n">
-        <v>36.81999969482422</v>
+        <v>30.05938720703125</v>
       </c>
       <c r="K58" t="n">
-        <v>188.4274597167969</v>
+        <v>178.3986206054688</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2278.8701171875</v>
       </c>
     </row>
     <row r="59">
@@ -2477,34 +2653,37 @@
         <v>42767</v>
       </c>
       <c r="B59" t="n">
-        <v>34.24750137329102</v>
+        <v>31.62500762939453</v>
       </c>
       <c r="C59" t="n">
-        <v>63.97999954223633</v>
+        <v>57.54270172119141</v>
       </c>
       <c r="D59" t="n">
-        <v>42.24649810791016</v>
+        <v>41.84828567504883</v>
       </c>
       <c r="E59" t="n">
         <v>42.25199890136719</v>
       </c>
       <c r="F59" t="n">
-        <v>2.536999940872192</v>
+        <v>2.496468067169189</v>
       </c>
       <c r="G59" t="n">
-        <v>135.5399932861328</v>
+        <v>134.2541351318359</v>
       </c>
       <c r="H59" t="n">
-        <v>38440</v>
+        <v>30459.341796875</v>
       </c>
       <c r="I59" t="n">
         <v>16.66600036621094</v>
       </c>
       <c r="J59" t="n">
-        <v>36.20000076293945</v>
+        <v>29.76419258117676</v>
       </c>
       <c r="K59" t="n">
-        <v>190.8242797851562</v>
+        <v>180.6678771972656</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2363.639892578125</v>
       </c>
     </row>
     <row r="60">
@@ -2512,34 +2691,37 @@
         <v>42795</v>
       </c>
       <c r="B60" t="n">
-        <v>35.91500091552734</v>
+        <v>33.16481781005859</v>
       </c>
       <c r="C60" t="n">
-        <v>65.86000061035156</v>
+        <v>59.2335319519043</v>
       </c>
       <c r="D60" t="n">
-        <v>42.38999938964844</v>
+        <v>41.99043273925781</v>
       </c>
       <c r="E60" t="n">
         <v>44.32699966430664</v>
       </c>
       <c r="F60" t="n">
-        <v>2.723249912261963</v>
+        <v>2.679741382598877</v>
       </c>
       <c r="G60" t="n">
-        <v>142.0500030517578</v>
+        <v>140.7023773193359</v>
       </c>
       <c r="H60" t="n">
-        <v>41200</v>
+        <v>32756.111328125</v>
       </c>
       <c r="I60" t="n">
         <v>18.5533332824707</v>
       </c>
       <c r="J60" t="n">
-        <v>36.06999969482422</v>
+        <v>29.65731048583984</v>
       </c>
       <c r="K60" t="n">
-        <v>205.3896179199219</v>
+        <v>194.4579772949219</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2362.719970703125</v>
       </c>
     </row>
     <row r="61">
@@ -2547,34 +2729,37 @@
         <v>42826</v>
       </c>
       <c r="B61" t="n">
-        <v>35.91249847412109</v>
+        <v>33.16250610351562</v>
       </c>
       <c r="C61" t="n">
-        <v>68.45999908447266</v>
+        <v>61.57195663452148</v>
       </c>
       <c r="D61" t="n">
-        <v>46.22600173950195</v>
+        <v>45.79027938842773</v>
       </c>
       <c r="E61" t="n">
         <v>46.2495002746582</v>
       </c>
       <c r="F61" t="n">
-        <v>2.607500076293945</v>
+        <v>2.56584095954895</v>
       </c>
       <c r="G61" t="n">
-        <v>150.25</v>
+        <v>148.8246002197266</v>
       </c>
       <c r="H61" t="n">
-        <v>44620</v>
+        <v>35475.1640625</v>
       </c>
       <c r="I61" t="n">
         <v>20.9379997253418</v>
       </c>
       <c r="J61" t="n">
-        <v>36.15000152587891</v>
+        <v>29.72308349609375</v>
       </c>
       <c r="K61" t="n">
-        <v>224.3798522949219</v>
+        <v>212.4374694824219</v>
+      </c>
+      <c r="L61" t="n">
+        <v>2384.199951171875</v>
       </c>
     </row>
     <row r="62">
@@ -2582,34 +2767,37 @@
         <v>42856</v>
       </c>
       <c r="B62" t="n">
-        <v>38.18999862670898</v>
+        <v>35.41116714477539</v>
       </c>
       <c r="C62" t="n">
-        <v>69.83999633789062</v>
+        <v>63.17312622070312</v>
       </c>
       <c r="D62" t="n">
-        <v>49.35449981689453</v>
+        <v>48.88928604125977</v>
       </c>
       <c r="E62" t="n">
         <v>49.73099899291992</v>
       </c>
       <c r="F62" t="n">
-        <v>3.608750104904175</v>
+        <v>3.55483341217041</v>
       </c>
       <c r="G62" t="n">
-        <v>151.4600067138672</v>
+        <v>150.0231475830078</v>
       </c>
       <c r="H62" t="n">
-        <v>44700</v>
+        <v>35538.78125</v>
       </c>
       <c r="I62" t="n">
         <v>22.73399925231934</v>
       </c>
       <c r="J62" t="n">
-        <v>36.11000061035156</v>
+        <v>29.91108131408691</v>
       </c>
       <c r="K62" t="n">
-        <v>246.6887817382812</v>
+        <v>234.1459503173828</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2411.800048828125</v>
       </c>
     </row>
     <row r="63">
@@ -2617,34 +2805,37 @@
         <v>42887</v>
       </c>
       <c r="B63" t="n">
-        <v>36.00500106811523</v>
+        <v>33.38517379760742</v>
       </c>
       <c r="C63" t="n">
-        <v>68.93000030517578</v>
+        <v>62.35000228881836</v>
       </c>
       <c r="D63" t="n">
-        <v>46.48400115966797</v>
+        <v>46.04584121704102</v>
       </c>
       <c r="E63" t="n">
         <v>48.40000152587891</v>
       </c>
       <c r="F63" t="n">
-        <v>3.614000082015991</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="G63" t="n">
-        <v>150.9799957275391</v>
+        <v>149.5476989746094</v>
       </c>
       <c r="H63" t="n">
-        <v>47540</v>
+        <v>37907.984375</v>
       </c>
       <c r="I63" t="n">
         <v>24.10733222961426</v>
       </c>
       <c r="J63" t="n">
-        <v>33.7400016784668</v>
+        <v>27.94793128967285</v>
       </c>
       <c r="K63" t="n">
-        <v>257.38232421875</v>
+        <v>244.2957611083984</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2423.409912109375</v>
       </c>
     </row>
     <row r="64">
@@ -2652,34 +2843,37 @@
         <v>42917</v>
       </c>
       <c r="B64" t="n">
-        <v>37.18249893188477</v>
+        <v>34.47698593139648</v>
       </c>
       <c r="C64" t="n">
-        <v>72.69999694824219</v>
+        <v>65.76010894775391</v>
       </c>
       <c r="D64" t="n">
-        <v>47.27500152587891</v>
+        <v>46.82939147949219</v>
       </c>
       <c r="E64" t="n">
         <v>49.38899993896484</v>
       </c>
       <c r="F64" t="n">
-        <v>4.062749862670898</v>
+        <v>4.002049922943115</v>
       </c>
       <c r="G64" t="n">
-        <v>169.25</v>
+        <v>167.6443328857422</v>
       </c>
       <c r="H64" t="n">
-        <v>48200</v>
+        <v>38434.26171875</v>
       </c>
       <c r="I64" t="n">
         <v>21.56466674804688</v>
       </c>
       <c r="J64" t="n">
-        <v>35.47000122070312</v>
+        <v>29.38093948364258</v>
       </c>
       <c r="K64" t="n">
-        <v>288.9098205566406</v>
+        <v>274.2202453613281</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2470.300048828125</v>
       </c>
     </row>
     <row r="65">
@@ -2687,34 +2881,37 @@
         <v>42948</v>
       </c>
       <c r="B65" t="n">
-        <v>41</v>
+        <v>38.16599655151367</v>
       </c>
       <c r="C65" t="n">
-        <v>74.76999664306641</v>
+        <v>67.99285888671875</v>
       </c>
       <c r="D65" t="n">
-        <v>47.76200103759766</v>
+        <v>47.31179809570312</v>
       </c>
       <c r="E65" t="n">
         <v>49.02999877929688</v>
       </c>
       <c r="F65" t="n">
-        <v>4.236000061035156</v>
+        <v>4.176386833190918</v>
       </c>
       <c r="G65" t="n">
-        <v>171.9700012207031</v>
+        <v>170.3385620117188</v>
       </c>
       <c r="H65" t="n">
-        <v>46320</v>
+        <v>36935.171875</v>
       </c>
       <c r="I65" t="n">
         <v>23.7266674041748</v>
       </c>
       <c r="J65" t="n">
-        <v>35.06999969482422</v>
+        <v>29.26767349243164</v>
       </c>
       <c r="K65" t="n">
-        <v>303.290771484375</v>
+        <v>287.8699340820312</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2471.64990234375</v>
       </c>
     </row>
     <row r="66">
@@ -2722,34 +2919,37 @@
         <v>42979</v>
       </c>
       <c r="B66" t="n">
-        <v>38.52999877929688</v>
+        <v>35.86673736572266</v>
       </c>
       <c r="C66" t="n">
-        <v>74.48999786376953</v>
+        <v>67.73822021484375</v>
       </c>
       <c r="D66" t="n">
-        <v>48.68600082397461</v>
+        <v>48.22708511352539</v>
       </c>
       <c r="E66" t="n">
         <v>48.06750106811523</v>
       </c>
       <c r="F66" t="n">
-        <v>4.469250202178955</v>
+        <v>4.40635347366333</v>
       </c>
       <c r="G66" t="n">
-        <v>170.8699951171875</v>
+        <v>169.2489776611328</v>
       </c>
       <c r="H66" t="n">
-        <v>51280</v>
+        <v>41001.296875</v>
       </c>
       <c r="I66" t="n">
         <v>22.73999977111816</v>
       </c>
       <c r="J66" t="n">
-        <v>38.08000183105469</v>
+        <v>31.77967643737793</v>
       </c>
       <c r="K66" t="n">
-        <v>309.9281311035156</v>
+        <v>294.1698608398438</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2519.360107421875</v>
       </c>
     </row>
     <row r="67">
@@ -2757,34 +2957,37 @@
         <v>43009</v>
       </c>
       <c r="B67" t="n">
-        <v>42.2599983215332</v>
+        <v>39.33891677856445</v>
       </c>
       <c r="C67" t="n">
-        <v>83.18000030517578</v>
+        <v>75.64057922363281</v>
       </c>
       <c r="D67" t="n">
-        <v>51.65200042724609</v>
+        <v>51.16513442993164</v>
       </c>
       <c r="E67" t="n">
         <v>55.26399993896484</v>
       </c>
       <c r="F67" t="n">
-        <v>5.170249938964844</v>
+        <v>5.097487926483154</v>
       </c>
       <c r="G67" t="n">
-        <v>180.0599975585938</v>
+        <v>178.3517761230469</v>
       </c>
       <c r="H67" t="n">
-        <v>55080</v>
+        <v>44039.6015625</v>
       </c>
       <c r="I67" t="n">
         <v>22.10199928283691</v>
       </c>
       <c r="J67" t="n">
-        <v>45.4900016784668</v>
+        <v>37.96368408203125</v>
       </c>
       <c r="K67" t="n">
-        <v>322.4653930664062</v>
+        <v>306.0696716308594</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2575.260009765625</v>
       </c>
     </row>
     <row r="68">
@@ -2792,34 +2995,37 @@
         <v>43040</v>
       </c>
       <c r="B68" t="n">
-        <v>42.96250152587891</v>
+        <v>40.13661193847656</v>
       </c>
       <c r="C68" t="n">
-        <v>84.16999816894531</v>
+        <v>76.92522430419922</v>
       </c>
       <c r="D68" t="n">
-        <v>51.80849838256836</v>
+        <v>51.32015228271484</v>
       </c>
       <c r="E68" t="n">
         <v>58.83750152587891</v>
       </c>
       <c r="F68" t="n">
-        <v>5.017749786376953</v>
+        <v>4.95057201385498</v>
       </c>
       <c r="G68" t="n">
-        <v>177.1799926757812</v>
+        <v>175.4991455078125</v>
       </c>
       <c r="H68" t="n">
-        <v>50800</v>
+        <v>40617.50390625</v>
       </c>
       <c r="I68" t="n">
         <v>20.59000015258789</v>
       </c>
       <c r="J68" t="n">
-        <v>44.84000015258789</v>
+        <v>37.64300537109375</v>
       </c>
       <c r="K68" t="n">
-        <v>366.8988647460938</v>
+        <v>348.2439270019531</v>
+      </c>
+      <c r="L68" t="n">
+        <v>2647.580078125</v>
       </c>
     </row>
     <row r="69">
@@ -2827,34 +3033,37 @@
         <v>43070</v>
       </c>
       <c r="B69" t="n">
-        <v>42.30749893188477</v>
+        <v>39.52470779418945</v>
       </c>
       <c r="C69" t="n">
-        <v>85.54000091552734</v>
+        <v>78.17731475830078</v>
       </c>
       <c r="D69" t="n">
-        <v>52.66999816894531</v>
+        <v>52.17353820800781</v>
       </c>
       <c r="E69" t="n">
         <v>58.4734992980957</v>
       </c>
       <c r="F69" t="n">
-        <v>4.837500095367432</v>
+        <v>4.772736549377441</v>
       </c>
       <c r="G69" t="n">
-        <v>176.4600067138672</v>
+        <v>174.7859191894531</v>
       </c>
       <c r="H69" t="n">
-        <v>50960</v>
+        <v>41112.19921875</v>
       </c>
       <c r="I69" t="n">
         <v>20.75666618347168</v>
       </c>
       <c r="J69" t="n">
-        <v>46.15999984741211</v>
+        <v>38.75112915039062</v>
       </c>
       <c r="K69" t="n">
-        <v>374.2737121582031</v>
+        <v>355.2438354492188</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2673.610107421875</v>
       </c>
     </row>
     <row r="70">
@@ -2862,34 +3071,37 @@
         <v>43101</v>
       </c>
       <c r="B70" t="n">
-        <v>41.85749816894531</v>
+        <v>39.10430526733398</v>
       </c>
       <c r="C70" t="n">
-        <v>95.01000213623047</v>
+        <v>86.83221435546875</v>
       </c>
       <c r="D70" t="n">
-        <v>59.11100006103516</v>
+        <v>58.5538215637207</v>
       </c>
       <c r="E70" t="n">
         <v>72.54450225830078</v>
       </c>
       <c r="F70" t="n">
-        <v>6.144999980926514</v>
+        <v>6.062731742858887</v>
       </c>
       <c r="G70" t="n">
-        <v>186.8899993896484</v>
+        <v>185.1170043945312</v>
       </c>
       <c r="H70" t="n">
-        <v>49900</v>
+        <v>40257.046875</v>
       </c>
       <c r="I70" t="n">
         <v>23.62066650390625</v>
       </c>
       <c r="J70" t="n">
-        <v>48.13999938964844</v>
+        <v>40.41332626342773</v>
       </c>
       <c r="K70" t="n">
-        <v>427.3726501464844</v>
+        <v>405.6429138183594</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2823.81005859375</v>
       </c>
     </row>
     <row r="71">
@@ -2897,34 +3109,37 @@
         <v>43132</v>
       </c>
       <c r="B71" t="n">
-        <v>44.52999877929688</v>
+        <v>41.77063369750977</v>
       </c>
       <c r="C71" t="n">
-        <v>93.76999664306641</v>
+        <v>86.10151672363281</v>
       </c>
       <c r="D71" t="n">
-        <v>55.19599914550781</v>
+        <v>54.67572402954102</v>
       </c>
       <c r="E71" t="n">
         <v>75.62249755859375</v>
       </c>
       <c r="F71" t="n">
-        <v>6.050000190734863</v>
+        <v>5.972712516784668</v>
       </c>
       <c r="G71" t="n">
-        <v>178.3200073242188</v>
+        <v>176.6283264160156</v>
       </c>
       <c r="H71" t="n">
-        <v>47060</v>
+        <v>37965.8515625</v>
       </c>
       <c r="I71" t="n">
         <v>22.87066650390625</v>
       </c>
       <c r="J71" t="n">
-        <v>49.29000091552734</v>
+        <v>41.65947341918945</v>
       </c>
       <c r="K71" t="n">
-        <v>398.4263610839844</v>
+        <v>378.1684875488281</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2713.830078125</v>
       </c>
     </row>
     <row r="72">
@@ -2932,34 +3147,37 @@
         <v>43160</v>
       </c>
       <c r="B72" t="n">
-        <v>41.94499969482422</v>
+        <v>39.3458137512207</v>
       </c>
       <c r="C72" t="n">
-        <v>91.26999664306641</v>
+        <v>83.80595397949219</v>
       </c>
       <c r="D72" t="n">
-        <v>51.85699844360352</v>
+        <v>51.36819458007812</v>
       </c>
       <c r="E72" t="n">
         <v>72.36699676513672</v>
       </c>
       <c r="F72" t="n">
-        <v>5.789750099182129</v>
+        <v>5.715786457061768</v>
       </c>
       <c r="G72" t="n">
-        <v>159.7899932861328</v>
+        <v>158.2740936279297</v>
       </c>
       <c r="H72" t="n">
-        <v>49220</v>
+        <v>39999.203125</v>
       </c>
       <c r="I72" t="n">
         <v>17.74200057983398</v>
       </c>
       <c r="J72" t="n">
-        <v>52.08000183105469</v>
+        <v>44.01756286621094</v>
       </c>
       <c r="K72" t="n">
-        <v>377.5924072265625</v>
+        <v>358.393798828125</v>
+      </c>
+      <c r="L72" t="n">
+        <v>2640.8701171875</v>
       </c>
     </row>
     <row r="73">
@@ -2967,34 +3185,37 @@
         <v>43191</v>
       </c>
       <c r="B73" t="n">
-        <v>41.31499862670898</v>
+        <v>38.75485229492188</v>
       </c>
       <c r="C73" t="n">
-        <v>93.51999664306641</v>
+        <v>85.8719482421875</v>
       </c>
       <c r="D73" t="n">
-        <v>50.92900085449219</v>
+        <v>50.44895172119141</v>
       </c>
       <c r="E73" t="n">
         <v>78.30650329589844</v>
       </c>
       <c r="F73" t="n">
-        <v>5.622499942779541</v>
+        <v>5.55067253112793</v>
       </c>
       <c r="G73" t="n">
-        <v>172</v>
+        <v>170.3682556152344</v>
       </c>
       <c r="H73" t="n">
-        <v>53000</v>
+        <v>43071.0625</v>
       </c>
       <c r="I73" t="n">
         <v>19.59333229064941</v>
       </c>
       <c r="J73" t="n">
-        <v>51.61999893188477</v>
+        <v>43.62876129150391</v>
       </c>
       <c r="K73" t="n">
-        <v>360.4458618164062</v>
+        <v>342.1190185546875</v>
+      </c>
+      <c r="L73" t="n">
+        <v>2648.050048828125</v>
       </c>
     </row>
     <row r="74">
@@ -3002,34 +3223,37 @@
         <v>43221</v>
       </c>
       <c r="B74" t="n">
-        <v>46.71749877929688</v>
+        <v>43.99156188964844</v>
       </c>
       <c r="C74" t="n">
-        <v>98.83999633789062</v>
+        <v>91.15026092529297</v>
       </c>
       <c r="D74" t="n">
-        <v>55</v>
+        <v>54.4815673828125</v>
       </c>
       <c r="E74" t="n">
         <v>81.48100280761719</v>
       </c>
       <c r="F74" t="n">
-        <v>6.304749965667725</v>
+        <v>6.22805643081665</v>
       </c>
       <c r="G74" t="n">
-        <v>191.7799987792969</v>
+        <v>189.9606323242188</v>
       </c>
       <c r="H74" t="n">
-        <v>50700</v>
+        <v>41201.9453125</v>
       </c>
       <c r="I74" t="n">
         <v>18.98200035095215</v>
       </c>
       <c r="J74" t="n">
-        <v>55.20000076293945</v>
+        <v>46.92382049560547</v>
       </c>
       <c r="K74" t="n">
-        <v>368.0050964355469</v>
+        <v>350.1071472167969</v>
+      </c>
+      <c r="L74" t="n">
+        <v>2705.27001953125</v>
       </c>
     </row>
     <row r="75">
@@ -3037,34 +3261,37 @@
         <v>43252</v>
       </c>
       <c r="B75" t="n">
-        <v>46.27750015258789</v>
+        <v>43.57722473144531</v>
       </c>
       <c r="C75" t="n">
-        <v>98.61000061035156</v>
+        <v>90.93817138671875</v>
       </c>
       <c r="D75" t="n">
-        <v>56.45949935913086</v>
+        <v>55.92731475830078</v>
       </c>
       <c r="E75" t="n">
         <v>84.98999786376953</v>
       </c>
       <c r="F75" t="n">
-        <v>5.922500133514404</v>
+        <v>5.850456714630127</v>
       </c>
       <c r="G75" t="n">
-        <v>194.3200073242188</v>
+        <v>192.4765472412109</v>
       </c>
       <c r="H75" t="n">
-        <v>46650</v>
+        <v>38192.62890625</v>
       </c>
       <c r="I75" t="n">
         <v>22.86333274841309</v>
       </c>
       <c r="J75" t="n">
-        <v>49.70999908447266</v>
+        <v>42.25694274902344</v>
       </c>
       <c r="K75" t="n">
-        <v>363.0270690917969</v>
+        <v>345.3711547851562</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2718.3701171875</v>
       </c>
     </row>
     <row r="76">
@@ -3072,34 +3299,37 @@
         <v>43282</v>
       </c>
       <c r="B76" t="n">
-        <v>47.5724983215332</v>
+        <v>44.79666900634766</v>
       </c>
       <c r="C76" t="n">
-        <v>106.0800018310547</v>
+        <v>97.82697296142578</v>
       </c>
       <c r="D76" t="n">
-        <v>61.36100006103516</v>
+        <v>60.78260803222656</v>
       </c>
       <c r="E76" t="n">
         <v>88.87200164794922</v>
       </c>
       <c r="F76" t="n">
-        <v>6.121500015258789</v>
+        <v>6.04703426361084</v>
       </c>
       <c r="G76" t="n">
-        <v>172.5800018310547</v>
+        <v>170.9427795410156</v>
       </c>
       <c r="H76" t="n">
-        <v>46250</v>
+        <v>37865.14453125</v>
       </c>
       <c r="I76" t="n">
         <v>19.87599945068359</v>
       </c>
       <c r="J76" t="n">
-        <v>48.09999847412109</v>
+        <v>40.88832855224609</v>
       </c>
       <c r="K76" t="n">
-        <v>327.4434204101562</v>
+        <v>311.5181579589844</v>
+      </c>
+      <c r="L76" t="n">
+        <v>2816.2900390625</v>
       </c>
     </row>
     <row r="77">
@@ -3107,34 +3337,37 @@
         <v>43313</v>
       </c>
       <c r="B77" t="n">
-        <v>56.90750122070312</v>
+        <v>53.77492523193359</v>
       </c>
       <c r="C77" t="n">
-        <v>112.3300018310547</v>
+        <v>103.989372253418</v>
       </c>
       <c r="D77" t="n">
-        <v>61.59000015258789</v>
+        <v>61.00945663452148</v>
       </c>
       <c r="E77" t="n">
         <v>100.635498046875</v>
       </c>
       <c r="F77" t="n">
-        <v>7.017000198364258</v>
+        <v>6.935434818267822</v>
       </c>
       <c r="G77" t="n">
-        <v>175.7299957275391</v>
+        <v>174.0628967285156</v>
       </c>
       <c r="H77" t="n">
-        <v>48450</v>
+        <v>39666.3046875</v>
       </c>
       <c r="I77" t="n">
         <v>20.11066627502441</v>
       </c>
       <c r="J77" t="n">
-        <v>48.43000030517578</v>
+        <v>41.41922760009766</v>
       </c>
       <c r="K77" t="n">
-        <v>313.4311828613281</v>
+        <v>298.1873779296875</v>
+      </c>
+      <c r="L77" t="n">
+        <v>2901.52001953125</v>
       </c>
     </row>
     <row r="78">
@@ -3142,34 +3375,37 @@
         <v>43344</v>
       </c>
       <c r="B78" t="n">
-        <v>56.43500137329102</v>
+        <v>53.32842636108398</v>
       </c>
       <c r="C78" t="n">
-        <v>114.370002746582</v>
+        <v>105.8778991699219</v>
       </c>
       <c r="D78" t="n">
-        <v>60.35400009155273</v>
+        <v>59.78510665893555</v>
       </c>
       <c r="E78" t="n">
         <v>100.1500015258789</v>
       </c>
       <c r="F78" t="n">
-        <v>7.025499820709229</v>
+        <v>6.943834781646729</v>
       </c>
       <c r="G78" t="n">
-        <v>164.4600067138672</v>
+        <v>162.8997955322266</v>
       </c>
       <c r="H78" t="n">
-        <v>46450</v>
+        <v>38315.046875</v>
       </c>
       <c r="I78" t="n">
         <v>17.65133285522461</v>
       </c>
       <c r="J78" t="n">
-        <v>47.29000091552734</v>
+        <v>40.44424819946289</v>
       </c>
       <c r="K78" t="n">
-        <v>297.9440002441406</v>
+        <v>283.4534301757812</v>
+      </c>
+      <c r="L78" t="n">
+        <v>2913.97998046875</v>
       </c>
     </row>
     <row r="79">
@@ -3177,34 +3413,37 @@
         <v>43374</v>
       </c>
       <c r="B79" t="n">
-        <v>54.71500015258789</v>
+        <v>51.70310211181641</v>
       </c>
       <c r="C79" t="n">
-        <v>106.8099975585938</v>
+        <v>98.87925720214844</v>
       </c>
       <c r="D79" t="n">
-        <v>54.52899932861328</v>
+        <v>54.01501083374023</v>
       </c>
       <c r="E79" t="n">
         <v>79.90049743652344</v>
       </c>
       <c r="F79" t="n">
-        <v>5.270750045776367</v>
+        <v>5.209481716156006</v>
       </c>
       <c r="G79" t="n">
-        <v>151.7899932861328</v>
+        <v>150.3500061035156</v>
       </c>
       <c r="H79" t="n">
-        <v>42400</v>
+        <v>34974.33984375</v>
       </c>
       <c r="I79" t="n">
         <v>22.48800086975098</v>
       </c>
       <c r="J79" t="n">
-        <v>46.88000106811523</v>
+        <v>40.09360504150391</v>
       </c>
       <c r="K79" t="n">
-        <v>246.1356658935547</v>
+        <v>234.1647796630859</v>
+      </c>
+      <c r="L79" t="n">
+        <v>2711.739990234375</v>
       </c>
     </row>
     <row r="80">
@@ -3212,34 +3451,37 @@
         <v>43405</v>
       </c>
       <c r="B80" t="n">
-        <v>44.64500045776367</v>
+        <v>42.33463287353516</v>
       </c>
       <c r="C80" t="n">
-        <v>110.8899993896484</v>
+        <v>103.0998077392578</v>
       </c>
       <c r="D80" t="n">
-        <v>55.48249816894531</v>
+        <v>54.95952224731445</v>
       </c>
       <c r="E80" t="n">
         <v>84.50849914550781</v>
       </c>
       <c r="F80" t="n">
-        <v>4.085750102996826</v>
+        <v>4.042298793792725</v>
       </c>
       <c r="G80" t="n">
-        <v>140.6100006103516</v>
+        <v>139.2760772705078</v>
       </c>
       <c r="H80" t="n">
-        <v>41850</v>
+        <v>34520.66015625</v>
       </c>
       <c r="I80" t="n">
         <v>23.36533355712891</v>
       </c>
       <c r="J80" t="n">
-        <v>49.31000137329102</v>
+        <v>42.43722915649414</v>
       </c>
       <c r="K80" t="n">
-        <v>287.6192016601562</v>
+        <v>273.6307678222656</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2760.169921875</v>
       </c>
     </row>
     <row r="81">
@@ -3247,34 +3489,37 @@
         <v>43435</v>
       </c>
       <c r="B81" t="n">
-        <v>39.43500137329102</v>
+        <v>37.39425277709961</v>
       </c>
       <c r="C81" t="n">
-        <v>101.5699996948242</v>
+        <v>94.43453216552734</v>
       </c>
       <c r="D81" t="n">
-        <v>52.24800109863281</v>
+        <v>51.75550842285156</v>
       </c>
       <c r="E81" t="n">
         <v>75.09850311279297</v>
       </c>
       <c r="F81" t="n">
-        <v>3.337500095367432</v>
+        <v>3.302005767822266</v>
       </c>
       <c r="G81" t="n">
-        <v>131.0899963378906</v>
+        <v>129.8463592529297</v>
       </c>
       <c r="H81" t="n">
-        <v>38700</v>
+        <v>32219.74609375</v>
       </c>
       <c r="I81" t="n">
         <v>22.18666648864746</v>
       </c>
       <c r="J81" t="n">
-        <v>46.93000030517578</v>
+        <v>40.38895416259766</v>
       </c>
       <c r="K81" t="n">
-        <v>289.4629211425781</v>
+        <v>275.3847961425781</v>
+      </c>
+      <c r="L81" t="n">
+        <v>2506.85009765625</v>
       </c>
     </row>
     <row r="82">
@@ -3282,34 +3527,37 @@
         <v>43466</v>
       </c>
       <c r="B82" t="n">
-        <v>41.61000061035156</v>
+        <v>39.45669174194336</v>
       </c>
       <c r="C82" t="n">
-        <v>104.4300003051758</v>
+        <v>97.09362030029297</v>
       </c>
       <c r="D82" t="n">
-        <v>56.29449844360352</v>
+        <v>55.76386260986328</v>
       </c>
       <c r="E82" t="n">
         <v>85.93650054931641</v>
       </c>
       <c r="F82" t="n">
-        <v>3.59375</v>
+        <v>3.555529117584229</v>
       </c>
       <c r="G82" t="n">
-        <v>166.6900024414062</v>
+        <v>165.1086578369141</v>
       </c>
       <c r="H82" t="n">
-        <v>46150</v>
+        <v>38422.24609375</v>
       </c>
       <c r="I82" t="n">
         <v>20.4680004119873</v>
       </c>
       <c r="J82" t="n">
-        <v>47.11999893188477</v>
+        <v>40.55246734619141</v>
       </c>
       <c r="K82" t="n">
-        <v>318.9623413085938</v>
+        <v>303.4495239257812</v>
+      </c>
+      <c r="L82" t="n">
+        <v>2704.10009765625</v>
       </c>
     </row>
     <row r="83">
@@ -3317,34 +3565,37 @@
         <v>43497</v>
       </c>
       <c r="B83" t="n">
-        <v>43.28749847412109</v>
+        <v>41.22343063354492</v>
       </c>
       <c r="C83" t="n">
-        <v>112.0299987792969</v>
+        <v>104.6045455932617</v>
       </c>
       <c r="D83" t="n">
-        <v>56.32749938964844</v>
+        <v>55.79655838012695</v>
       </c>
       <c r="E83" t="n">
         <v>81.99150085449219</v>
       </c>
       <c r="F83" t="n">
-        <v>3.856499910354614</v>
+        <v>3.819418430328369</v>
       </c>
       <c r="G83" t="n">
-        <v>161.4499969482422</v>
+        <v>159.9183502197266</v>
       </c>
       <c r="H83" t="n">
-        <v>45100</v>
+        <v>37548.06640625</v>
       </c>
       <c r="I83" t="n">
         <v>21.32533264160156</v>
       </c>
       <c r="J83" t="n">
-        <v>52.95999908447266</v>
+        <v>45.86740112304688</v>
       </c>
       <c r="K83" t="n">
-        <v>309.5593872070312</v>
+        <v>294.50390625</v>
+      </c>
+      <c r="L83" t="n">
+        <v>2784.489990234375</v>
       </c>
     </row>
     <row r="84">
@@ -3352,34 +3603,37 @@
         <v>43525</v>
       </c>
       <c r="B84" t="n">
-        <v>47.48749923706055</v>
+        <v>45.22315979003906</v>
       </c>
       <c r="C84" t="n">
-        <v>117.9400024414062</v>
+        <v>110.1228103637695</v>
       </c>
       <c r="D84" t="n">
-        <v>58.84450149536133</v>
+        <v>58.28983306884766</v>
       </c>
       <c r="E84" t="n">
         <v>89.03749847412109</v>
       </c>
       <c r="F84" t="n">
-        <v>4.488999843597412</v>
+        <v>4.445836544036865</v>
       </c>
       <c r="G84" t="n">
-        <v>166.6900024414062</v>
+        <v>165.1086578369141</v>
       </c>
       <c r="H84" t="n">
-        <v>44650</v>
+        <v>37465.875</v>
       </c>
       <c r="I84" t="n">
         <v>18.65733337402344</v>
       </c>
       <c r="J84" t="n">
-        <v>53.70000076293945</v>
+        <v>46.50830841064453</v>
       </c>
       <c r="K84" t="n">
-        <v>332.7901916503906</v>
+        <v>316.6048583984375</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2834.39990234375</v>
       </c>
     </row>
     <row r="85">
@@ -3387,34 +3641,37 @@
         <v>43556</v>
       </c>
       <c r="B85" t="n">
-        <v>50.16749954223633</v>
+        <v>47.77536392211914</v>
       </c>
       <c r="C85" t="n">
-        <v>130.6000061035156</v>
+        <v>121.9437026977539</v>
       </c>
       <c r="D85" t="n">
-        <v>59.94800186157227</v>
+        <v>59.38292694091797</v>
       </c>
       <c r="E85" t="n">
         <v>96.32599639892578</v>
       </c>
       <c r="F85" t="n">
-        <v>4.525000095367432</v>
+        <v>4.481490135192871</v>
       </c>
       <c r="G85" t="n">
-        <v>193.3999938964844</v>
+        <v>191.5652465820312</v>
       </c>
       <c r="H85" t="n">
-        <v>45850</v>
+        <v>38472.80078125</v>
       </c>
       <c r="I85" t="n">
         <v>15.9126672744751</v>
       </c>
       <c r="J85" t="n">
-        <v>51.04000091552734</v>
+        <v>44.20454406738281</v>
       </c>
       <c r="K85" t="n">
-        <v>357.6802978515625</v>
+        <v>340.2843933105469</v>
+      </c>
+      <c r="L85" t="n">
+        <v>2945.830078125</v>
       </c>
     </row>
     <row r="86">
@@ -3422,34 +3679,37 @@
         <v>43586</v>
       </c>
       <c r="B86" t="n">
-        <v>43.76750183105469</v>
+        <v>41.8410530090332</v>
       </c>
       <c r="C86" t="n">
-        <v>123.6800003051758</v>
+        <v>115.9098358154297</v>
       </c>
       <c r="D86" t="n">
-        <v>55.32500076293945</v>
+        <v>54.80350112915039</v>
       </c>
       <c r="E86" t="n">
         <v>88.75350189208984</v>
       </c>
       <c r="F86" t="n">
-        <v>3.386499881744385</v>
+        <v>3.357765913009644</v>
       </c>
       <c r="G86" t="n">
-        <v>177.4700012207031</v>
+        <v>175.7863922119141</v>
       </c>
       <c r="H86" t="n">
-        <v>42500</v>
+        <v>35661.80078125</v>
       </c>
       <c r="I86" t="n">
         <v>12.3439998626709</v>
       </c>
       <c r="J86" t="n">
-        <v>44.04000091552734</v>
+        <v>38.3755989074707</v>
       </c>
       <c r="K86" t="n">
-        <v>300.5252075195312</v>
+        <v>286.7599487304688</v>
+      </c>
+      <c r="L86" t="n">
+        <v>2752.06005859375</v>
       </c>
     </row>
     <row r="87">
@@ -3457,34 +3717,37 @@
         <v>43617</v>
       </c>
       <c r="B87" t="n">
-        <v>49.47999954223633</v>
+        <v>47.30210113525391</v>
       </c>
       <c r="C87" t="n">
-        <v>133.9600067138672</v>
+        <v>125.5440139770508</v>
       </c>
       <c r="D87" t="n">
-        <v>54.13999938964844</v>
+        <v>53.62968444824219</v>
       </c>
       <c r="E87" t="n">
         <v>94.68150329589844</v>
       </c>
       <c r="F87" t="n">
-        <v>4.10575008392334</v>
+        <v>4.07091236114502</v>
       </c>
       <c r="G87" t="n">
-        <v>193</v>
+        <v>191.1690368652344</v>
       </c>
       <c r="H87" t="n">
-        <v>47000</v>
+        <v>39745.63671875</v>
       </c>
       <c r="I87" t="n">
         <v>14.8973331451416</v>
       </c>
       <c r="J87" t="n">
-        <v>47.86999893188477</v>
+        <v>41.71298599243164</v>
       </c>
       <c r="K87" t="n">
-        <v>325.0465698242188</v>
+        <v>310.1581420898438</v>
+      </c>
+      <c r="L87" t="n">
+        <v>2941.760009765625</v>
       </c>
     </row>
     <row r="88">
@@ -3492,34 +3755,37 @@
         <v>43647</v>
       </c>
       <c r="B88" t="n">
-        <v>53.2599983215332</v>
+        <v>50.91572952270508</v>
       </c>
       <c r="C88" t="n">
-        <v>136.2700042724609</v>
+        <v>127.7088851928711</v>
       </c>
       <c r="D88" t="n">
-        <v>60.90999984741211</v>
+        <v>60.33586120605469</v>
       </c>
       <c r="E88" t="n">
         <v>93.33899688720703</v>
       </c>
       <c r="F88" t="n">
-        <v>4.217999935150146</v>
+        <v>4.182210445404053</v>
       </c>
       <c r="G88" t="n">
-        <v>194.2299957275391</v>
+        <v>192.3873596191406</v>
       </c>
       <c r="H88" t="n">
-        <v>45350</v>
+        <v>38350.3125</v>
       </c>
       <c r="I88" t="n">
         <v>16.10733222961426</v>
       </c>
       <c r="J88" t="n">
-        <v>50.54999923706055</v>
+        <v>44.04827880859375</v>
       </c>
       <c r="K88" t="n">
-        <v>339.4275512695312</v>
+        <v>323.8804016113281</v>
+      </c>
+      <c r="L88" t="n">
+        <v>2980.3798828125</v>
       </c>
     </row>
     <row r="89">
@@ -3527,34 +3793,37 @@
         <v>43678</v>
       </c>
       <c r="B89" t="n">
-        <v>52.18500137329102</v>
+        <v>50.07759475708008</v>
       </c>
       <c r="C89" t="n">
-        <v>137.8600006103516</v>
+        <v>129.6291809082031</v>
       </c>
       <c r="D89" t="n">
-        <v>59.5265007019043</v>
+        <v>58.96540451049805</v>
       </c>
       <c r="E89" t="n">
         <v>88.81449890136719</v>
       </c>
       <c r="F89" t="n">
-        <v>4.187749862670898</v>
+        <v>4.156326293945312</v>
       </c>
       <c r="G89" t="n">
-        <v>185.6699981689453</v>
+        <v>183.9085693359375</v>
       </c>
       <c r="H89" t="n">
-        <v>44000</v>
+        <v>37208.6796875</v>
       </c>
       <c r="I89" t="n">
         <v>15.0406665802002</v>
       </c>
       <c r="J89" t="n">
-        <v>47.40999984741211</v>
+        <v>41.5910758972168</v>
       </c>
       <c r="K89" t="n">
-        <v>299.4189758300781</v>
+        <v>285.7043762207031</v>
+      </c>
+      <c r="L89" t="n">
+        <v>2926.4599609375</v>
       </c>
     </row>
     <row r="90">
@@ -3562,34 +3831,37 @@
         <v>43709</v>
       </c>
       <c r="B90" t="n">
-        <v>55.99250030517578</v>
+        <v>53.7313346862793</v>
       </c>
       <c r="C90" t="n">
-        <v>139.0299987792969</v>
+        <v>130.7293395996094</v>
       </c>
       <c r="D90" t="n">
-        <v>61.05699920654297</v>
+        <v>60.48147583007812</v>
       </c>
       <c r="E90" t="n">
         <v>86.79550170898438</v>
       </c>
       <c r="F90" t="n">
-        <v>4.351749897003174</v>
+        <v>4.319096565246582</v>
       </c>
       <c r="G90" t="n">
-        <v>178.0800018310547</v>
+        <v>176.3905639648438</v>
       </c>
       <c r="H90" t="n">
-        <v>49050</v>
+        <v>41779.83984375</v>
       </c>
       <c r="I90" t="n">
         <v>16.0580005645752</v>
       </c>
       <c r="J90" t="n">
-        <v>51.52999877929688</v>
+        <v>45.20540618896484</v>
       </c>
       <c r="K90" t="n">
-        <v>304.3970031738281</v>
+        <v>290.454345703125</v>
+      </c>
+      <c r="L90" t="n">
+        <v>2976.739990234375</v>
       </c>
     </row>
     <row r="91">
@@ -3597,34 +3869,37 @@
         <v>43739</v>
       </c>
       <c r="B91" t="n">
-        <v>62.18999862670898</v>
+        <v>59.67855834960938</v>
       </c>
       <c r="C91" t="n">
-        <v>143.3699951171875</v>
+        <v>134.8102416992188</v>
       </c>
       <c r="D91" t="n">
-        <v>62.93999862670898</v>
+        <v>62.34672927856445</v>
       </c>
       <c r="E91" t="n">
         <v>88.83300018310547</v>
       </c>
       <c r="F91" t="n">
-        <v>5.025499820709229</v>
+        <v>4.987791061401367</v>
       </c>
       <c r="G91" t="n">
-        <v>191.6499938964844</v>
+        <v>189.8318634033203</v>
       </c>
       <c r="H91" t="n">
-        <v>50400</v>
+        <v>42929.7421875</v>
       </c>
       <c r="I91" t="n">
         <v>20.99466705322266</v>
       </c>
       <c r="J91" t="n">
-        <v>56.52999877929688</v>
+        <v>49.59171295166016</v>
       </c>
       <c r="K91" t="n">
-        <v>295.7315368652344</v>
+        <v>282.1858215332031</v>
+      </c>
+      <c r="L91" t="n">
+        <v>3037.56005859375</v>
       </c>
     </row>
     <row r="92">
@@ -3632,34 +3907,37 @@
         <v>43770</v>
       </c>
       <c r="B92" t="n">
-        <v>66.8125</v>
+        <v>64.30686187744141</v>
       </c>
       <c r="C92" t="n">
-        <v>151.3800048828125</v>
+        <v>142.8264007568359</v>
       </c>
       <c r="D92" t="n">
-        <v>65.20449829101562</v>
+        <v>64.58988189697266</v>
       </c>
       <c r="E92" t="n">
         <v>90.04000091552734</v>
       </c>
       <c r="F92" t="n">
-        <v>5.418499946594238</v>
+        <v>5.381810665130615</v>
       </c>
       <c r="G92" t="n">
-        <v>201.6399993896484</v>
+        <v>199.7270965576172</v>
       </c>
       <c r="H92" t="n">
-        <v>50300</v>
+        <v>42844.546875</v>
       </c>
       <c r="I92" t="n">
         <v>21.99600028991699</v>
       </c>
       <c r="J92" t="n">
-        <v>58.04999923706055</v>
+        <v>51.20542907714844</v>
       </c>
       <c r="K92" t="n">
-        <v>305.8719787597656</v>
+        <v>291.86181640625</v>
+      </c>
+      <c r="L92" t="n">
+        <v>3140.97998046875</v>
       </c>
     </row>
     <row r="93">
@@ -3667,34 +3945,37 @@
         <v>43800</v>
       </c>
       <c r="B93" t="n">
-        <v>73.41249847412109</v>
+        <v>70.65934753417969</v>
       </c>
       <c r="C93" t="n">
-        <v>157.6999969482422</v>
+        <v>148.7892150878906</v>
       </c>
       <c r="D93" t="n">
-        <v>66.96949768066406</v>
+        <v>66.33823394775391</v>
       </c>
       <c r="E93" t="n">
         <v>92.39199829101562</v>
       </c>
       <c r="F93" t="n">
-        <v>5.882500171661377</v>
+        <v>5.84266996383667</v>
       </c>
       <c r="G93" t="n">
-        <v>205.25</v>
+        <v>203.3028411865234</v>
       </c>
       <c r="H93" t="n">
-        <v>55800</v>
+        <v>47835.0234375</v>
       </c>
       <c r="I93" t="n">
         <v>27.8886661529541</v>
       </c>
       <c r="J93" t="n">
-        <v>59.84999847412109</v>
+        <v>52.79319381713867</v>
       </c>
       <c r="K93" t="n">
-        <v>346.249267578125</v>
+        <v>330.3896484375</v>
+      </c>
+      <c r="L93" t="n">
+        <v>3230.780029296875</v>
       </c>
     </row>
     <row r="94">
@@ -3702,34 +3983,37 @@
         <v>43831</v>
       </c>
       <c r="B94" t="n">
-        <v>77.37750244140625</v>
+        <v>74.47565460205078</v>
       </c>
       <c r="C94" t="n">
-        <v>170.2299957275391</v>
+        <v>160.6112365722656</v>
       </c>
       <c r="D94" t="n">
-        <v>71.63899993896484</v>
+        <v>70.96372985839844</v>
       </c>
       <c r="E94" t="n">
         <v>100.4359970092773</v>
       </c>
       <c r="F94" t="n">
-        <v>5.910749912261963</v>
+        <v>5.870727062225342</v>
       </c>
       <c r="G94" t="n">
-        <v>201.9100036621094</v>
+        <v>199.9945220947266</v>
       </c>
       <c r="H94" t="n">
-        <v>56400</v>
+        <v>48349.36328125</v>
       </c>
       <c r="I94" t="n">
         <v>43.37133407592773</v>
       </c>
       <c r="J94" t="n">
-        <v>63.93000030517578</v>
+        <v>56.39212799072266</v>
       </c>
       <c r="K94" t="n">
-        <v>343.8524475097656</v>
+        <v>328.1026000976562</v>
+      </c>
+      <c r="L94" t="n">
+        <v>3225.52001953125</v>
       </c>
     </row>
     <row r="95">
@@ -3737,34 +4021,37 @@
         <v>43862</v>
       </c>
       <c r="B95" t="n">
-        <v>68.33999633789062</v>
+        <v>65.93318939208984</v>
       </c>
       <c r="C95" t="n">
-        <v>162.0099945068359</v>
+        <v>153.273193359375</v>
       </c>
       <c r="D95" t="n">
-        <v>66.96250152587891</v>
+        <v>66.33131408691406</v>
       </c>
       <c r="E95" t="n">
         <v>94.1875</v>
       </c>
       <c r="F95" t="n">
-        <v>6.751749992370605</v>
+        <v>6.710043430328369</v>
       </c>
       <c r="G95" t="n">
-        <v>192.4700012207031</v>
+        <v>190.6440734863281</v>
       </c>
       <c r="H95" t="n">
-        <v>54200</v>
+        <v>46463.40625</v>
       </c>
       <c r="I95" t="n">
         <v>44.53266525268555</v>
       </c>
       <c r="J95" t="n">
-        <v>55.52000045776367</v>
+        <v>49.21491241455078</v>
       </c>
       <c r="K95" t="n">
-        <v>355.8365783691406</v>
+        <v>339.5377807617188</v>
+      </c>
+      <c r="L95" t="n">
+        <v>2954.219970703125</v>
       </c>
     </row>
     <row r="96">
@@ -3772,34 +4059,37 @@
         <v>43891</v>
       </c>
       <c r="B96" t="n">
-        <v>63.5724983215332</v>
+        <v>61.33361053466797</v>
       </c>
       <c r="C96" t="n">
-        <v>157.7100067138672</v>
+        <v>149.2051391601562</v>
       </c>
       <c r="D96" t="n">
-        <v>58.09749984741211</v>
+        <v>57.54986953735352</v>
       </c>
       <c r="E96" t="n">
         <v>97.48600006103516</v>
       </c>
       <c r="F96" t="n">
-        <v>6.590000152587891</v>
+        <v>6.54929256439209</v>
       </c>
       <c r="G96" t="n">
-        <v>166.8000030517578</v>
+        <v>165.2175903320312</v>
       </c>
       <c r="H96" t="n">
-        <v>47750</v>
+        <v>41236.3203125</v>
       </c>
       <c r="I96" t="n">
         <v>34.93333435058594</v>
       </c>
       <c r="J96" t="n">
-        <v>54.11999893188477</v>
+        <v>47.97391128540039</v>
       </c>
       <c r="K96" t="n">
-        <v>350.4898071289062</v>
+        <v>334.4359436035156</v>
+      </c>
+      <c r="L96" t="n">
+        <v>2584.590087890625</v>
       </c>
     </row>
     <row r="97">
@@ -3807,34 +4097,37 @@
         <v>43922</v>
       </c>
       <c r="B97" t="n">
-        <v>73.44999694824219</v>
+        <v>70.86323547363281</v>
       </c>
       <c r="C97" t="n">
-        <v>179.2100067138672</v>
+        <v>169.5457000732422</v>
       </c>
       <c r="D97" t="n">
-        <v>67.33499908447266</v>
+        <v>66.70030212402344</v>
       </c>
       <c r="E97" t="n">
         <v>123.6999969482422</v>
       </c>
       <c r="F97" t="n">
-        <v>7.307000160217285</v>
+        <v>7.261863231658936</v>
       </c>
       <c r="G97" t="n">
-        <v>204.7100067138672</v>
+        <v>202.7679748535156</v>
       </c>
       <c r="H97" t="n">
-        <v>50000</v>
+        <v>43179.3828125</v>
       </c>
       <c r="I97" t="n">
         <v>52.12533187866211</v>
       </c>
       <c r="J97" t="n">
-        <v>59.97999954223633</v>
+        <v>53.16842269897461</v>
       </c>
       <c r="K97" t="n">
-        <v>384.4141540527344</v>
+        <v>366.8064270019531</v>
+      </c>
+      <c r="L97" t="n">
+        <v>2912.429931640625</v>
       </c>
     </row>
     <row r="98">
@@ -3842,34 +4135,37 @@
         <v>43952</v>
       </c>
       <c r="B98" t="n">
-        <v>79.48500061035156</v>
+        <v>76.89329528808594</v>
       </c>
       <c r="C98" t="n">
-        <v>183.25</v>
+        <v>173.8506622314453</v>
       </c>
       <c r="D98" t="n">
-        <v>71.67600250244141</v>
+        <v>71.00038909912109</v>
       </c>
       <c r="E98" t="n">
         <v>122.1184997558594</v>
       </c>
       <c r="F98" t="n">
-        <v>8.875499725341797</v>
+        <v>8.820676803588867</v>
       </c>
       <c r="G98" t="n">
-        <v>225.0899963378906</v>
+        <v>222.95458984375</v>
       </c>
       <c r="H98" t="n">
-        <v>50700</v>
+        <v>43783.890625</v>
       </c>
       <c r="I98" t="n">
         <v>55.66666793823242</v>
       </c>
       <c r="J98" t="n">
-        <v>62.93000030517578</v>
+        <v>56.09851455688477</v>
       </c>
       <c r="K98" t="n">
-        <v>378.3298950195312</v>
+        <v>362.0954895019531</v>
+      </c>
+      <c r="L98" t="n">
+        <v>3044.31005859375</v>
       </c>
     </row>
     <row r="99">
@@ -3877,34 +4173,37 @@
         <v>43983</v>
       </c>
       <c r="B99" t="n">
-        <v>91.19999694824219</v>
+        <v>88.22629547119141</v>
       </c>
       <c r="C99" t="n">
-        <v>203.5099945068359</v>
+        <v>193.0715179443359</v>
       </c>
       <c r="D99" t="n">
-        <v>70.90249633789062</v>
+        <v>70.23416137695312</v>
       </c>
       <c r="E99" t="n">
         <v>137.9409942626953</v>
       </c>
       <c r="F99" t="n">
-        <v>9.497750282287598</v>
+        <v>9.443387985229492</v>
       </c>
       <c r="G99" t="n">
-        <v>227.0700073242188</v>
+        <v>224.9158325195312</v>
       </c>
       <c r="H99" t="n">
-        <v>52800</v>
+        <v>45902.30078125</v>
       </c>
       <c r="I99" t="n">
         <v>71.98733520507812</v>
       </c>
       <c r="J99" t="n">
-        <v>59.83000183105469</v>
+        <v>53.33504867553711</v>
       </c>
       <c r="K99" t="n">
-        <v>459.6376342773438</v>
+        <v>439.9142150878906</v>
+      </c>
+      <c r="L99" t="n">
+        <v>3100.2900390625</v>
       </c>
     </row>
     <row r="100">
@@ -3912,34 +4211,37 @@
         <v>44013</v>
       </c>
       <c r="B100" t="n">
-        <v>106.2600021362305</v>
+        <v>102.7952423095703</v>
       </c>
       <c r="C100" t="n">
-        <v>205.0099945068359</v>
+        <v>194.4945220947266</v>
       </c>
       <c r="D100" t="n">
-        <v>74.39749908447266</v>
+        <v>73.69624328613281</v>
       </c>
       <c r="E100" t="n">
         <v>158.2339935302734</v>
       </c>
       <c r="F100" t="n">
-        <v>10.61474990844727</v>
+        <v>10.55399513244629</v>
       </c>
       <c r="G100" t="n">
-        <v>253.6699981689453</v>
+        <v>251.2634735107422</v>
       </c>
       <c r="H100" t="n">
-        <v>57900</v>
+        <v>50336.046875</v>
       </c>
       <c r="I100" t="n">
         <v>95.38400268554688</v>
       </c>
       <c r="J100" t="n">
-        <v>47.72999954223633</v>
+        <v>42.54858779907227</v>
       </c>
       <c r="K100" t="n">
-        <v>492.2713317871094</v>
+        <v>471.1475524902344</v>
+      </c>
+      <c r="L100" t="n">
+        <v>3271.1201171875</v>
       </c>
     </row>
     <row r="101">
@@ -3947,34 +4249,37 @@
         <v>44044</v>
       </c>
       <c r="B101" t="n">
-        <v>129.0399932861328</v>
+        <v>125.0575332641602</v>
       </c>
       <c r="C101" t="n">
-        <v>225.5299987792969</v>
+        <v>214.4792327880859</v>
       </c>
       <c r="D101" t="n">
-        <v>81.47650146484375</v>
+        <v>80.70849609375</v>
       </c>
       <c r="E101" t="n">
         <v>172.5480041503906</v>
       </c>
       <c r="F101" t="n">
-        <v>13.3745002746582</v>
+        <v>13.29794883728027</v>
       </c>
       <c r="G101" t="n">
-        <v>293.2000122070312</v>
+        <v>290.4184875488281</v>
       </c>
       <c r="H101" t="n">
-        <v>54000</v>
+        <v>46945.53515625</v>
       </c>
       <c r="I101" t="n">
         <v>166.1066741943359</v>
       </c>
       <c r="J101" t="n">
-        <v>50.95000076293945</v>
+        <v>45.72748947143555</v>
       </c>
       <c r="K101" t="n">
-        <v>489.0448608398438</v>
+        <v>468.0595703125</v>
+      </c>
+      <c r="L101" t="n">
+        <v>3500.31005859375</v>
       </c>
     </row>
     <row r="102">
@@ -3982,34 +4287,37 @@
         <v>44075</v>
       </c>
       <c r="B102" t="n">
-        <v>115.8099975585938</v>
+        <v>112.2358627319336</v>
       </c>
       <c r="C102" t="n">
-        <v>210.3300018310547</v>
+        <v>200.0240173339844</v>
       </c>
       <c r="D102" t="n">
-        <v>73.27999877929688</v>
+        <v>72.58926391601562</v>
       </c>
       <c r="E102" t="n">
         <v>157.4364929199219</v>
       </c>
       <c r="F102" t="n">
-        <v>13.5305004119873</v>
+        <v>13.4570837020874</v>
       </c>
       <c r="G102" t="n">
-        <v>261.8999938964844</v>
+        <v>259.4154052734375</v>
       </c>
       <c r="H102" t="n">
-        <v>58200</v>
+        <v>50908.09375</v>
       </c>
       <c r="I102" t="n">
         <v>143.0033264160156</v>
       </c>
       <c r="J102" t="n">
-        <v>51.77999877929688</v>
+        <v>46.47240829467773</v>
       </c>
       <c r="K102" t="n">
-        <v>471.5295715332031</v>
+        <v>451.2958984375</v>
+      </c>
+      <c r="L102" t="n">
+        <v>3363</v>
       </c>
     </row>
     <row r="103">
@@ -4017,34 +4325,37 @@
         <v>44105</v>
       </c>
       <c r="B103" t="n">
-        <v>108.8600006103516</v>
+        <v>105.5003509521484</v>
       </c>
       <c r="C103" t="n">
-        <v>202.4700012207031</v>
+        <v>192.5491180419922</v>
       </c>
       <c r="D103" t="n">
-        <v>80.80549621582031</v>
+        <v>80.0438232421875</v>
       </c>
       <c r="E103" t="n">
         <v>151.8074951171875</v>
       </c>
       <c r="F103" t="n">
-        <v>12.53400039672852</v>
+        <v>12.46598720550537</v>
       </c>
       <c r="G103" t="n">
-        <v>263.1099853515625</v>
+        <v>260.6138610839844</v>
       </c>
       <c r="H103" t="n">
-        <v>56600</v>
+        <v>49508.5703125</v>
       </c>
       <c r="I103" t="n">
         <v>129.3466644287109</v>
       </c>
       <c r="J103" t="n">
-        <v>44.27999877929688</v>
+        <v>39.74117660522461</v>
       </c>
       <c r="K103" t="n">
-        <v>544.817138671875</v>
+        <v>521.438720703125</v>
+      </c>
+      <c r="L103" t="n">
+        <v>3269.9599609375</v>
       </c>
     </row>
     <row r="104">
@@ -4052,34 +4363,37 @@
         <v>44136</v>
       </c>
       <c r="B104" t="n">
-        <v>119.0500030517578</v>
+        <v>115.5749130249023</v>
       </c>
       <c r="C104" t="n">
-        <v>214.0700073242188</v>
+        <v>204.1137542724609</v>
       </c>
       <c r="D104" t="n">
-        <v>87.72000122070312</v>
+        <v>86.89315032958984</v>
       </c>
       <c r="E104" t="n">
         <v>158.4019927978516</v>
       </c>
       <c r="F104" t="n">
-        <v>13.40149974822998</v>
+        <v>13.328782081604</v>
       </c>
       <c r="G104" t="n">
-        <v>276.9700012207031</v>
+        <v>274.3424682617188</v>
       </c>
       <c r="H104" t="n">
-        <v>66700</v>
+        <v>58343.13671875</v>
       </c>
       <c r="I104" t="n">
         <v>189.1999969482422</v>
       </c>
       <c r="J104" t="n">
-        <v>48.34999847412109</v>
+        <v>43.70962142944336</v>
       </c>
       <c r="K104" t="n">
-        <v>519.0051879882812</v>
+        <v>496.7342834472656</v>
+      </c>
+      <c r="L104" t="n">
+        <v>3621.6298828125</v>
       </c>
     </row>
     <row r="105">
@@ -4087,34 +4401,37 @@
         <v>44166</v>
       </c>
       <c r="B105" t="n">
-        <v>132.6900024414062</v>
+        <v>128.8167266845703</v>
       </c>
       <c r="C105" t="n">
-        <v>222.4199981689453</v>
+        <v>212.0753784179688</v>
       </c>
       <c r="D105" t="n">
-        <v>87.63200378417969</v>
+        <v>86.80598449707031</v>
       </c>
       <c r="E105" t="n">
         <v>162.8464965820312</v>
       </c>
       <c r="F105" t="n">
-        <v>13.05500030517578</v>
+        <v>12.98799705505371</v>
       </c>
       <c r="G105" t="n">
-        <v>273.1600036621094</v>
+        <v>270.568603515625</v>
       </c>
       <c r="H105" t="n">
-        <v>81000</v>
+        <v>72634.6015625</v>
       </c>
       <c r="I105" t="n">
         <v>235.2233276367188</v>
       </c>
       <c r="J105" t="n">
-        <v>49.81999969482422</v>
+        <v>45.03854370117188</v>
       </c>
       <c r="K105" t="n">
-        <v>521.770751953125</v>
+        <v>499.3811645507812</v>
+      </c>
+      <c r="L105" t="n">
+        <v>3756.070068359375</v>
       </c>
     </row>
     <row r="106">
@@ -4122,34 +4439,37 @@
         <v>44197</v>
       </c>
       <c r="B106" t="n">
-        <v>131.9600067138672</v>
+        <v>128.1080780029297</v>
       </c>
       <c r="C106" t="n">
-        <v>231.9600067138672</v>
+        <v>221.1716613769531</v>
       </c>
       <c r="D106" t="n">
-        <v>91.36799621582031</v>
+        <v>90.50675964355469</v>
       </c>
       <c r="E106" t="n">
         <v>160.3099975585938</v>
       </c>
       <c r="F106" t="n">
-        <v>12.98974990844727</v>
+        <v>12.92308235168457</v>
       </c>
       <c r="G106" t="n">
-        <v>258.3299865722656</v>
+        <v>255.8792114257812</v>
       </c>
       <c r="H106" t="n">
-        <v>82000</v>
+        <v>73531.3125</v>
       </c>
       <c r="I106" t="n">
         <v>264.510009765625</v>
       </c>
       <c r="J106" t="n">
-        <v>55.5099983215332</v>
+        <v>50.18244171142578</v>
       </c>
       <c r="K106" t="n">
-        <v>628.2451782226562</v>
+        <v>601.2867431640625</v>
+      </c>
+      <c r="L106" t="n">
+        <v>3714.239990234375</v>
       </c>
     </row>
     <row r="107">
@@ -4157,34 +4477,37 @@
         <v>44228</v>
       </c>
       <c r="B107" t="n">
-        <v>121.2600021362305</v>
+        <v>117.8962936401367</v>
       </c>
       <c r="C107" t="n">
-        <v>232.3800048828125</v>
+        <v>222.0824737548828</v>
       </c>
       <c r="D107" t="n">
-        <v>101.0954971313477</v>
+        <v>100.1425704956055</v>
       </c>
       <c r="E107" t="n">
         <v>154.6464996337891</v>
       </c>
       <c r="F107" t="n">
-        <v>13.71450042724609</v>
+        <v>13.6441125869751</v>
       </c>
       <c r="G107" t="n">
-        <v>257.6199951171875</v>
+        <v>255.1759948730469</v>
       </c>
       <c r="H107" t="n">
-        <v>82500</v>
+        <v>73979.671875</v>
       </c>
       <c r="I107" t="n">
         <v>225.1666717529297</v>
       </c>
       <c r="J107" t="n">
-        <v>60.77999877929688</v>
+        <v>55.28018188476562</v>
       </c>
       <c r="K107" t="n">
-        <v>610.7299194335938</v>
+        <v>584.5230102539062</v>
+      </c>
+      <c r="L107" t="n">
+        <v>3811.14990234375</v>
       </c>
     </row>
     <row r="108">
@@ -4192,34 +4515,37 @@
         <v>44256</v>
       </c>
       <c r="B108" t="n">
-        <v>122.1500015258789</v>
+        <v>118.7616271972656</v>
       </c>
       <c r="C108" t="n">
-        <v>235.7700042724609</v>
+        <v>225.3222503662109</v>
       </c>
       <c r="D108" t="n">
-        <v>103.1259994506836</v>
+        <v>102.153923034668</v>
       </c>
       <c r="E108" t="n">
         <v>154.7039947509766</v>
       </c>
       <c r="F108" t="n">
-        <v>13.34825038909912</v>
+        <v>13.28432655334473</v>
       </c>
       <c r="G108" t="n">
-        <v>294.5299987792969</v>
+        <v>291.7358703613281</v>
       </c>
       <c r="H108" t="n">
-        <v>81400</v>
+        <v>73317.65625</v>
       </c>
       <c r="I108" t="n">
         <v>222.6433258056641</v>
       </c>
       <c r="J108" t="n">
-        <v>64</v>
+        <v>58.20880508422852</v>
       </c>
       <c r="K108" t="n">
-        <v>562.3324584960938</v>
+        <v>538.2022705078125</v>
+      </c>
+      <c r="L108" t="n">
+        <v>3972.889892578125</v>
       </c>
     </row>
     <row r="109">
@@ -4227,34 +4553,37 @@
         <v>44287</v>
       </c>
       <c r="B109" t="n">
-        <v>131.4600067138672</v>
+        <v>127.8133850097656</v>
       </c>
       <c r="C109" t="n">
-        <v>252.1799926757812</v>
+        <v>241.0050659179688</v>
       </c>
       <c r="D109" t="n">
-        <v>117.6750030517578</v>
+        <v>116.5658111572266</v>
       </c>
       <c r="E109" t="n">
         <v>173.3710021972656</v>
       </c>
       <c r="F109" t="n">
-        <v>15.00949954986572</v>
+        <v>14.93762111663818</v>
       </c>
       <c r="G109" t="n">
-        <v>325.0799865722656</v>
+        <v>321.9960021972656</v>
       </c>
       <c r="H109" t="n">
-        <v>81500</v>
+        <v>73407.6953125</v>
       </c>
       <c r="I109" t="n">
         <v>236.4799957275391</v>
       </c>
       <c r="J109" t="n">
-        <v>57.52999877929688</v>
+        <v>52.32426834106445</v>
       </c>
       <c r="K109" t="n">
-        <v>574.3165893554688</v>
+        <v>549.6722412109375</v>
+      </c>
+      <c r="L109" t="n">
+        <v>4181.169921875</v>
       </c>
     </row>
     <row r="110">
@@ -4262,34 +4591,37 @@
         <v>44317</v>
       </c>
       <c r="B110" t="n">
-        <v>124.6100006103516</v>
+        <v>121.3591842651367</v>
       </c>
       <c r="C110" t="n">
-        <v>249.6799926757812</v>
+        <v>239.1668243408203</v>
       </c>
       <c r="D110" t="n">
-        <v>117.8424987792969</v>
+        <v>116.7317199707031</v>
       </c>
       <c r="E110" t="n">
         <v>161.1535034179688</v>
       </c>
       <c r="F110" t="n">
-        <v>16.24449920654297</v>
+        <v>16.16670417785645</v>
       </c>
       <c r="G110" t="n">
-        <v>328.7300109863281</v>
+        <v>325.6114196777344</v>
       </c>
       <c r="H110" t="n">
-        <v>80500</v>
+        <v>72507.015625</v>
       </c>
       <c r="I110" t="n">
         <v>208.4066619873047</v>
       </c>
       <c r="J110" t="n">
-        <v>57.11999893188477</v>
+        <v>52.27133941650391</v>
       </c>
       <c r="K110" t="n">
-        <v>570.629150390625</v>
+        <v>547.758544921875</v>
+      </c>
+      <c r="L110" t="n">
+        <v>4204.10986328125</v>
       </c>
     </row>
     <row r="111">
@@ -4297,34 +4629,37 @@
         <v>44348</v>
       </c>
       <c r="B111" t="n">
-        <v>136.9600067138672</v>
+        <v>133.3869781494141</v>
       </c>
       <c r="C111" t="n">
-        <v>270.8999938964844</v>
+        <v>259.4934692382812</v>
       </c>
       <c r="D111" t="n">
-        <v>122.0895004272461</v>
+        <v>120.9386901855469</v>
       </c>
       <c r="E111" t="n">
         <v>172.0079956054688</v>
       </c>
       <c r="F111" t="n">
-        <v>20.00250053405762</v>
+        <v>19.91127395629883</v>
       </c>
       <c r="G111" t="n">
-        <v>347.7099914550781</v>
+        <v>344.4113464355469</v>
       </c>
       <c r="H111" t="n">
-        <v>80700</v>
+        <v>73008.953125</v>
       </c>
       <c r="I111" t="n">
         <v>226.5666656494141</v>
       </c>
       <c r="J111" t="n">
-        <v>56.13999938964844</v>
+        <v>51.37452697753906</v>
       </c>
       <c r="K111" t="n">
-        <v>538.3641357421875</v>
+        <v>516.78662109375</v>
+      </c>
+      <c r="L111" t="n">
+        <v>4297.5</v>
       </c>
     </row>
     <row r="112">
@@ -4332,34 +4667,37 @@
         <v>44378</v>
       </c>
       <c r="B112" t="n">
-        <v>145.8600006103516</v>
+        <v>142.0548095703125</v>
       </c>
       <c r="C112" t="n">
-        <v>284.9100036621094</v>
+        <v>272.9134216308594</v>
       </c>
       <c r="D112" t="n">
-        <v>134.7265014648438</v>
+        <v>133.4565582275391</v>
       </c>
       <c r="E112" t="n">
         <v>166.3795013427734</v>
       </c>
       <c r="F112" t="n">
-        <v>19.49900054931641</v>
+        <v>19.41007232666016</v>
       </c>
       <c r="G112" t="n">
-        <v>356.2999877929688</v>
+        <v>352.9197998046875</v>
       </c>
       <c r="H112" t="n">
-        <v>78500</v>
+        <v>71018.625</v>
       </c>
       <c r="I112" t="n">
         <v>229.0666656494141</v>
       </c>
       <c r="J112" t="n">
-        <v>53.72000122070312</v>
+        <v>49.15994644165039</v>
       </c>
       <c r="K112" t="n">
-        <v>441.5692443847656</v>
+        <v>423.8712768554688</v>
+      </c>
+      <c r="L112" t="n">
+        <v>4395.259765625</v>
       </c>
     </row>
     <row r="113">
@@ -4367,34 +4705,37 @@
         <v>44409</v>
       </c>
       <c r="B113" t="n">
-        <v>151.8300018310547</v>
+        <v>148.0906219482422</v>
       </c>
       <c r="C113" t="n">
-        <v>301.8800048828125</v>
+        <v>289.7224731445312</v>
       </c>
       <c r="D113" t="n">
-        <v>144.6974945068359</v>
+        <v>143.3335723876953</v>
       </c>
       <c r="E113" t="n">
         <v>173.5395050048828</v>
       </c>
       <c r="F113" t="n">
-        <v>22.38500022888184</v>
+        <v>22.28683662414551</v>
       </c>
       <c r="G113" t="n">
-        <v>379.3800048828125</v>
+        <v>375.7808227539062</v>
       </c>
       <c r="H113" t="n">
-        <v>76700</v>
+        <v>69390.1875</v>
       </c>
       <c r="I113" t="n">
         <v>245.2400054931641</v>
       </c>
       <c r="J113" t="n">
-        <v>54.06000137329102</v>
+        <v>49.79256439208984</v>
       </c>
       <c r="K113" t="n">
-        <v>443.5973205566406</v>
+        <v>425.8180847167969</v>
+      </c>
+      <c r="L113" t="n">
+        <v>4522.68017578125</v>
       </c>
     </row>
     <row r="114">
@@ -4402,34 +4743,37 @@
         <v>44440</v>
       </c>
       <c r="B114" t="n">
-        <v>141.5</v>
+        <v>138.0150299072266</v>
       </c>
       <c r="C114" t="n">
-        <v>281.9200134277344</v>
+        <v>270.5663146972656</v>
       </c>
       <c r="D114" t="n">
-        <v>133.6759948730469</v>
+        <v>132.4159698486328</v>
       </c>
       <c r="E114" t="n">
         <v>164.2519989013672</v>
       </c>
       <c r="F114" t="n">
-        <v>20.71599960327148</v>
+        <v>20.62515830993652</v>
       </c>
       <c r="G114" t="n">
-        <v>339.3900146484375</v>
+        <v>336.1702880859375</v>
       </c>
       <c r="H114" t="n">
-        <v>74100</v>
+        <v>67356.6484375</v>
       </c>
       <c r="I114" t="n">
         <v>258.4933471679688</v>
       </c>
       <c r="J114" t="n">
-        <v>53.27999877929688</v>
+        <v>49.07412719726562</v>
       </c>
       <c r="K114" t="n">
-        <v>425.3445739746094</v>
+        <v>408.296875</v>
+      </c>
+      <c r="L114" t="n">
+        <v>4307.5400390625</v>
       </c>
     </row>
     <row r="115">
@@ -4437,34 +4781,37 @@
         <v>44470</v>
       </c>
       <c r="B115" t="n">
-        <v>149.8000030517578</v>
+        <v>146.1105651855469</v>
       </c>
       <c r="C115" t="n">
-        <v>331.6199951171875</v>
+        <v>318.2647705078125</v>
       </c>
       <c r="D115" t="n">
-        <v>148.0460052490234</v>
+        <v>146.6505279541016</v>
       </c>
       <c r="E115" t="n">
         <v>168.6215057373047</v>
       </c>
       <c r="F115" t="n">
-        <v>25.5669994354248</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="G115" t="n">
-        <v>323.5700073242188</v>
+        <v>320.5003051757812</v>
       </c>
       <c r="H115" t="n">
-        <v>69800</v>
+        <v>63447.953125</v>
       </c>
       <c r="I115" t="n">
         <v>371.3333435058594</v>
       </c>
       <c r="J115" t="n">
-        <v>49</v>
+        <v>45.13199996948242</v>
       </c>
       <c r="K115" t="n">
-        <v>443.4129638671875</v>
+        <v>425.6410827636719</v>
+      </c>
+      <c r="L115" t="n">
+        <v>4605.3798828125</v>
       </c>
     </row>
     <row r="116">
@@ -4472,34 +4819,37 @@
         <v>44501</v>
       </c>
       <c r="B116" t="n">
-        <v>165.3000030517578</v>
+        <v>161.4641265869141</v>
       </c>
       <c r="C116" t="n">
-        <v>330.5899963378906</v>
+        <v>317.8566589355469</v>
       </c>
       <c r="D116" t="n">
-        <v>141.8975067138672</v>
+        <v>140.5599975585938</v>
       </c>
       <c r="E116" t="n">
         <v>175.3535003662109</v>
       </c>
       <c r="F116" t="n">
-        <v>32.67599868774414</v>
+        <v>32.53270721435547</v>
       </c>
       <c r="G116" t="n">
-        <v>324.4599914550781</v>
+        <v>321.3819580078125</v>
       </c>
       <c r="H116" t="n">
-        <v>71300</v>
+        <v>64811.45703125</v>
       </c>
       <c r="I116" t="n">
         <v>381.586669921875</v>
       </c>
       <c r="J116" t="n">
-        <v>49.20000076293945</v>
+        <v>45.63134765625</v>
       </c>
       <c r="K116" t="n">
-        <v>423.5008544921875</v>
+        <v>406.5270690917969</v>
+      </c>
+      <c r="L116" t="n">
+        <v>4567</v>
       </c>
     </row>
     <row r="117">
@@ -4507,34 +4857,37 @@
         <v>44531</v>
       </c>
       <c r="B117" t="n">
-        <v>177.5700073242188</v>
+        <v>173.4494476318359</v>
       </c>
       <c r="C117" t="n">
-        <v>336.3200073242188</v>
+        <v>323.3659973144531</v>
       </c>
       <c r="D117" t="n">
-        <v>144.8520050048828</v>
+        <v>143.4866333007812</v>
       </c>
       <c r="E117" t="n">
         <v>166.7169952392578</v>
       </c>
       <c r="F117" t="n">
-        <v>29.4109992980957</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="G117" t="n">
-        <v>336.3500061035156</v>
+        <v>333.1590881347656</v>
       </c>
       <c r="H117" t="n">
-        <v>78300</v>
+        <v>71495.8515625</v>
       </c>
       <c r="I117" t="n">
         <v>352.260009765625</v>
       </c>
       <c r="J117" t="n">
-        <v>51.5</v>
+        <v>47.7645149230957</v>
       </c>
       <c r="K117" t="n">
-        <v>421.1040344238281</v>
+        <v>404.226318359375</v>
+      </c>
+      <c r="L117" t="n">
+        <v>4766.18017578125</v>
       </c>
     </row>
     <row r="118">
@@ -4542,34 +4895,37 @@
         <v>44562</v>
       </c>
       <c r="B118" t="n">
-        <v>174.7799987792969</v>
+        <v>170.7241516113281</v>
       </c>
       <c r="C118" t="n">
-        <v>310.9800109863281</v>
+        <v>299.0020141601562</v>
       </c>
       <c r="D118" t="n">
-        <v>135.3034973144531</v>
+        <v>134.0281219482422</v>
       </c>
       <c r="E118" t="n">
         <v>149.5735015869141</v>
       </c>
       <c r="F118" t="n">
-        <v>24.48600006103516</v>
+        <v>24.38160514831543</v>
       </c>
       <c r="G118" t="n">
-        <v>313.260009765625</v>
+        <v>310.2882080078125</v>
       </c>
       <c r="H118" t="n">
-        <v>73300</v>
+        <v>66930.3515625</v>
       </c>
       <c r="I118" t="n">
         <v>312.239990234375</v>
       </c>
       <c r="J118" t="n">
-        <v>48.81999969482422</v>
+        <v>45.27890396118164</v>
       </c>
       <c r="K118" t="n">
-        <v>447.53564453125</v>
+        <v>429.5985107421875</v>
+      </c>
+      <c r="L118" t="n">
+        <v>4515.5498046875</v>
       </c>
     </row>
     <row r="119">
@@ -4577,34 +4933,37 @@
         <v>44593</v>
       </c>
       <c r="B119" t="n">
-        <v>165.1199951171875</v>
+        <v>161.4937896728516</v>
       </c>
       <c r="C119" t="n">
-        <v>298.7900085449219</v>
+        <v>287.8755798339844</v>
       </c>
       <c r="D119" t="n">
-        <v>135.0570068359375</v>
+        <v>133.7839660644531</v>
       </c>
       <c r="E119" t="n">
         <v>153.5630035400391</v>
       </c>
       <c r="F119" t="n">
-        <v>24.38500022888184</v>
+        <v>24.28103828430176</v>
       </c>
       <c r="G119" t="n">
-        <v>211.0299987792969</v>
+        <v>209.0279693603516</v>
       </c>
       <c r="H119" t="n">
-        <v>71900</v>
+        <v>65651.9921875</v>
       </c>
       <c r="I119" t="n">
         <v>290.1433410644531</v>
       </c>
       <c r="J119" t="n">
-        <v>47.70000076293945</v>
+        <v>44.57715225219727</v>
       </c>
       <c r="K119" t="n">
-        <v>400.0467224121094</v>
+        <v>384.012939453125</v>
+      </c>
+      <c r="L119" t="n">
+        <v>4373.93994140625</v>
       </c>
     </row>
     <row r="120">
@@ -4612,34 +4971,37 @@
         <v>44621</v>
       </c>
       <c r="B120" t="n">
-        <v>174.6100006103516</v>
+        <v>170.7754211425781</v>
       </c>
       <c r="C120" t="n">
-        <v>308.3099975585938</v>
+        <v>297.0478515625</v>
       </c>
       <c r="D120" t="n">
-        <v>139.0675048828125</v>
+        <v>137.7566375732422</v>
       </c>
       <c r="E120" t="n">
         <v>162.9974975585938</v>
       </c>
       <c r="F120" t="n">
-        <v>27.2859992980957</v>
+        <v>27.17430305480957</v>
       </c>
       <c r="G120" t="n">
-        <v>222.3600006103516</v>
+        <v>220.2505187988281</v>
       </c>
       <c r="H120" t="n">
-        <v>69600</v>
+        <v>63880.35546875</v>
       </c>
       <c r="I120" t="n">
         <v>359.2000122070312</v>
       </c>
       <c r="J120" t="n">
-        <v>49.56000137329102</v>
+        <v>46.31538391113281</v>
       </c>
       <c r="K120" t="n">
-        <v>355.4071350097656</v>
+        <v>341.1625366210938</v>
+      </c>
+      <c r="L120" t="n">
+        <v>4530.41015625</v>
       </c>
     </row>
     <row r="121">
@@ -4647,34 +5009,37 @@
         <v>44652</v>
       </c>
       <c r="B121" t="n">
-        <v>157.6499938964844</v>
+        <v>154.1878509521484</v>
       </c>
       <c r="C121" t="n">
-        <v>277.5199890136719</v>
+        <v>267.3825378417969</v>
       </c>
       <c r="D121" t="n">
-        <v>114.1094970703125</v>
+        <v>113.0339050292969</v>
       </c>
       <c r="E121" t="n">
         <v>124.2815017700195</v>
       </c>
       <c r="F121" t="n">
-        <v>18.54700088500977</v>
+        <v>18.47107315063477</v>
       </c>
       <c r="G121" t="n">
-        <v>200.4700012207031</v>
+        <v>198.5681915283203</v>
       </c>
       <c r="H121" t="n">
-        <v>67400</v>
+        <v>61861.1640625</v>
       </c>
       <c r="I121" t="n">
         <v>290.2533264160156</v>
       </c>
       <c r="J121" t="n">
-        <v>43.59000015258789</v>
+        <v>40.73622512817383</v>
       </c>
       <c r="K121" t="n">
-        <v>358.4464416503906</v>
+        <v>344.0800170898438</v>
+      </c>
+      <c r="L121" t="n">
+        <v>4131.93017578125</v>
       </c>
     </row>
     <row r="122">
@@ -4682,34 +5047,37 @@
         <v>44682</v>
       </c>
       <c r="B122" t="n">
-        <v>148.8399963378906</v>
+        <v>145.7852478027344</v>
       </c>
       <c r="C122" t="n">
-        <v>271.8699951171875</v>
+        <v>262.5490112304688</v>
       </c>
       <c r="D122" t="n">
-        <v>113.7620010375977</v>
+        <v>112.6896896362305</v>
       </c>
       <c r="E122" t="n">
         <v>120.2095031738281</v>
       </c>
       <c r="F122" t="n">
-        <v>18.67200088500977</v>
+        <v>18.59556579589844</v>
       </c>
       <c r="G122" t="n">
-        <v>193.6399993896484</v>
+        <v>191.802978515625</v>
       </c>
       <c r="H122" t="n">
-        <v>67400</v>
+        <v>61861.1640625</v>
       </c>
       <c r="I122" t="n">
         <v>252.7533264160156</v>
       </c>
       <c r="J122" t="n">
-        <v>44.41999816894531</v>
+        <v>41.84003067016602</v>
       </c>
       <c r="K122" t="n">
-        <v>344.1997375488281</v>
+        <v>332.0408325195312</v>
+      </c>
+      <c r="L122" t="n">
+        <v>4132.14990234375</v>
       </c>
     </row>
     <row r="123">
@@ -4717,34 +5085,37 @@
         <v>44713</v>
       </c>
       <c r="B123" t="n">
-        <v>136.7200012207031</v>
+        <v>133.9139709472656</v>
       </c>
       <c r="C123" t="n">
-        <v>256.8299865722656</v>
+        <v>248.0246124267578</v>
       </c>
       <c r="D123" t="n">
-        <v>108.9629974365234</v>
+        <v>107.9359130859375</v>
       </c>
       <c r="E123" t="n">
         <v>106.2099990844727</v>
       </c>
       <c r="F123" t="n">
-        <v>15.15900039672852</v>
+        <v>15.10013484954834</v>
       </c>
       <c r="G123" t="n">
-        <v>161.25</v>
+        <v>159.7202453613281</v>
       </c>
       <c r="H123" t="n">
-        <v>57000</v>
+        <v>52635.71484375</v>
       </c>
       <c r="I123" t="n">
         <v>224.4733276367188</v>
       </c>
       <c r="J123" t="n">
-        <v>37.40999984741211</v>
+        <v>35.23717498779297</v>
       </c>
       <c r="K123" t="n">
-        <v>336.6015319824219</v>
+        <v>324.7109985351562</v>
+      </c>
+      <c r="L123" t="n">
+        <v>3785.3798828125</v>
       </c>
     </row>
     <row r="124">
@@ -4752,34 +5123,37 @@
         <v>44743</v>
       </c>
       <c r="B124" t="n">
-        <v>162.5099945068359</v>
+        <v>159.1746826171875</v>
       </c>
       <c r="C124" t="n">
-        <v>280.739990234375</v>
+        <v>271.1149597167969</v>
       </c>
       <c r="D124" t="n">
-        <v>116.3199996948242</v>
+        <v>115.2235717773438</v>
       </c>
       <c r="E124" t="n">
         <v>134.9499969482422</v>
       </c>
       <c r="F124" t="n">
-        <v>18.16300010681152</v>
+        <v>18.09247207641602</v>
       </c>
       <c r="G124" t="n">
-        <v>159.1000061035156</v>
+        <v>157.5906524658203</v>
       </c>
       <c r="H124" t="n">
-        <v>61400</v>
+        <v>56698.8125</v>
       </c>
       <c r="I124" t="n">
         <v>297.1499938964844</v>
       </c>
       <c r="J124" t="n">
-        <v>36.31000137329102</v>
+        <v>34.20107269287109</v>
       </c>
       <c r="K124" t="n">
-        <v>291.3920593261719</v>
+        <v>281.0985717773438</v>
+      </c>
+      <c r="L124" t="n">
+        <v>4130.2900390625</v>
       </c>
     </row>
     <row r="125">
@@ -4787,34 +5161,37 @@
         <v>44774</v>
       </c>
       <c r="B125" t="n">
-        <v>157.2200012207031</v>
+        <v>154.2071380615234</v>
       </c>
       <c r="C125" t="n">
-        <v>261.4700012207031</v>
+        <v>253.0415802001953</v>
       </c>
       <c r="D125" t="n">
-        <v>108.2200012207031</v>
+        <v>107.1999282836914</v>
       </c>
       <c r="E125" t="n">
         <v>126.7699966430664</v>
       </c>
       <c r="F125" t="n">
-        <v>15.0939998626709</v>
+        <v>15.03538608551025</v>
       </c>
       <c r="G125" t="n">
-        <v>162.9299926757812</v>
+        <v>161.3842926025391</v>
       </c>
       <c r="H125" t="n">
-        <v>59700</v>
+        <v>55128.98046875</v>
       </c>
       <c r="I125" t="n">
         <v>275.6099853515625</v>
       </c>
       <c r="J125" t="n">
-        <v>31.92000007629395</v>
+        <v>30.36957168579102</v>
       </c>
       <c r="K125" t="n">
-        <v>310.7675476074219</v>
+        <v>299.7896118164062</v>
+      </c>
+      <c r="L125" t="n">
+        <v>3955</v>
       </c>
     </row>
     <row r="126">
@@ -4822,34 +5199,37 @@
         <v>44805</v>
       </c>
       <c r="B126" t="n">
-        <v>138.1999969482422</v>
+        <v>135.5515899658203</v>
       </c>
       <c r="C126" t="n">
-        <v>232.8999938964844</v>
+        <v>225.3924865722656</v>
       </c>
       <c r="D126" t="n">
-        <v>95.65000152587891</v>
+        <v>94.7484130859375</v>
       </c>
       <c r="E126" t="n">
         <v>113</v>
       </c>
       <c r="F126" t="n">
-        <v>12.13899993896484</v>
+        <v>12.09545421600342</v>
       </c>
       <c r="G126" t="n">
-        <v>135.6799926757812</v>
+        <v>134.3928375244141</v>
       </c>
       <c r="H126" t="n">
-        <v>53100</v>
+        <v>49371.23046875</v>
       </c>
       <c r="I126" t="n">
         <v>265.25</v>
       </c>
       <c r="J126" t="n">
-        <v>25.77000045776367</v>
+        <v>24.51829528808594</v>
       </c>
       <c r="K126" t="n">
-        <v>253.0210113525391</v>
+        <v>244.0829925537109</v>
+      </c>
+      <c r="L126" t="n">
+        <v>3585.6201171875</v>
       </c>
     </row>
     <row r="127">
@@ -4857,34 +5237,37 @@
         <v>44835</v>
       </c>
       <c r="B127" t="n">
-        <v>153.3399963378906</v>
+        <v>150.4014892578125</v>
       </c>
       <c r="C127" t="n">
-        <v>232.1300048828125</v>
+        <v>224.6473388671875</v>
       </c>
       <c r="D127" t="n">
-        <v>94.51000213623047</v>
+        <v>93.61914825439453</v>
       </c>
       <c r="E127" t="n">
         <v>102.4400024414062</v>
       </c>
       <c r="F127" t="n">
-        <v>13.49699974060059</v>
+        <v>13.44858264923096</v>
       </c>
       <c r="G127" t="n">
-        <v>93.16000366210938</v>
+        <v>92.27621459960938</v>
       </c>
       <c r="H127" t="n">
-        <v>59400</v>
+        <v>55228.83984375</v>
       </c>
       <c r="I127" t="n">
         <v>227.5399932861328</v>
       </c>
       <c r="J127" t="n">
-        <v>28.43000030517578</v>
+        <v>27.04909324645996</v>
       </c>
       <c r="K127" t="n">
-        <v>195.2744750976562</v>
+        <v>188.3763885498047</v>
+      </c>
+      <c r="L127" t="n">
+        <v>3871.97998046875</v>
       </c>
     </row>
     <row r="128">
@@ -4892,34 +5275,37 @@
         <v>44866</v>
       </c>
       <c r="B128" t="n">
-        <v>148.0299987792969</v>
+        <v>145.43408203125</v>
       </c>
       <c r="C128" t="n">
-        <v>255.1399993896484</v>
+        <v>247.6114196777344</v>
       </c>
       <c r="D128" t="n">
-        <v>100.9899978637695</v>
+        <v>100.0380630493164</v>
       </c>
       <c r="E128" t="n">
         <v>96.54000091552734</v>
       </c>
       <c r="F128" t="n">
-        <v>16.92300033569336</v>
+        <v>16.86660957336426</v>
       </c>
       <c r="G128" t="n">
-        <v>118.0999984741211</v>
+        <v>116.979606628418</v>
       </c>
       <c r="H128" t="n">
-        <v>62200</v>
+        <v>57832.21875</v>
       </c>
       <c r="I128" t="n">
         <v>194.6999969482422</v>
       </c>
       <c r="J128" t="n">
-        <v>30.06999969482422</v>
+        <v>28.99583435058594</v>
       </c>
       <c r="K128" t="n">
-        <v>272.7763977050781</v>
+        <v>263.1405029296875</v>
+      </c>
+      <c r="L128" t="n">
+        <v>4080.110107421875</v>
       </c>
     </row>
     <row r="129">
@@ -4927,34 +5313,37 @@
         <v>44896</v>
       </c>
       <c r="B129" t="n">
-        <v>129.9299926757812</v>
+        <v>127.6515045166016</v>
       </c>
       <c r="C129" t="n">
-        <v>239.8200073242188</v>
+        <v>232.7434844970703</v>
       </c>
       <c r="D129" t="n">
-        <v>88.23000335693359</v>
+        <v>87.39835357666016</v>
       </c>
       <c r="E129" t="n">
         <v>84</v>
       </c>
       <c r="F129" t="n">
-        <v>14.61400032043457</v>
+        <v>14.56530380249023</v>
       </c>
       <c r="G129" t="n">
-        <v>120.3399963378906</v>
+        <v>119.198356628418</v>
       </c>
       <c r="H129" t="n">
-        <v>55300</v>
+        <v>51738.22265625</v>
       </c>
       <c r="I129" t="n">
         <v>123.1800003051758</v>
       </c>
       <c r="J129" t="n">
-        <v>26.43000030517578</v>
+        <v>25.48586082458496</v>
       </c>
       <c r="K129" t="n">
-        <v>317.2260437011719</v>
+        <v>306.0199890136719</v>
+      </c>
+      <c r="L129" t="n">
+        <v>3839.5</v>
       </c>
     </row>
     <row r="130">
@@ -4962,34 +5351,37 @@
         <v>44927</v>
       </c>
       <c r="B130" t="n">
-        <v>144.2899932861328</v>
+        <v>141.7597045898438</v>
       </c>
       <c r="C130" t="n">
-        <v>247.8099975585938</v>
+        <v>240.4976959228516</v>
       </c>
       <c r="D130" t="n">
-        <v>98.83999633789062</v>
+        <v>97.9083251953125</v>
       </c>
       <c r="E130" t="n">
         <v>103.129997253418</v>
       </c>
       <c r="F130" t="n">
-        <v>19.53700065612793</v>
+        <v>19.47189903259277</v>
       </c>
       <c r="G130" t="n">
-        <v>148.9700012207031</v>
+        <v>147.5567474365234</v>
       </c>
       <c r="H130" t="n">
-        <v>61400</v>
+        <v>57445.33203125</v>
       </c>
       <c r="I130" t="n">
         <v>173.2200012207031</v>
       </c>
       <c r="J130" t="n">
-        <v>28.26000022888184</v>
+        <v>27.25049209594727</v>
       </c>
       <c r="K130" t="n">
-        <v>382.2000122070312</v>
+        <v>368.6986999511719</v>
+      </c>
+      <c r="L130" t="n">
+        <v>4076.60009765625</v>
       </c>
     </row>
     <row r="131">
@@ -4997,34 +5389,37 @@
         <v>44958</v>
       </c>
       <c r="B131" t="n">
-        <v>147.4100036621094</v>
+        <v>145.0460968017578</v>
       </c>
       <c r="C131" t="n">
-        <v>249.4199981689453</v>
+        <v>242.66650390625</v>
       </c>
       <c r="D131" t="n">
-        <v>90.05999755859375</v>
+        <v>89.21110534667969</v>
       </c>
       <c r="E131" t="n">
         <v>94.23000335693359</v>
       </c>
       <c r="F131" t="n">
-        <v>23.21599960327148</v>
+        <v>23.13863563537598</v>
       </c>
       <c r="G131" t="n">
-        <v>174.9400024414062</v>
+        <v>173.2804107666016</v>
       </c>
       <c r="H131" t="n">
-        <v>60600</v>
+        <v>56696.86328125</v>
       </c>
       <c r="I131" t="n">
         <v>205.7100067138672</v>
       </c>
       <c r="J131" t="n">
-        <v>24.93000030517578</v>
+        <v>24.33236312866211</v>
       </c>
       <c r="K131" t="n">
-        <v>343.6000061035156</v>
+        <v>331.4622497558594</v>
+      </c>
+      <c r="L131" t="n">
+        <v>3970.14990234375</v>
       </c>
     </row>
     <row r="132">
@@ -5032,34 +5427,37 @@
         <v>44986</v>
       </c>
       <c r="B132" t="n">
-        <v>164.8999938964844</v>
+        <v>162.2556304931641</v>
       </c>
       <c r="C132" t="n">
-        <v>288.2999877929688</v>
+        <v>280.4937133789062</v>
       </c>
       <c r="D132" t="n">
-        <v>103.7300033569336</v>
+        <v>102.7522430419922</v>
       </c>
       <c r="E132" t="n">
         <v>103.2900009155273</v>
       </c>
       <c r="F132" t="n">
-        <v>27.77700042724609</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="G132" t="n">
-        <v>211.9400024414062</v>
+        <v>209.9293670654297</v>
       </c>
       <c r="H132" t="n">
-        <v>64000</v>
+        <v>60224.6171875</v>
       </c>
       <c r="I132" t="n">
         <v>207.4600067138672</v>
       </c>
       <c r="J132" t="n">
-        <v>32.66999816894531</v>
+        <v>31.88681221008301</v>
       </c>
       <c r="K132" t="n">
-        <v>385.7999877929688</v>
+        <v>372.1715087890625</v>
+      </c>
+      <c r="L132" t="n">
+        <v>4109.31005859375</v>
       </c>
     </row>
     <row r="133">
@@ -5067,34 +5465,37 @@
         <v>45017</v>
       </c>
       <c r="B133" t="n">
-        <v>169.6799926757812</v>
+        <v>166.9589385986328</v>
       </c>
       <c r="C133" t="n">
-        <v>307.260009765625</v>
+        <v>298.9403686523438</v>
       </c>
       <c r="D133" t="n">
-        <v>107.3399963378906</v>
+        <v>106.3282089233398</v>
       </c>
       <c r="E133" t="n">
         <v>105.4499969482422</v>
       </c>
       <c r="F133" t="n">
-        <v>27.74900054931641</v>
+        <v>27.66123008728027</v>
       </c>
       <c r="G133" t="n">
-        <v>240.3200073242188</v>
+        <v>238.0401153564453</v>
       </c>
       <c r="H133" t="n">
-        <v>65500</v>
+        <v>61636.140625</v>
       </c>
       <c r="I133" t="n">
         <v>164.3099975585938</v>
       </c>
       <c r="J133" t="n">
-        <v>31.05999946594238</v>
+        <v>30.31541061401367</v>
       </c>
       <c r="K133" t="n">
-        <v>344.3999938964844</v>
+        <v>332.2340087890625</v>
+      </c>
+      <c r="L133" t="n">
+        <v>4169.47998046875</v>
       </c>
     </row>
     <row r="134">
@@ -5102,34 +5503,37 @@
         <v>45047</v>
       </c>
       <c r="B134" t="n">
-        <v>177.25</v>
+        <v>174.6488342285156</v>
       </c>
       <c r="C134" t="n">
-        <v>328.3900146484375</v>
+        <v>320.1966857910156</v>
       </c>
       <c r="D134" t="n">
-        <v>122.870002746582</v>
+        <v>121.7118301391602</v>
       </c>
       <c r="E134" t="n">
         <v>120.5800018310547</v>
       </c>
       <c r="F134" t="n">
-        <v>37.83399963378906</v>
+        <v>37.71432876586914</v>
       </c>
       <c r="G134" t="n">
-        <v>264.7200012207031</v>
+        <v>262.2086486816406</v>
       </c>
       <c r="H134" t="n">
-        <v>71400</v>
+        <v>67188.09375</v>
       </c>
       <c r="I134" t="n">
         <v>203.9299926757812</v>
       </c>
       <c r="J134" t="n">
-        <v>31.44000053405762</v>
+        <v>30.81196403503418</v>
       </c>
       <c r="K134" t="n">
-        <v>310.6000061035156</v>
+        <v>301.7593383789062</v>
+      </c>
+      <c r="L134" t="n">
+        <v>4179.830078125</v>
       </c>
     </row>
     <row r="135">
@@ -5137,34 +5541,37 @@
         <v>45078</v>
       </c>
       <c r="B135" t="n">
-        <v>193.9700012207031</v>
+        <v>191.1234588623047</v>
       </c>
       <c r="C135" t="n">
-        <v>340.5400085449219</v>
+        <v>332.0435485839844</v>
       </c>
       <c r="D135" t="n">
-        <v>119.6999969482422</v>
+        <v>118.5716934204102</v>
       </c>
       <c r="E135" t="n">
         <v>130.3600006103516</v>
       </c>
       <c r="F135" t="n">
-        <v>42.30199813842773</v>
+        <v>42.17256164550781</v>
       </c>
       <c r="G135" t="n">
-        <v>286.9800109863281</v>
+        <v>284.2574768066406</v>
       </c>
       <c r="H135" t="n">
-        <v>72200</v>
+        <v>68279.953125</v>
       </c>
       <c r="I135" t="n">
         <v>261.7699890136719</v>
       </c>
       <c r="J135" t="n">
-        <v>33.43999862670898</v>
+        <v>32.77201080322266</v>
       </c>
       <c r="K135" t="n">
-        <v>331.6000061035156</v>
+        <v>322.1615905761719</v>
+      </c>
+      <c r="L135" t="n">
+        <v>4450.3798828125</v>
       </c>
     </row>
     <row r="136">
@@ -5172,34 +5579,37 @@
         <v>45108</v>
       </c>
       <c r="B136" t="n">
-        <v>196.4499969482422</v>
+        <v>193.5670623779297</v>
       </c>
       <c r="C136" t="n">
-        <v>335.9200134277344</v>
+        <v>327.538818359375</v>
       </c>
       <c r="D136" t="n">
-        <v>132.7200012207031</v>
+        <v>131.4689636230469</v>
       </c>
       <c r="E136" t="n">
         <v>133.6799926757812</v>
       </c>
       <c r="F136" t="n">
-        <v>46.72900009155273</v>
+        <v>46.58601379394531</v>
       </c>
       <c r="G136" t="n">
-        <v>318.6000061035156</v>
+        <v>315.5775451660156</v>
       </c>
       <c r="H136" t="n">
-        <v>69800</v>
+        <v>66010.25</v>
       </c>
       <c r="I136" t="n">
         <v>267.4299926757812</v>
       </c>
       <c r="J136" t="n">
-        <v>35.77000045776367</v>
+        <v>35.05546569824219</v>
       </c>
       <c r="K136" t="n">
-        <v>354.3999938964844</v>
+        <v>344.3126220703125</v>
+      </c>
+      <c r="L136" t="n">
+        <v>4588.9599609375</v>
       </c>
     </row>
     <row r="137">
@@ -5207,34 +5617,37 @@
         <v>45139</v>
       </c>
       <c r="B137" t="n">
-        <v>187.8699951171875</v>
+        <v>185.3629302978516</v>
       </c>
       <c r="C137" t="n">
-        <v>327.760009765625</v>
+        <v>320.259033203125</v>
       </c>
       <c r="D137" t="n">
-        <v>136.1699981689453</v>
+        <v>134.8864440917969</v>
       </c>
       <c r="E137" t="n">
         <v>138.0099945068359</v>
       </c>
       <c r="F137" t="n">
-        <v>49.35499954223633</v>
+        <v>49.2039794921875</v>
       </c>
       <c r="G137" t="n">
-        <v>295.8900146484375</v>
+        <v>293.0830078125</v>
       </c>
       <c r="H137" t="n">
-        <v>66900</v>
+        <v>63267.69921875</v>
       </c>
       <c r="I137" t="n">
         <v>258.0799865722656</v>
       </c>
       <c r="J137" t="n">
-        <v>35.13999938964844</v>
+        <v>34.56194686889648</v>
       </c>
       <c r="K137" t="n">
-        <v>325</v>
+        <v>315.7494506835938</v>
+      </c>
+      <c r="L137" t="n">
+        <v>4507.66015625</v>
       </c>
     </row>
     <row r="138">
@@ -5242,34 +5655,37 @@
         <v>45170</v>
       </c>
       <c r="B138" t="n">
-        <v>171.2100067138672</v>
+        <v>168.9252777099609</v>
       </c>
       <c r="C138" t="n">
-        <v>315.75</v>
+        <v>308.52392578125</v>
       </c>
       <c r="D138" t="n">
-        <v>130.8600006103516</v>
+        <v>129.6265258789062</v>
       </c>
       <c r="E138" t="n">
         <v>127.120002746582</v>
       </c>
       <c r="F138" t="n">
-        <v>43.49900054931641</v>
+        <v>43.36947250366211</v>
       </c>
       <c r="G138" t="n">
-        <v>300.2099914550781</v>
+        <v>297.3619689941406</v>
       </c>
       <c r="H138" t="n">
-        <v>68400</v>
+        <v>65024.5078125</v>
       </c>
       <c r="I138" t="n">
         <v>250.2200012207031</v>
       </c>
       <c r="J138" t="n">
-        <v>35.54999923706055</v>
+        <v>34.96520233154297</v>
       </c>
       <c r="K138" t="n">
-        <v>306.2000122070312</v>
+        <v>297.4845581054688</v>
+      </c>
+      <c r="L138" t="n">
+        <v>4288.0498046875</v>
       </c>
     </row>
     <row r="139">
@@ -5277,34 +5693,37 @@
         <v>45200</v>
       </c>
       <c r="B139" t="n">
-        <v>170.7700042724609</v>
+        <v>168.4911499023438</v>
       </c>
       <c r="C139" t="n">
-        <v>338.1099853515625</v>
+        <v>330.3721923828125</v>
       </c>
       <c r="D139" t="n">
-        <v>124.0800018310547</v>
+        <v>122.9104232788086</v>
       </c>
       <c r="E139" t="n">
         <v>133.0899963378906</v>
       </c>
       <c r="F139" t="n">
-        <v>40.77999877929688</v>
+        <v>40.65856552124023</v>
       </c>
       <c r="G139" t="n">
-        <v>301.2699890136719</v>
+        <v>298.4118957519531</v>
       </c>
       <c r="H139" t="n">
-        <v>66900</v>
+        <v>63598.5234375</v>
       </c>
       <c r="I139" t="n">
         <v>200.8399963378906</v>
       </c>
       <c r="J139" t="n">
-        <v>36.5</v>
+        <v>35.89957809448242</v>
       </c>
       <c r="K139" t="n">
-        <v>289.2000122070312</v>
+        <v>280.9684448242188</v>
+      </c>
+      <c r="L139" t="n">
+        <v>4193.7998046875</v>
       </c>
     </row>
     <row r="140">
@@ -5312,34 +5731,37 @@
         <v>45231</v>
       </c>
       <c r="B140" t="n">
-        <v>189.9499969482422</v>
+        <v>187.662109375</v>
       </c>
       <c r="C140" t="n">
-        <v>378.9100036621094</v>
+        <v>370.9898681640625</v>
       </c>
       <c r="D140" t="n">
-        <v>132.5299987792969</v>
+        <v>131.2807312011719</v>
       </c>
       <c r="E140" t="n">
         <v>146.0899963378906</v>
       </c>
       <c r="F140" t="n">
-        <v>46.77000045776367</v>
+        <v>46.63072967529297</v>
       </c>
       <c r="G140" t="n">
-        <v>327.1499938964844</v>
+        <v>324.0463562011719</v>
       </c>
       <c r="H140" t="n">
-        <v>72800</v>
+        <v>69207.3671875</v>
       </c>
       <c r="I140" t="n">
         <v>240.0800018310547</v>
       </c>
       <c r="J140" t="n">
-        <v>44.70000076293945</v>
+        <v>44.1092529296875</v>
       </c>
       <c r="K140" t="n">
-        <v>327</v>
+        <v>317.6925048828125</v>
+      </c>
+      <c r="L140" t="n">
+        <v>4567.7998046875</v>
       </c>
     </row>
     <row r="141">
@@ -5347,34 +5769,37 @@
         <v>45261</v>
       </c>
       <c r="B141" t="n">
-        <v>192.5299987792969</v>
+        <v>190.2110137939453</v>
       </c>
       <c r="C141" t="n">
-        <v>376.0400085449219</v>
+        <v>368.1798706054688</v>
       </c>
       <c r="D141" t="n">
-        <v>139.6900024414062</v>
+        <v>138.3732757568359</v>
       </c>
       <c r="E141" t="n">
         <v>151.9400024414062</v>
       </c>
       <c r="F141" t="n">
-        <v>49.52199935913086</v>
+        <v>49.37887954711914</v>
       </c>
       <c r="G141" t="n">
-        <v>353.9599914550781</v>
+        <v>350.6020202636719</v>
       </c>
       <c r="H141" t="n">
-        <v>78500</v>
+        <v>74979.4453125</v>
       </c>
       <c r="I141" t="n">
         <v>248.4799957275391</v>
       </c>
       <c r="J141" t="n">
-        <v>50.25</v>
+        <v>49.58590316772461</v>
       </c>
       <c r="K141" t="n">
-        <v>293.6000061035156</v>
+        <v>285.2431945800781</v>
+      </c>
+      <c r="L141" t="n">
+        <v>4769.830078125</v>
       </c>
     </row>
     <row r="142">
@@ -5382,34 +5807,37 @@
         <v>45292</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3999938964844</v>
+        <v>182.1789245605469</v>
       </c>
       <c r="C142" t="n">
-        <v>397.5799865722656</v>
+        <v>389.2696228027344</v>
       </c>
       <c r="D142" t="n">
-        <v>140.1000061035156</v>
+        <v>138.7794036865234</v>
       </c>
       <c r="E142" t="n">
         <v>155.1999969482422</v>
       </c>
       <c r="F142" t="n">
-        <v>61.52700042724609</v>
+        <v>61.34919357299805</v>
       </c>
       <c r="G142" t="n">
-        <v>390.1400146484375</v>
+        <v>386.4388122558594</v>
       </c>
       <c r="H142" t="n">
-        <v>72700</v>
+        <v>69439.5625</v>
       </c>
       <c r="I142" t="n">
         <v>187.2899932861328</v>
       </c>
       <c r="J142" t="n">
-        <v>43.08000183105469</v>
+        <v>42.51066207885742</v>
       </c>
       <c r="K142" t="n">
-        <v>270.6000061035156</v>
+        <v>262.8978271484375</v>
+      </c>
+      <c r="L142" t="n">
+        <v>4845.64990234375</v>
       </c>
     </row>
     <row r="143">
@@ -5417,34 +5845,37 @@
         <v>45323</v>
       </c>
       <c r="B143" t="n">
-        <v>180.75</v>
+        <v>178.80078125</v>
       </c>
       <c r="C143" t="n">
-        <v>413.6400146484375</v>
+        <v>405.742919921875</v>
       </c>
       <c r="D143" t="n">
-        <v>138.4600067138672</v>
+        <v>137.1548767089844</v>
       </c>
       <c r="E143" t="n">
         <v>176.7599945068359</v>
       </c>
       <c r="F143" t="n">
-        <v>79.11199951171875</v>
+        <v>78.88335418701172</v>
       </c>
       <c r="G143" t="n">
-        <v>490.1300048828125</v>
+        <v>485.9953002929688</v>
       </c>
       <c r="H143" t="n">
-        <v>73400</v>
+        <v>70108.1640625</v>
       </c>
       <c r="I143" t="n">
         <v>201.8800048828125</v>
       </c>
       <c r="J143" t="n">
-        <v>43.04999923706055</v>
+        <v>42.60557556152344</v>
       </c>
       <c r="K143" t="n">
-        <v>277.2000122070312</v>
+        <v>269.3099975585938</v>
+      </c>
+      <c r="L143" t="n">
+        <v>5096.27001953125</v>
       </c>
     </row>
     <row r="144">
@@ -5452,34 +5883,37 @@
         <v>45352</v>
       </c>
       <c r="B144" t="n">
-        <v>171.4799957275391</v>
+        <v>169.6307525634766</v>
       </c>
       <c r="C144" t="n">
-        <v>420.7200012207031</v>
+        <v>412.6876831054688</v>
       </c>
       <c r="D144" t="n">
-        <v>150.9299926757812</v>
+        <v>149.50732421875</v>
       </c>
       <c r="E144" t="n">
         <v>180.3800048828125</v>
       </c>
       <c r="F144" t="n">
-        <v>90.35600280761719</v>
+        <v>90.09909057617188</v>
       </c>
       <c r="G144" t="n">
-        <v>485.5799865722656</v>
+        <v>481.4837036132812</v>
       </c>
       <c r="H144" t="n">
-        <v>82400</v>
+        <v>79062.1875</v>
       </c>
       <c r="I144" t="n">
         <v>175.7899932861328</v>
       </c>
       <c r="J144" t="n">
-        <v>44.16999816894531</v>
+        <v>43.71401214599609</v>
       </c>
       <c r="K144" t="n">
-        <v>303.7999877929688</v>
+        <v>295.1528625488281</v>
+      </c>
+      <c r="L144" t="n">
+        <v>5254.35009765625</v>
       </c>
     </row>
     <row r="145">
@@ -5487,34 +5921,37 @@
         <v>45383</v>
       </c>
       <c r="B145" t="n">
-        <v>170.3300018310547</v>
+        <v>168.4931488037109</v>
       </c>
       <c r="C145" t="n">
-        <v>389.3299865722656</v>
+        <v>381.8969421386719</v>
       </c>
       <c r="D145" t="n">
-        <v>162.7799987792969</v>
+        <v>161.2456359863281</v>
       </c>
       <c r="E145" t="n">
         <v>175</v>
       </c>
       <c r="F145" t="n">
-        <v>86.40200042724609</v>
+        <v>86.15634155273438</v>
       </c>
       <c r="G145" t="n">
-        <v>430.1700134277344</v>
+        <v>426.5411682128906</v>
       </c>
       <c r="H145" t="n">
-        <v>77500</v>
+        <v>74360.6875</v>
       </c>
       <c r="I145" t="n">
         <v>183.2799987792969</v>
       </c>
       <c r="J145" t="n">
-        <v>30.46999931335449</v>
+        <v>30.15544509887695</v>
       </c>
       <c r="K145" t="n">
-        <v>347.2000122070312</v>
+        <v>337.3175659179688</v>
+      </c>
+      <c r="L145" t="n">
+        <v>5035.68994140625</v>
       </c>
     </row>
     <row r="146">
@@ -5522,34 +5959,37 @@
         <v>45413</v>
       </c>
       <c r="B146" t="n">
-        <v>192.25</v>
+        <v>190.4346923828125</v>
       </c>
       <c r="C146" t="n">
-        <v>415.1300048828125</v>
+        <v>407.9389038085938</v>
       </c>
       <c r="D146" t="n">
-        <v>172.5</v>
+        <v>170.8740081787109</v>
       </c>
       <c r="E146" t="n">
         <v>176.4400024414062</v>
       </c>
       <c r="F146" t="n">
-        <v>109.6330032348633</v>
+        <v>109.3212890625</v>
       </c>
       <c r="G146" t="n">
-        <v>466.8299865722656</v>
+        <v>462.8918762207031</v>
       </c>
       <c r="H146" t="n">
-        <v>73500</v>
+        <v>70522.7109375</v>
       </c>
       <c r="I146" t="n">
         <v>178.0800018310547</v>
       </c>
       <c r="J146" t="n">
-        <v>30.85000038146973</v>
+        <v>30.6555347442627</v>
       </c>
       <c r="K146" t="n">
-        <v>359.7999877929688</v>
+        <v>352.5784606933594</v>
+      </c>
+      <c r="L146" t="n">
+        <v>5277.509765625</v>
       </c>
     </row>
     <row r="147">
@@ -5557,34 +5997,37 @@
         <v>45444</v>
       </c>
       <c r="B147" t="n">
-        <v>210.6199951171875</v>
+        <v>208.6312255859375</v>
       </c>
       <c r="C147" t="n">
-        <v>446.9500122070312</v>
+        <v>439.207763671875</v>
       </c>
       <c r="D147" t="n">
-        <v>182.1499938964844</v>
+        <v>180.64013671875</v>
       </c>
       <c r="E147" t="n">
         <v>193.25</v>
       </c>
       <c r="F147" t="n">
-        <v>123.5400009155273</v>
+        <v>123.1988677978516</v>
       </c>
       <c r="G147" t="n">
-        <v>504.2200012207031</v>
+        <v>500.462890625</v>
       </c>
       <c r="H147" t="n">
-        <v>81500</v>
+        <v>78547.4296875</v>
       </c>
       <c r="I147" t="n">
         <v>197.8800048828125</v>
       </c>
       <c r="J147" t="n">
-        <v>30.96999931335449</v>
+        <v>30.77477645874023</v>
       </c>
       <c r="K147" t="n">
-        <v>372.3999938964844</v>
+        <v>364.9255981445312</v>
+      </c>
+      <c r="L147" t="n">
+        <v>5460.47998046875</v>
       </c>
     </row>
     <row r="148">
@@ -5592,34 +6035,37 @@
         <v>45474</v>
       </c>
       <c r="B148" t="n">
-        <v>222.0800018310547</v>
+        <v>219.9830627441406</v>
       </c>
       <c r="C148" t="n">
-        <v>418.3500061035156</v>
+        <v>411.1031799316406</v>
       </c>
       <c r="D148" t="n">
-        <v>171.5399932861328</v>
+        <v>170.1180572509766</v>
       </c>
       <c r="E148" t="n">
         <v>186.9799957275391</v>
       </c>
       <c r="F148" t="n">
-        <v>117.0199966430664</v>
+        <v>116.6968460083008</v>
       </c>
       <c r="G148" t="n">
-        <v>474.8299865722656</v>
+        <v>471.2918395996094</v>
       </c>
       <c r="H148" t="n">
-        <v>83900</v>
+        <v>80860.4921875</v>
       </c>
       <c r="I148" t="n">
         <v>232.0700073242188</v>
       </c>
       <c r="J148" t="n">
-        <v>30.73999977111816</v>
+        <v>30.54622650146484</v>
       </c>
       <c r="K148" t="n">
-        <v>362.2000122070312</v>
+        <v>354.9303588867188</v>
+      </c>
+      <c r="L148" t="n">
+        <v>5522.2998046875</v>
       </c>
     </row>
     <row r="149">
@@ -5627,25 +6073,25 @@
         <v>45505</v>
       </c>
       <c r="B149" t="n">
-        <v>229</v>
+        <v>227.1002655029297</v>
       </c>
       <c r="C149" t="n">
-        <v>417.1400146484375</v>
+        <v>410.6529541015625</v>
       </c>
       <c r="D149" t="n">
-        <v>163.3800048828125</v>
+        <v>162.0257263183594</v>
       </c>
       <c r="E149" t="n">
         <v>178.5</v>
       </c>
       <c r="F149" t="n">
-        <v>119.370002746582</v>
+        <v>119.0403823852539</v>
       </c>
       <c r="G149" t="n">
-        <v>521.3099975585938</v>
+        <v>517.425537109375</v>
       </c>
       <c r="H149" t="n">
-        <v>74300</v>
+        <v>71608.2890625</v>
       </c>
       <c r="I149" t="n">
         <v>214.1100006103516</v>
@@ -5654,7 +6100,10 @@
         <v>22.04000091552734</v>
       </c>
       <c r="K149" t="n">
-        <v>382</v>
+        <v>374.3329162597656</v>
+      </c>
+      <c r="L149" t="n">
+        <v>5648.39990234375</v>
       </c>
     </row>
     <row r="150">
@@ -5662,25 +6111,25 @@
         <v>45536</v>
       </c>
       <c r="B150" t="n">
-        <v>233</v>
+        <v>231.0670776367188</v>
       </c>
       <c r="C150" t="n">
-        <v>430.2999877929688</v>
+        <v>423.6082153320312</v>
       </c>
       <c r="D150" t="n">
-        <v>165.8500061035156</v>
+        <v>164.6935119628906</v>
       </c>
       <c r="E150" t="n">
         <v>186.3300018310547</v>
       </c>
       <c r="F150" t="n">
-        <v>121.4400024414062</v>
+        <v>121.1150283813477</v>
       </c>
       <c r="G150" t="n">
-        <v>572.4400024414062</v>
+        <v>568.716552734375</v>
       </c>
       <c r="H150" t="n">
-        <v>61500</v>
+        <v>59604.55859375</v>
       </c>
       <c r="I150" t="n">
         <v>261.6300048828125</v>
@@ -5689,7 +6138,10 @@
         <v>23.45999908447266</v>
       </c>
       <c r="K150" t="n">
-        <v>444.6000061035156</v>
+        <v>435.6764831542969</v>
+      </c>
+      <c r="L150" t="n">
+        <v>5762.47998046875</v>
       </c>
     </row>
     <row r="151">
@@ -5697,25 +6149,25 @@
         <v>45566</v>
       </c>
       <c r="B151" t="n">
-        <v>225.9100036621094</v>
+        <v>224.035888671875</v>
       </c>
       <c r="C151" t="n">
-        <v>406.3500061035156</v>
+        <v>400.0307312011719</v>
       </c>
       <c r="D151" t="n">
-        <v>171.1100006103516</v>
+        <v>169.9168090820312</v>
       </c>
       <c r="E151" t="n">
         <v>186.3999938964844</v>
       </c>
       <c r="F151" t="n">
-        <v>132.7599945068359</v>
+        <v>132.4047088623047</v>
       </c>
       <c r="G151" t="n">
-        <v>567.5800170898438</v>
+        <v>563.88818359375</v>
       </c>
       <c r="H151" t="n">
-        <v>59200</v>
+        <v>57375.4453125</v>
       </c>
       <c r="I151" t="n">
         <v>249.8500061035156</v>
@@ -5724,7 +6176,10 @@
         <v>21.52000045776367</v>
       </c>
       <c r="K151" t="n">
-        <v>404.6000061035156</v>
+        <v>396.4793090820312</v>
+      </c>
+      <c r="L151" t="n">
+        <v>5705.4501953125</v>
       </c>
     </row>
     <row r="152">
@@ -5732,25 +6187,25 @@
         <v>45597</v>
       </c>
       <c r="B152" t="n">
-        <v>237.3300018310547</v>
+        <v>235.6200866699219</v>
       </c>
       <c r="C152" t="n">
-        <v>423.4599914550781</v>
+        <v>417.7090759277344</v>
       </c>
       <c r="D152" t="n">
-        <v>168.9499969482422</v>
+        <v>167.7718811035156</v>
       </c>
       <c r="E152" t="n">
         <v>207.8899993896484</v>
       </c>
       <c r="F152" t="n">
-        <v>138.25</v>
+        <v>137.8800354003906</v>
       </c>
       <c r="G152" t="n">
-        <v>574.3200073242188</v>
+        <v>570.5842895507812</v>
       </c>
       <c r="H152" t="n">
-        <v>54200</v>
+        <v>52529.55078125</v>
       </c>
       <c r="I152" t="n">
         <v>345.1600036621094</v>
@@ -5759,7 +6214,10 @@
         <v>24.04999923706055</v>
       </c>
       <c r="K152" t="n">
-        <v>398</v>
+        <v>390.0117797851562</v>
+      </c>
+      <c r="L152" t="n">
+        <v>6032.3798828125</v>
       </c>
     </row>
     <row r="153">
@@ -5767,25 +6225,25 @@
         <v>45627</v>
       </c>
       <c r="B153" t="n">
-        <v>250.4199981689453</v>
+        <v>248.6157989501953</v>
       </c>
       <c r="C153" t="n">
-        <v>421.5</v>
+        <v>415.7756652832031</v>
       </c>
       <c r="D153" t="n">
-        <v>189.3000030517578</v>
+        <v>188.1954193115234</v>
       </c>
       <c r="E153" t="n">
         <v>219.3899993896484</v>
       </c>
       <c r="F153" t="n">
-        <v>134.2899932861328</v>
+        <v>133.9398651123047</v>
       </c>
       <c r="G153" t="n">
-        <v>585.510009765625</v>
+        <v>582.1707763671875</v>
       </c>
       <c r="H153" t="n">
-        <v>53200</v>
+        <v>51911.93359375</v>
       </c>
       <c r="I153" t="n">
         <v>403.8399963378906</v>
@@ -5794,7 +6252,10 @@
         <v>20.04999923706055</v>
       </c>
       <c r="K153" t="n">
-        <v>419.7999877929688</v>
+        <v>411.3742065429688</v>
+      </c>
+      <c r="L153" t="n">
+        <v>5881.6298828125</v>
       </c>
     </row>
     <row r="154">
@@ -5802,25 +6263,25 @@
         <v>45658</v>
       </c>
       <c r="B154" t="n">
-        <v>236</v>
+        <v>234.2996673583984</v>
       </c>
       <c r="C154" t="n">
-        <v>415.0599975585938</v>
+        <v>409.4231262207031</v>
       </c>
       <c r="D154" t="n">
-        <v>204.0200042724609</v>
+        <v>202.8295440673828</v>
       </c>
       <c r="E154" t="n">
         <v>237.6799926757812</v>
       </c>
       <c r="F154" t="n">
-        <v>120.0699996948242</v>
+        <v>119.7569351196289</v>
       </c>
       <c r="G154" t="n">
-        <v>689.1799926757812</v>
+        <v>685.2495727539062</v>
       </c>
       <c r="H154" t="n">
-        <v>52400</v>
+        <v>51131.30078125</v>
       </c>
       <c r="I154" t="n">
         <v>404.6000061035156</v>
@@ -5829,7 +6290,10 @@
         <v>19.43000030517578</v>
       </c>
       <c r="K154" t="n">
-        <v>402</v>
+        <v>393.9315185546875</v>
+      </c>
+      <c r="L154" t="n">
+        <v>6040.52978515625</v>
       </c>
     </row>
     <row r="155">
@@ -5837,25 +6301,25 @@
         <v>45689</v>
       </c>
       <c r="B155" t="n">
-        <v>241.8399963378906</v>
+        <v>240.3616027832031</v>
       </c>
       <c r="C155" t="n">
-        <v>396.989990234375</v>
+        <v>392.3837585449219</v>
       </c>
       <c r="D155" t="n">
-        <v>170.2799987792969</v>
+        <v>169.2863922119141</v>
       </c>
       <c r="E155" t="n">
         <v>212.2799987792969</v>
       </c>
       <c r="F155" t="n">
-        <v>124.9199981689453</v>
+        <v>124.5942993164062</v>
       </c>
       <c r="G155" t="n">
-        <v>668.2000122070312</v>
+        <v>664.38916015625</v>
       </c>
       <c r="H155" t="n">
-        <v>54500</v>
+        <v>53180.45703125</v>
       </c>
       <c r="I155" t="n">
         <v>292.9800109863281</v>
@@ -5864,7 +6328,10 @@
         <v>23.72999954223633</v>
       </c>
       <c r="K155" t="n">
-        <v>478.6000061035156</v>
+        <v>468.9940795898438</v>
+      </c>
+      <c r="L155" t="n">
+        <v>5954.5</v>
       </c>
     </row>
     <row r="156">
@@ -5872,25 +6339,25 @@
         <v>45717</v>
       </c>
       <c r="B156" t="n">
-        <v>222.1300048828125</v>
+        <v>220.7720947265625</v>
       </c>
       <c r="C156" t="n">
-        <v>375.3900146484375</v>
+        <v>371.0343933105469</v>
       </c>
       <c r="D156" t="n">
-        <v>154.6399993896484</v>
+        <v>153.9147186279297</v>
       </c>
       <c r="E156" t="n">
         <v>190.2599945068359</v>
       </c>
       <c r="F156" t="n">
-        <v>108.379997253418</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="G156" t="n">
-        <v>576.3599853515625</v>
+        <v>573.5828247070312</v>
       </c>
       <c r="H156" t="n">
-        <v>57800</v>
+        <v>56735.65234375</v>
       </c>
       <c r="I156" t="n">
         <v>259.1600036621094</v>
@@ -5899,7 +6366,10 @@
         <v>22.70999908447266</v>
       </c>
       <c r="K156" t="n">
-        <v>497</v>
+        <v>487.0247802734375</v>
+      </c>
+      <c r="L156" t="n">
+        <v>5611.85009765625</v>
       </c>
     </row>
     <row r="157">
@@ -5907,25 +6377,25 @@
         <v>45748</v>
       </c>
       <c r="B157" t="n">
-        <v>212.5</v>
+        <v>211.2009582519531</v>
       </c>
       <c r="C157" t="n">
-        <v>395.260009765625</v>
+        <v>390.6738586425781</v>
       </c>
       <c r="D157" t="n">
-        <v>158.8000030517578</v>
+        <v>158.0552215576172</v>
       </c>
       <c r="E157" t="n">
         <v>184.4199981689453</v>
       </c>
       <c r="F157" t="n">
-        <v>108.9199981689453</v>
+        <v>108.64599609375</v>
       </c>
       <c r="G157" t="n">
-        <v>549</v>
+        <v>546.3546752929688</v>
       </c>
       <c r="H157" t="n">
-        <v>55500</v>
+        <v>54478.0078125</v>
       </c>
       <c r="I157" t="n">
         <v>282.1600036621094</v>
@@ -5934,7 +6404,10 @@
         <v>20.10000038146973</v>
       </c>
       <c r="K157" t="n">
-        <v>477.2000122070312</v>
+        <v>467.6221618652344</v>
+      </c>
+      <c r="L157" t="n">
+        <v>5569.06005859375</v>
       </c>
     </row>
     <row r="158">
@@ -5942,25 +6415,25 @@
         <v>45778</v>
       </c>
       <c r="B158" t="n">
-        <v>200.8500061035156</v>
+        <v>199.8839416503906</v>
       </c>
       <c r="C158" t="n">
-        <v>460.3599853515625</v>
+        <v>455.8538208007812</v>
       </c>
       <c r="D158" t="n">
-        <v>171.7400054931641</v>
+        <v>170.9345397949219</v>
       </c>
       <c r="E158" t="n">
         <v>205.0099945068359</v>
       </c>
       <c r="F158" t="n">
-        <v>135.1300048828125</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="G158" t="n">
-        <v>647.489990234375</v>
+        <v>644.3699951171875</v>
       </c>
       <c r="H158" t="n">
-        <v>56200</v>
+        <v>55165.11328125</v>
       </c>
       <c r="I158" t="n">
         <v>346.4599914550781</v>
@@ -5969,7 +6442,10 @@
         <v>19.54999923706055</v>
       </c>
       <c r="K158" t="n">
-        <v>498.2000122070312</v>
+        <v>492.4623718261719</v>
+      </c>
+      <c r="L158" t="n">
+        <v>5911.68994140625</v>
       </c>
     </row>
     <row r="159">
@@ -5977,25 +6453,25 @@
         <v>45809</v>
       </c>
       <c r="B159" t="n">
-        <v>205.1699981689453</v>
+        <v>204.1831665039062</v>
       </c>
       <c r="C159" t="n">
-        <v>497.4100036621094</v>
+        <v>492.5411987304688</v>
       </c>
       <c r="D159" t="n">
-        <v>176.2299957275391</v>
+        <v>175.6157989501953</v>
       </c>
       <c r="E159" t="n">
         <v>219.3899993896484</v>
       </c>
       <c r="F159" t="n">
-        <v>157.9900054931641</v>
+        <v>157.6035003662109</v>
       </c>
       <c r="G159" t="n">
-        <v>738.0900268554688</v>
+        <v>735.0987548828125</v>
       </c>
       <c r="H159" t="n">
-        <v>59800</v>
+        <v>59058.8671875</v>
       </c>
       <c r="I159" t="n">
         <v>317.6600036621094</v>
@@ -6004,7 +6480,10 @@
         <v>22.39999961853027</v>
       </c>
       <c r="K159" t="n">
-        <v>503</v>
+        <v>497.2070617675781</v>
+      </c>
+      <c r="L159" t="n">
+        <v>6204.9501953125</v>
       </c>
     </row>
     <row r="160">
@@ -6012,25 +6491,25 @@
         <v>45839</v>
       </c>
       <c r="B160" t="n">
-        <v>207.5700073242188</v>
+        <v>206.5716247558594</v>
       </c>
       <c r="C160" t="n">
-        <v>533.5</v>
+        <v>528.27783203125</v>
       </c>
       <c r="D160" t="n">
-        <v>191.8999938964844</v>
+        <v>191.2311706542969</v>
       </c>
       <c r="E160" t="n">
         <v>234.1100006103516</v>
       </c>
       <c r="F160" t="n">
-        <v>177.8699951171875</v>
+        <v>177.4348754882812</v>
       </c>
       <c r="G160" t="n">
-        <v>773.4400024414062</v>
+        <v>770.305419921875</v>
       </c>
       <c r="H160" t="n">
-        <v>71400</v>
+        <v>70515.109375</v>
       </c>
       <c r="I160" t="n">
         <v>308.2699890136719</v>
@@ -6039,7 +6518,10 @@
         <v>19.79999923706055</v>
       </c>
       <c r="K160" t="n">
-        <v>550</v>
+        <v>543.665771484375</v>
+      </c>
+      <c r="L160" t="n">
+        <v>6339.39013671875</v>
       </c>
     </row>
     <row r="161">
@@ -6047,25 +6529,25 @@
         <v>45870</v>
       </c>
       <c r="B161" t="n">
-        <v>232.1399993896484</v>
+        <v>231.2856292724609</v>
       </c>
       <c r="C161" t="n">
-        <v>506.6900024414062</v>
+        <v>502.5551452636719</v>
       </c>
       <c r="D161" t="n">
-        <v>212.9100036621094</v>
+        <v>212.16796875</v>
       </c>
       <c r="E161" t="n">
         <v>229</v>
       </c>
       <c r="F161" t="n">
-        <v>174.1799926757812</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="G161" t="n">
-        <v>738.7000122070312</v>
+        <v>735.7061157226562</v>
       </c>
       <c r="H161" t="n">
-        <v>69700</v>
+        <v>68836.171875</v>
       </c>
       <c r="I161" t="n">
         <v>333.8699951171875</v>
@@ -6074,7 +6556,10 @@
         <v>24.35000038146973</v>
       </c>
       <c r="K161" t="n">
-        <v>596.5</v>
+        <v>589.6302490234375</v>
+      </c>
+      <c r="L161" t="n">
+        <v>6460.259765625</v>
       </c>
     </row>
     <row r="162">
@@ -6082,25 +6567,25 @@
         <v>45901</v>
       </c>
       <c r="B162" t="n">
-        <v>254.6300048828125</v>
+        <v>253.6928558349609</v>
       </c>
       <c r="C162" t="n">
-        <v>517.9500122070312</v>
+        <v>513.7232666015625</v>
       </c>
       <c r="D162" t="n">
-        <v>243.1000061035156</v>
+        <v>242.4694366455078</v>
       </c>
       <c r="E162" t="n">
         <v>219.5700073242188</v>
       </c>
       <c r="F162" t="n">
-        <v>186.5800018310547</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="G162" t="n">
-        <v>734.3800048828125</v>
+        <v>731.8973388671875</v>
       </c>
       <c r="H162" t="n">
-        <v>83900</v>
+        <v>83229.875</v>
       </c>
       <c r="I162" t="n">
         <v>444.7200012207031</v>
@@ -6109,7 +6594,10 @@
         <v>33.54999923706055</v>
       </c>
       <c r="K162" t="n">
-        <v>663</v>
+        <v>655.3643798828125</v>
+      </c>
+      <c r="L162" t="n">
+        <v>6688.4599609375</v>
       </c>
     </row>
     <row r="163">
@@ -6117,25 +6605,25 @@
         <v>45931</v>
       </c>
       <c r="B163" t="n">
-        <v>270.3699951171875</v>
+        <v>269.3749389648438</v>
       </c>
       <c r="C163" t="n">
-        <v>517.8099975585938</v>
+        <v>513.5843505859375</v>
       </c>
       <c r="D163" t="n">
-        <v>281.1900024414062</v>
+        <v>280.4606323242188</v>
       </c>
       <c r="E163" t="n">
         <v>244.2200012207031</v>
       </c>
       <c r="F163" t="n">
-        <v>202.4900054931641</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="G163" t="n">
-        <v>648.3499755859375</v>
+        <v>646.1581420898438</v>
       </c>
       <c r="H163" t="n">
-        <v>107500</v>
+        <v>106641.375</v>
       </c>
       <c r="I163" t="n">
         <v>456.5599975585938</v>
@@ -6144,7 +6632,10 @@
         <v>39.9900016784668</v>
       </c>
       <c r="K163" t="n">
-        <v>629</v>
+        <v>621.7559814453125</v>
+      </c>
+      <c r="L163" t="n">
+        <v>6840.2001953125</v>
       </c>
     </row>
     <row r="164">
@@ -6152,25 +6643,25 @@
         <v>45962</v>
       </c>
       <c r="B164" t="n">
-        <v>278.8500061035156</v>
+        <v>278.093017578125</v>
       </c>
       <c r="C164" t="n">
-        <v>492.010009765625</v>
+        <v>488.9082946777344</v>
       </c>
       <c r="D164" t="n">
-        <v>320.1799926757812</v>
+        <v>319.3494873046875</v>
       </c>
       <c r="E164" t="n">
         <v>233.2200012207031</v>
       </c>
       <c r="F164" t="n">
-        <v>177</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="G164" t="n">
-        <v>647.9500122070312</v>
+        <v>645.759521484375</v>
       </c>
       <c r="H164" t="n">
-        <v>100500</v>
+        <v>99697.2890625</v>
       </c>
       <c r="I164" t="n">
         <v>430.1700134277344</v>
@@ -6179,7 +6670,10 @@
         <v>40.56000137329102</v>
       </c>
       <c r="K164" t="n">
-        <v>611.5</v>
+        <v>604.45751953125</v>
+      </c>
+      <c r="L164" t="n">
+        <v>6849.08984375</v>
       </c>
     </row>
     <row r="165">
@@ -6187,25 +6681,25 @@
         <v>45992</v>
       </c>
       <c r="B165" t="n">
-        <v>271.8599853515625</v>
+        <v>271.1220092773438</v>
       </c>
       <c r="C165" t="n">
-        <v>483.6199951171875</v>
+        <v>480.5711669921875</v>
       </c>
       <c r="D165" t="n">
-        <v>313</v>
+        <v>312.3923034667969</v>
       </c>
       <c r="E165" t="n">
         <v>230.8200073242188</v>
       </c>
       <c r="F165" t="n">
-        <v>186.5</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="G165" t="n">
-        <v>660.0900268554688</v>
+        <v>658.3950805664062</v>
       </c>
       <c r="H165" t="n">
-        <v>119900</v>
+        <v>119520.53125</v>
       </c>
       <c r="I165" t="n">
         <v>449.7200012207031</v>
@@ -6214,7 +6708,10 @@
         <v>36.90000152587891</v>
       </c>
       <c r="K165" t="n">
-        <v>599</v>
+        <v>592.1014404296875</v>
+      </c>
+      <c r="L165" t="n">
+        <v>6845.5</v>
       </c>
     </row>
     <row r="166">
@@ -6222,25 +6719,25 @@
         <v>46023</v>
       </c>
       <c r="B166" t="n">
-        <v>259.4800109863281</v>
+        <v>258.775634765625</v>
       </c>
       <c r="C166" t="n">
-        <v>430.2900085449219</v>
+        <v>427.577392578125</v>
       </c>
       <c r="D166" t="n">
-        <v>338</v>
+        <v>337.3437805175781</v>
       </c>
       <c r="E166" t="n">
         <v>239.3000030517578</v>
       </c>
       <c r="F166" t="n">
-        <v>191.1300048828125</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="G166" t="n">
-        <v>716.5</v>
+        <v>714.66015625</v>
       </c>
       <c r="H166" t="n">
-        <v>160500</v>
+        <v>159992.03125</v>
       </c>
       <c r="I166" t="n">
         <v>430.4100036621094</v>
@@ -6249,7 +6746,10 @@
         <v>46.47000122070312</v>
       </c>
       <c r="K166" t="n">
-        <v>606</v>
+        <v>599.0208740234375</v>
+      </c>
+      <c r="L166" t="n">
+        <v>6939.02978515625</v>
       </c>
     </row>
     <row r="167">
@@ -6257,25 +6757,25 @@
         <v>46054</v>
       </c>
       <c r="B167" t="n">
-        <v>264.1799926757812</v>
+        <v>263.7094116210938</v>
       </c>
       <c r="C167" t="n">
-        <v>392.739990234375</v>
+        <v>391.1548461914062</v>
       </c>
       <c r="D167" t="n">
-        <v>311.760009765625</v>
+        <v>311.1547241210938</v>
       </c>
       <c r="E167" t="n">
         <v>210</v>
       </c>
       <c r="F167" t="n">
-        <v>177.1900024414062</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="G167" t="n">
-        <v>648.1799926757812</v>
+        <v>646.515625</v>
       </c>
       <c r="H167" t="n">
-        <v>216500</v>
+        <v>215814.796875</v>
       </c>
       <c r="I167" t="n">
         <v>402.510009765625</v>
@@ -6284,7 +6784,10 @@
         <v>45.61000061035156</v>
       </c>
       <c r="K167" t="n">
-        <v>518</v>
+        <v>512.0343017578125</v>
+      </c>
+      <c r="L167" t="n">
+        <v>6878.8798828125</v>
       </c>
     </row>
     <row r="168">
@@ -6292,25 +6795,25 @@
         <v>46082</v>
       </c>
       <c r="B168" t="n">
-        <v>253.7899932861328</v>
+        <v>253.3379058837891</v>
       </c>
       <c r="C168" t="n">
-        <v>370.1700134277344</v>
+        <v>368.6759643554688</v>
       </c>
       <c r="D168" t="n">
-        <v>287.5599975585938</v>
+        <v>287.2037353515625</v>
       </c>
       <c r="E168" t="n">
         <v>208.2700042724609</v>
       </c>
       <c r="F168" t="n">
-        <v>174.3999938964844</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="G168" t="n">
-        <v>572.1300048828125</v>
+        <v>571.1494750976562</v>
       </c>
       <c r="H168" t="n">
-        <v>167200</v>
+        <v>167015.8125</v>
       </c>
       <c r="I168" t="n">
         <v>371.75</v>
@@ -6319,7 +6822,10 @@
         <v>44.13000106811523</v>
       </c>
       <c r="K168" t="n">
-        <v>484</v>
+        <v>478.4259033203125</v>
+      </c>
+      <c r="L168" t="n">
+        <v>6528.52001953125</v>
       </c>
     </row>
     <row r="169">
@@ -6327,25 +6833,25 @@
         <v>46113</v>
       </c>
       <c r="B169" t="n">
-        <v>271.3500061035156</v>
+        <v>270.8666381835938</v>
       </c>
       <c r="C169" t="n">
-        <v>407.7799987792969</v>
+        <v>406.1341552734375</v>
       </c>
       <c r="D169" t="n">
-        <v>384.7999877929688</v>
+        <v>384.3232421875</v>
       </c>
       <c r="E169" t="n">
         <v>265.0599975585938</v>
       </c>
       <c r="F169" t="n">
-        <v>199.5700073242188</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="G169" t="n">
-        <v>611.9099731445312</v>
+        <v>610.8612670898438</v>
       </c>
       <c r="H169" t="n">
-        <v>220500</v>
+        <v>220257.09375</v>
       </c>
       <c r="I169" t="n">
         <v>381.6300048828125</v>
@@ -6354,7 +6860,10 @@
         <v>94.48000335693359</v>
       </c>
       <c r="K169" t="n">
-        <v>467.7999877929688</v>
+        <v>462.4124450683594</v>
+      </c>
+      <c r="L169" t="n">
+        <v>7209.009765625</v>
       </c>
     </row>
     <row r="170">
@@ -6362,25 +6871,25 @@
         <v>46143</v>
       </c>
       <c r="B170" t="n">
-        <v>312.0599975585938</v>
+        <v>311.7911071777344</v>
       </c>
       <c r="C170" t="n">
-        <v>450.239990234375</v>
+        <v>449.3940124511719</v>
       </c>
       <c r="D170" t="n">
-        <v>380.3399963378906</v>
+        <v>379.8687744140625</v>
       </c>
       <c r="E170" t="n">
         <v>270.6400146484375</v>
       </c>
       <c r="F170" t="n">
-        <v>211.1399993896484</v>
+        <v>210.6584930419922</v>
       </c>
       <c r="G170" t="n">
-        <v>632.510009765625</v>
+        <v>631.426025390625</v>
       </c>
       <c r="H170" t="n">
-        <v>317000</v>
+        <v>316650.78125</v>
       </c>
       <c r="I170" t="n">
         <v>435.7900085449219</v>
@@ -6390,6 +6899,9 @@
       </c>
       <c r="K170" t="n">
         <v>427.2000122070312</v>
+      </c>
+      <c r="L170" t="n">
+        <v>7580.06005859375</v>
       </c>
     </row>
     <row r="171">
@@ -6397,22 +6909,22 @@
         <v>46174</v>
       </c>
       <c r="B171" t="n">
-        <v>289.3599853515625</v>
+        <v>289.1106567382812</v>
       </c>
       <c r="C171" t="n">
-        <v>373.0199890136719</v>
+        <v>372.319091796875</v>
       </c>
       <c r="D171" t="n">
-        <v>357.3699951171875</v>
+        <v>357.1404418945312</v>
       </c>
       <c r="E171" t="n">
         <v>238.3399963378906</v>
       </c>
       <c r="F171" t="n">
-        <v>200.0899963378906</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="G171" t="n">
-        <v>563.2899780273438</v>
+        <v>562.8457641601562</v>
       </c>
       <c r="H171" t="n">
         <v>334000</v>
@@ -6425,6 +6937,9 @@
       </c>
       <c r="K171" t="n">
         <v>429.7999877929688</v>
+      </c>
+      <c r="L171" t="n">
+        <v>7499.35986328125</v>
       </c>
     </row>
     <row r="172">
@@ -6432,22 +6947,22 @@
         <v>46204</v>
       </c>
       <c r="B172" t="n">
-        <v>308.9100036621094</v>
+        <v>308.6438293457031</v>
       </c>
       <c r="C172" t="n">
-        <v>464.7200012207031</v>
+        <v>463.8468017578125</v>
       </c>
       <c r="D172" t="n">
-        <v>356.1300048828125</v>
+        <v>355.9012451171875</v>
       </c>
       <c r="E172" t="n">
         <v>271.5799865722656</v>
       </c>
       <c r="F172" t="n">
-        <v>200.75</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="G172" t="n">
-        <v>556.7100219726562</v>
+        <v>556.27099609375</v>
       </c>
       <c r="H172" t="n">
         <v>262500</v>
@@ -6460,6 +6975,9 @@
       </c>
       <c r="K172" t="n">
         <v>475.2000122070312</v>
+      </c>
+      <c r="L172" t="n">
+        <v>7489.72021484375</v>
       </c>
     </row>
     <row r="173">
@@ -6473,16 +6991,16 @@
         <v>507.2900085449219</v>
       </c>
       <c r="D173" t="n">
-        <v>339.3500061035156</v>
+        <v>339.1320190429688</v>
       </c>
       <c r="E173" t="n">
         <v>259.7699890136719</v>
       </c>
       <c r="F173" t="n">
-        <v>220.7799987792969</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="G173" t="n">
-        <v>572.3400268554688</v>
+        <v>571.888671875</v>
       </c>
       <c r="H173" t="n">
         <v>260000</v>
@@ -6495,6 +7013,9 @@
       </c>
       <c r="K173" t="n">
         <v>453</v>
+      </c>
+      <c r="L173" t="n">
+        <v>7686.14013671875</v>
       </c>
     </row>
     <row r="174">
@@ -6531,40 +7052,46 @@
       <c r="K174" t="n">
         <v>431</v>
       </c>
+      <c r="L174" t="n">
+        <v>7651.5400390625</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
         <v>46296</v>
       </c>
       <c r="B175" t="n">
-        <v>336.6700134277344</v>
+        <v>337.6900024414062</v>
       </c>
       <c r="C175" t="n">
-        <v>529.760009765625</v>
+        <v>530.22998046875</v>
       </c>
       <c r="D175" t="n">
-        <v>350.5</v>
+        <v>350.2749938964844</v>
       </c>
       <c r="E175" t="n">
-        <v>259.9200134277344</v>
+        <v>258.3299865722656</v>
       </c>
       <c r="F175" t="n">
-        <v>237.4700012207031</v>
+        <v>236.0399932861328</v>
       </c>
       <c r="G175" t="n">
-        <v>721.3099975585938</v>
+        <v>721.5449829101562</v>
       </c>
       <c r="H175" t="n">
         <v>262000</v>
       </c>
       <c r="I175" t="n">
-        <v>377.8099975585938</v>
+        <v>372.3150024414062</v>
       </c>
       <c r="J175" t="n">
-        <v>113.120002746582</v>
+        <v>109.5</v>
       </c>
       <c r="K175" t="n">
-        <v>411.7999877929688</v>
+        <v>411.3999938964844</v>
+      </c>
+      <c r="L175" t="n">
+        <v>7772.490234375</v>
       </c>
     </row>
   </sheetData>

--- a/monthly.xlsx
+++ b/monthly.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Tencent</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -487,34 +487,34 @@
         <v>41030</v>
       </c>
       <c r="B2" t="n">
-        <v>17.27968597412109</v>
+        <v>17.27969551086426</v>
       </c>
       <c r="C2" t="n">
-        <v>23.01616859436035</v>
+        <v>23.01618003845215</v>
       </c>
       <c r="D2" t="n">
-        <v>14.39901924133301</v>
+        <v>14.39901828765869</v>
       </c>
       <c r="E2" t="n">
         <v>10.64550018310547</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2842410802841187</v>
+        <v>0.2842411696910858</v>
       </c>
       <c r="G2" t="n">
         <v>29.31919097900391</v>
       </c>
       <c r="H2" t="n">
-        <v>18010.4453125</v>
+        <v>6.079999923706055</v>
       </c>
       <c r="I2" t="n">
         <v>1.966667056083679</v>
       </c>
       <c r="J2" t="n">
-        <v>18.13143730163574</v>
+        <v>18.13142967224121</v>
       </c>
       <c r="K2" t="n">
-        <v>36.81422805786133</v>
+        <v>2.36237907409668</v>
       </c>
       <c r="L2" t="n">
         <v>1310.329956054688</v>
@@ -525,34 +525,34 @@
         <v>41061</v>
       </c>
       <c r="B3" t="n">
-        <v>17.46721839904785</v>
+        <v>17.46722412109375</v>
       </c>
       <c r="C3" t="n">
-        <v>24.12006759643555</v>
+        <v>24.12006950378418</v>
       </c>
       <c r="D3" t="n">
-        <v>14.37943363189697</v>
+        <v>14.37943458557129</v>
       </c>
       <c r="E3" t="n">
         <v>11.41749954223633</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3160267770290375</v>
+        <v>0.3160269558429718</v>
       </c>
       <c r="G3" t="n">
-        <v>30.80495834350586</v>
+        <v>30.80496025085449</v>
       </c>
       <c r="H3" t="n">
-        <v>17869.375</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="I3" t="n">
         <v>2.085999965667725</v>
       </c>
       <c r="J3" t="n">
-        <v>18.69979095458984</v>
+        <v>18.69979476928711</v>
       </c>
       <c r="K3" t="n">
-        <v>38.98789215087891</v>
+        <v>2.57355809211731</v>
       </c>
       <c r="L3" t="n">
         <v>1362.160034179688</v>
@@ -563,34 +563,34 @@
         <v>41091</v>
       </c>
       <c r="B4" t="n">
-        <v>18.26760482788086</v>
+        <v>18.26760864257812</v>
       </c>
       <c r="C4" t="n">
-        <v>23.23696136474609</v>
+        <v>23.23695945739746</v>
       </c>
       <c r="D4" t="n">
-        <v>15.69078254699707</v>
+        <v>15.69077968597412</v>
       </c>
       <c r="E4" t="n">
         <v>11.66499996185303</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3096238970756531</v>
+        <v>0.3096239864826202</v>
       </c>
       <c r="G4" t="n">
-        <v>21.50404167175293</v>
+        <v>21.50403785705566</v>
       </c>
       <c r="H4" t="n">
-        <v>19476.28125</v>
+        <v>4.059999942779541</v>
       </c>
       <c r="I4" t="n">
         <v>1.827999949455261</v>
       </c>
       <c r="J4" t="n">
-        <v>18.03320121765137</v>
+        <v>18.0331974029541</v>
       </c>
       <c r="K4" t="n">
-        <v>39.98846435546875</v>
+        <v>2.64524507522583</v>
       </c>
       <c r="L4" t="n">
         <v>1379.319946289062</v>
@@ -601,34 +601,34 @@
         <v>41122</v>
       </c>
       <c r="B5" t="n">
-        <v>19.98251342773438</v>
+        <v>19.98250961303711</v>
       </c>
       <c r="C5" t="n">
         <v>24.4624137878418</v>
       </c>
       <c r="D5" t="n">
-        <v>16.9827880859375</v>
+        <v>16.98279190063477</v>
       </c>
       <c r="E5" t="n">
         <v>12.41349983215332</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3208290338516235</v>
+        <v>0.3208289742469788</v>
       </c>
       <c r="G5" t="n">
         <v>17.8886661529541</v>
       </c>
       <c r="H5" t="n">
-        <v>18345.501953125</v>
+        <v>3.720000028610229</v>
       </c>
       <c r="I5" t="n">
         <v>1.901332974433899</v>
       </c>
       <c r="J5" t="n">
-        <v>17.57535934448242</v>
+        <v>17.57535743713379</v>
       </c>
       <c r="K5" t="n">
-        <v>40.88553237915039</v>
+        <v>2.621588468551636</v>
       </c>
       <c r="L5" t="n">
         <v>1406.579956054688</v>
@@ -639,10 +639,10 @@
         <v>41153</v>
       </c>
       <c r="B6" t="n">
-        <v>20.03837966918945</v>
+        <v>20.03838157653809</v>
       </c>
       <c r="C6" t="n">
-        <v>23.62107276916504</v>
+        <v>23.62106895446777</v>
       </c>
       <c r="D6" t="n">
         <v>18.70340538024902</v>
@@ -651,22 +651,22 @@
         <v>12.71599960327148</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3050504326820374</v>
+        <v>0.3050503730773926</v>
       </c>
       <c r="G6" t="n">
-        <v>21.45451164245605</v>
+        <v>21.45451736450195</v>
       </c>
       <c r="H6" t="n">
-        <v>20026.787109375</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="I6" t="n">
         <v>1.952000021934509</v>
       </c>
       <c r="J6" t="n">
-        <v>16.03937339782715</v>
+        <v>16.03936767578125</v>
       </c>
       <c r="K6" t="n">
-        <v>45.57787322998047</v>
+        <v>2.511109113693237</v>
       </c>
       <c r="L6" t="n">
         <v>1440.670043945312</v>
@@ -677,34 +677,34 @@
         <v>41183</v>
       </c>
       <c r="B7" t="n">
-        <v>17.88224601745605</v>
+        <v>17.88224411010742</v>
       </c>
       <c r="C7" t="n">
-        <v>22.65273666381836</v>
+        <v>22.65273094177246</v>
       </c>
       <c r="D7" t="n">
-        <v>16.86404991149902</v>
+        <v>16.86405372619629</v>
       </c>
       <c r="E7" t="n">
         <v>11.64449977874756</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2739509046077728</v>
+        <v>0.2739508748054504</v>
       </c>
       <c r="G7" t="n">
-        <v>20.90973281860352</v>
+        <v>20.90973091125488</v>
       </c>
       <c r="H7" t="n">
-        <v>19491.1640625</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I7" t="n">
         <v>1.875332951545715</v>
       </c>
       <c r="J7" t="n">
-        <v>15.31031131744385</v>
+        <v>15.31031227111816</v>
       </c>
       <c r="K7" t="n">
-        <v>47.26849746704102</v>
+        <v>2.378604173660278</v>
       </c>
       <c r="L7" t="n">
         <v>1412.160034179688</v>
@@ -715,34 +715,34 @@
         <v>41214</v>
       </c>
       <c r="B8" t="n">
-        <v>17.66096496582031</v>
+        <v>17.66096305847168</v>
       </c>
       <c r="C8" t="n">
-        <v>21.30241775512695</v>
+        <v>21.30241012573242</v>
       </c>
       <c r="D8" t="n">
-        <v>17.31199264526367</v>
+        <v>17.31199073791504</v>
       </c>
       <c r="E8" t="n">
         <v>12.60249996185303</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2754881680011749</v>
+        <v>0.2754880785942078</v>
       </c>
       <c r="G8" t="n">
-        <v>27.73436737060547</v>
+        <v>27.73436546325684</v>
       </c>
       <c r="H8" t="n">
-        <v>20919.51953125</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I8" t="n">
         <v>2.254667043685913</v>
       </c>
       <c r="J8" t="n">
-        <v>13.99492645263672</v>
+        <v>13.99492454528809</v>
       </c>
       <c r="K8" t="n">
-        <v>43.68023681640625</v>
+        <v>2.527671813964844</v>
       </c>
       <c r="L8" t="n">
         <v>1416.180053710938</v>
@@ -753,34 +753,34 @@
         <v>41244</v>
       </c>
       <c r="B9" t="n">
-        <v>16.05835914611816</v>
+        <v>16.0583610534668</v>
       </c>
       <c r="C9" t="n">
-        <v>21.37443351745605</v>
+        <v>21.37444114685059</v>
       </c>
       <c r="D9" t="n">
-        <v>17.53533935546875</v>
+        <v>17.53534507751465</v>
       </c>
       <c r="E9" t="n">
         <v>12.54349994659424</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2821625173091888</v>
+        <v>0.2821624577045441</v>
       </c>
       <c r="G9" t="n">
-        <v>26.36746406555176</v>
+        <v>26.36746025085449</v>
       </c>
       <c r="H9" t="n">
-        <v>22761.583984375</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="I9" t="n">
         <v>2.257999897003174</v>
       </c>
       <c r="J9" t="n">
-        <v>14.74580478668213</v>
+        <v>14.74580383300781</v>
       </c>
       <c r="K9" t="n">
-        <v>42.95568084716797</v>
+        <v>2.290489673614502</v>
       </c>
       <c r="L9" t="n">
         <v>1426.18994140625</v>
@@ -791,10 +791,10 @@
         <v>41275</v>
       </c>
       <c r="B10" t="n">
-        <v>13.7445240020752</v>
+        <v>13.74452495574951</v>
       </c>
       <c r="C10" t="n">
-        <v>21.96661949157715</v>
+        <v>21.96661186218262</v>
       </c>
       <c r="D10" t="n">
         <v>18.73290824890137</v>
@@ -803,22 +803,22 @@
         <v>13.27499961853027</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2821625173091888</v>
+        <v>0.2821624577045441</v>
       </c>
       <c r="G10" t="n">
         <v>30.68609619140625</v>
       </c>
       <c r="H10" t="n">
-        <v>21654.91015625</v>
+        <v>2.599999904632568</v>
       </c>
       <c r="I10" t="n">
         <v>2.500667095184326</v>
       </c>
       <c r="J10" t="n">
-        <v>15.04615592956543</v>
+        <v>15.04615306854248</v>
       </c>
       <c r="K10" t="n">
-        <v>46.81996536254883</v>
+        <v>2.588650941848755</v>
       </c>
       <c r="L10" t="n">
         <v>1498.109985351562</v>
@@ -829,34 +829,34 @@
         <v>41306</v>
       </c>
       <c r="B11" t="n">
-        <v>13.39697551727295</v>
+        <v>13.39697742462158</v>
       </c>
       <c r="C11" t="n">
-        <v>22.43087768554688</v>
+        <v>22.43089294433594</v>
       </c>
       <c r="D11" t="n">
-        <v>19.86105537414551</v>
+        <v>19.86106300354004</v>
       </c>
       <c r="E11" t="n">
         <v>13.21350002288818</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2931559681892395</v>
+        <v>0.2931560277938843</v>
       </c>
       <c r="G11" t="n">
         <v>26.99148368835449</v>
       </c>
       <c r="H11" t="n">
-        <v>23090.59375</v>
+        <v>2.490000009536743</v>
       </c>
       <c r="I11" t="n">
         <v>2.322000026702881</v>
       </c>
       <c r="J11" t="n">
-        <v>15.09221458435059</v>
+        <v>15.092209815979</v>
       </c>
       <c r="K11" t="n">
-        <v>46.26792144775391</v>
+        <v>2.476478099822998</v>
       </c>
       <c r="L11" t="n">
         <v>1514.680053710938</v>
@@ -870,10 +870,10 @@
         <v>13.43521976470947</v>
       </c>
       <c r="C12" t="n">
-        <v>23.08444786071777</v>
+        <v>23.08444595336914</v>
       </c>
       <c r="D12" t="n">
-        <v>19.68729019165039</v>
+        <v>19.68728446960449</v>
       </c>
       <c r="E12" t="n">
         <v>13.32450008392334</v>
@@ -882,10 +882,10 @@
         <v>0.2970924973487854</v>
       </c>
       <c r="G12" t="n">
-        <v>25.33732795715332</v>
+        <v>25.33732414245605</v>
       </c>
       <c r="H12" t="n">
-        <v>22836.361328125</v>
+        <v>2.549999952316284</v>
       </c>
       <c r="I12" t="n">
         <v>2.526000022888184</v>
@@ -894,7 +894,7 @@
         <v>15.78610801696777</v>
       </c>
       <c r="K12" t="n">
-        <v>42.57615661621094</v>
+        <v>2.613325595855713</v>
       </c>
       <c r="L12" t="n">
         <v>1569.18994140625</v>
@@ -905,13 +905,13 @@
         <v>41365</v>
       </c>
       <c r="B13" t="n">
-        <v>13.43886470794678</v>
+        <v>13.43886184692383</v>
       </c>
       <c r="C13" t="n">
-        <v>26.70727920532227</v>
+        <v>26.70728302001953</v>
       </c>
       <c r="D13" t="n">
-        <v>20.44038391113281</v>
+        <v>20.44038200378418</v>
       </c>
       <c r="E13" t="n">
         <v>12.69050025939941</v>
@@ -920,19 +920,19 @@
         <v>0.318859189748764</v>
       </c>
       <c r="G13" t="n">
-        <v>27.50655555725098</v>
+        <v>27.50654792785645</v>
       </c>
       <c r="H13" t="n">
-        <v>22731.6796875</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="I13" t="n">
         <v>3.599333047866821</v>
       </c>
       <c r="J13" t="n">
-        <v>17.31123733520508</v>
+        <v>17.31123542785645</v>
       </c>
       <c r="K13" t="n">
-        <v>45.92290496826172</v>
+        <v>2.325219631195068</v>
       </c>
       <c r="L13" t="n">
         <v>1597.569946289062</v>
@@ -943,34 +943,34 @@
         <v>41395</v>
       </c>
       <c r="B14" t="n">
-        <v>13.74015426635742</v>
+        <v>13.74015045166016</v>
       </c>
       <c r="C14" t="n">
-        <v>28.35711288452148</v>
+        <v>28.35710334777832</v>
       </c>
       <c r="D14" t="n">
-        <v>21.59679222106934</v>
+        <v>21.5967960357666</v>
       </c>
       <c r="E14" t="n">
         <v>13.46000003814697</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3367705047130585</v>
+        <v>0.3367703557014465</v>
       </c>
       <c r="G14" t="n">
         <v>24.11899757385254</v>
       </c>
       <c r="H14" t="n">
-        <v>23000.865234375</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>6.517333030700684</v>
       </c>
       <c r="J14" t="n">
-        <v>17.715087890625</v>
+        <v>17.71508598327637</v>
       </c>
       <c r="K14" t="n">
-        <v>53.29729461669922</v>
+        <v>2.745010375976562</v>
       </c>
       <c r="L14" t="n">
         <v>1630.739990234375</v>
@@ -984,7 +984,7 @@
         <v>12.11478710174561</v>
       </c>
       <c r="C15" t="n">
-        <v>28.0645866394043</v>
+        <v>28.0645923614502</v>
       </c>
       <c r="D15" t="n">
         <v>21.8236141204834</v>
@@ -993,13 +993,13 @@
         <v>13.88449954986572</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3267627656459808</v>
+        <v>0.3267627358436584</v>
       </c>
       <c r="G15" t="n">
-        <v>24.64397048950195</v>
+        <v>24.64396667480469</v>
       </c>
       <c r="H15" t="n">
-        <v>20077.638671875</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="I15" t="n">
         <v>7.157332897186279</v>
@@ -1008,7 +1008,7 @@
         <v>17.67859840393066</v>
       </c>
       <c r="K15" t="n">
-        <v>52.67393493652344</v>
+        <v>2.735513687133789</v>
       </c>
       <c r="L15" t="n">
         <v>1606.280029296875</v>
@@ -1022,31 +1022,31 @@
         <v>13.82569789886475</v>
       </c>
       <c r="C16" t="n">
-        <v>25.87077331542969</v>
+        <v>25.87077140808105</v>
       </c>
       <c r="D16" t="n">
-        <v>22.00655746459961</v>
+        <v>22.00655364990234</v>
       </c>
       <c r="E16" t="n">
         <v>15.06099987030029</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3360721468925476</v>
+        <v>0.3360722959041595</v>
       </c>
       <c r="G16" t="n">
-        <v>36.45088195800781</v>
+        <v>36.45087814331055</v>
       </c>
       <c r="H16" t="n">
-        <v>19150.052734375</v>
+        <v>3.769999980926514</v>
       </c>
       <c r="I16" t="n">
         <v>8.951999664306641</v>
       </c>
       <c r="J16" t="n">
-        <v>17.02923583984375</v>
+        <v>17.02924156188965</v>
       </c>
       <c r="K16" t="n">
-        <v>60.91614151000977</v>
+        <v>2.684286594390869</v>
       </c>
       <c r="L16" t="n">
         <v>1685.72998046875</v>
@@ -1057,10 +1057,10 @@
         <v>41487</v>
       </c>
       <c r="B17" t="n">
-        <v>14.98383522033691</v>
+        <v>14.98383045196533</v>
       </c>
       <c r="C17" t="n">
-        <v>27.32954406738281</v>
+        <v>27.32955169677734</v>
       </c>
       <c r="D17" t="n">
         <v>20.99392318725586</v>
@@ -1069,22 +1069,22 @@
         <v>14.04899978637695</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3450179994106293</v>
+        <v>0.3450179696083069</v>
       </c>
       <c r="G17" t="n">
-        <v>40.89828491210938</v>
+        <v>40.89829254150391</v>
       </c>
       <c r="H17" t="n">
-        <v>20466.62109375</v>
+        <v>3.269999980926514</v>
       </c>
       <c r="I17" t="n">
         <v>11.26666736602783</v>
       </c>
       <c r="J17" t="n">
-        <v>16.19388198852539</v>
+        <v>16.19388008117676</v>
       </c>
       <c r="K17" t="n">
-        <v>62.95937347412109</v>
+        <v>2.818207025527954</v>
       </c>
       <c r="L17" t="n">
         <v>1632.969970703125</v>
@@ -1095,7 +1095,7 @@
         <v>41518</v>
       </c>
       <c r="B18" t="n">
-        <v>14.66183757781982</v>
+        <v>14.66184329986572</v>
       </c>
       <c r="C18" t="n">
         <v>27.23135375976562</v>
@@ -1107,13 +1107,13 @@
         <v>15.63199996948242</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3639646768569946</v>
+        <v>0.3639648258686066</v>
       </c>
       <c r="G18" t="n">
-        <v>49.75347900390625</v>
+        <v>49.75347137451172</v>
       </c>
       <c r="H18" t="n">
-        <v>20451.662109375</v>
+        <v>3.809999942779541</v>
       </c>
       <c r="I18" t="n">
         <v>12.89133262634277</v>
@@ -1122,7 +1122,7 @@
         <v>16.88643455505371</v>
       </c>
       <c r="K18" t="n">
-        <v>70.43968963623047</v>
+        <v>3.171213865280151</v>
       </c>
       <c r="L18" t="n">
         <v>1681.550048828125</v>
@@ -1133,10 +1133,10 @@
         <v>41548</v>
       </c>
       <c r="B19" t="n">
-        <v>16.07497215270996</v>
+        <v>16.07497406005859</v>
       </c>
       <c r="C19" t="n">
-        <v>28.97423362731934</v>
+        <v>28.97422218322754</v>
       </c>
       <c r="D19" t="n">
         <v>25.54719161987305</v>
@@ -1145,22 +1145,22 @@
         <v>18.20149993896484</v>
       </c>
       <c r="F19" t="n">
-        <v>0.355309933423996</v>
+        <v>0.3553101420402527</v>
       </c>
       <c r="G19" t="n">
-        <v>49.73366165161133</v>
+        <v>49.73366546630859</v>
       </c>
       <c r="H19" t="n">
-        <v>21917.8359375</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="I19" t="n">
         <v>10.6626672744751</v>
       </c>
       <c r="J19" t="n">
-        <v>18.02840232849121</v>
+        <v>18.02840614318848</v>
       </c>
       <c r="K19" t="n">
-        <v>73.27944183349609</v>
+        <v>3.344204664230347</v>
       </c>
       <c r="L19" t="n">
         <v>1756.5400390625</v>
@@ -1171,13 +1171,13 @@
         <v>41579</v>
       </c>
       <c r="B20" t="n">
-        <v>17.20106887817383</v>
+        <v>17.20107460021973</v>
       </c>
       <c r="C20" t="n">
-        <v>31.43649482727051</v>
+        <v>31.43649673461914</v>
       </c>
       <c r="D20" t="n">
-        <v>26.26632308959961</v>
+        <v>26.26632118225098</v>
       </c>
       <c r="E20" t="n">
         <v>19.68099975585938</v>
@@ -1186,19 +1186,19 @@
         <v>0.3668766021728516</v>
       </c>
       <c r="G20" t="n">
-        <v>46.56402206420898</v>
+        <v>46.56401824951172</v>
       </c>
       <c r="H20" t="n">
-        <v>22351.70703125</v>
+        <v>3.640000104904175</v>
       </c>
       <c r="I20" t="n">
         <v>8.485333442687988</v>
       </c>
       <c r="J20" t="n">
-        <v>17.72867202758789</v>
+        <v>17.72867012023926</v>
       </c>
       <c r="K20" t="n">
-        <v>77.64295959472656</v>
+        <v>3.292674541473389</v>
       </c>
       <c r="L20" t="n">
         <v>1805.81005859375</v>
@@ -1209,10 +1209,10 @@
         <v>41609</v>
       </c>
       <c r="B21" t="n">
-        <v>17.35419082641602</v>
+        <v>17.35419654846191</v>
       </c>
       <c r="C21" t="n">
-        <v>30.84288024902344</v>
+        <v>30.84288215637207</v>
       </c>
       <c r="D21" t="n">
         <v>27.78143501281738</v>
@@ -1221,22 +1221,22 @@
         <v>19.93950080871582</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3767540156841278</v>
+        <v>0.3767539858818054</v>
       </c>
       <c r="G21" t="n">
-        <v>54.13154983520508</v>
+        <v>54.13155364990234</v>
       </c>
       <c r="H21" t="n">
-        <v>20729.638671875</v>
+        <v>3.869999885559082</v>
       </c>
       <c r="I21" t="n">
         <v>10.02866744995117</v>
       </c>
       <c r="J21" t="n">
-        <v>19.30521011352539</v>
+        <v>19.30521583557129</v>
       </c>
       <c r="K21" t="n">
-        <v>85.64276123046875</v>
+        <v>3.910868883132935</v>
       </c>
       <c r="L21" t="n">
         <v>1848.359985351562</v>
@@ -1247,34 +1247,34 @@
         <v>41640</v>
       </c>
       <c r="B22" t="n">
-        <v>15.48520088195801</v>
+        <v>15.48520755767822</v>
       </c>
       <c r="C22" t="n">
-        <v>31.1973991394043</v>
+        <v>31.19738578796387</v>
       </c>
       <c r="D22" t="n">
-        <v>29.27522659301758</v>
+        <v>29.27523422241211</v>
       </c>
       <c r="E22" t="n">
         <v>17.93449974060059</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3692283928394318</v>
+        <v>0.3692283034324646</v>
       </c>
       <c r="G22" t="n">
-        <v>61.97640991210938</v>
+        <v>61.97641372680664</v>
       </c>
       <c r="H22" t="n">
-        <v>19339.603515625</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="I22" t="n">
         <v>12.0939998626709</v>
       </c>
       <c r="J22" t="n">
-        <v>18.24922943115234</v>
+        <v>18.24923324584961</v>
       </c>
       <c r="K22" t="n">
-        <v>94.11006164550781</v>
+        <v>4.041032314300537</v>
       </c>
       <c r="L22" t="n">
         <v>1782.589965820312</v>
@@ -1288,31 +1288,31 @@
         <v>16.37577247619629</v>
       </c>
       <c r="C23" t="n">
-        <v>31.82174110412598</v>
+        <v>31.82174301147461</v>
       </c>
       <c r="D23" t="n">
-        <v>30.13491439819336</v>
+        <v>30.13492012023926</v>
       </c>
       <c r="E23" t="n">
         <v>18.10499954223633</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4342077076435089</v>
+        <v>0.4342075288295746</v>
       </c>
       <c r="G23" t="n">
-        <v>67.81053924560547</v>
+        <v>67.81053161621094</v>
       </c>
       <c r="H23" t="n">
-        <v>20382.12890625</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="I23" t="n">
         <v>16.3206672668457</v>
       </c>
       <c r="J23" t="n">
-        <v>18.58841323852539</v>
+        <v>18.58841896057129</v>
       </c>
       <c r="K23" t="n">
-        <v>107.7893600463867</v>
+        <v>4.56317138671875</v>
       </c>
       <c r="L23" t="n">
         <v>1859.449951171875</v>
@@ -1323,34 +1323,34 @@
         <v>41699</v>
       </c>
       <c r="B24" t="n">
-        <v>16.70251846313477</v>
+        <v>16.70252227783203</v>
       </c>
       <c r="C24" t="n">
         <v>34.04784393310547</v>
       </c>
       <c r="D24" t="n">
-        <v>27.62774085998535</v>
+        <v>27.62774276733398</v>
       </c>
       <c r="E24" t="n">
         <v>16.81850051879883</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4231044352054596</v>
+        <v>0.4231044054031372</v>
       </c>
       <c r="G24" t="n">
-        <v>59.66851425170898</v>
+        <v>59.66851806640625</v>
       </c>
       <c r="H24" t="n">
-        <v>20291.482421875</v>
+        <v>4.010000228881836</v>
       </c>
       <c r="I24" t="n">
         <v>13.89666652679443</v>
       </c>
       <c r="J24" t="n">
-        <v>19.3766975402832</v>
+        <v>19.37669563293457</v>
       </c>
       <c r="K24" t="n">
-        <v>93.41743469238281</v>
+        <v>4.783967018127441</v>
       </c>
       <c r="L24" t="n">
         <v>1872.339965820312</v>
@@ -1361,34 +1361,34 @@
         <v>41730</v>
       </c>
       <c r="B25" t="n">
-        <v>18.36268043518066</v>
+        <v>18.36268615722656</v>
       </c>
       <c r="C25" t="n">
-        <v>33.55776214599609</v>
+        <v>33.55777359008789</v>
       </c>
       <c r="D25" t="n">
-        <v>26.49190902709961</v>
+        <v>26.49191284179688</v>
       </c>
       <c r="E25" t="n">
         <v>15.20650005340576</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4363337159156799</v>
+        <v>0.4363337755203247</v>
       </c>
       <c r="G25" t="n">
         <v>59.21287536621094</v>
       </c>
       <c r="H25" t="n">
-        <v>20291.482421875</v>
+        <v>4.090000152587891</v>
       </c>
       <c r="I25" t="n">
         <v>13.85933303833008</v>
       </c>
       <c r="J25" t="n">
-        <v>20.03735160827637</v>
+        <v>20.037353515625</v>
       </c>
       <c r="K25" t="n">
-        <v>83.66878509521484</v>
+        <v>4.716379642486572</v>
       </c>
       <c r="L25" t="n">
         <v>1883.949951171875</v>
@@ -1399,25 +1399,25 @@
         <v>41760</v>
       </c>
       <c r="B26" t="n">
-        <v>19.80799865722656</v>
+        <v>19.8080005645752</v>
       </c>
       <c r="C26" t="n">
-        <v>34.24623107910156</v>
+        <v>34.24621200561523</v>
       </c>
       <c r="D26" t="n">
-        <v>28.31308174133301</v>
+        <v>28.31307983398438</v>
       </c>
       <c r="E26" t="n">
         <v>15.6274995803833</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4509217739105225</v>
+        <v>0.4509217441082001</v>
       </c>
       <c r="G26" t="n">
-        <v>62.69948577880859</v>
+        <v>62.69948196411133</v>
       </c>
       <c r="H26" t="n">
-        <v>21802.384765625</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>13.85133266448975</v>
@@ -1426,7 +1426,7 @@
         <v>20.68655967712402</v>
       </c>
       <c r="K26" t="n">
-        <v>94.85652160644531</v>
+        <v>5.248920440673828</v>
       </c>
       <c r="L26" t="n">
         <v>1923.569946289062</v>
@@ -1437,10 +1437,10 @@
         <v>41791</v>
       </c>
       <c r="B27" t="n">
-        <v>20.35593223571777</v>
+        <v>20.35592842102051</v>
       </c>
       <c r="C27" t="n">
-        <v>34.88195419311523</v>
+        <v>34.88196182250977</v>
       </c>
       <c r="D27" t="n">
         <v>28.95794486999512</v>
@@ -1449,22 +1449,22 @@
         <v>16.23900032043457</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4400046467781067</v>
+        <v>0.4400047361850739</v>
       </c>
       <c r="G27" t="n">
         <v>66.65163421630859</v>
       </c>
       <c r="H27" t="n">
-        <v>19981.7265625</v>
+        <v>4.190000057220459</v>
       </c>
       <c r="I27" t="n">
         <v>16.00399971008301</v>
       </c>
       <c r="J27" t="n">
-        <v>23.39731788635254</v>
+        <v>23.39731407165527</v>
       </c>
       <c r="K27" t="n">
-        <v>102.5804214477539</v>
+        <v>5.374894142150879</v>
       </c>
       <c r="L27" t="n">
         <v>1960.22998046875</v>
@@ -1475,13 +1475,13 @@
         <v>41821</v>
       </c>
       <c r="B28" t="n">
-        <v>20.94077301025391</v>
+        <v>20.94077491760254</v>
       </c>
       <c r="C28" t="n">
-        <v>36.10324478149414</v>
+        <v>36.10324096679688</v>
       </c>
       <c r="D28" t="n">
-        <v>28.7043571472168</v>
+        <v>28.70435905456543</v>
       </c>
       <c r="E28" t="n">
         <v>15.64949989318848</v>
@@ -1490,19 +1490,19 @@
         <v>0.4153226613998413</v>
       </c>
       <c r="G28" t="n">
-        <v>71.96078491210938</v>
+        <v>71.96079254150391</v>
       </c>
       <c r="H28" t="n">
-        <v>20299.14453125</v>
+        <v>3.910000085830688</v>
       </c>
       <c r="I28" t="n">
         <v>14.88666725158691</v>
       </c>
       <c r="J28" t="n">
-        <v>25.66132545471191</v>
+        <v>25.66132736206055</v>
       </c>
       <c r="K28" t="n">
-        <v>111.4325561523438</v>
+        <v>5.174277782440186</v>
       </c>
       <c r="L28" t="n">
         <v>1930.670043945312</v>
@@ -1513,34 +1513,34 @@
         <v>41852</v>
       </c>
       <c r="B29" t="n">
-        <v>22.56387329101562</v>
+        <v>22.56386947631836</v>
       </c>
       <c r="C29" t="n">
-        <v>38.23944854736328</v>
+        <v>38.23945236206055</v>
       </c>
       <c r="D29" t="n">
-        <v>28.84353065490723</v>
+        <v>28.84353446960449</v>
       </c>
       <c r="E29" t="n">
         <v>16.95199966430664</v>
       </c>
       <c r="F29" t="n">
-        <v>0.463643491268158</v>
+        <v>0.4636433124542236</v>
       </c>
       <c r="G29" t="n">
-        <v>74.11019134521484</v>
+        <v>74.11019897460938</v>
       </c>
       <c r="H29" t="n">
-        <v>18651.623046875</v>
+        <v>4.170000076293945</v>
       </c>
       <c r="I29" t="n">
         <v>17.97999954223633</v>
       </c>
       <c r="J29" t="n">
-        <v>26.61711883544922</v>
+        <v>26.61711692810059</v>
       </c>
       <c r="K29" t="n">
-        <v>109.7836151123047</v>
+        <v>6.122174263000488</v>
       </c>
       <c r="L29" t="n">
         <v>2003.369995117188</v>
@@ -1551,34 +1551,34 @@
         <v>41883</v>
       </c>
       <c r="B30" t="n">
-        <v>22.17863845825195</v>
+        <v>22.17863464355469</v>
       </c>
       <c r="C30" t="n">
-        <v>39.02223968505859</v>
+        <v>39.02224731445312</v>
       </c>
       <c r="D30" t="n">
-        <v>29.1431827545166</v>
+        <v>29.14318084716797</v>
       </c>
       <c r="E30" t="n">
         <v>16.12199974060059</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4398057162761688</v>
+        <v>0.4398056268692017</v>
       </c>
       <c r="G30" t="n">
-        <v>78.29016876220703</v>
+        <v>78.29017639160156</v>
       </c>
       <c r="H30" t="n">
-        <v>17895.88671875</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="I30" t="n">
         <v>16.17866706848145</v>
       </c>
       <c r="J30" t="n">
-        <v>26.54090118408203</v>
+        <v>26.54090690612793</v>
       </c>
       <c r="K30" t="n">
-        <v>100.2372207641602</v>
+        <v>6.512059688568115</v>
       </c>
       <c r="L30" t="n">
         <v>1972.2900390625</v>
@@ -1589,34 +1589,34 @@
         <v>41913</v>
       </c>
       <c r="B31" t="n">
-        <v>23.77461433410645</v>
+        <v>23.77462196350098</v>
       </c>
       <c r="C31" t="n">
-        <v>39.51885223388672</v>
+        <v>39.51885604858398</v>
       </c>
       <c r="D31" t="n">
-        <v>28.12586402893066</v>
+        <v>28.12586212158203</v>
       </c>
       <c r="E31" t="n">
         <v>15.27299976348877</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4657888412475586</v>
+        <v>0.4657887518405914</v>
       </c>
       <c r="G31" t="n">
-        <v>74.27860260009766</v>
+        <v>74.27857971191406</v>
       </c>
       <c r="H31" t="n">
-        <v>18802.7734375</v>
+        <v>2.799999952316284</v>
       </c>
       <c r="I31" t="n">
         <v>16.11333274841309</v>
       </c>
       <c r="J31" t="n">
-        <v>25.92349243164062</v>
+        <v>25.92349624633789</v>
       </c>
       <c r="K31" t="n">
-        <v>107.2668380737305</v>
+        <v>6.455920696258545</v>
       </c>
       <c r="L31" t="n">
         <v>2018.050048828125</v>
@@ -1627,13 +1627,13 @@
         <v>41944</v>
       </c>
       <c r="B32" t="n">
-        <v>26.29422187805176</v>
+        <v>26.29421615600586</v>
       </c>
       <c r="C32" t="n">
-        <v>40.49655914306641</v>
+        <v>40.49656677246094</v>
       </c>
       <c r="D32" t="n">
-        <v>27.19521903991699</v>
+        <v>27.19522094726562</v>
       </c>
       <c r="E32" t="n">
         <v>16.93199920654297</v>
@@ -1642,19 +1642,19 @@
         <v>0.5019922256469727</v>
       </c>
       <c r="G32" t="n">
-        <v>76.96286010742188</v>
+        <v>76.96287536621094</v>
       </c>
       <c r="H32" t="n">
-        <v>19452.712890625</v>
+        <v>2.789999961853027</v>
       </c>
       <c r="I32" t="n">
         <v>16.30133247375488</v>
       </c>
       <c r="J32" t="n">
-        <v>28.57929039001465</v>
+        <v>28.57929801940918</v>
       </c>
       <c r="K32" t="n">
-        <v>107.6139755249023</v>
+        <v>6.991106033325195</v>
       </c>
       <c r="L32" t="n">
         <v>2067.56005859375</v>
@@ -1665,10 +1665,10 @@
         <v>41974</v>
       </c>
       <c r="B33" t="n">
-        <v>24.40389823913574</v>
+        <v>24.40390014648438</v>
       </c>
       <c r="C33" t="n">
-        <v>39.34459686279297</v>
+        <v>39.3446044921875</v>
       </c>
       <c r="D33" t="n">
         <v>26.28290176391602</v>
@@ -1677,22 +1677,22 @@
         <v>15.51749992370605</v>
       </c>
       <c r="F33" t="n">
-        <v>0.479968786239624</v>
+        <v>0.4799687266349792</v>
       </c>
       <c r="G33" t="n">
-        <v>77.27983856201172</v>
+        <v>77.27982330322266</v>
       </c>
       <c r="H33" t="n">
-        <v>20350.82421875</v>
+        <v>2.670000076293945</v>
       </c>
       <c r="I33" t="n">
         <v>14.82733345031738</v>
       </c>
       <c r="J33" t="n">
-        <v>27.84275436401367</v>
+        <v>27.84275054931641</v>
       </c>
       <c r="K33" t="n">
-        <v>97.63363647460938</v>
+        <v>7.556460380554199</v>
       </c>
       <c r="L33" t="n">
         <v>2058.89990234375</v>
@@ -1703,34 +1703,34 @@
         <v>42005</v>
       </c>
       <c r="B34" t="n">
-        <v>25.90288734436035</v>
+        <v>25.90289497375488</v>
       </c>
       <c r="C34" t="n">
-        <v>34.22006225585938</v>
+        <v>34.22006988525391</v>
       </c>
       <c r="D34" t="n">
-        <v>26.6241512298584</v>
+        <v>26.62415313720703</v>
       </c>
       <c r="E34" t="n">
         <v>17.72649955749512</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4596208333969116</v>
+        <v>0.459620863199234</v>
       </c>
       <c r="G34" t="n">
-        <v>75.18986511230469</v>
+        <v>75.18985748291016</v>
       </c>
       <c r="H34" t="n">
-        <v>20933.587890625</v>
+        <v>2.569999933242798</v>
       </c>
       <c r="I34" t="n">
         <v>13.57333278656006</v>
       </c>
       <c r="J34" t="n">
-        <v>25.3492546081543</v>
+        <v>25.34925270080566</v>
       </c>
       <c r="K34" t="n">
-        <v>114.5568161010742</v>
+        <v>7.728487491607666</v>
       </c>
       <c r="L34" t="n">
         <v>1994.989990234375</v>
@@ -1741,13 +1741,13 @@
         <v>42036</v>
       </c>
       <c r="B35" t="n">
-        <v>28.5132942199707</v>
+        <v>28.51329231262207</v>
       </c>
       <c r="C35" t="n">
-        <v>37.40664672851562</v>
+        <v>37.40665435791016</v>
       </c>
       <c r="D35" t="n">
-        <v>27.8663330078125</v>
+        <v>27.86633110046387</v>
       </c>
       <c r="E35" t="n">
         <v>19.00799942016602</v>
@@ -1759,16 +1759,16 @@
         <v>78.2208251953125</v>
       </c>
       <c r="H35" t="n">
-        <v>20810.900390625</v>
+        <v>3.109999895095825</v>
       </c>
       <c r="I35" t="n">
         <v>13.55599975585938</v>
       </c>
       <c r="J35" t="n">
-        <v>25.69334983825684</v>
+        <v>25.69335746765137</v>
       </c>
       <c r="K35" t="n">
-        <v>117.9414443969727</v>
+        <v>9.586992263793945</v>
       </c>
       <c r="L35" t="n">
         <v>2104.5</v>
@@ -1782,7 +1782,7 @@
         <v>27.61878395080566</v>
       </c>
       <c r="C36" t="n">
-        <v>34.68539047241211</v>
+        <v>34.68539810180664</v>
       </c>
       <c r="D36" t="n">
         <v>27.47357177734375</v>
@@ -1791,22 +1791,22 @@
         <v>18.60499954223633</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5029637217521667</v>
+        <v>0.5029639601707458</v>
       </c>
       <c r="G36" t="n">
-        <v>81.43999481201172</v>
+        <v>81.43998718261719</v>
       </c>
       <c r="H36" t="n">
-        <v>22099.123046875</v>
+        <v>2.680000066757202</v>
       </c>
       <c r="I36" t="n">
         <v>12.58466720581055</v>
       </c>
       <c r="J36" t="n">
-        <v>24.16333961486816</v>
+        <v>24.16334533691406</v>
       </c>
       <c r="K36" t="n">
-        <v>127.7481994628906</v>
+        <v>9.567073822021484</v>
       </c>
       <c r="L36" t="n">
         <v>2067.889892578125</v>
@@ -1820,7 +1820,7 @@
         <v>27.77860260009766</v>
       </c>
       <c r="C37" t="n">
-        <v>41.49279022216797</v>
+        <v>41.4928092956543</v>
       </c>
       <c r="D37" t="n">
         <v>27.17986297607422</v>
@@ -1829,22 +1829,22 @@
         <v>21.0890007019043</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5334829688072205</v>
+        <v>0.5334831476211548</v>
       </c>
       <c r="G37" t="n">
-        <v>78.02271270751953</v>
+        <v>78.02272033691406</v>
       </c>
       <c r="H37" t="n">
-        <v>21623.708984375</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I37" t="n">
         <v>15.06999969482422</v>
       </c>
       <c r="J37" t="n">
-        <v>25.15244293212891</v>
+        <v>25.15243911743164</v>
       </c>
       <c r="K37" t="n">
-        <v>139.6378173828125</v>
+        <v>8.806108474731445</v>
       </c>
       <c r="L37" t="n">
         <v>2085.510009765625</v>
@@ -1855,34 +1855,34 @@
         <v>42125</v>
       </c>
       <c r="B38" t="n">
-        <v>29.03806114196777</v>
+        <v>29.03805541992188</v>
       </c>
       <c r="C38" t="n">
         <v>40.23413467407227</v>
       </c>
       <c r="D38" t="n">
-        <v>27.00899314880371</v>
+        <v>27.00899124145508</v>
       </c>
       <c r="E38" t="n">
         <v>21.46150016784668</v>
       </c>
       <c r="F38" t="n">
-        <v>0.534262478351593</v>
+        <v>0.5342625379562378</v>
       </c>
       <c r="G38" t="n">
-        <v>78.43874359130859</v>
+        <v>78.43873596191406</v>
       </c>
       <c r="H38" t="n">
-        <v>20044.1015625</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="I38" t="n">
         <v>16.71999931335449</v>
       </c>
       <c r="J38" t="n">
-        <v>26.8209114074707</v>
+        <v>26.8209056854248</v>
       </c>
       <c r="K38" t="n">
-        <v>135.4529418945312</v>
+        <v>11.15606212615967</v>
       </c>
       <c r="L38" t="n">
         <v>2107.389892578125</v>
@@ -1893,34 +1893,34 @@
         <v>42156</v>
       </c>
       <c r="B39" t="n">
-        <v>27.95704078674316</v>
+        <v>27.95703506469727</v>
       </c>
       <c r="C39" t="n">
         <v>37.90732955932617</v>
       </c>
       <c r="D39" t="n">
-        <v>26.74748039245605</v>
+        <v>26.74747848510742</v>
       </c>
       <c r="E39" t="n">
         <v>21.70450019836426</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4854954779148102</v>
+        <v>0.4854955077171326</v>
       </c>
       <c r="G39" t="n">
-        <v>84.95630645751953</v>
+        <v>84.95632171630859</v>
       </c>
       <c r="H39" t="n">
-        <v>19461.2265625</v>
+        <v>2.400000095367432</v>
       </c>
       <c r="I39" t="n">
         <v>17.88400077819824</v>
       </c>
       <c r="J39" t="n">
-        <v>23.6764965057373</v>
+        <v>23.67650604248047</v>
       </c>
       <c r="K39" t="n">
-        <v>134.5829467773438</v>
+        <v>10.04366016387939</v>
       </c>
       <c r="L39" t="n">
         <v>2063.110107421875</v>
@@ -1931,34 +1931,34 @@
         <v>42186</v>
       </c>
       <c r="B40" t="n">
-        <v>27.03650856018066</v>
+        <v>27.0365104675293</v>
       </c>
       <c r="C40" t="n">
-        <v>40.09676742553711</v>
+        <v>40.09676361083984</v>
       </c>
       <c r="D40" t="n">
-        <v>32.56512069702148</v>
+        <v>32.56511688232422</v>
       </c>
       <c r="E40" t="n">
         <v>26.8075008392334</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4816329479217529</v>
+        <v>0.481632798910141</v>
       </c>
       <c r="G40" t="n">
-        <v>93.11814880371094</v>
+        <v>93.11813354492188</v>
       </c>
       <c r="H40" t="n">
-        <v>18187.3515625</v>
+        <v>1.929999947547913</v>
       </c>
       <c r="I40" t="n">
         <v>17.74333381652832</v>
       </c>
       <c r="J40" t="n">
-        <v>22.53237342834473</v>
+        <v>22.53236961364746</v>
       </c>
       <c r="K40" t="n">
-        <v>125.8833312988281</v>
+        <v>9.455080032348633</v>
       </c>
       <c r="L40" t="n">
         <v>2103.840087890625</v>
@@ -1969,34 +1969,34 @@
         <v>42217</v>
       </c>
       <c r="B41" t="n">
-        <v>25.24679946899414</v>
+        <v>25.24678611755371</v>
       </c>
       <c r="C41" t="n">
         <v>37.61282348632812</v>
       </c>
       <c r="D41" t="n">
-        <v>32.08567428588867</v>
+        <v>32.08567810058594</v>
       </c>
       <c r="E41" t="n">
         <v>25.64450073242188</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5449954867362976</v>
+        <v>0.5449955463409424</v>
       </c>
       <c r="G41" t="n">
-        <v>88.58158111572266</v>
+        <v>88.58158874511719</v>
       </c>
       <c r="H41" t="n">
-        <v>16713.943359375</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="I41" t="n">
         <v>16.60400009155273</v>
       </c>
       <c r="J41" t="n">
-        <v>22.39779090881348</v>
+        <v>22.39778900146484</v>
       </c>
       <c r="K41" t="n">
-        <v>114.6608581542969</v>
+        <v>9.517791748046875</v>
       </c>
       <c r="L41" t="n">
         <v>1972.180053710938</v>
@@ -2007,34 +2007,34 @@
         <v>42248</v>
       </c>
       <c r="B42" t="n">
-        <v>24.69600486755371</v>
+        <v>24.69600296020508</v>
       </c>
       <c r="C42" t="n">
-        <v>38.25236892700195</v>
+        <v>38.25237655639648</v>
       </c>
       <c r="D42" t="n">
-        <v>31.61763572692871</v>
+        <v>31.61763763427734</v>
       </c>
       <c r="E42" t="n">
         <v>25.5944995880127</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5976042747497559</v>
+        <v>0.5976040959358215</v>
       </c>
       <c r="G42" t="n">
         <v>89.04713439941406</v>
       </c>
       <c r="H42" t="n">
-        <v>17404.59765625</v>
+        <v>1.720000028610229</v>
       </c>
       <c r="I42" t="n">
         <v>16.55999946594238</v>
       </c>
       <c r="J42" t="n">
-        <v>23.65345573425293</v>
+        <v>23.6534481048584</v>
       </c>
       <c r="K42" t="n">
-        <v>112.4859466552734</v>
+        <v>9.474867820739746</v>
       </c>
       <c r="L42" t="n">
         <v>1920.030029296875</v>
@@ -2045,13 +2045,13 @@
         <v>42278</v>
       </c>
       <c r="B43" t="n">
-        <v>26.75586700439453</v>
+        <v>26.7558650970459</v>
       </c>
       <c r="C43" t="n">
-        <v>45.49491500854492</v>
+        <v>45.49492645263672</v>
       </c>
       <c r="D43" t="n">
-        <v>36.52196502685547</v>
+        <v>36.52197265625</v>
       </c>
       <c r="E43" t="n">
         <v>31.29500007629395</v>
@@ -2063,7 +2063,7 @@
         <v>101.0026321411133</v>
       </c>
       <c r="H43" t="n">
-        <v>21057.412109375</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I43" t="n">
         <v>13.79533290863037</v>
@@ -2072,7 +2072,7 @@
         <v>26.57285118103027</v>
       </c>
       <c r="K43" t="n">
-        <v>127.5362548828125</v>
+        <v>9.332377433776855</v>
       </c>
       <c r="L43" t="n">
         <v>2079.360107421875</v>
@@ -2083,7 +2083,7 @@
         <v>42309</v>
       </c>
       <c r="B44" t="n">
-        <v>26.6005687713623</v>
+        <v>26.60057258605957</v>
       </c>
       <c r="C44" t="n">
         <v>47.28942108154297</v>
@@ -2095,22 +2095,22 @@
         <v>33.2400016784668</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7719261050224304</v>
+        <v>0.7719262838363647</v>
       </c>
       <c r="G44" t="n">
-        <v>103.251091003418</v>
+        <v>103.2510833740234</v>
       </c>
       <c r="H44" t="n">
-        <v>19706.798828125</v>
+        <v>2.359999895095825</v>
       </c>
       <c r="I44" t="n">
         <v>15.35066699981689</v>
       </c>
       <c r="J44" t="n">
-        <v>27.47923469543457</v>
+        <v>27.47922706604004</v>
       </c>
       <c r="K44" t="n">
-        <v>134.2349548339844</v>
+        <v>9.887185096740723</v>
       </c>
       <c r="L44" t="n">
         <v>2080.409912109375</v>
@@ -2124,10 +2124,10 @@
         <v>23.66843605041504</v>
       </c>
       <c r="C45" t="n">
-        <v>48.27262115478516</v>
+        <v>48.27262496948242</v>
       </c>
       <c r="D45" t="n">
-        <v>38.5338134765625</v>
+        <v>38.53382873535156</v>
       </c>
       <c r="E45" t="n">
         <v>33.79449844360352</v>
@@ -2136,19 +2136,19 @@
         <v>0.8021023869514465</v>
       </c>
       <c r="G45" t="n">
-        <v>103.6671142578125</v>
+        <v>103.667106628418</v>
       </c>
       <c r="H45" t="n">
-        <v>19648.849609375</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="I45" t="n">
         <v>16.00066757202148</v>
       </c>
       <c r="J45" t="n">
-        <v>27.22632026672363</v>
+        <v>27.22632598876953</v>
       </c>
       <c r="K45" t="n">
-        <v>132.6690368652344</v>
+        <v>11.03522872924805</v>
       </c>
       <c r="L45" t="n">
         <v>2043.93994140625</v>
@@ -2159,25 +2159,25 @@
         <v>42370</v>
       </c>
       <c r="B46" t="n">
-        <v>21.8875732421875</v>
+        <v>21.88756370544434</v>
       </c>
       <c r="C46" t="n">
-        <v>47.93328857421875</v>
+        <v>47.93329238891602</v>
       </c>
       <c r="D46" t="n">
-        <v>37.70867919921875</v>
+        <v>37.70867538452148</v>
       </c>
       <c r="E46" t="n">
         <v>29.35000038146973</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7127906680107117</v>
+        <v>0.7127906084060669</v>
       </c>
       <c r="G46" t="n">
-        <v>111.1454925537109</v>
+        <v>111.1454772949219</v>
       </c>
       <c r="H46" t="n">
-        <v>17933.474609375</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I46" t="n">
         <v>12.74666690826416</v>
@@ -2186,7 +2186,7 @@
         <v>24.51554489135742</v>
       </c>
       <c r="K46" t="n">
-        <v>126.0573425292969</v>
+        <v>10.16548919677734</v>
       </c>
       <c r="L46" t="n">
         <v>1940.239990234375</v>
@@ -2197,34 +2197,34 @@
         <v>42401</v>
       </c>
       <c r="B47" t="n">
-        <v>21.85938262939453</v>
+        <v>21.8593864440918</v>
       </c>
       <c r="C47" t="n">
-        <v>44.58805465698242</v>
+        <v>44.58806610107422</v>
       </c>
       <c r="D47" t="n">
-        <v>35.52297973632812</v>
+        <v>35.52297592163086</v>
       </c>
       <c r="E47" t="n">
         <v>27.62599945068359</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7659457325935364</v>
+        <v>0.7659458518028259</v>
       </c>
       <c r="G47" t="n">
-        <v>105.9056701660156</v>
+        <v>105.9056625366211</v>
       </c>
       <c r="H47" t="n">
-        <v>18370.11328125</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I47" t="n">
         <v>12.79533290863037</v>
       </c>
       <c r="J47" t="n">
-        <v>23.59122657775879</v>
+        <v>23.59122276306152</v>
       </c>
       <c r="K47" t="n">
-        <v>123.4474716186523</v>
+        <v>10.18525505065918</v>
       </c>
       <c r="L47" t="n">
         <v>1932.22998046875</v>
@@ -2235,25 +2235,25 @@
         <v>42430</v>
       </c>
       <c r="B48" t="n">
-        <v>24.64013290405273</v>
+        <v>24.64013671875</v>
       </c>
       <c r="C48" t="n">
         <v>48.4001350402832</v>
       </c>
       <c r="D48" t="n">
-        <v>37.78544235229492</v>
+        <v>37.78543853759766</v>
       </c>
       <c r="E48" t="n">
         <v>29.68199920654297</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8702376484870911</v>
+        <v>0.8702375292778015</v>
       </c>
       <c r="G48" t="n">
         <v>113.0175552368164</v>
       </c>
       <c r="H48" t="n">
-        <v>20459.7578125</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="I48" t="n">
         <v>15.31799983978271</v>
@@ -2262,7 +2262,7 @@
         <v>25.79169273376465</v>
       </c>
       <c r="K48" t="n">
-        <v>137.8018188476562</v>
+        <v>11.78496742248535</v>
       </c>
       <c r="L48" t="n">
         <v>2059.739990234375</v>
@@ -2276,31 +2276,31 @@
         <v>21.19246292114258</v>
       </c>
       <c r="C49" t="n">
-        <v>43.70295333862305</v>
+        <v>43.70296478271484</v>
       </c>
       <c r="D49" t="n">
-        <v>35.06037521362305</v>
+        <v>35.06038284301758</v>
       </c>
       <c r="E49" t="n">
         <v>32.97949981689453</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8677952885627747</v>
+        <v>0.8677949905395508</v>
       </c>
       <c r="G49" t="n">
-        <v>116.4645462036133</v>
+        <v>116.4645385742188</v>
       </c>
       <c r="H49" t="n">
-        <v>19414.94140625</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="I49" t="n">
         <v>16.05066680908203</v>
       </c>
       <c r="J49" t="n">
-        <v>24.14134407043457</v>
+        <v>24.14133834838867</v>
       </c>
       <c r="K49" t="n">
-        <v>138.2367706298828</v>
+        <v>11.11753463745117</v>
       </c>
       <c r="L49" t="n">
         <v>2065.300048828125</v>
@@ -2314,31 +2314,31 @@
         <v>22.7135066986084</v>
       </c>
       <c r="C50" t="n">
-        <v>46.77076721191406</v>
+        <v>46.770751953125</v>
       </c>
       <c r="D50" t="n">
-        <v>37.08957672119141</v>
+        <v>37.08956527709961</v>
       </c>
       <c r="E50" t="n">
         <v>36.13949966430664</v>
       </c>
       <c r="F50" t="n">
-        <v>1.144065976142883</v>
+        <v>1.144066214561462</v>
       </c>
       <c r="G50" t="n">
-        <v>117.6828765869141</v>
+        <v>117.682861328125</v>
       </c>
       <c r="H50" t="n">
-        <v>20147.87109375</v>
+        <v>4.570000171661377</v>
       </c>
       <c r="I50" t="n">
         <v>14.88199996948242</v>
       </c>
       <c r="J50" t="n">
-        <v>25.40331649780273</v>
+        <v>25.40332221984863</v>
       </c>
       <c r="K50" t="n">
-        <v>151.2547912597656</v>
+        <v>11.77429103851318</v>
       </c>
       <c r="L50" t="n">
         <v>2096.949951171875</v>
@@ -2349,10 +2349,10 @@
         <v>42522</v>
       </c>
       <c r="B51" t="n">
-        <v>21.74455642700195</v>
+        <v>21.74455451965332</v>
       </c>
       <c r="C51" t="n">
-        <v>45.15584564208984</v>
+        <v>45.15584945678711</v>
       </c>
       <c r="D51" t="n">
         <v>34.84492492675781</v>
@@ -2361,22 +2361,22 @@
         <v>35.78099822998047</v>
       </c>
       <c r="F51" t="n">
-        <v>1.151167869567871</v>
+        <v>1.151167750358582</v>
       </c>
       <c r="G51" t="n">
-        <v>113.1958541870117</v>
+        <v>113.1958465576172</v>
       </c>
       <c r="H51" t="n">
-        <v>22237.8125</v>
+        <v>5.139999866485596</v>
       </c>
       <c r="I51" t="n">
         <v>14.15200042724609</v>
       </c>
       <c r="J51" t="n">
-        <v>26.3763484954834</v>
+        <v>26.37635040283203</v>
       </c>
       <c r="K51" t="n">
-        <v>153.6986083984375</v>
+        <v>11.89101409912109</v>
       </c>
       <c r="L51" t="n">
         <v>2098.860107421875</v>
@@ -2387,10 +2387,10 @@
         <v>42552</v>
       </c>
       <c r="B52" t="n">
-        <v>23.70293045043945</v>
+        <v>23.70293235778809</v>
       </c>
       <c r="C52" t="n">
-        <v>50.01823806762695</v>
+        <v>50.01823425292969</v>
       </c>
       <c r="D52" t="n">
         <v>39.19403839111328</v>
@@ -2402,10 +2402,10 @@
         <v>1.398248672485352</v>
       </c>
       <c r="G52" t="n">
-        <v>122.7642059326172</v>
+        <v>122.7641906738281</v>
       </c>
       <c r="H52" t="n">
-        <v>24016.83984375</v>
+        <v>6.860000133514404</v>
       </c>
       <c r="I52" t="n">
         <v>15.65266704559326</v>
@@ -2414,7 +2414,7 @@
         <v>28.03290939331055</v>
       </c>
       <c r="K52" t="n">
-        <v>162.7756195068359</v>
+        <v>12.39450931549072</v>
       </c>
       <c r="L52" t="n">
         <v>2173.60009765625</v>
@@ -2425,34 +2425,34 @@
         <v>42583</v>
       </c>
       <c r="B53" t="n">
-        <v>24.26354598999023</v>
+        <v>24.26355171203613</v>
       </c>
       <c r="C53" t="n">
-        <v>51.02260589599609</v>
+        <v>51.02258682250977</v>
       </c>
       <c r="D53" t="n">
-        <v>39.1202507019043</v>
+        <v>39.12024307250977</v>
       </c>
       <c r="E53" t="n">
         <v>38.45800018310547</v>
       </c>
       <c r="F53" t="n">
-        <v>1.504844903945923</v>
+        <v>1.504844546318054</v>
       </c>
       <c r="G53" t="n">
-        <v>124.9235153198242</v>
+        <v>124.9235229492188</v>
       </c>
       <c r="H53" t="n">
-        <v>25280.890625</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I53" t="n">
         <v>14.13399982452393</v>
       </c>
       <c r="J53" t="n">
-        <v>29.0799617767334</v>
+        <v>29.07996368408203</v>
       </c>
       <c r="K53" t="n">
-        <v>176.1293334960938</v>
+        <v>13.49943923950195</v>
       </c>
       <c r="L53" t="n">
         <v>2170.949951171875</v>
@@ -2463,10 +2463,10 @@
         <v>42614</v>
       </c>
       <c r="B54" t="n">
-        <v>25.85291290283203</v>
+        <v>25.85290908813477</v>
       </c>
       <c r="C54" t="n">
-        <v>51.14691925048828</v>
+        <v>51.14691162109375</v>
       </c>
       <c r="D54" t="n">
         <v>39.82404708862305</v>
@@ -2478,19 +2478,19 @@
         <v>1.680990815162659</v>
       </c>
       <c r="G54" t="n">
-        <v>127.0531311035156</v>
+        <v>127.0531158447266</v>
       </c>
       <c r="H54" t="n">
-        <v>24937.564453125</v>
+        <v>6.909999847412109</v>
       </c>
       <c r="I54" t="n">
         <v>13.60200023651123</v>
       </c>
       <c r="J54" t="n">
-        <v>30.58702659606934</v>
+        <v>30.58703804016113</v>
       </c>
       <c r="K54" t="n">
-        <v>185.9046325683594</v>
+        <v>13.2408275604248</v>
       </c>
       <c r="L54" t="n">
         <v>2168.27001953125</v>
@@ -2501,10 +2501,10 @@
         <v>42644</v>
       </c>
       <c r="B55" t="n">
-        <v>25.96496963500977</v>
+        <v>25.9649658203125</v>
       </c>
       <c r="C55" t="n">
-        <v>53.20698547363281</v>
+        <v>53.20700073242188</v>
       </c>
       <c r="D55" t="n">
         <v>40.11328887939453</v>
@@ -2519,16 +2519,16 @@
         <v>129.747314453125</v>
       </c>
       <c r="H55" t="n">
-        <v>25577.38671875</v>
+        <v>7.230000019073486</v>
       </c>
       <c r="I55" t="n">
         <v>13.18200016021729</v>
       </c>
       <c r="J55" t="n">
-        <v>28.25350379943848</v>
+        <v>28.25351142883301</v>
       </c>
       <c r="K55" t="n">
-        <v>179.6204986572266</v>
+        <v>13.06891059875488</v>
       </c>
       <c r="L55" t="n">
         <v>2126.14990234375</v>
@@ -2539,10 +2539,10 @@
         <v>42675</v>
       </c>
       <c r="B56" t="n">
-        <v>25.40410804748535</v>
+        <v>25.40409660339355</v>
       </c>
       <c r="C56" t="n">
-        <v>53.87038803100586</v>
+        <v>53.87038421630859</v>
       </c>
       <c r="D56" t="n">
         <v>38.42832183837891</v>
@@ -2551,22 +2551,22 @@
         <v>37.52849960327148</v>
       </c>
       <c r="F56" t="n">
-        <v>2.265314817428589</v>
+        <v>2.265315055847168</v>
       </c>
       <c r="G56" t="n">
-        <v>117.2965621948242</v>
+        <v>117.2965698242188</v>
       </c>
       <c r="H56" t="n">
-        <v>27247.16796875</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="I56" t="n">
         <v>12.62666702270508</v>
       </c>
       <c r="J56" t="n">
-        <v>28.32864189147949</v>
+        <v>28.32863807678223</v>
       </c>
       <c r="K56" t="n">
-        <v>169.0597381591797</v>
+        <v>13.08502674102783</v>
       </c>
       <c r="L56" t="n">
         <v>2198.81005859375</v>
@@ -2577,10 +2577,10 @@
         <v>42705</v>
       </c>
       <c r="B57" t="n">
-        <v>26.62235450744629</v>
+        <v>26.62235260009766</v>
       </c>
       <c r="C57" t="n">
-        <v>55.55104064941406</v>
+        <v>55.55105209350586</v>
       </c>
       <c r="D57" t="n">
         <v>39.24901962280273</v>
@@ -2589,22 +2589,22 @@
         <v>37.49349975585938</v>
       </c>
       <c r="F57" t="n">
-        <v>2.622556447982788</v>
+        <v>2.62255597114563</v>
       </c>
       <c r="G57" t="n">
-        <v>113.9585418701172</v>
+        <v>113.9585571289062</v>
       </c>
       <c r="H57" t="n">
-        <v>28557.62109375</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="I57" t="n">
         <v>14.24600028991699</v>
       </c>
       <c r="J57" t="n">
-        <v>29.61037063598633</v>
+        <v>29.6103687286377</v>
       </c>
       <c r="K57" t="n">
-        <v>165.5685729980469</v>
+        <v>13.64457893371582</v>
       </c>
       <c r="L57" t="n">
         <v>2238.830078125</v>
@@ -2615,13 +2615,13 @@
         <v>42736</v>
       </c>
       <c r="B58" t="n">
-        <v>27.89347839355469</v>
+        <v>27.89348602294922</v>
       </c>
       <c r="C58" t="n">
-        <v>57.7949104309082</v>
+        <v>57.79491424560547</v>
       </c>
       <c r="D58" t="n">
-        <v>40.62295150756836</v>
+        <v>40.6229362487793</v>
       </c>
       <c r="E58" t="n">
         <v>41.17399978637695</v>
@@ -2633,16 +2633,16 @@
         <v>129.0836944580078</v>
       </c>
       <c r="H58" t="n">
-        <v>31267.580078125</v>
+        <v>10.36999988555908</v>
       </c>
       <c r="I58" t="n">
         <v>16.79533386230469</v>
       </c>
       <c r="J58" t="n">
-        <v>30.05938720703125</v>
+        <v>30.05938148498535</v>
       </c>
       <c r="K58" t="n">
-        <v>178.3986206054688</v>
+        <v>15.39906978607178</v>
       </c>
       <c r="L58" t="n">
         <v>2278.8701171875</v>
@@ -2653,25 +2653,25 @@
         <v>42767</v>
       </c>
       <c r="B59" t="n">
-        <v>31.62500762939453</v>
+        <v>31.62500953674316</v>
       </c>
       <c r="C59" t="n">
-        <v>57.54270172119141</v>
+        <v>57.54269790649414</v>
       </c>
       <c r="D59" t="n">
-        <v>41.84828567504883</v>
+        <v>41.84828186035156</v>
       </c>
       <c r="E59" t="n">
         <v>42.25199890136719</v>
       </c>
       <c r="F59" t="n">
-        <v>2.496468067169189</v>
+        <v>2.496467351913452</v>
       </c>
       <c r="G59" t="n">
-        <v>134.2541351318359</v>
+        <v>134.2541656494141</v>
       </c>
       <c r="H59" t="n">
-        <v>30459.341796875</v>
+        <v>14.46000003814697</v>
       </c>
       <c r="I59" t="n">
         <v>16.66600036621094</v>
@@ -2680,7 +2680,7 @@
         <v>29.76419258117676</v>
       </c>
       <c r="K59" t="n">
-        <v>180.6678771972656</v>
+        <v>16.28133201599121</v>
       </c>
       <c r="L59" t="n">
         <v>2363.639892578125</v>
@@ -2691,34 +2691,34 @@
         <v>42795</v>
       </c>
       <c r="B60" t="n">
-        <v>33.16481781005859</v>
+        <v>33.16482162475586</v>
       </c>
       <c r="C60" t="n">
-        <v>59.2335319519043</v>
+        <v>59.23354339599609</v>
       </c>
       <c r="D60" t="n">
-        <v>41.99043273925781</v>
+        <v>41.99044036865234</v>
       </c>
       <c r="E60" t="n">
         <v>44.32699966430664</v>
       </c>
       <c r="F60" t="n">
-        <v>2.679741382598877</v>
+        <v>2.679741144180298</v>
       </c>
       <c r="G60" t="n">
         <v>140.7023773193359</v>
       </c>
       <c r="H60" t="n">
-        <v>32756.111328125</v>
+        <v>14.55000019073486</v>
       </c>
       <c r="I60" t="n">
         <v>18.5533332824707</v>
       </c>
       <c r="J60" t="n">
-        <v>29.65731048583984</v>
+        <v>29.65730857849121</v>
       </c>
       <c r="K60" t="n">
-        <v>194.4579772949219</v>
+        <v>16.97779846191406</v>
       </c>
       <c r="L60" t="n">
         <v>2362.719970703125</v>
@@ -2732,31 +2732,31 @@
         <v>33.16250610351562</v>
       </c>
       <c r="C61" t="n">
-        <v>61.57195663452148</v>
+        <v>61.57194900512695</v>
       </c>
       <c r="D61" t="n">
-        <v>45.79027938842773</v>
+        <v>45.79027557373047</v>
       </c>
       <c r="E61" t="n">
         <v>46.2495002746582</v>
       </c>
       <c r="F61" t="n">
-        <v>2.56584095954895</v>
+        <v>2.565840244293213</v>
       </c>
       <c r="G61" t="n">
-        <v>148.8246002197266</v>
+        <v>148.8246154785156</v>
       </c>
       <c r="H61" t="n">
-        <v>35475.1640625</v>
+        <v>13.30000019073486</v>
       </c>
       <c r="I61" t="n">
         <v>20.9379997253418</v>
       </c>
       <c r="J61" t="n">
-        <v>29.72308349609375</v>
+        <v>29.72309684753418</v>
       </c>
       <c r="K61" t="n">
-        <v>212.4374694824219</v>
+        <v>17.12124824523926</v>
       </c>
       <c r="L61" t="n">
         <v>2384.199951171875</v>
@@ -2767,34 +2767,34 @@
         <v>42856</v>
       </c>
       <c r="B62" t="n">
-        <v>35.41116714477539</v>
+        <v>35.41117095947266</v>
       </c>
       <c r="C62" t="n">
-        <v>63.17312622070312</v>
+        <v>63.17313003540039</v>
       </c>
       <c r="D62" t="n">
-        <v>48.88928604125977</v>
+        <v>48.8892822265625</v>
       </c>
       <c r="E62" t="n">
         <v>49.73099899291992</v>
       </c>
       <c r="F62" t="n">
-        <v>3.55483341217041</v>
+        <v>3.554834365844727</v>
       </c>
       <c r="G62" t="n">
-        <v>150.0231475830078</v>
+        <v>150.0231323242188</v>
       </c>
       <c r="H62" t="n">
-        <v>35538.78125</v>
+        <v>11.1899995803833</v>
       </c>
       <c r="I62" t="n">
         <v>22.73399925231934</v>
       </c>
       <c r="J62" t="n">
-        <v>29.91108131408691</v>
+        <v>29.91107177734375</v>
       </c>
       <c r="K62" t="n">
-        <v>234.1459503173828</v>
+        <v>18.56888771057129</v>
       </c>
       <c r="L62" t="n">
         <v>2411.800048828125</v>
@@ -2805,34 +2805,34 @@
         <v>42887</v>
       </c>
       <c r="B63" t="n">
-        <v>33.38517379760742</v>
+        <v>33.38515472412109</v>
       </c>
       <c r="C63" t="n">
-        <v>62.35000228881836</v>
+        <v>62.34999847412109</v>
       </c>
       <c r="D63" t="n">
-        <v>46.04584121704102</v>
+        <v>46.04583740234375</v>
       </c>
       <c r="E63" t="n">
         <v>48.40000152587891</v>
       </c>
       <c r="F63" t="n">
-        <v>3.560005664825439</v>
+        <v>3.560005903244019</v>
       </c>
       <c r="G63" t="n">
-        <v>149.5476989746094</v>
+        <v>149.5476837158203</v>
       </c>
       <c r="H63" t="n">
-        <v>37907.984375</v>
+        <v>12.47999954223633</v>
       </c>
       <c r="I63" t="n">
         <v>24.10733222961426</v>
       </c>
       <c r="J63" t="n">
-        <v>27.94793128967285</v>
+        <v>27.94792938232422</v>
       </c>
       <c r="K63" t="n">
-        <v>244.2957611083984</v>
+        <v>18.14727783203125</v>
       </c>
       <c r="L63" t="n">
         <v>2423.409912109375</v>
@@ -2843,25 +2843,25 @@
         <v>42917</v>
       </c>
       <c r="B64" t="n">
-        <v>34.47698593139648</v>
+        <v>34.47698974609375</v>
       </c>
       <c r="C64" t="n">
-        <v>65.76010894775391</v>
+        <v>65.76011657714844</v>
       </c>
       <c r="D64" t="n">
-        <v>46.82939147949219</v>
+        <v>46.82938385009766</v>
       </c>
       <c r="E64" t="n">
         <v>49.38899993896484</v>
       </c>
       <c r="F64" t="n">
-        <v>4.002049922943115</v>
+        <v>4.002050876617432</v>
       </c>
       <c r="G64" t="n">
-        <v>167.6443328857422</v>
+        <v>167.6443786621094</v>
       </c>
       <c r="H64" t="n">
-        <v>38434.26171875</v>
+        <v>13.60999965667725</v>
       </c>
       <c r="I64" t="n">
         <v>21.56466674804688</v>
@@ -2870,7 +2870,7 @@
         <v>29.38093948364258</v>
       </c>
       <c r="K64" t="n">
-        <v>274.2202453613281</v>
+        <v>19.20706367492676</v>
       </c>
       <c r="L64" t="n">
         <v>2470.300048828125</v>
@@ -2881,7 +2881,7 @@
         <v>42948</v>
       </c>
       <c r="B65" t="n">
-        <v>38.16599655151367</v>
+        <v>38.16600799560547</v>
       </c>
       <c r="C65" t="n">
         <v>67.99285888671875</v>
@@ -2893,22 +2893,22 @@
         <v>49.02999877929688</v>
       </c>
       <c r="F65" t="n">
-        <v>4.176386833190918</v>
+        <v>4.176387786865234</v>
       </c>
       <c r="G65" t="n">
-        <v>170.3385620117188</v>
+        <v>170.3385314941406</v>
       </c>
       <c r="H65" t="n">
-        <v>36935.171875</v>
+        <v>13</v>
       </c>
       <c r="I65" t="n">
         <v>23.7266674041748</v>
       </c>
       <c r="J65" t="n">
-        <v>29.26767349243164</v>
+        <v>29.26767730712891</v>
       </c>
       <c r="K65" t="n">
-        <v>287.8699340820312</v>
+        <v>19.62832832336426</v>
       </c>
       <c r="L65" t="n">
         <v>2471.64990234375</v>
@@ -2919,34 +2919,34 @@
         <v>42979</v>
       </c>
       <c r="B66" t="n">
-        <v>35.86673736572266</v>
+        <v>35.86673355102539</v>
       </c>
       <c r="C66" t="n">
-        <v>67.73822021484375</v>
+        <v>67.73822784423828</v>
       </c>
       <c r="D66" t="n">
-        <v>48.22708511352539</v>
+        <v>48.22708892822266</v>
       </c>
       <c r="E66" t="n">
         <v>48.06750106811523</v>
       </c>
       <c r="F66" t="n">
-        <v>4.40635347366333</v>
+        <v>4.406355857849121</v>
       </c>
       <c r="G66" t="n">
         <v>169.2489776611328</v>
       </c>
       <c r="H66" t="n">
-        <v>41001.296875</v>
+        <v>12.75</v>
       </c>
       <c r="I66" t="n">
         <v>22.73999977111816</v>
       </c>
       <c r="J66" t="n">
-        <v>31.77967643737793</v>
+        <v>31.7796688079834</v>
       </c>
       <c r="K66" t="n">
-        <v>294.1698608398438</v>
+        <v>18.96344757080078</v>
       </c>
       <c r="L66" t="n">
         <v>2519.360107421875</v>
@@ -2957,34 +2957,34 @@
         <v>43009</v>
       </c>
       <c r="B67" t="n">
-        <v>39.33891677856445</v>
+        <v>39.33891296386719</v>
       </c>
       <c r="C67" t="n">
         <v>75.64057922363281</v>
       </c>
       <c r="D67" t="n">
-        <v>51.16513442993164</v>
+        <v>51.16512680053711</v>
       </c>
       <c r="E67" t="n">
         <v>55.26399993896484</v>
       </c>
       <c r="F67" t="n">
-        <v>5.097487926483154</v>
+        <v>5.097490310668945</v>
       </c>
       <c r="G67" t="n">
-        <v>178.3517761230469</v>
+        <v>178.351806640625</v>
       </c>
       <c r="H67" t="n">
-        <v>44039.6015625</v>
+        <v>10.98999977111816</v>
       </c>
       <c r="I67" t="n">
         <v>22.10199928283691</v>
       </c>
       <c r="J67" t="n">
-        <v>37.96368408203125</v>
+        <v>37.96368789672852</v>
       </c>
       <c r="K67" t="n">
-        <v>306.0696716308594</v>
+        <v>20.63430023193359</v>
       </c>
       <c r="L67" t="n">
         <v>2575.260009765625</v>
@@ -2995,10 +2995,10 @@
         <v>43040</v>
       </c>
       <c r="B68" t="n">
-        <v>40.13661193847656</v>
+        <v>40.13661575317383</v>
       </c>
       <c r="C68" t="n">
-        <v>76.92522430419922</v>
+        <v>76.92524719238281</v>
       </c>
       <c r="D68" t="n">
         <v>51.32015228271484</v>
@@ -3007,22 +3007,22 @@
         <v>58.83750152587891</v>
       </c>
       <c r="F68" t="n">
-        <v>4.95057201385498</v>
+        <v>4.950572967529297</v>
       </c>
       <c r="G68" t="n">
-        <v>175.4991455078125</v>
+        <v>175.4991302490234</v>
       </c>
       <c r="H68" t="n">
-        <v>40617.50390625</v>
+        <v>10.89000034332275</v>
       </c>
       <c r="I68" t="n">
         <v>20.59000015258789</v>
       </c>
       <c r="J68" t="n">
-        <v>37.64300537109375</v>
+        <v>37.64299774169922</v>
       </c>
       <c r="K68" t="n">
-        <v>348.2439270019531</v>
+        <v>21.73125839233398</v>
       </c>
       <c r="L68" t="n">
         <v>2647.580078125</v>
@@ -3036,31 +3036,31 @@
         <v>39.52470779418945</v>
       </c>
       <c r="C69" t="n">
-        <v>78.17731475830078</v>
+        <v>78.17732238769531</v>
       </c>
       <c r="D69" t="n">
-        <v>52.17353820800781</v>
+        <v>52.17352676391602</v>
       </c>
       <c r="E69" t="n">
         <v>58.4734992980957</v>
       </c>
       <c r="F69" t="n">
-        <v>4.772736549377441</v>
+        <v>4.772736072540283</v>
       </c>
       <c r="G69" t="n">
-        <v>174.7859191894531</v>
+        <v>174.7859649658203</v>
       </c>
       <c r="H69" t="n">
-        <v>41112.19921875</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="I69" t="n">
         <v>20.75666618347168</v>
       </c>
       <c r="J69" t="n">
-        <v>38.75112915039062</v>
+        <v>38.75113677978516</v>
       </c>
       <c r="K69" t="n">
-        <v>355.2438354492188</v>
+        <v>20.21936225891113</v>
       </c>
       <c r="L69" t="n">
         <v>2673.610107421875</v>
@@ -3071,34 +3071,34 @@
         <v>43101</v>
       </c>
       <c r="B70" t="n">
-        <v>39.10430526733398</v>
+        <v>39.10429000854492</v>
       </c>
       <c r="C70" t="n">
         <v>86.83221435546875</v>
       </c>
       <c r="D70" t="n">
-        <v>58.5538215637207</v>
+        <v>58.55382537841797</v>
       </c>
       <c r="E70" t="n">
         <v>72.54450225830078</v>
       </c>
       <c r="F70" t="n">
-        <v>6.062731742858887</v>
+        <v>6.062728404998779</v>
       </c>
       <c r="G70" t="n">
         <v>185.1170043945312</v>
       </c>
       <c r="H70" t="n">
-        <v>40257.046875</v>
+        <v>13.73999977111816</v>
       </c>
       <c r="I70" t="n">
         <v>23.62066650390625</v>
       </c>
       <c r="J70" t="n">
-        <v>40.41332626342773</v>
+        <v>40.4133415222168</v>
       </c>
       <c r="K70" t="n">
-        <v>405.6429138183594</v>
+        <v>19.5212459564209</v>
       </c>
       <c r="L70" t="n">
         <v>2823.81005859375</v>
@@ -3109,13 +3109,13 @@
         <v>43132</v>
       </c>
       <c r="B71" t="n">
-        <v>41.77063369750977</v>
+        <v>41.7706298828125</v>
       </c>
       <c r="C71" t="n">
-        <v>86.10151672363281</v>
+        <v>86.10150909423828</v>
       </c>
       <c r="D71" t="n">
-        <v>54.67572402954102</v>
+        <v>54.67573165893555</v>
       </c>
       <c r="E71" t="n">
         <v>75.62249755859375</v>
@@ -3124,19 +3124,19 @@
         <v>5.972712516784668</v>
       </c>
       <c r="G71" t="n">
-        <v>176.6283264160156</v>
+        <v>176.6283111572266</v>
       </c>
       <c r="H71" t="n">
-        <v>37965.8515625</v>
+        <v>12.10999965667725</v>
       </c>
       <c r="I71" t="n">
         <v>22.87066650390625</v>
       </c>
       <c r="J71" t="n">
-        <v>41.65947341918945</v>
+        <v>41.65947723388672</v>
       </c>
       <c r="K71" t="n">
-        <v>378.1684875488281</v>
+        <v>19.39768028259277</v>
       </c>
       <c r="L71" t="n">
         <v>2713.830078125</v>
@@ -3147,34 +3147,34 @@
         <v>43160</v>
       </c>
       <c r="B72" t="n">
-        <v>39.3458137512207</v>
+        <v>39.34581756591797</v>
       </c>
       <c r="C72" t="n">
-        <v>83.80595397949219</v>
+        <v>83.80594635009766</v>
       </c>
       <c r="D72" t="n">
-        <v>51.36819458007812</v>
+        <v>51.36819076538086</v>
       </c>
       <c r="E72" t="n">
         <v>72.36699676513672</v>
       </c>
       <c r="F72" t="n">
-        <v>5.715786457061768</v>
+        <v>5.715787410736084</v>
       </c>
       <c r="G72" t="n">
         <v>158.2740936279297</v>
       </c>
       <c r="H72" t="n">
-        <v>39999.203125</v>
+        <v>10.05000019073486</v>
       </c>
       <c r="I72" t="n">
         <v>17.74200057983398</v>
       </c>
       <c r="J72" t="n">
-        <v>44.01756286621094</v>
+        <v>44.0175666809082</v>
       </c>
       <c r="K72" t="n">
-        <v>358.393798828125</v>
+        <v>18.81864738464355</v>
       </c>
       <c r="L72" t="n">
         <v>2640.8701171875</v>
@@ -3185,34 +3185,34 @@
         <v>43191</v>
       </c>
       <c r="B73" t="n">
-        <v>38.75485229492188</v>
+        <v>38.75485610961914</v>
       </c>
       <c r="C73" t="n">
-        <v>85.8719482421875</v>
+        <v>85.87196350097656</v>
       </c>
       <c r="D73" t="n">
-        <v>50.44895172119141</v>
+        <v>50.44894027709961</v>
       </c>
       <c r="E73" t="n">
         <v>78.30650329589844</v>
       </c>
       <c r="F73" t="n">
-        <v>5.55067253112793</v>
+        <v>5.550673007965088</v>
       </c>
       <c r="G73" t="n">
-        <v>170.3682556152344</v>
+        <v>170.3682708740234</v>
       </c>
       <c r="H73" t="n">
-        <v>43071.0625</v>
+        <v>10.88000011444092</v>
       </c>
       <c r="I73" t="n">
         <v>19.59333229064941</v>
       </c>
       <c r="J73" t="n">
-        <v>43.62876129150391</v>
+        <v>43.62877655029297</v>
       </c>
       <c r="K73" t="n">
-        <v>342.1190185546875</v>
+        <v>18.32112503051758</v>
       </c>
       <c r="L73" t="n">
         <v>2648.050048828125</v>
@@ -3223,10 +3223,10 @@
         <v>43221</v>
       </c>
       <c r="B74" t="n">
-        <v>43.99156188964844</v>
+        <v>43.9915657043457</v>
       </c>
       <c r="C74" t="n">
-        <v>91.15026092529297</v>
+        <v>91.1502685546875</v>
       </c>
       <c r="D74" t="n">
         <v>54.4815673828125</v>
@@ -3235,22 +3235,22 @@
         <v>81.48100280761719</v>
       </c>
       <c r="F74" t="n">
-        <v>6.22805643081665</v>
+        <v>6.228055477142334</v>
       </c>
       <c r="G74" t="n">
-        <v>189.9606323242188</v>
+        <v>189.9606170654297</v>
       </c>
       <c r="H74" t="n">
-        <v>41201.9453125</v>
+        <v>13.72999954223633</v>
       </c>
       <c r="I74" t="n">
         <v>18.98200035095215</v>
       </c>
       <c r="J74" t="n">
-        <v>46.92382049560547</v>
+        <v>46.92382431030273</v>
       </c>
       <c r="K74" t="n">
-        <v>350.1071472167969</v>
+        <v>20.12992095947266</v>
       </c>
       <c r="L74" t="n">
         <v>2705.27001953125</v>
@@ -3261,13 +3261,13 @@
         <v>43252</v>
       </c>
       <c r="B75" t="n">
-        <v>43.57722473144531</v>
+        <v>43.57723236083984</v>
       </c>
       <c r="C75" t="n">
-        <v>90.93817138671875</v>
+        <v>90.93814086914062</v>
       </c>
       <c r="D75" t="n">
-        <v>55.92731475830078</v>
+        <v>55.92730712890625</v>
       </c>
       <c r="E75" t="n">
         <v>84.98999786376953</v>
@@ -3276,19 +3276,19 @@
         <v>5.850456714630127</v>
       </c>
       <c r="G75" t="n">
-        <v>192.4765472412109</v>
+        <v>192.4765319824219</v>
       </c>
       <c r="H75" t="n">
-        <v>38192.62890625</v>
+        <v>14.98999977111816</v>
       </c>
       <c r="I75" t="n">
         <v>22.86333274841309</v>
       </c>
       <c r="J75" t="n">
-        <v>42.25694274902344</v>
+        <v>42.2569465637207</v>
       </c>
       <c r="K75" t="n">
-        <v>345.3711547851562</v>
+        <v>19.6367015838623</v>
       </c>
       <c r="L75" t="n">
         <v>2718.3701171875</v>
@@ -3302,7 +3302,7 @@
         <v>44.79666900634766</v>
       </c>
       <c r="C76" t="n">
-        <v>97.82697296142578</v>
+        <v>97.82698822021484</v>
       </c>
       <c r="D76" t="n">
         <v>60.78260803222656</v>
@@ -3311,22 +3311,22 @@
         <v>88.87200164794922</v>
       </c>
       <c r="F76" t="n">
-        <v>6.04703426361084</v>
+        <v>6.047035217285156</v>
       </c>
       <c r="G76" t="n">
-        <v>170.9427795410156</v>
+        <v>170.9427642822266</v>
       </c>
       <c r="H76" t="n">
-        <v>37865.14453125</v>
+        <v>18.32999992370605</v>
       </c>
       <c r="I76" t="n">
         <v>19.87599945068359</v>
       </c>
       <c r="J76" t="n">
-        <v>40.88832855224609</v>
+        <v>40.88832092285156</v>
       </c>
       <c r="K76" t="n">
-        <v>311.5181579589844</v>
+        <v>17.94770240783691</v>
       </c>
       <c r="L76" t="n">
         <v>2816.2900390625</v>
@@ -3337,10 +3337,10 @@
         <v>43313</v>
       </c>
       <c r="B77" t="n">
-        <v>53.77492523193359</v>
+        <v>53.77492141723633</v>
       </c>
       <c r="C77" t="n">
-        <v>103.989372253418</v>
+        <v>103.9893951416016</v>
       </c>
       <c r="D77" t="n">
         <v>61.00945663452148</v>
@@ -3349,13 +3349,13 @@
         <v>100.635498046875</v>
       </c>
       <c r="F77" t="n">
-        <v>6.935434818267822</v>
+        <v>6.935434341430664</v>
       </c>
       <c r="G77" t="n">
-        <v>174.0628967285156</v>
+        <v>174.0628509521484</v>
       </c>
       <c r="H77" t="n">
-        <v>39666.3046875</v>
+        <v>25.17000007629395</v>
       </c>
       <c r="I77" t="n">
         <v>20.11066627502441</v>
@@ -3364,7 +3364,7 @@
         <v>41.41922760009766</v>
       </c>
       <c r="K77" t="n">
-        <v>298.1873779296875</v>
+        <v>17.72595405578613</v>
       </c>
       <c r="L77" t="n">
         <v>2901.52001953125</v>
@@ -3375,10 +3375,10 @@
         <v>43344</v>
       </c>
       <c r="B78" t="n">
-        <v>53.32842636108398</v>
+        <v>53.32843399047852</v>
       </c>
       <c r="C78" t="n">
-        <v>105.8778991699219</v>
+        <v>105.8779220581055</v>
       </c>
       <c r="D78" t="n">
         <v>59.78510665893555</v>
@@ -3390,19 +3390,19 @@
         <v>6.943834781646729</v>
       </c>
       <c r="G78" t="n">
-        <v>162.8997955322266</v>
+        <v>162.8997802734375</v>
       </c>
       <c r="H78" t="n">
-        <v>38315.046875</v>
+        <v>30.88999938964844</v>
       </c>
       <c r="I78" t="n">
         <v>17.65133285522461</v>
       </c>
       <c r="J78" t="n">
-        <v>40.44424819946289</v>
+        <v>40.44425201416016</v>
       </c>
       <c r="K78" t="n">
-        <v>283.4534301757812</v>
+        <v>20.11761665344238</v>
       </c>
       <c r="L78" t="n">
         <v>2913.97998046875</v>
@@ -3413,7 +3413,7 @@
         <v>43374</v>
       </c>
       <c r="B79" t="n">
-        <v>51.70310211181641</v>
+        <v>51.70310592651367</v>
       </c>
       <c r="C79" t="n">
         <v>98.87925720214844</v>
@@ -3425,13 +3425,13 @@
         <v>79.90049743652344</v>
       </c>
       <c r="F79" t="n">
-        <v>5.209481716156006</v>
+        <v>5.209482192993164</v>
       </c>
       <c r="G79" t="n">
-        <v>150.3500061035156</v>
+        <v>150.3499603271484</v>
       </c>
       <c r="H79" t="n">
-        <v>34974.33984375</v>
+        <v>18.20999908447266</v>
       </c>
       <c r="I79" t="n">
         <v>22.48800086975098</v>
@@ -3440,7 +3440,7 @@
         <v>40.09360504150391</v>
       </c>
       <c r="K79" t="n">
-        <v>234.1647796630859</v>
+        <v>18.22270011901855</v>
       </c>
       <c r="L79" t="n">
         <v>2711.739990234375</v>
@@ -3451,10 +3451,10 @@
         <v>43405</v>
       </c>
       <c r="B80" t="n">
-        <v>42.33463287353516</v>
+        <v>42.33462905883789</v>
       </c>
       <c r="C80" t="n">
-        <v>103.0998077392578</v>
+        <v>103.0997848510742</v>
       </c>
       <c r="D80" t="n">
         <v>54.95952224731445</v>
@@ -3463,13 +3463,13 @@
         <v>84.50849914550781</v>
       </c>
       <c r="F80" t="n">
-        <v>4.042298793792725</v>
+        <v>4.04229736328125</v>
       </c>
       <c r="G80" t="n">
-        <v>139.2760772705078</v>
+        <v>139.2760467529297</v>
       </c>
       <c r="H80" t="n">
-        <v>34520.66015625</v>
+        <v>21.29999923706055</v>
       </c>
       <c r="I80" t="n">
         <v>23.36533355712891</v>
@@ -3478,7 +3478,7 @@
         <v>42.43722915649414</v>
       </c>
       <c r="K80" t="n">
-        <v>273.6307678222656</v>
+        <v>19.35769653320312</v>
       </c>
       <c r="L80" t="n">
         <v>2760.169921875</v>
@@ -3489,34 +3489,34 @@
         <v>43435</v>
       </c>
       <c r="B81" t="n">
-        <v>37.39425277709961</v>
+        <v>37.39424133300781</v>
       </c>
       <c r="C81" t="n">
-        <v>94.43453216552734</v>
+        <v>94.43453979492188</v>
       </c>
       <c r="D81" t="n">
-        <v>51.75550842285156</v>
+        <v>51.75551605224609</v>
       </c>
       <c r="E81" t="n">
         <v>75.09850311279297</v>
       </c>
       <c r="F81" t="n">
-        <v>3.302005767822266</v>
+        <v>3.302005529403687</v>
       </c>
       <c r="G81" t="n">
-        <v>129.8463592529297</v>
+        <v>129.8463897705078</v>
       </c>
       <c r="H81" t="n">
-        <v>32219.74609375</v>
+        <v>18.45999908447266</v>
       </c>
       <c r="I81" t="n">
         <v>22.18666648864746</v>
       </c>
       <c r="J81" t="n">
-        <v>40.38895416259766</v>
+        <v>40.38895797729492</v>
       </c>
       <c r="K81" t="n">
-        <v>275.3847961425781</v>
+        <v>20.95170402526855</v>
       </c>
       <c r="L81" t="n">
         <v>2506.85009765625</v>
@@ -3527,10 +3527,10 @@
         <v>43466</v>
       </c>
       <c r="B82" t="n">
-        <v>39.45669174194336</v>
+        <v>39.45669555664062</v>
       </c>
       <c r="C82" t="n">
-        <v>97.09362030029297</v>
+        <v>97.09359741210938</v>
       </c>
       <c r="D82" t="n">
         <v>55.76386260986328</v>
@@ -3539,22 +3539,22 @@
         <v>85.93650054931641</v>
       </c>
       <c r="F82" t="n">
-        <v>3.555529117584229</v>
+        <v>3.555529594421387</v>
       </c>
       <c r="G82" t="n">
-        <v>165.1086578369141</v>
+        <v>165.108642578125</v>
       </c>
       <c r="H82" t="n">
-        <v>38422.24609375</v>
+        <v>24.40999984741211</v>
       </c>
       <c r="I82" t="n">
         <v>20.4680004119873</v>
       </c>
       <c r="J82" t="n">
-        <v>40.55246734619141</v>
+        <v>40.55246353149414</v>
       </c>
       <c r="K82" t="n">
-        <v>303.4495239257812</v>
+        <v>22.102783203125</v>
       </c>
       <c r="L82" t="n">
         <v>2704.10009765625</v>
@@ -3565,7 +3565,7 @@
         <v>43497</v>
       </c>
       <c r="B83" t="n">
-        <v>41.22343063354492</v>
+        <v>41.22341537475586</v>
       </c>
       <c r="C83" t="n">
         <v>104.6045455932617</v>
@@ -3577,13 +3577,13 @@
         <v>81.99150085449219</v>
       </c>
       <c r="F83" t="n">
-        <v>3.819418430328369</v>
+        <v>3.819417476654053</v>
       </c>
       <c r="G83" t="n">
         <v>159.9183502197266</v>
       </c>
       <c r="H83" t="n">
-        <v>37548.06640625</v>
+        <v>23.53000068664551</v>
       </c>
       <c r="I83" t="n">
         <v>21.32533264160156</v>
@@ -3592,7 +3592,7 @@
         <v>45.86740112304688</v>
       </c>
       <c r="K83" t="n">
-        <v>294.50390625</v>
+        <v>22.68861389160156</v>
       </c>
       <c r="L83" t="n">
         <v>2784.489990234375</v>
@@ -3603,34 +3603,34 @@
         <v>43525</v>
       </c>
       <c r="B84" t="n">
-        <v>45.22315979003906</v>
+        <v>45.22315216064453</v>
       </c>
       <c r="C84" t="n">
         <v>110.1228103637695</v>
       </c>
       <c r="D84" t="n">
-        <v>58.28983306884766</v>
+        <v>58.28983688354492</v>
       </c>
       <c r="E84" t="n">
         <v>89.03749847412109</v>
       </c>
       <c r="F84" t="n">
-        <v>4.445836544036865</v>
+        <v>4.445836067199707</v>
       </c>
       <c r="G84" t="n">
-        <v>165.1086578369141</v>
+        <v>165.108642578125</v>
       </c>
       <c r="H84" t="n">
-        <v>37465.875</v>
+        <v>25.52000045776367</v>
       </c>
       <c r="I84" t="n">
         <v>18.65733337402344</v>
       </c>
       <c r="J84" t="n">
-        <v>46.50830841064453</v>
+        <v>46.50830078125</v>
       </c>
       <c r="K84" t="n">
-        <v>316.6048583984375</v>
+        <v>24.99868965148926</v>
       </c>
       <c r="L84" t="n">
         <v>2834.39990234375</v>
@@ -3641,34 +3641,34 @@
         <v>43556</v>
       </c>
       <c r="B85" t="n">
-        <v>47.77536392211914</v>
+        <v>47.77536773681641</v>
       </c>
       <c r="C85" t="n">
         <v>121.9437026977539</v>
       </c>
       <c r="D85" t="n">
-        <v>59.38292694091797</v>
+        <v>59.38293075561523</v>
       </c>
       <c r="E85" t="n">
         <v>96.32599639892578</v>
       </c>
       <c r="F85" t="n">
-        <v>4.481490135192871</v>
+        <v>4.481489181518555</v>
       </c>
       <c r="G85" t="n">
         <v>191.5652465820312</v>
       </c>
       <c r="H85" t="n">
-        <v>38472.80078125</v>
+        <v>27.6299991607666</v>
       </c>
       <c r="I85" t="n">
         <v>15.9126672744751</v>
       </c>
       <c r="J85" t="n">
-        <v>44.20454406738281</v>
+        <v>44.20453643798828</v>
       </c>
       <c r="K85" t="n">
-        <v>340.2843933105469</v>
+        <v>26.46929931640625</v>
       </c>
       <c r="L85" t="n">
         <v>2945.830078125</v>
@@ -3679,10 +3679,10 @@
         <v>43586</v>
       </c>
       <c r="B86" t="n">
-        <v>41.8410530090332</v>
+        <v>41.84104156494141</v>
       </c>
       <c r="C86" t="n">
-        <v>115.9098358154297</v>
+        <v>115.9098434448242</v>
       </c>
       <c r="D86" t="n">
         <v>54.80350112915039</v>
@@ -3691,22 +3691,22 @@
         <v>88.75350189208984</v>
       </c>
       <c r="F86" t="n">
-        <v>3.357765913009644</v>
+        <v>3.357765674591064</v>
       </c>
       <c r="G86" t="n">
-        <v>175.7863922119141</v>
+        <v>175.786376953125</v>
       </c>
       <c r="H86" t="n">
-        <v>35661.80078125</v>
+        <v>27.40999984741211</v>
       </c>
       <c r="I86" t="n">
         <v>12.3439998626709</v>
       </c>
       <c r="J86" t="n">
-        <v>38.3755989074707</v>
+        <v>38.37558746337891</v>
       </c>
       <c r="K86" t="n">
-        <v>286.7599487304688</v>
+        <v>20.91939163208008</v>
       </c>
       <c r="L86" t="n">
         <v>2752.06005859375</v>
@@ -3717,13 +3717,13 @@
         <v>43617</v>
       </c>
       <c r="B87" t="n">
-        <v>47.30210113525391</v>
+        <v>47.30210876464844</v>
       </c>
       <c r="C87" t="n">
-        <v>125.5440139770508</v>
+        <v>125.5440216064453</v>
       </c>
       <c r="D87" t="n">
-        <v>53.62968444824219</v>
+        <v>53.62967300415039</v>
       </c>
       <c r="E87" t="n">
         <v>94.68150329589844</v>
@@ -3735,16 +3735,16 @@
         <v>191.1690368652344</v>
       </c>
       <c r="H87" t="n">
-        <v>39745.63671875</v>
+        <v>30.3700008392334</v>
       </c>
       <c r="I87" t="n">
         <v>14.8973331451416</v>
       </c>
       <c r="J87" t="n">
-        <v>41.71298599243164</v>
+        <v>41.71298217773438</v>
       </c>
       <c r="K87" t="n">
-        <v>310.1581420898438</v>
+        <v>24.15987205505371</v>
       </c>
       <c r="L87" t="n">
         <v>2941.760009765625</v>
@@ -3755,34 +3755,34 @@
         <v>43647</v>
       </c>
       <c r="B88" t="n">
-        <v>50.91572952270508</v>
+        <v>50.91572189331055</v>
       </c>
       <c r="C88" t="n">
-        <v>127.7088851928711</v>
+        <v>127.7088241577148</v>
       </c>
       <c r="D88" t="n">
-        <v>60.33586120605469</v>
+        <v>60.33585739135742</v>
       </c>
       <c r="E88" t="n">
         <v>93.33899688720703</v>
       </c>
       <c r="F88" t="n">
-        <v>4.182210445404053</v>
+        <v>4.182209491729736</v>
       </c>
       <c r="G88" t="n">
-        <v>192.3873596191406</v>
+        <v>192.3873748779297</v>
       </c>
       <c r="H88" t="n">
-        <v>38350.3125</v>
+        <v>30.45000076293945</v>
       </c>
       <c r="I88" t="n">
         <v>16.10733222961426</v>
       </c>
       <c r="J88" t="n">
-        <v>44.04827880859375</v>
+        <v>44.04828262329102</v>
       </c>
       <c r="K88" t="n">
-        <v>323.8804016113281</v>
+        <v>24.33864593505859</v>
       </c>
       <c r="L88" t="n">
         <v>2980.3798828125</v>
@@ -3793,10 +3793,10 @@
         <v>43678</v>
       </c>
       <c r="B89" t="n">
-        <v>50.07759475708008</v>
+        <v>50.07759857177734</v>
       </c>
       <c r="C89" t="n">
-        <v>129.6291809082031</v>
+        <v>129.6291656494141</v>
       </c>
       <c r="D89" t="n">
         <v>58.96540451049805</v>
@@ -3805,22 +3805,22 @@
         <v>88.81449890136719</v>
       </c>
       <c r="F89" t="n">
-        <v>4.156326293945312</v>
+        <v>4.156328678131104</v>
       </c>
       <c r="G89" t="n">
-        <v>183.9085693359375</v>
+        <v>183.9085845947266</v>
       </c>
       <c r="H89" t="n">
-        <v>37208.6796875</v>
+        <v>31.45000076293945</v>
       </c>
       <c r="I89" t="n">
         <v>15.0406665802002</v>
       </c>
       <c r="J89" t="n">
-        <v>41.5910758972168</v>
+        <v>41.59106826782227</v>
       </c>
       <c r="K89" t="n">
-        <v>285.7043762207031</v>
+        <v>23.72176170349121</v>
       </c>
       <c r="L89" t="n">
         <v>2926.4599609375</v>
@@ -3831,10 +3831,10 @@
         <v>43709</v>
       </c>
       <c r="B90" t="n">
-        <v>53.7313346862793</v>
+        <v>53.73132705688477</v>
       </c>
       <c r="C90" t="n">
-        <v>130.7293395996094</v>
+        <v>130.7293701171875</v>
       </c>
       <c r="D90" t="n">
         <v>60.48147583007812</v>
@@ -3843,22 +3843,22 @@
         <v>86.79550170898438</v>
       </c>
       <c r="F90" t="n">
-        <v>4.319096565246582</v>
+        <v>4.319097518920898</v>
       </c>
       <c r="G90" t="n">
-        <v>176.3905639648438</v>
+        <v>176.3905944824219</v>
       </c>
       <c r="H90" t="n">
-        <v>41779.83984375</v>
+        <v>28.98999977111816</v>
       </c>
       <c r="I90" t="n">
         <v>16.0580005645752</v>
       </c>
       <c r="J90" t="n">
-        <v>45.20540618896484</v>
+        <v>45.20539474487305</v>
       </c>
       <c r="K90" t="n">
-        <v>290.454345703125</v>
+        <v>23.38355445861816</v>
       </c>
       <c r="L90" t="n">
         <v>2976.739990234375</v>
@@ -3872,31 +3872,31 @@
         <v>59.67855834960938</v>
       </c>
       <c r="C91" t="n">
-        <v>134.8102416992188</v>
+        <v>134.8102264404297</v>
       </c>
       <c r="D91" t="n">
-        <v>62.34672927856445</v>
+        <v>62.34672546386719</v>
       </c>
       <c r="E91" t="n">
         <v>88.83300018310547</v>
       </c>
       <c r="F91" t="n">
-        <v>4.987791061401367</v>
+        <v>4.987790107727051</v>
       </c>
       <c r="G91" t="n">
         <v>189.8318634033203</v>
       </c>
       <c r="H91" t="n">
-        <v>42929.7421875</v>
+        <v>33.93000030517578</v>
       </c>
       <c r="I91" t="n">
         <v>20.99466705322266</v>
       </c>
       <c r="J91" t="n">
-        <v>49.59171295166016</v>
+        <v>49.59171676635742</v>
       </c>
       <c r="K91" t="n">
-        <v>282.1858215332031</v>
+        <v>24.80484390258789</v>
       </c>
       <c r="L91" t="n">
         <v>3037.56005859375</v>
@@ -3907,25 +3907,25 @@
         <v>43770</v>
       </c>
       <c r="B92" t="n">
-        <v>64.30686187744141</v>
+        <v>64.30685424804688</v>
       </c>
       <c r="C92" t="n">
-        <v>142.8264007568359</v>
+        <v>142.8263854980469</v>
       </c>
       <c r="D92" t="n">
-        <v>64.58988189697266</v>
+        <v>64.58987426757812</v>
       </c>
       <c r="E92" t="n">
         <v>90.04000091552734</v>
       </c>
       <c r="F92" t="n">
-        <v>5.381810665130615</v>
+        <v>5.381809234619141</v>
       </c>
       <c r="G92" t="n">
-        <v>199.7270965576172</v>
+        <v>199.7270812988281</v>
       </c>
       <c r="H92" t="n">
-        <v>42844.546875</v>
+        <v>39.15000152587891</v>
       </c>
       <c r="I92" t="n">
         <v>21.99600028991699</v>
@@ -3934,7 +3934,7 @@
         <v>51.20542907714844</v>
       </c>
       <c r="K92" t="n">
-        <v>291.86181640625</v>
+        <v>26.78347778320312</v>
       </c>
       <c r="L92" t="n">
         <v>3140.97998046875</v>
@@ -3945,34 +3945,34 @@
         <v>43800</v>
       </c>
       <c r="B93" t="n">
-        <v>70.65934753417969</v>
+        <v>70.65937042236328</v>
       </c>
       <c r="C93" t="n">
-        <v>148.7892150878906</v>
+        <v>148.7892761230469</v>
       </c>
       <c r="D93" t="n">
-        <v>66.33823394775391</v>
+        <v>66.33824157714844</v>
       </c>
       <c r="E93" t="n">
         <v>92.39199829101562</v>
       </c>
       <c r="F93" t="n">
-        <v>5.84266996383667</v>
+        <v>5.842668533325195</v>
       </c>
       <c r="G93" t="n">
-        <v>203.3028411865234</v>
+        <v>203.3028259277344</v>
       </c>
       <c r="H93" t="n">
-        <v>47835.0234375</v>
+        <v>45.86000061035156</v>
       </c>
       <c r="I93" t="n">
         <v>27.8886661529541</v>
       </c>
       <c r="J93" t="n">
-        <v>52.79319381713867</v>
+        <v>52.79319763183594</v>
       </c>
       <c r="K93" t="n">
-        <v>330.3896484375</v>
+        <v>27.03851890563965</v>
       </c>
       <c r="L93" t="n">
         <v>3230.780029296875</v>
@@ -3983,13 +3983,13 @@
         <v>43831</v>
       </c>
       <c r="B94" t="n">
-        <v>74.47565460205078</v>
+        <v>74.47563171386719</v>
       </c>
       <c r="C94" t="n">
-        <v>160.6112365722656</v>
+        <v>160.6112670898438</v>
       </c>
       <c r="D94" t="n">
-        <v>70.96372985839844</v>
+        <v>70.96372222900391</v>
       </c>
       <c r="E94" t="n">
         <v>100.4359970092773</v>
@@ -4001,16 +4001,16 @@
         <v>199.9945220947266</v>
       </c>
       <c r="H94" t="n">
-        <v>48349.36328125</v>
+        <v>47</v>
       </c>
       <c r="I94" t="n">
         <v>43.37133407592773</v>
       </c>
       <c r="J94" t="n">
-        <v>56.39212799072266</v>
+        <v>56.39213180541992</v>
       </c>
       <c r="K94" t="n">
-        <v>328.1026000976562</v>
+        <v>26.10933876037598</v>
       </c>
       <c r="L94" t="n">
         <v>3225.52001953125</v>
@@ -4021,10 +4021,10 @@
         <v>43862</v>
       </c>
       <c r="B95" t="n">
-        <v>65.93318939208984</v>
+        <v>65.93319702148438</v>
       </c>
       <c r="C95" t="n">
-        <v>153.273193359375</v>
+        <v>153.2732391357422</v>
       </c>
       <c r="D95" t="n">
         <v>66.33131408691406</v>
@@ -4036,10 +4036,10 @@
         <v>6.710043430328369</v>
       </c>
       <c r="G95" t="n">
-        <v>190.6440734863281</v>
+        <v>190.6441040039062</v>
       </c>
       <c r="H95" t="n">
-        <v>46463.40625</v>
+        <v>45.47999954223633</v>
       </c>
       <c r="I95" t="n">
         <v>44.53266525268555</v>
@@ -4048,7 +4048,7 @@
         <v>49.21491241455078</v>
       </c>
       <c r="K95" t="n">
-        <v>339.5377807617188</v>
+        <v>23.32523536682129</v>
       </c>
       <c r="L95" t="n">
         <v>2954.219970703125</v>
@@ -4059,13 +4059,13 @@
         <v>43891</v>
       </c>
       <c r="B96" t="n">
-        <v>61.33361053466797</v>
+        <v>61.33359909057617</v>
       </c>
       <c r="C96" t="n">
         <v>149.2051391601562</v>
       </c>
       <c r="D96" t="n">
-        <v>57.54986953735352</v>
+        <v>57.54987335205078</v>
       </c>
       <c r="E96" t="n">
         <v>97.48600006103516</v>
@@ -4074,19 +4074,19 @@
         <v>6.54929256439209</v>
       </c>
       <c r="G96" t="n">
-        <v>165.2175903320312</v>
+        <v>165.2176208496094</v>
       </c>
       <c r="H96" t="n">
-        <v>41236.3203125</v>
+        <v>45.47999954223633</v>
       </c>
       <c r="I96" t="n">
         <v>34.93333435058594</v>
       </c>
       <c r="J96" t="n">
-        <v>47.97391128540039</v>
+        <v>47.97390365600586</v>
       </c>
       <c r="K96" t="n">
-        <v>334.4359436035156</v>
+        <v>20.63097953796387</v>
       </c>
       <c r="L96" t="n">
         <v>2584.590087890625</v>
@@ -4097,10 +4097,10 @@
         <v>43922</v>
       </c>
       <c r="B97" t="n">
-        <v>70.86323547363281</v>
+        <v>70.86322784423828</v>
       </c>
       <c r="C97" t="n">
-        <v>169.5457000732422</v>
+        <v>169.545654296875</v>
       </c>
       <c r="D97" t="n">
         <v>66.70030212402344</v>
@@ -4109,13 +4109,13 @@
         <v>123.6999969482422</v>
       </c>
       <c r="F97" t="n">
-        <v>7.261863231658936</v>
+        <v>7.261862277984619</v>
       </c>
       <c r="G97" t="n">
-        <v>202.7679748535156</v>
+        <v>202.7679443359375</v>
       </c>
       <c r="H97" t="n">
-        <v>43179.3828125</v>
+        <v>52.38999938964844</v>
       </c>
       <c r="I97" t="n">
         <v>52.12533187866211</v>
@@ -4124,7 +4124,7 @@
         <v>53.16842269897461</v>
       </c>
       <c r="K97" t="n">
-        <v>366.8064270019531</v>
+        <v>23.63470077514648</v>
       </c>
       <c r="L97" t="n">
         <v>2912.429931640625</v>
@@ -4138,10 +4138,10 @@
         <v>76.89329528808594</v>
       </c>
       <c r="C98" t="n">
-        <v>173.8506622314453</v>
+        <v>173.8506774902344</v>
       </c>
       <c r="D98" t="n">
-        <v>71.00038909912109</v>
+        <v>71.00037384033203</v>
       </c>
       <c r="E98" t="n">
         <v>122.1184997558594</v>
@@ -4150,19 +4150,19 @@
         <v>8.820676803588867</v>
       </c>
       <c r="G98" t="n">
-        <v>222.95458984375</v>
+        <v>222.9546051025391</v>
       </c>
       <c r="H98" t="n">
-        <v>43783.890625</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="I98" t="n">
         <v>55.66666793823242</v>
       </c>
       <c r="J98" t="n">
-        <v>56.09851455688477</v>
+        <v>56.09851837158203</v>
       </c>
       <c r="K98" t="n">
-        <v>362.0954895019531</v>
+        <v>25.34452247619629</v>
       </c>
       <c r="L98" t="n">
         <v>3044.31005859375</v>
@@ -4176,31 +4176,31 @@
         <v>88.22629547119141</v>
       </c>
       <c r="C99" t="n">
-        <v>193.0715179443359</v>
+        <v>193.0714721679688</v>
       </c>
       <c r="D99" t="n">
-        <v>70.23416137695312</v>
+        <v>70.23418426513672</v>
       </c>
       <c r="E99" t="n">
         <v>137.9409942626953</v>
       </c>
       <c r="F99" t="n">
-        <v>9.443387985229492</v>
+        <v>9.443388938903809</v>
       </c>
       <c r="G99" t="n">
         <v>224.9158325195312</v>
       </c>
       <c r="H99" t="n">
-        <v>45902.30078125</v>
+        <v>52.61000061035156</v>
       </c>
       <c r="I99" t="n">
         <v>71.98733520507812</v>
       </c>
       <c r="J99" t="n">
-        <v>53.33504867553711</v>
+        <v>53.33504486083984</v>
       </c>
       <c r="K99" t="n">
-        <v>439.9142150878906</v>
+        <v>27.74537086486816</v>
       </c>
       <c r="L99" t="n">
         <v>3100.2900390625</v>
@@ -4211,34 +4211,34 @@
         <v>44013</v>
       </c>
       <c r="B100" t="n">
-        <v>102.7952423095703</v>
+        <v>102.7952575683594</v>
       </c>
       <c r="C100" t="n">
-        <v>194.4945220947266</v>
+        <v>194.4945526123047</v>
       </c>
       <c r="D100" t="n">
-        <v>73.69624328613281</v>
+        <v>73.69622802734375</v>
       </c>
       <c r="E100" t="n">
         <v>158.2339935302734</v>
       </c>
       <c r="F100" t="n">
-        <v>10.55399513244629</v>
+        <v>10.55399608612061</v>
       </c>
       <c r="G100" t="n">
-        <v>251.2634735107422</v>
+        <v>251.2634887695312</v>
       </c>
       <c r="H100" t="n">
-        <v>50336.046875</v>
+        <v>77.43000030517578</v>
       </c>
       <c r="I100" t="n">
         <v>95.38400268554688</v>
       </c>
       <c r="J100" t="n">
-        <v>42.54858779907227</v>
+        <v>42.54858016967773</v>
       </c>
       <c r="K100" t="n">
-        <v>471.1475524902344</v>
+        <v>27.84558868408203</v>
       </c>
       <c r="L100" t="n">
         <v>3271.1201171875</v>
@@ -4249,25 +4249,25 @@
         <v>44044</v>
       </c>
       <c r="B101" t="n">
-        <v>125.0575332641602</v>
+        <v>125.0575485229492</v>
       </c>
       <c r="C101" t="n">
         <v>214.4792327880859</v>
       </c>
       <c r="D101" t="n">
-        <v>80.70849609375</v>
+        <v>80.70850372314453</v>
       </c>
       <c r="E101" t="n">
         <v>172.5480041503906</v>
       </c>
       <c r="F101" t="n">
-        <v>13.29794883728027</v>
+        <v>13.29795169830322</v>
       </c>
       <c r="G101" t="n">
-        <v>290.4184875488281</v>
+        <v>290.4183959960938</v>
       </c>
       <c r="H101" t="n">
-        <v>46945.53515625</v>
+        <v>90.81999969482422</v>
       </c>
       <c r="I101" t="n">
         <v>166.1066741943359</v>
@@ -4276,7 +4276,7 @@
         <v>45.72748947143555</v>
       </c>
       <c r="K101" t="n">
-        <v>468.0595703125</v>
+        <v>30.51805686950684</v>
       </c>
       <c r="L101" t="n">
         <v>3500.31005859375</v>
@@ -4287,13 +4287,13 @@
         <v>44075</v>
       </c>
       <c r="B102" t="n">
-        <v>112.2358627319336</v>
+        <v>112.2358322143555</v>
       </c>
       <c r="C102" t="n">
         <v>200.0240173339844</v>
       </c>
       <c r="D102" t="n">
-        <v>72.58926391601562</v>
+        <v>72.58924865722656</v>
       </c>
       <c r="E102" t="n">
         <v>157.4364929199219</v>
@@ -4302,10 +4302,10 @@
         <v>13.4570837020874</v>
       </c>
       <c r="G102" t="n">
-        <v>259.4154052734375</v>
+        <v>259.4153747558594</v>
       </c>
       <c r="H102" t="n">
-        <v>50908.09375</v>
+        <v>81.98999786376953</v>
       </c>
       <c r="I102" t="n">
         <v>143.0033264160156</v>
@@ -4314,7 +4314,7 @@
         <v>46.47240829467773</v>
       </c>
       <c r="K102" t="n">
-        <v>451.2958984375</v>
+        <v>32.3194694519043</v>
       </c>
       <c r="L102" t="n">
         <v>3363</v>
@@ -4328,7 +4328,7 @@
         <v>105.5003509521484</v>
       </c>
       <c r="C103" t="n">
-        <v>192.5491180419922</v>
+        <v>192.5491485595703</v>
       </c>
       <c r="D103" t="n">
         <v>80.0438232421875</v>
@@ -4337,22 +4337,22 @@
         <v>151.8074951171875</v>
       </c>
       <c r="F103" t="n">
-        <v>12.46598720550537</v>
+        <v>12.46599102020264</v>
       </c>
       <c r="G103" t="n">
-        <v>260.6138610839844</v>
+        <v>260.6139526367188</v>
       </c>
       <c r="H103" t="n">
-        <v>49508.5703125</v>
+        <v>75.29000091552734</v>
       </c>
       <c r="I103" t="n">
         <v>129.3466644287109</v>
       </c>
       <c r="J103" t="n">
-        <v>39.74117660522461</v>
+        <v>39.74118804931641</v>
       </c>
       <c r="K103" t="n">
-        <v>521.438720703125</v>
+        <v>31.01629447937012</v>
       </c>
       <c r="L103" t="n">
         <v>3269.9599609375</v>
@@ -4363,10 +4363,10 @@
         <v>44136</v>
       </c>
       <c r="B104" t="n">
-        <v>115.5749130249023</v>
+        <v>115.5749359130859</v>
       </c>
       <c r="C104" t="n">
-        <v>204.1137542724609</v>
+        <v>204.1137084960938</v>
       </c>
       <c r="D104" t="n">
         <v>86.89315032958984</v>
@@ -4375,13 +4375,13 @@
         <v>158.4019927978516</v>
       </c>
       <c r="F104" t="n">
-        <v>13.328782081604</v>
+        <v>13.32878494262695</v>
       </c>
       <c r="G104" t="n">
-        <v>274.3424682617188</v>
+        <v>274.3424377441406</v>
       </c>
       <c r="H104" t="n">
-        <v>58343.13671875</v>
+        <v>92.66000366210938</v>
       </c>
       <c r="I104" t="n">
         <v>189.1999969482422</v>
@@ -4390,7 +4390,7 @@
         <v>43.70962142944336</v>
       </c>
       <c r="K104" t="n">
-        <v>496.7342834472656</v>
+        <v>35.6248779296875</v>
       </c>
       <c r="L104" t="n">
         <v>3621.6298828125</v>
@@ -4401,13 +4401,13 @@
         <v>44166</v>
       </c>
       <c r="B105" t="n">
-        <v>128.8167266845703</v>
+        <v>128.8167572021484</v>
       </c>
       <c r="C105" t="n">
-        <v>212.0753784179688</v>
+        <v>212.0753936767578</v>
       </c>
       <c r="D105" t="n">
-        <v>86.80598449707031</v>
+        <v>86.80597686767578</v>
       </c>
       <c r="E105" t="n">
         <v>162.8464965820312</v>
@@ -4416,19 +4416,19 @@
         <v>12.98799705505371</v>
       </c>
       <c r="G105" t="n">
-        <v>270.568603515625</v>
+        <v>270.5685424804688</v>
       </c>
       <c r="H105" t="n">
-        <v>72634.6015625</v>
+        <v>91.70999908447266</v>
       </c>
       <c r="I105" t="n">
         <v>235.2233276367188</v>
       </c>
       <c r="J105" t="n">
-        <v>45.03854370117188</v>
+        <v>45.03853988647461</v>
       </c>
       <c r="K105" t="n">
-        <v>499.3811645507812</v>
+        <v>39.17340850830078</v>
       </c>
       <c r="L105" t="n">
         <v>3756.070068359375</v>
@@ -4442,31 +4442,31 @@
         <v>128.1080780029297</v>
       </c>
       <c r="C106" t="n">
-        <v>221.1716613769531</v>
+        <v>221.1716766357422</v>
       </c>
       <c r="D106" t="n">
-        <v>90.50675964355469</v>
+        <v>90.50676727294922</v>
       </c>
       <c r="E106" t="n">
         <v>160.3099975585938</v>
       </c>
       <c r="F106" t="n">
-        <v>12.92308235168457</v>
+        <v>12.92308330535889</v>
       </c>
       <c r="G106" t="n">
-        <v>255.8792114257812</v>
+        <v>255.8792419433594</v>
       </c>
       <c r="H106" t="n">
-        <v>73531.3125</v>
+        <v>85.63999938964844</v>
       </c>
       <c r="I106" t="n">
         <v>264.510009765625</v>
       </c>
       <c r="J106" t="n">
-        <v>50.18244171142578</v>
+        <v>50.18243789672852</v>
       </c>
       <c r="K106" t="n">
-        <v>601.2867431640625</v>
+        <v>40.3051872253418</v>
       </c>
       <c r="L106" t="n">
         <v>3714.239990234375</v>
@@ -4477,34 +4477,34 @@
         <v>44228</v>
       </c>
       <c r="B107" t="n">
-        <v>117.8962936401367</v>
+        <v>117.8963165283203</v>
       </c>
       <c r="C107" t="n">
-        <v>222.0824737548828</v>
+        <v>222.0824890136719</v>
       </c>
       <c r="D107" t="n">
-        <v>100.1425704956055</v>
+        <v>100.1425628662109</v>
       </c>
       <c r="E107" t="n">
         <v>154.6464996337891</v>
       </c>
       <c r="F107" t="n">
-        <v>13.6441125869751</v>
+        <v>13.64411067962646</v>
       </c>
       <c r="G107" t="n">
-        <v>255.1759948730469</v>
+        <v>255.1760101318359</v>
       </c>
       <c r="H107" t="n">
-        <v>73979.671875</v>
+        <v>84.51000213623047</v>
       </c>
       <c r="I107" t="n">
         <v>225.1666717529297</v>
       </c>
       <c r="J107" t="n">
-        <v>55.28018188476562</v>
+        <v>55.28017807006836</v>
       </c>
       <c r="K107" t="n">
-        <v>584.5230102539062</v>
+        <v>42.03816986083984</v>
       </c>
       <c r="L107" t="n">
         <v>3811.14990234375</v>
@@ -4515,34 +4515,34 @@
         <v>44256</v>
       </c>
       <c r="B108" t="n">
-        <v>118.7616271972656</v>
+        <v>118.7616348266602</v>
       </c>
       <c r="C108" t="n">
         <v>225.3222503662109</v>
       </c>
       <c r="D108" t="n">
-        <v>102.153923034668</v>
+        <v>102.153938293457</v>
       </c>
       <c r="E108" t="n">
         <v>154.7039947509766</v>
       </c>
       <c r="F108" t="n">
-        <v>13.28432655334473</v>
+        <v>13.28432750701904</v>
       </c>
       <c r="G108" t="n">
-        <v>291.7358703613281</v>
+        <v>291.7358093261719</v>
       </c>
       <c r="H108" t="n">
-        <v>73317.65625</v>
+        <v>78.5</v>
       </c>
       <c r="I108" t="n">
         <v>222.6433258056641</v>
       </c>
       <c r="J108" t="n">
-        <v>58.20880508422852</v>
+        <v>58.20881271362305</v>
       </c>
       <c r="K108" t="n">
-        <v>538.2022705078125</v>
+        <v>41.80682754516602</v>
       </c>
       <c r="L108" t="n">
         <v>3972.889892578125</v>
@@ -4553,13 +4553,13 @@
         <v>44287</v>
       </c>
       <c r="B109" t="n">
-        <v>127.8133850097656</v>
+        <v>127.8133773803711</v>
       </c>
       <c r="C109" t="n">
-        <v>241.0050659179688</v>
+        <v>241.0050506591797</v>
       </c>
       <c r="D109" t="n">
-        <v>116.5658111572266</v>
+        <v>116.5657958984375</v>
       </c>
       <c r="E109" t="n">
         <v>173.3710021972656</v>
@@ -4568,19 +4568,19 @@
         <v>14.93762111663818</v>
       </c>
       <c r="G109" t="n">
-        <v>321.9960021972656</v>
+        <v>321.9960327148438</v>
       </c>
       <c r="H109" t="n">
-        <v>73407.6953125</v>
+        <v>81.62000274658203</v>
       </c>
       <c r="I109" t="n">
         <v>236.4799957275391</v>
       </c>
       <c r="J109" t="n">
-        <v>52.32426834106445</v>
+        <v>52.32425689697266</v>
       </c>
       <c r="K109" t="n">
-        <v>549.6722412109375</v>
+        <v>41.13418579101562</v>
       </c>
       <c r="L109" t="n">
         <v>4181.169921875</v>
@@ -4591,25 +4591,25 @@
         <v>44317</v>
       </c>
       <c r="B110" t="n">
-        <v>121.3591842651367</v>
+        <v>121.3591690063477</v>
       </c>
       <c r="C110" t="n">
-        <v>239.1668243408203</v>
+        <v>239.1668395996094</v>
       </c>
       <c r="D110" t="n">
-        <v>116.7317199707031</v>
+        <v>116.7317123413086</v>
       </c>
       <c r="E110" t="n">
         <v>161.1535034179688</v>
       </c>
       <c r="F110" t="n">
-        <v>16.16670417785645</v>
+        <v>16.16670036315918</v>
       </c>
       <c r="G110" t="n">
-        <v>325.6114196777344</v>
+        <v>325.6113891601562</v>
       </c>
       <c r="H110" t="n">
-        <v>72507.015625</v>
+        <v>80.08000183105469</v>
       </c>
       <c r="I110" t="n">
         <v>208.4066619873047</v>
@@ -4618,7 +4618,7 @@
         <v>52.27133941650391</v>
       </c>
       <c r="K110" t="n">
-        <v>547.758544921875</v>
+        <v>42.58858489990234</v>
       </c>
       <c r="L110" t="n">
         <v>4204.10986328125</v>
@@ -4629,10 +4629,10 @@
         <v>44348</v>
       </c>
       <c r="B111" t="n">
-        <v>133.3869781494141</v>
+        <v>133.386962890625</v>
       </c>
       <c r="C111" t="n">
-        <v>259.4934692382812</v>
+        <v>259.4933166503906</v>
       </c>
       <c r="D111" t="n">
         <v>120.9386901855469</v>
@@ -4641,22 +4641,22 @@
         <v>172.0079956054688</v>
       </c>
       <c r="F111" t="n">
-        <v>19.91127395629883</v>
+        <v>19.91127014160156</v>
       </c>
       <c r="G111" t="n">
-        <v>344.4113464355469</v>
+        <v>344.4113159179688</v>
       </c>
       <c r="H111" t="n">
-        <v>73008.953125</v>
+        <v>93.93000030517578</v>
       </c>
       <c r="I111" t="n">
         <v>226.5666656494141</v>
       </c>
       <c r="J111" t="n">
-        <v>51.37452697753906</v>
+        <v>51.37451934814453</v>
       </c>
       <c r="K111" t="n">
-        <v>516.78662109375</v>
+        <v>43.331787109375</v>
       </c>
       <c r="L111" t="n">
         <v>4297.5</v>
@@ -4667,34 +4667,34 @@
         <v>44378</v>
       </c>
       <c r="B112" t="n">
-        <v>142.0548095703125</v>
+        <v>142.0547790527344</v>
       </c>
       <c r="C112" t="n">
-        <v>272.9134216308594</v>
+        <v>272.9134521484375</v>
       </c>
       <c r="D112" t="n">
-        <v>133.4565582275391</v>
+        <v>133.4565887451172</v>
       </c>
       <c r="E112" t="n">
         <v>166.3795013427734</v>
       </c>
       <c r="F112" t="n">
-        <v>19.41007232666016</v>
+        <v>19.41006278991699</v>
       </c>
       <c r="G112" t="n">
-        <v>352.9197998046875</v>
+        <v>352.9198303222656</v>
       </c>
       <c r="H112" t="n">
-        <v>71018.625</v>
+        <v>106.1900024414062</v>
       </c>
       <c r="I112" t="n">
         <v>229.0666656494141</v>
       </c>
       <c r="J112" t="n">
-        <v>49.15994644165039</v>
+        <v>49.15994262695312</v>
       </c>
       <c r="K112" t="n">
-        <v>423.8712768554688</v>
+        <v>44.10965728759766</v>
       </c>
       <c r="L112" t="n">
         <v>4395.259765625</v>
@@ -4705,7 +4705,7 @@
         <v>44409</v>
       </c>
       <c r="B113" t="n">
-        <v>148.0906219482422</v>
+        <v>148.0905914306641</v>
       </c>
       <c r="C113" t="n">
         <v>289.7224731445312</v>
@@ -4717,22 +4717,22 @@
         <v>173.5395050048828</v>
       </c>
       <c r="F113" t="n">
-        <v>22.28683662414551</v>
+        <v>22.28683471679688</v>
       </c>
       <c r="G113" t="n">
-        <v>375.7808227539062</v>
+        <v>375.7809448242188</v>
       </c>
       <c r="H113" t="n">
-        <v>69390.1875</v>
+        <v>110.7200012207031</v>
       </c>
       <c r="I113" t="n">
         <v>245.2400054931641</v>
       </c>
       <c r="J113" t="n">
-        <v>49.79256439208984</v>
+        <v>49.79256057739258</v>
       </c>
       <c r="K113" t="n">
-        <v>425.8180847167969</v>
+        <v>45.18286514282227</v>
       </c>
       <c r="L113" t="n">
         <v>4522.68017578125</v>
@@ -4743,7 +4743,7 @@
         <v>44440</v>
       </c>
       <c r="B114" t="n">
-        <v>138.0150299072266</v>
+        <v>138.0150146484375</v>
       </c>
       <c r="C114" t="n">
         <v>270.5663146972656</v>
@@ -4755,22 +4755,22 @@
         <v>164.2519989013672</v>
       </c>
       <c r="F114" t="n">
-        <v>20.62515830993652</v>
+        <v>20.62515068054199</v>
       </c>
       <c r="G114" t="n">
-        <v>336.1702880859375</v>
+        <v>336.1702575683594</v>
       </c>
       <c r="H114" t="n">
-        <v>67356.6484375</v>
+        <v>102.9000015258789</v>
       </c>
       <c r="I114" t="n">
         <v>258.4933471679688</v>
       </c>
       <c r="J114" t="n">
-        <v>49.07412719726562</v>
+        <v>49.07413482666016</v>
       </c>
       <c r="K114" t="n">
-        <v>408.296875</v>
+        <v>44.38990020751953</v>
       </c>
       <c r="L114" t="n">
         <v>4307.5400390625</v>
@@ -4781,10 +4781,10 @@
         <v>44470</v>
       </c>
       <c r="B115" t="n">
-        <v>146.1105651855469</v>
+        <v>146.110595703125</v>
       </c>
       <c r="C115" t="n">
-        <v>318.2647705078125</v>
+        <v>318.2646789550781</v>
       </c>
       <c r="D115" t="n">
         <v>146.6505279541016</v>
@@ -4793,22 +4793,22 @@
         <v>168.6215057373047</v>
       </c>
       <c r="F115" t="n">
-        <v>25.45487785339355</v>
+        <v>25.45488548278809</v>
       </c>
       <c r="G115" t="n">
-        <v>320.5003051757812</v>
+        <v>320.5003662109375</v>
       </c>
       <c r="H115" t="n">
-        <v>63447.953125</v>
+        <v>120.2300033569336</v>
       </c>
       <c r="I115" t="n">
         <v>371.3333435058594</v>
       </c>
       <c r="J115" t="n">
-        <v>45.13199996948242</v>
+        <v>45.13200378417969</v>
       </c>
       <c r="K115" t="n">
-        <v>425.6410827636719</v>
+        <v>48.66841506958008</v>
       </c>
       <c r="L115" t="n">
         <v>4605.3798828125</v>
@@ -4819,34 +4819,34 @@
         <v>44501</v>
       </c>
       <c r="B116" t="n">
-        <v>161.4641265869141</v>
+        <v>161.4641418457031</v>
       </c>
       <c r="C116" t="n">
         <v>317.8566589355469</v>
       </c>
       <c r="D116" t="n">
-        <v>140.5599975585938</v>
+        <v>140.5599822998047</v>
       </c>
       <c r="E116" t="n">
         <v>175.3535003662109</v>
       </c>
       <c r="F116" t="n">
-        <v>32.53270721435547</v>
+        <v>32.53269958496094</v>
       </c>
       <c r="G116" t="n">
-        <v>321.3819580078125</v>
+        <v>321.3819274902344</v>
       </c>
       <c r="H116" t="n">
-        <v>64811.45703125</v>
+        <v>158.3699951171875</v>
       </c>
       <c r="I116" t="n">
         <v>381.586669921875</v>
       </c>
       <c r="J116" t="n">
-        <v>45.63134765625</v>
+        <v>45.63135147094727</v>
       </c>
       <c r="K116" t="n">
-        <v>406.5270690917969</v>
+        <v>50.68319702148438</v>
       </c>
       <c r="L116" t="n">
         <v>4567</v>
@@ -4860,7 +4860,7 @@
         <v>173.4494476318359</v>
       </c>
       <c r="C117" t="n">
-        <v>323.3659973144531</v>
+        <v>323.365966796875</v>
       </c>
       <c r="D117" t="n">
         <v>143.4866333007812</v>
@@ -4869,22 +4869,22 @@
         <v>166.7169952392578</v>
       </c>
       <c r="F117" t="n">
-        <v>29.28561210632324</v>
+        <v>29.28560829162598</v>
       </c>
       <c r="G117" t="n">
         <v>333.1590881347656</v>
       </c>
       <c r="H117" t="n">
-        <v>71495.8515625</v>
+        <v>143.8999938964844</v>
       </c>
       <c r="I117" t="n">
         <v>352.260009765625</v>
       </c>
       <c r="J117" t="n">
-        <v>47.7645149230957</v>
+        <v>47.76452255249023</v>
       </c>
       <c r="K117" t="n">
-        <v>404.226318359375</v>
+        <v>61.30045700073242</v>
       </c>
       <c r="L117" t="n">
         <v>4766.18017578125</v>
@@ -4895,10 +4895,10 @@
         <v>44562</v>
       </c>
       <c r="B118" t="n">
-        <v>170.7241516113281</v>
+        <v>170.7241668701172</v>
       </c>
       <c r="C118" t="n">
-        <v>299.0020141601562</v>
+        <v>299.001953125</v>
       </c>
       <c r="D118" t="n">
         <v>134.0281219482422</v>
@@ -4910,19 +4910,19 @@
         <v>24.38160514831543</v>
       </c>
       <c r="G118" t="n">
-        <v>310.2882080078125</v>
+        <v>310.2881469726562</v>
       </c>
       <c r="H118" t="n">
-        <v>66930.3515625</v>
+        <v>114.25</v>
       </c>
       <c r="I118" t="n">
         <v>312.239990234375</v>
       </c>
       <c r="J118" t="n">
-        <v>45.27890396118164</v>
+        <v>45.27891159057617</v>
       </c>
       <c r="K118" t="n">
-        <v>429.5985107421875</v>
+        <v>53.97382736206055</v>
       </c>
       <c r="L118" t="n">
         <v>4515.5498046875</v>
@@ -4936,7 +4936,7 @@
         <v>161.4937896728516</v>
       </c>
       <c r="C119" t="n">
-        <v>287.8755798339844</v>
+        <v>287.8755187988281</v>
       </c>
       <c r="D119" t="n">
         <v>133.7839660644531</v>
@@ -4945,22 +4945,22 @@
         <v>153.5630035400391</v>
       </c>
       <c r="F119" t="n">
-        <v>24.28103828430176</v>
+        <v>24.28103637695312</v>
       </c>
       <c r="G119" t="n">
         <v>209.0279693603516</v>
       </c>
       <c r="H119" t="n">
-        <v>65651.9921875</v>
+        <v>123.3399963378906</v>
       </c>
       <c r="I119" t="n">
         <v>290.1433410644531</v>
       </c>
       <c r="J119" t="n">
-        <v>44.57715225219727</v>
+        <v>44.5771484375</v>
       </c>
       <c r="K119" t="n">
-        <v>384.012939453125</v>
+        <v>54.11753463745117</v>
       </c>
       <c r="L119" t="n">
         <v>4373.93994140625</v>
@@ -4971,10 +4971,10 @@
         <v>44621</v>
       </c>
       <c r="B120" t="n">
-        <v>170.7754211425781</v>
+        <v>170.7754516601562</v>
       </c>
       <c r="C120" t="n">
-        <v>297.0478515625</v>
+        <v>297.0478210449219</v>
       </c>
       <c r="D120" t="n">
         <v>137.7566375732422</v>
@@ -4983,13 +4983,13 @@
         <v>162.9974975585938</v>
       </c>
       <c r="F120" t="n">
-        <v>27.17430305480957</v>
+        <v>27.17430114746094</v>
       </c>
       <c r="G120" t="n">
-        <v>220.2505187988281</v>
+        <v>220.2505035400391</v>
       </c>
       <c r="H120" t="n">
-        <v>63880.35546875</v>
+        <v>109.3399963378906</v>
       </c>
       <c r="I120" t="n">
         <v>359.2000122070312</v>
@@ -4998,7 +4998,7 @@
         <v>46.31538391113281</v>
       </c>
       <c r="K120" t="n">
-        <v>341.1625366210938</v>
+        <v>58.40113067626953</v>
       </c>
       <c r="L120" t="n">
         <v>4530.41015625</v>
@@ -5012,7 +5012,7 @@
         <v>154.1878509521484</v>
       </c>
       <c r="C121" t="n">
-        <v>267.3825378417969</v>
+        <v>267.3824768066406</v>
       </c>
       <c r="D121" t="n">
         <v>113.0339050292969</v>
@@ -5024,19 +5024,19 @@
         <v>18.47107315063477</v>
       </c>
       <c r="G121" t="n">
-        <v>198.5681915283203</v>
+        <v>198.5681762695312</v>
       </c>
       <c r="H121" t="n">
-        <v>61861.1640625</v>
+        <v>85.51999664306641</v>
       </c>
       <c r="I121" t="n">
         <v>290.2533264160156</v>
       </c>
       <c r="J121" t="n">
-        <v>40.73622512817383</v>
+        <v>40.73623275756836</v>
       </c>
       <c r="K121" t="n">
-        <v>344.0800170898438</v>
+        <v>51.41817855834961</v>
       </c>
       <c r="L121" t="n">
         <v>4131.93017578125</v>
@@ -5047,34 +5047,34 @@
         <v>44682</v>
       </c>
       <c r="B122" t="n">
-        <v>145.7852478027344</v>
+        <v>145.7852172851562</v>
       </c>
       <c r="C122" t="n">
         <v>262.5490112304688</v>
       </c>
       <c r="D122" t="n">
-        <v>112.6896896362305</v>
+        <v>112.6896820068359</v>
       </c>
       <c r="E122" t="n">
         <v>120.2095031738281</v>
       </c>
       <c r="F122" t="n">
-        <v>18.59556579589844</v>
+        <v>18.59556198120117</v>
       </c>
       <c r="G122" t="n">
-        <v>191.802978515625</v>
+        <v>191.8029479980469</v>
       </c>
       <c r="H122" t="n">
-        <v>61861.1640625</v>
+        <v>101.8600006103516</v>
       </c>
       <c r="I122" t="n">
         <v>252.7533264160156</v>
       </c>
       <c r="J122" t="n">
-        <v>41.84003067016602</v>
+        <v>41.84002685546875</v>
       </c>
       <c r="K122" t="n">
-        <v>332.0408325195312</v>
+        <v>53.80550384521484</v>
       </c>
       <c r="L122" t="n">
         <v>4132.14990234375</v>
@@ -5088,7 +5088,7 @@
         <v>133.9139709472656</v>
       </c>
       <c r="C123" t="n">
-        <v>248.0246124267578</v>
+        <v>248.0245971679688</v>
       </c>
       <c r="D123" t="n">
         <v>107.9359130859375</v>
@@ -5097,22 +5097,22 @@
         <v>106.2099990844727</v>
       </c>
       <c r="F123" t="n">
-        <v>15.10013484954834</v>
+        <v>15.10013580322266</v>
       </c>
       <c r="G123" t="n">
-        <v>159.7202453613281</v>
+        <v>159.7202606201172</v>
       </c>
       <c r="H123" t="n">
-        <v>52635.71484375</v>
+        <v>76.47000122070312</v>
       </c>
       <c r="I123" t="n">
         <v>224.4733276367188</v>
       </c>
       <c r="J123" t="n">
-        <v>35.23717498779297</v>
+        <v>35.23717880249023</v>
       </c>
       <c r="K123" t="n">
-        <v>324.7109985351562</v>
+        <v>45.43112564086914</v>
       </c>
       <c r="L123" t="n">
         <v>3785.3798828125</v>
@@ -5123,34 +5123,34 @@
         <v>44743</v>
       </c>
       <c r="B124" t="n">
-        <v>159.1746826171875</v>
+        <v>159.1746520996094</v>
       </c>
       <c r="C124" t="n">
-        <v>271.1149597167969</v>
+        <v>271.1148986816406</v>
       </c>
       <c r="D124" t="n">
-        <v>115.2235717773438</v>
+        <v>115.2235565185547</v>
       </c>
       <c r="E124" t="n">
         <v>134.9499969482422</v>
       </c>
       <c r="F124" t="n">
-        <v>18.09247207641602</v>
+        <v>18.09247398376465</v>
       </c>
       <c r="G124" t="n">
         <v>157.5906524658203</v>
       </c>
       <c r="H124" t="n">
-        <v>56698.8125</v>
+        <v>94.47000122070312</v>
       </c>
       <c r="I124" t="n">
         <v>297.1499938964844</v>
       </c>
       <c r="J124" t="n">
-        <v>34.20107269287109</v>
+        <v>34.20106506347656</v>
       </c>
       <c r="K124" t="n">
-        <v>281.0985717773438</v>
+        <v>50.07607269287109</v>
       </c>
       <c r="L124" t="n">
         <v>4130.2900390625</v>
@@ -5164,31 +5164,31 @@
         <v>154.2071380615234</v>
       </c>
       <c r="C125" t="n">
-        <v>253.0415802001953</v>
+        <v>253.0415344238281</v>
       </c>
       <c r="D125" t="n">
-        <v>107.1999282836914</v>
+        <v>107.1999206542969</v>
       </c>
       <c r="E125" t="n">
         <v>126.7699966430664</v>
       </c>
       <c r="F125" t="n">
-        <v>15.03538608551025</v>
+        <v>15.0353889465332</v>
       </c>
       <c r="G125" t="n">
         <v>161.3842926025391</v>
       </c>
       <c r="H125" t="n">
-        <v>55128.98046875</v>
+        <v>84.87000274658203</v>
       </c>
       <c r="I125" t="n">
         <v>275.6099853515625</v>
       </c>
       <c r="J125" t="n">
-        <v>30.36957168579102</v>
+        <v>30.36957359313965</v>
       </c>
       <c r="K125" t="n">
-        <v>299.7896118164062</v>
+        <v>46.67488098144531</v>
       </c>
       <c r="L125" t="n">
         <v>3955</v>
@@ -5199,34 +5199,34 @@
         <v>44805</v>
       </c>
       <c r="B126" t="n">
-        <v>135.5515899658203</v>
+        <v>135.5516510009766</v>
       </c>
       <c r="C126" t="n">
-        <v>225.3924865722656</v>
+        <v>225.3924560546875</v>
       </c>
       <c r="D126" t="n">
-        <v>94.7484130859375</v>
+        <v>94.74839782714844</v>
       </c>
       <c r="E126" t="n">
         <v>113</v>
       </c>
       <c r="F126" t="n">
-        <v>12.09545421600342</v>
+        <v>12.09545612335205</v>
       </c>
       <c r="G126" t="n">
         <v>134.3928375244141</v>
       </c>
       <c r="H126" t="n">
-        <v>49371.23046875</v>
+        <v>63.36000061035156</v>
       </c>
       <c r="I126" t="n">
         <v>265.25</v>
       </c>
       <c r="J126" t="n">
-        <v>24.51829528808594</v>
+        <v>24.51829719543457</v>
       </c>
       <c r="K126" t="n">
-        <v>244.0829925537109</v>
+        <v>41.87031173706055</v>
       </c>
       <c r="L126" t="n">
         <v>3585.6201171875</v>
@@ -5240,31 +5240,31 @@
         <v>150.4014892578125</v>
       </c>
       <c r="C127" t="n">
-        <v>224.6473388671875</v>
+        <v>224.6472930908203</v>
       </c>
       <c r="D127" t="n">
-        <v>93.61914825439453</v>
+        <v>93.61915588378906</v>
       </c>
       <c r="E127" t="n">
         <v>102.4400024414062</v>
       </c>
       <c r="F127" t="n">
-        <v>13.44858264923096</v>
+        <v>13.44858360290527</v>
       </c>
       <c r="G127" t="n">
         <v>92.27621459960938</v>
       </c>
       <c r="H127" t="n">
-        <v>55228.83984375</v>
+        <v>60.06000137329102</v>
       </c>
       <c r="I127" t="n">
         <v>227.5399932861328</v>
       </c>
       <c r="J127" t="n">
-        <v>27.04909324645996</v>
+        <v>27.04909515380859</v>
       </c>
       <c r="K127" t="n">
-        <v>188.3763885498047</v>
+        <v>44.33249664306641</v>
       </c>
       <c r="L127" t="n">
         <v>3871.97998046875</v>
@@ -5275,34 +5275,34 @@
         <v>44866</v>
       </c>
       <c r="B128" t="n">
-        <v>145.43408203125</v>
+        <v>145.4341430664062</v>
       </c>
       <c r="C128" t="n">
-        <v>247.6114196777344</v>
+        <v>247.6114044189453</v>
       </c>
       <c r="D128" t="n">
-        <v>100.0380630493164</v>
+        <v>100.0380706787109</v>
       </c>
       <c r="E128" t="n">
         <v>96.54000091552734</v>
       </c>
       <c r="F128" t="n">
-        <v>16.86660957336426</v>
+        <v>16.86660575866699</v>
       </c>
       <c r="G128" t="n">
-        <v>116.979606628418</v>
+        <v>116.9795913696289</v>
       </c>
       <c r="H128" t="n">
-        <v>57832.21875</v>
+        <v>77.62999725341797</v>
       </c>
       <c r="I128" t="n">
         <v>194.6999969482422</v>
       </c>
       <c r="J128" t="n">
-        <v>28.99583435058594</v>
+        <v>28.99583053588867</v>
       </c>
       <c r="K128" t="n">
-        <v>263.1405029296875</v>
+        <v>51.96234130859375</v>
       </c>
       <c r="L128" t="n">
         <v>4080.110107421875</v>
@@ -5316,7 +5316,7 @@
         <v>127.6515045166016</v>
       </c>
       <c r="C129" t="n">
-        <v>232.7434844970703</v>
+        <v>232.7435150146484</v>
       </c>
       <c r="D129" t="n">
         <v>87.39835357666016</v>
@@ -5325,22 +5325,22 @@
         <v>84</v>
       </c>
       <c r="F129" t="n">
-        <v>14.56530380249023</v>
+        <v>14.5653018951416</v>
       </c>
       <c r="G129" t="n">
-        <v>119.198356628418</v>
+        <v>119.1983489990234</v>
       </c>
       <c r="H129" t="n">
-        <v>51738.22265625</v>
+        <v>64.76999664306641</v>
       </c>
       <c r="I129" t="n">
         <v>123.1800003051758</v>
       </c>
       <c r="J129" t="n">
-        <v>25.48586082458496</v>
+        <v>25.48586273193359</v>
       </c>
       <c r="K129" t="n">
-        <v>306.0199890136719</v>
+        <v>53.16610717773438</v>
       </c>
       <c r="L129" t="n">
         <v>3839.5</v>
@@ -5351,34 +5351,34 @@
         <v>44927</v>
       </c>
       <c r="B130" t="n">
-        <v>141.7597045898438</v>
+        <v>141.7596740722656</v>
       </c>
       <c r="C130" t="n">
-        <v>240.4976959228516</v>
+        <v>240.4977416992188</v>
       </c>
       <c r="D130" t="n">
-        <v>97.9083251953125</v>
+        <v>97.90831756591797</v>
       </c>
       <c r="E130" t="n">
         <v>103.129997253418</v>
       </c>
       <c r="F130" t="n">
-        <v>19.47189903259277</v>
+        <v>19.47189712524414</v>
       </c>
       <c r="G130" t="n">
         <v>147.5567474365234</v>
       </c>
       <c r="H130" t="n">
-        <v>57445.33203125</v>
+        <v>75.15000152587891</v>
       </c>
       <c r="I130" t="n">
         <v>173.2200012207031</v>
       </c>
       <c r="J130" t="n">
-        <v>27.25049209594727</v>
+        <v>27.25048828125</v>
       </c>
       <c r="K130" t="n">
-        <v>368.6986999511719</v>
+        <v>55.62696075439453</v>
       </c>
       <c r="L130" t="n">
         <v>4076.60009765625</v>
@@ -5395,19 +5395,19 @@
         <v>242.66650390625</v>
       </c>
       <c r="D131" t="n">
-        <v>89.21110534667969</v>
+        <v>89.21108245849609</v>
       </c>
       <c r="E131" t="n">
         <v>94.23000335693359</v>
       </c>
       <c r="F131" t="n">
-        <v>23.13863563537598</v>
+        <v>23.13863945007324</v>
       </c>
       <c r="G131" t="n">
-        <v>173.2804107666016</v>
+        <v>173.2803649902344</v>
       </c>
       <c r="H131" t="n">
-        <v>56696.86328125</v>
+        <v>78.58000183105469</v>
       </c>
       <c r="I131" t="n">
         <v>205.7100067138672</v>
@@ -5416,7 +5416,7 @@
         <v>24.33236312866211</v>
       </c>
       <c r="K131" t="n">
-        <v>331.4622497558594</v>
+        <v>56.50937652587891</v>
       </c>
       <c r="L131" t="n">
         <v>3970.14990234375</v>
@@ -5433,28 +5433,28 @@
         <v>280.4937133789062</v>
       </c>
       <c r="D132" t="n">
-        <v>102.7522430419922</v>
+        <v>102.7522354125977</v>
       </c>
       <c r="E132" t="n">
         <v>103.2900009155273</v>
       </c>
       <c r="F132" t="n">
-        <v>27.68914031982422</v>
+        <v>27.68914413452148</v>
       </c>
       <c r="G132" t="n">
-        <v>209.9293670654297</v>
+        <v>209.9293518066406</v>
       </c>
       <c r="H132" t="n">
-        <v>60224.6171875</v>
+        <v>98.01000213623047</v>
       </c>
       <c r="I132" t="n">
         <v>207.4600067138672</v>
       </c>
       <c r="J132" t="n">
-        <v>31.88681221008301</v>
+        <v>31.88681030273438</v>
       </c>
       <c r="K132" t="n">
-        <v>372.1715087890625</v>
+        <v>61.44130325317383</v>
       </c>
       <c r="L132" t="n">
         <v>4109.31005859375</v>
@@ -5465,7 +5465,7 @@
         <v>45017</v>
       </c>
       <c r="B133" t="n">
-        <v>166.9589385986328</v>
+        <v>166.9589691162109</v>
       </c>
       <c r="C133" t="n">
         <v>298.9403686523438</v>
@@ -5477,22 +5477,22 @@
         <v>105.4499969482422</v>
       </c>
       <c r="F133" t="n">
-        <v>27.66123008728027</v>
+        <v>27.66123580932617</v>
       </c>
       <c r="G133" t="n">
         <v>238.0401153564453</v>
       </c>
       <c r="H133" t="n">
-        <v>61636.140625</v>
+        <v>89.37000274658203</v>
       </c>
       <c r="I133" t="n">
         <v>164.3099975585938</v>
       </c>
       <c r="J133" t="n">
-        <v>30.31541061401367</v>
+        <v>30.3154125213623</v>
       </c>
       <c r="K133" t="n">
-        <v>332.2340087890625</v>
+        <v>60.00090789794922</v>
       </c>
       <c r="L133" t="n">
         <v>4169.47998046875</v>
@@ -5515,22 +5515,22 @@
         <v>120.5800018310547</v>
       </c>
       <c r="F134" t="n">
-        <v>37.71432876586914</v>
+        <v>37.71432495117188</v>
       </c>
       <c r="G134" t="n">
-        <v>262.2086486816406</v>
+        <v>262.2086181640625</v>
       </c>
       <c r="H134" t="n">
-        <v>67188.09375</v>
+        <v>118.2099990844727</v>
       </c>
       <c r="I134" t="n">
         <v>203.9299926757812</v>
       </c>
       <c r="J134" t="n">
-        <v>30.81196403503418</v>
+        <v>30.81196212768555</v>
       </c>
       <c r="K134" t="n">
-        <v>301.7593383789062</v>
+        <v>77.37961578369141</v>
       </c>
       <c r="L134" t="n">
         <v>4179.830078125</v>
@@ -5544,22 +5544,22 @@
         <v>191.1234588623047</v>
       </c>
       <c r="C135" t="n">
-        <v>332.0435485839844</v>
+        <v>332.0434875488281</v>
       </c>
       <c r="D135" t="n">
-        <v>118.5716934204102</v>
+        <v>118.5717086791992</v>
       </c>
       <c r="E135" t="n">
         <v>130.3600006103516</v>
       </c>
       <c r="F135" t="n">
-        <v>42.17256164550781</v>
+        <v>42.17255783081055</v>
       </c>
       <c r="G135" t="n">
-        <v>284.2574768066406</v>
+        <v>284.2575378417969</v>
       </c>
       <c r="H135" t="n">
-        <v>68279.953125</v>
+        <v>113.9100036621094</v>
       </c>
       <c r="I135" t="n">
         <v>261.7699890136719</v>
@@ -5568,7 +5568,7 @@
         <v>32.77201080322266</v>
       </c>
       <c r="K135" t="n">
-        <v>322.1615905761719</v>
+        <v>83.51773834228516</v>
       </c>
       <c r="L135" t="n">
         <v>4450.3798828125</v>
@@ -5579,13 +5579,13 @@
         <v>45108</v>
       </c>
       <c r="B136" t="n">
-        <v>193.5670623779297</v>
+        <v>193.5670471191406</v>
       </c>
       <c r="C136" t="n">
-        <v>327.538818359375</v>
+        <v>327.5388793945312</v>
       </c>
       <c r="D136" t="n">
-        <v>131.4689636230469</v>
+        <v>131.4689788818359</v>
       </c>
       <c r="E136" t="n">
         <v>133.6799926757812</v>
@@ -5594,19 +5594,19 @@
         <v>46.58601379394531</v>
       </c>
       <c r="G136" t="n">
-        <v>315.5775451660156</v>
+        <v>315.5775146484375</v>
       </c>
       <c r="H136" t="n">
-        <v>66010.25</v>
+        <v>114.4000015258789</v>
       </c>
       <c r="I136" t="n">
         <v>267.4299926757812</v>
       </c>
       <c r="J136" t="n">
-        <v>35.05546569824219</v>
+        <v>35.05546951293945</v>
       </c>
       <c r="K136" t="n">
-        <v>344.3126220703125</v>
+        <v>86.52365875244141</v>
       </c>
       <c r="L136" t="n">
         <v>4588.9599609375</v>
@@ -5617,34 +5617,34 @@
         <v>45139</v>
       </c>
       <c r="B137" t="n">
-        <v>185.3629302978516</v>
+        <v>185.3629455566406</v>
       </c>
       <c r="C137" t="n">
         <v>320.259033203125</v>
       </c>
       <c r="D137" t="n">
-        <v>134.8864440917969</v>
+        <v>134.886474609375</v>
       </c>
       <c r="E137" t="n">
         <v>138.0099945068359</v>
       </c>
       <c r="F137" t="n">
-        <v>49.2039794921875</v>
+        <v>49.20398330688477</v>
       </c>
       <c r="G137" t="n">
         <v>293.0830078125</v>
       </c>
       <c r="H137" t="n">
-        <v>63267.69921875</v>
+        <v>105.7200012207031</v>
       </c>
       <c r="I137" t="n">
         <v>258.0799865722656</v>
       </c>
       <c r="J137" t="n">
-        <v>34.56194686889648</v>
+        <v>34.56195068359375</v>
       </c>
       <c r="K137" t="n">
-        <v>315.7494506835938</v>
+        <v>88.85752868652344</v>
       </c>
       <c r="L137" t="n">
         <v>4507.66015625</v>
@@ -5655,34 +5655,34 @@
         <v>45170</v>
       </c>
       <c r="B138" t="n">
-        <v>168.9252777099609</v>
+        <v>168.92529296875</v>
       </c>
       <c r="C138" t="n">
-        <v>308.52392578125</v>
+        <v>308.5238647460938</v>
       </c>
       <c r="D138" t="n">
-        <v>129.6265258789062</v>
+        <v>129.6264953613281</v>
       </c>
       <c r="E138" t="n">
         <v>127.120002746582</v>
       </c>
       <c r="F138" t="n">
-        <v>43.36947250366211</v>
+        <v>43.36946868896484</v>
       </c>
       <c r="G138" t="n">
         <v>297.3619689941406</v>
       </c>
       <c r="H138" t="n">
-        <v>65024.5078125</v>
+        <v>102.8199996948242</v>
       </c>
       <c r="I138" t="n">
         <v>250.2200012207031</v>
       </c>
       <c r="J138" t="n">
-        <v>34.96520233154297</v>
+        <v>34.96520614624023</v>
       </c>
       <c r="K138" t="n">
-        <v>297.4845581054688</v>
+        <v>80.40529632568359</v>
       </c>
       <c r="L138" t="n">
         <v>4288.0498046875</v>
@@ -5696,10 +5696,10 @@
         <v>168.4911499023438</v>
       </c>
       <c r="C139" t="n">
-        <v>330.3721923828125</v>
+        <v>330.3721313476562</v>
       </c>
       <c r="D139" t="n">
-        <v>122.9104232788086</v>
+        <v>122.9104156494141</v>
       </c>
       <c r="E139" t="n">
         <v>133.0899963378906</v>
@@ -5711,16 +5711,16 @@
         <v>298.4118957519531</v>
       </c>
       <c r="H139" t="n">
-        <v>63598.5234375</v>
+        <v>98.5</v>
       </c>
       <c r="I139" t="n">
         <v>200.8399963378906</v>
       </c>
       <c r="J139" t="n">
-        <v>35.89957809448242</v>
+        <v>35.89957427978516</v>
       </c>
       <c r="K139" t="n">
-        <v>280.9684448242188</v>
+        <v>81.44983673095703</v>
       </c>
       <c r="L139" t="n">
         <v>4193.7998046875</v>
@@ -5731,25 +5731,25 @@
         <v>45231</v>
       </c>
       <c r="B140" t="n">
-        <v>187.662109375</v>
+        <v>187.6620635986328</v>
       </c>
       <c r="C140" t="n">
-        <v>370.9898681640625</v>
+        <v>370.9898986816406</v>
       </c>
       <c r="D140" t="n">
-        <v>131.2807312011719</v>
+        <v>131.28076171875</v>
       </c>
       <c r="E140" t="n">
         <v>146.0899963378906</v>
       </c>
       <c r="F140" t="n">
-        <v>46.63072967529297</v>
+        <v>46.63072204589844</v>
       </c>
       <c r="G140" t="n">
-        <v>324.0463562011719</v>
+        <v>324.0464477539062</v>
       </c>
       <c r="H140" t="n">
-        <v>69207.3671875</v>
+        <v>121.1600036621094</v>
       </c>
       <c r="I140" t="n">
         <v>240.0800018310547</v>
@@ -5758,7 +5758,7 @@
         <v>44.1092529296875</v>
       </c>
       <c r="K140" t="n">
-        <v>317.6925048828125</v>
+        <v>89.61640930175781</v>
       </c>
       <c r="L140" t="n">
         <v>4567.7998046875</v>
@@ -5769,10 +5769,10 @@
         <v>45261</v>
       </c>
       <c r="B141" t="n">
-        <v>190.2110137939453</v>
+        <v>190.2110290527344</v>
       </c>
       <c r="C141" t="n">
-        <v>368.1798706054688</v>
+        <v>368.1799011230469</v>
       </c>
       <c r="D141" t="n">
         <v>138.3732757568359</v>
@@ -5781,13 +5781,13 @@
         <v>151.9400024414062</v>
       </c>
       <c r="F141" t="n">
-        <v>49.37887954711914</v>
+        <v>49.37887573242188</v>
       </c>
       <c r="G141" t="n">
         <v>350.6020202636719</v>
       </c>
       <c r="H141" t="n">
-        <v>74979.4453125</v>
+        <v>147.4100036621094</v>
       </c>
       <c r="I141" t="n">
         <v>248.4799957275391</v>
@@ -5796,7 +5796,7 @@
         <v>49.58590316772461</v>
       </c>
       <c r="K141" t="n">
-        <v>285.2431945800781</v>
+        <v>108.5568161010742</v>
       </c>
       <c r="L141" t="n">
         <v>4769.830078125</v>
@@ -5810,22 +5810,22 @@
         <v>182.1789245605469</v>
       </c>
       <c r="C142" t="n">
-        <v>389.2696228027344</v>
+        <v>389.2697143554688</v>
       </c>
       <c r="D142" t="n">
-        <v>138.7794036865234</v>
+        <v>138.7794189453125</v>
       </c>
       <c r="E142" t="n">
         <v>155.1999969482422</v>
       </c>
       <c r="F142" t="n">
-        <v>61.34919357299805</v>
+        <v>61.34918975830078</v>
       </c>
       <c r="G142" t="n">
-        <v>386.4388122558594</v>
+        <v>386.4388427734375</v>
       </c>
       <c r="H142" t="n">
-        <v>69439.5625</v>
+        <v>167.6900024414062</v>
       </c>
       <c r="I142" t="n">
         <v>187.2899932861328</v>
@@ -5834,7 +5834,7 @@
         <v>42.51066207885742</v>
       </c>
       <c r="K142" t="n">
-        <v>262.8978271484375</v>
+        <v>114.7565765380859</v>
       </c>
       <c r="L142" t="n">
         <v>4845.64990234375</v>
@@ -5848,10 +5848,10 @@
         <v>178.80078125</v>
       </c>
       <c r="C143" t="n">
-        <v>405.742919921875</v>
+        <v>405.7428588867188</v>
       </c>
       <c r="D143" t="n">
-        <v>137.1548767089844</v>
+        <v>137.1548919677734</v>
       </c>
       <c r="E143" t="n">
         <v>176.7599945068359</v>
@@ -5863,7 +5863,7 @@
         <v>485.9953002929688</v>
       </c>
       <c r="H143" t="n">
-        <v>70108.1640625</v>
+        <v>192.5299987792969</v>
       </c>
       <c r="I143" t="n">
         <v>201.8800048828125</v>
@@ -5872,7 +5872,7 @@
         <v>42.60557556152344</v>
       </c>
       <c r="K143" t="n">
-        <v>269.3099975585938</v>
+        <v>126.4744033813477</v>
       </c>
       <c r="L143" t="n">
         <v>5096.27001953125</v>
@@ -5886,22 +5886,22 @@
         <v>169.6307525634766</v>
       </c>
       <c r="C144" t="n">
-        <v>412.6876831054688</v>
+        <v>412.6877136230469</v>
       </c>
       <c r="D144" t="n">
-        <v>149.50732421875</v>
+        <v>149.5073394775391</v>
       </c>
       <c r="E144" t="n">
         <v>180.3800048828125</v>
       </c>
       <c r="F144" t="n">
-        <v>90.09909057617188</v>
+        <v>90.09910583496094</v>
       </c>
       <c r="G144" t="n">
         <v>481.4837036132812</v>
       </c>
       <c r="H144" t="n">
-        <v>79062.1875</v>
+        <v>180.4900054931641</v>
       </c>
       <c r="I144" t="n">
         <v>175.7899932861328</v>
@@ -5910,7 +5910,7 @@
         <v>43.71401214599609</v>
       </c>
       <c r="K144" t="n">
-        <v>295.1528625488281</v>
+        <v>129.4468231201172</v>
       </c>
       <c r="L144" t="n">
         <v>5254.35009765625</v>
@@ -5936,10 +5936,10 @@
         <v>86.15634155273438</v>
       </c>
       <c r="G145" t="n">
-        <v>426.5411682128906</v>
+        <v>426.5411376953125</v>
       </c>
       <c r="H145" t="n">
-        <v>74360.6875</v>
+        <v>158.3800048828125</v>
       </c>
       <c r="I145" t="n">
         <v>183.2799987792969</v>
@@ -5948,7 +5948,7 @@
         <v>30.15544509887695</v>
       </c>
       <c r="K145" t="n">
-        <v>337.3175659179688</v>
+        <v>126.9915237426758</v>
       </c>
       <c r="L145" t="n">
         <v>5035.68994140625</v>
@@ -5959,25 +5959,25 @@
         <v>45413</v>
       </c>
       <c r="B146" t="n">
-        <v>190.4346923828125</v>
+        <v>190.4347229003906</v>
       </c>
       <c r="C146" t="n">
-        <v>407.9389038085938</v>
+        <v>407.9389343261719</v>
       </c>
       <c r="D146" t="n">
-        <v>170.8740081787109</v>
+        <v>170.8740234375</v>
       </c>
       <c r="E146" t="n">
         <v>176.4400024414062</v>
       </c>
       <c r="F146" t="n">
-        <v>109.3212890625</v>
+        <v>109.3212966918945</v>
       </c>
       <c r="G146" t="n">
-        <v>462.8918762207031</v>
+        <v>462.891845703125</v>
       </c>
       <c r="H146" t="n">
-        <v>70522.7109375</v>
+        <v>166.8999938964844</v>
       </c>
       <c r="I146" t="n">
         <v>178.0800018310547</v>
@@ -5986,7 +5986,7 @@
         <v>30.6555347442627</v>
       </c>
       <c r="K146" t="n">
-        <v>352.5784606933594</v>
+        <v>129.7534942626953</v>
       </c>
       <c r="L146" t="n">
         <v>5277.509765625</v>
@@ -5997,25 +5997,25 @@
         <v>45444</v>
       </c>
       <c r="B147" t="n">
-        <v>208.6312255859375</v>
+        <v>208.6312561035156</v>
       </c>
       <c r="C147" t="n">
-        <v>439.207763671875</v>
+        <v>439.2077026367188</v>
       </c>
       <c r="D147" t="n">
-        <v>180.64013671875</v>
+        <v>180.6401519775391</v>
       </c>
       <c r="E147" t="n">
         <v>193.25</v>
       </c>
       <c r="F147" t="n">
-        <v>123.1988677978516</v>
+        <v>123.1988754272461</v>
       </c>
       <c r="G147" t="n">
-        <v>500.462890625</v>
+        <v>500.4628295898438</v>
       </c>
       <c r="H147" t="n">
-        <v>78547.4296875</v>
+        <v>162.2100067138672</v>
       </c>
       <c r="I147" t="n">
         <v>197.8800048828125</v>
@@ -6024,7 +6024,7 @@
         <v>30.77477645874023</v>
       </c>
       <c r="K147" t="n">
-        <v>364.9255981445312</v>
+        <v>157.3028106689453</v>
       </c>
       <c r="L147" t="n">
         <v>5460.47998046875</v>
@@ -6035,25 +6035,25 @@
         <v>45474</v>
       </c>
       <c r="B148" t="n">
-        <v>219.9830627441406</v>
+        <v>219.9830474853516</v>
       </c>
       <c r="C148" t="n">
-        <v>411.1031799316406</v>
+        <v>411.1031188964844</v>
       </c>
       <c r="D148" t="n">
-        <v>170.1180572509766</v>
+        <v>170.1180877685547</v>
       </c>
       <c r="E148" t="n">
         <v>186.9799957275391</v>
       </c>
       <c r="F148" t="n">
-        <v>116.6968460083008</v>
+        <v>116.6968536376953</v>
       </c>
       <c r="G148" t="n">
-        <v>471.2918395996094</v>
+        <v>471.2918701171875</v>
       </c>
       <c r="H148" t="n">
-        <v>80860.4921875</v>
+        <v>144.4799957275391</v>
       </c>
       <c r="I148" t="n">
         <v>232.0700073242188</v>
@@ -6062,7 +6062,7 @@
         <v>30.54622650146484</v>
       </c>
       <c r="K148" t="n">
-        <v>354.9303588867188</v>
+        <v>157.4272308349609</v>
       </c>
       <c r="L148" t="n">
         <v>5522.2998046875</v>
@@ -6076,7 +6076,7 @@
         <v>227.1002655029297</v>
       </c>
       <c r="C149" t="n">
-        <v>410.6529541015625</v>
+        <v>410.6529235839844</v>
       </c>
       <c r="D149" t="n">
         <v>162.0257263183594</v>
@@ -6085,13 +6085,13 @@
         <v>178.5</v>
       </c>
       <c r="F149" t="n">
-        <v>119.0403823852539</v>
+        <v>119.0403747558594</v>
       </c>
       <c r="G149" t="n">
-        <v>517.425537109375</v>
+        <v>517.4255981445312</v>
       </c>
       <c r="H149" t="n">
-        <v>71608.2890625</v>
+        <v>148.5599975585938</v>
       </c>
       <c r="I149" t="n">
         <v>214.1100006103516</v>
@@ -6100,7 +6100,7 @@
         <v>22.04000091552734</v>
       </c>
       <c r="K149" t="n">
-        <v>374.3329162597656</v>
+        <v>159.5239410400391</v>
       </c>
       <c r="L149" t="n">
         <v>5648.39990234375</v>
@@ -6114,22 +6114,22 @@
         <v>231.0670776367188</v>
       </c>
       <c r="C150" t="n">
-        <v>423.6082153320312</v>
+        <v>423.6082458496094</v>
       </c>
       <c r="D150" t="n">
-        <v>164.6935119628906</v>
+        <v>164.6934967041016</v>
       </c>
       <c r="E150" t="n">
         <v>186.3300018310547</v>
       </c>
       <c r="F150" t="n">
-        <v>121.1150283813477</v>
+        <v>121.1150360107422</v>
       </c>
       <c r="G150" t="n">
         <v>568.716552734375</v>
       </c>
       <c r="H150" t="n">
-        <v>59604.55859375</v>
+        <v>164.0800018310547</v>
       </c>
       <c r="I150" t="n">
         <v>261.6300048828125</v>
@@ -6138,7 +6138,7 @@
         <v>23.45999908447266</v>
       </c>
       <c r="K150" t="n">
-        <v>435.6764831542969</v>
+        <v>169.5638427734375</v>
       </c>
       <c r="L150" t="n">
         <v>5762.47998046875</v>
@@ -6149,7 +6149,7 @@
         <v>45566</v>
       </c>
       <c r="B151" t="n">
-        <v>224.035888671875</v>
+        <v>224.0359039306641</v>
       </c>
       <c r="C151" t="n">
         <v>400.0307312011719</v>
@@ -6167,7 +6167,7 @@
         <v>563.88818359375</v>
       </c>
       <c r="H151" t="n">
-        <v>57375.4453125</v>
+        <v>144.0700073242188</v>
       </c>
       <c r="I151" t="n">
         <v>249.8500061035156</v>
@@ -6176,7 +6176,7 @@
         <v>21.52000045776367</v>
       </c>
       <c r="K151" t="n">
-        <v>396.4793090820312</v>
+        <v>166.8802947998047</v>
       </c>
       <c r="L151" t="n">
         <v>5705.4501953125</v>
@@ -6187,10 +6187,10 @@
         <v>45597</v>
       </c>
       <c r="B152" t="n">
-        <v>235.6200866699219</v>
+        <v>235.6201019287109</v>
       </c>
       <c r="C152" t="n">
-        <v>417.7090759277344</v>
+        <v>417.7091064453125</v>
       </c>
       <c r="D152" t="n">
         <v>167.7718811035156</v>
@@ -6199,13 +6199,13 @@
         <v>207.8899993896484</v>
       </c>
       <c r="F152" t="n">
-        <v>137.8800354003906</v>
+        <v>137.8800201416016</v>
       </c>
       <c r="G152" t="n">
         <v>570.5842895507812</v>
       </c>
       <c r="H152" t="n">
-        <v>52529.55078125</v>
+        <v>137.1799926757812</v>
       </c>
       <c r="I152" t="n">
         <v>345.1600036621094</v>
@@ -6214,7 +6214,7 @@
         <v>24.04999923706055</v>
       </c>
       <c r="K152" t="n">
-        <v>390.0117797851562</v>
+        <v>159.3211975097656</v>
       </c>
       <c r="L152" t="n">
         <v>6032.3798828125</v>
@@ -6228,10 +6228,10 @@
         <v>248.6157989501953</v>
       </c>
       <c r="C153" t="n">
-        <v>415.7756652832031</v>
+        <v>415.7757263183594</v>
       </c>
       <c r="D153" t="n">
-        <v>188.1954193115234</v>
+        <v>188.1954040527344</v>
       </c>
       <c r="E153" t="n">
         <v>219.3899993896484</v>
@@ -6243,7 +6243,7 @@
         <v>582.1707763671875</v>
       </c>
       <c r="H153" t="n">
-        <v>51911.93359375</v>
+        <v>120.7900009155273</v>
       </c>
       <c r="I153" t="n">
         <v>403.8399963378906</v>
@@ -6252,7 +6252,7 @@
         <v>20.04999923706055</v>
       </c>
       <c r="K153" t="n">
-        <v>411.3742065429688</v>
+        <v>228.5044097900391</v>
       </c>
       <c r="L153" t="n">
         <v>5881.6298828125</v>
@@ -6263,13 +6263,13 @@
         <v>45658</v>
       </c>
       <c r="B154" t="n">
-        <v>234.2996673583984</v>
+        <v>234.2996826171875</v>
       </c>
       <c r="C154" t="n">
-        <v>409.4231262207031</v>
+        <v>409.4231872558594</v>
       </c>
       <c r="D154" t="n">
-        <v>202.8295440673828</v>
+        <v>202.8295288085938</v>
       </c>
       <c r="E154" t="n">
         <v>237.6799926757812</v>
@@ -6278,10 +6278,10 @@
         <v>119.7569351196289</v>
       </c>
       <c r="G154" t="n">
-        <v>685.2495727539062</v>
+        <v>685.24951171875</v>
       </c>
       <c r="H154" t="n">
-        <v>51131.30078125</v>
+        <v>115.9499969482422</v>
       </c>
       <c r="I154" t="n">
         <v>404.6000061035156</v>
@@ -6290,7 +6290,7 @@
         <v>19.43000030517578</v>
       </c>
       <c r="K154" t="n">
-        <v>393.9315185546875</v>
+        <v>218.0864868164062</v>
       </c>
       <c r="L154" t="n">
         <v>6040.52978515625</v>
@@ -6301,13 +6301,13 @@
         <v>45689</v>
       </c>
       <c r="B155" t="n">
-        <v>240.3616027832031</v>
+        <v>240.361572265625</v>
       </c>
       <c r="C155" t="n">
-        <v>392.3837585449219</v>
+        <v>392.3837280273438</v>
       </c>
       <c r="D155" t="n">
-        <v>169.2863922119141</v>
+        <v>169.2864074707031</v>
       </c>
       <c r="E155" t="n">
         <v>212.2799987792969</v>
@@ -6316,10 +6316,10 @@
         <v>124.5942993164062</v>
       </c>
       <c r="G155" t="n">
-        <v>664.38916015625</v>
+        <v>664.3892211914062</v>
       </c>
       <c r="H155" t="n">
-        <v>53180.45703125</v>
+        <v>99.86000061035156</v>
       </c>
       <c r="I155" t="n">
         <v>292.9800109863281</v>
@@ -6328,7 +6328,7 @@
         <v>23.72999954223633</v>
       </c>
       <c r="K155" t="n">
-        <v>468.9940795898438</v>
+        <v>196.5606994628906</v>
       </c>
       <c r="L155" t="n">
         <v>5954.5</v>
@@ -6345,7 +6345,7 @@
         <v>371.0343933105469</v>
       </c>
       <c r="D156" t="n">
-        <v>153.9147186279297</v>
+        <v>153.9147033691406</v>
       </c>
       <c r="E156" t="n">
         <v>190.2599945068359</v>
@@ -6354,10 +6354,10 @@
         <v>108.1073608398438</v>
       </c>
       <c r="G156" t="n">
-        <v>573.5828247070312</v>
+        <v>573.5827026367188</v>
       </c>
       <c r="H156" t="n">
-        <v>56735.65234375</v>
+        <v>102.7399978637695</v>
       </c>
       <c r="I156" t="n">
         <v>259.1600036621094</v>
@@ -6366,7 +6366,7 @@
         <v>22.70999908447266</v>
       </c>
       <c r="K156" t="n">
-        <v>487.0247802734375</v>
+        <v>165.5204620361328</v>
       </c>
       <c r="L156" t="n">
         <v>5611.85009765625</v>
@@ -6377,13 +6377,13 @@
         <v>45748</v>
       </c>
       <c r="B157" t="n">
-        <v>211.2009582519531</v>
+        <v>211.2009429931641</v>
       </c>
       <c r="C157" t="n">
-        <v>390.6738586425781</v>
+        <v>390.6738891601562</v>
       </c>
       <c r="D157" t="n">
-        <v>158.0552215576172</v>
+        <v>158.0552062988281</v>
       </c>
       <c r="E157" t="n">
         <v>184.4199981689453</v>
@@ -6392,10 +6392,10 @@
         <v>108.64599609375</v>
       </c>
       <c r="G157" t="n">
-        <v>546.3546752929688</v>
+        <v>546.3545532226562</v>
       </c>
       <c r="H157" t="n">
-        <v>54478.0078125</v>
+        <v>97.34999847412109</v>
       </c>
       <c r="I157" t="n">
         <v>282.1600036621094</v>
@@ -6404,7 +6404,7 @@
         <v>20.10000038146973</v>
       </c>
       <c r="K157" t="n">
-        <v>467.6221618652344</v>
+        <v>190.2748870849609</v>
       </c>
       <c r="L157" t="n">
         <v>5569.06005859375</v>
@@ -6418,22 +6418,22 @@
         <v>199.8839416503906</v>
       </c>
       <c r="C158" t="n">
-        <v>455.8538208007812</v>
+        <v>455.8537902832031</v>
       </c>
       <c r="D158" t="n">
-        <v>170.9345397949219</v>
+        <v>170.9345245361328</v>
       </c>
       <c r="E158" t="n">
         <v>205.0099945068359</v>
       </c>
       <c r="F158" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="G158" t="n">
         <v>644.3699951171875</v>
       </c>
       <c r="H158" t="n">
-        <v>55165.11328125</v>
+        <v>110.7300033569336</v>
       </c>
       <c r="I158" t="n">
         <v>346.4599914550781</v>
@@ -6442,7 +6442,7 @@
         <v>19.54999923706055</v>
       </c>
       <c r="K158" t="n">
-        <v>492.4623718261719</v>
+        <v>239.3091735839844</v>
       </c>
       <c r="L158" t="n">
         <v>5911.68994140625</v>
@@ -6453,10 +6453,10 @@
         <v>45809</v>
       </c>
       <c r="B159" t="n">
-        <v>204.1831665039062</v>
+        <v>204.1831512451172</v>
       </c>
       <c r="C159" t="n">
-        <v>492.5411987304688</v>
+        <v>492.5411682128906</v>
       </c>
       <c r="D159" t="n">
         <v>175.6157989501953</v>
@@ -6465,13 +6465,13 @@
         <v>219.3899993896484</v>
       </c>
       <c r="F159" t="n">
-        <v>157.6035003662109</v>
+        <v>157.603515625</v>
       </c>
       <c r="G159" t="n">
         <v>735.0987548828125</v>
       </c>
       <c r="H159" t="n">
-        <v>59058.8671875</v>
+        <v>141.8999938964844</v>
       </c>
       <c r="I159" t="n">
         <v>317.6600036621094</v>
@@ -6480,7 +6480,7 @@
         <v>22.39999961853027</v>
       </c>
       <c r="K159" t="n">
-        <v>497.2070617675781</v>
+        <v>273.1475830078125</v>
       </c>
       <c r="L159" t="n">
         <v>6204.9501953125</v>
@@ -6494,10 +6494,10 @@
         <v>206.5716247558594</v>
       </c>
       <c r="C160" t="n">
-        <v>528.27783203125</v>
+        <v>528.2779541015625</v>
       </c>
       <c r="D160" t="n">
-        <v>191.2311706542969</v>
+        <v>191.2311859130859</v>
       </c>
       <c r="E160" t="n">
         <v>234.1100006103516</v>
@@ -6509,7 +6509,7 @@
         <v>770.305419921875</v>
       </c>
       <c r="H160" t="n">
-        <v>70515.109375</v>
+        <v>176.3099975585938</v>
       </c>
       <c r="I160" t="n">
         <v>308.2699890136719</v>
@@ -6518,7 +6518,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="K160" t="n">
-        <v>543.665771484375</v>
+        <v>291.0337219238281</v>
       </c>
       <c r="L160" t="n">
         <v>6339.39013671875</v>
@@ -6532,10 +6532,10 @@
         <v>231.2856292724609</v>
       </c>
       <c r="C161" t="n">
-        <v>502.5551452636719</v>
+        <v>502.5551147460938</v>
       </c>
       <c r="D161" t="n">
-        <v>212.16796875</v>
+        <v>212.1679534912109</v>
       </c>
       <c r="E161" t="n">
         <v>229</v>
@@ -6544,10 +6544,10 @@
         <v>173.7538909912109</v>
       </c>
       <c r="G161" t="n">
-        <v>735.7061157226562</v>
+        <v>735.7062377929688</v>
       </c>
       <c r="H161" t="n">
-        <v>68836.171875</v>
+        <v>162.6300048828125</v>
       </c>
       <c r="I161" t="n">
         <v>333.8699951171875</v>
@@ -6556,7 +6556,7 @@
         <v>24.35000038146973</v>
       </c>
       <c r="K161" t="n">
-        <v>589.6302490234375</v>
+        <v>294.6902465820312</v>
       </c>
       <c r="L161" t="n">
         <v>6460.259765625</v>
@@ -6567,7 +6567,7 @@
         <v>45901</v>
       </c>
       <c r="B162" t="n">
-        <v>253.6928558349609</v>
+        <v>253.69287109375</v>
       </c>
       <c r="C162" t="n">
         <v>513.7232666015625</v>
@@ -6585,7 +6585,7 @@
         <v>731.8973388671875</v>
       </c>
       <c r="H162" t="n">
-        <v>83229.875</v>
+        <v>161.7899932861328</v>
       </c>
       <c r="I162" t="n">
         <v>444.7200012207031</v>
@@ -6594,7 +6594,7 @@
         <v>33.54999923706055</v>
       </c>
       <c r="K162" t="n">
-        <v>655.3643798828125</v>
+        <v>327.4751281738281</v>
       </c>
       <c r="L162" t="n">
         <v>6688.4599609375</v>
@@ -6605,7 +6605,7 @@
         <v>45931</v>
       </c>
       <c r="B163" t="n">
-        <v>269.3749389648438</v>
+        <v>269.3749084472656</v>
       </c>
       <c r="C163" t="n">
         <v>513.5843505859375</v>
@@ -6623,7 +6623,7 @@
         <v>646.1581420898438</v>
       </c>
       <c r="H163" t="n">
-        <v>106641.375</v>
+        <v>256.1199951171875</v>
       </c>
       <c r="I163" t="n">
         <v>456.5599975585938</v>
@@ -6632,7 +6632,7 @@
         <v>39.9900016784668</v>
       </c>
       <c r="K163" t="n">
-        <v>621.7559814453125</v>
+        <v>366.9019470214844</v>
       </c>
       <c r="L163" t="n">
         <v>6840.2001953125</v>
@@ -6643,7 +6643,7 @@
         <v>45962</v>
       </c>
       <c r="B164" t="n">
-        <v>278.093017578125</v>
+        <v>278.0930480957031</v>
       </c>
       <c r="C164" t="n">
         <v>488.9082946777344</v>
@@ -6658,10 +6658,10 @@
         <v>176.5769653320312</v>
       </c>
       <c r="G164" t="n">
-        <v>645.759521484375</v>
+        <v>645.7595825195312</v>
       </c>
       <c r="H164" t="n">
-        <v>99697.2890625</v>
+        <v>217.5299987792969</v>
       </c>
       <c r="I164" t="n">
         <v>430.1700134277344</v>
@@ -6670,7 +6670,7 @@
         <v>40.56000137329102</v>
       </c>
       <c r="K164" t="n">
-        <v>604.45751953125</v>
+        <v>399.9859619140625</v>
       </c>
       <c r="L164" t="n">
         <v>6849.08984375</v>
@@ -6684,7 +6684,7 @@
         <v>271.1220092773438</v>
       </c>
       <c r="C165" t="n">
-        <v>480.5711669921875</v>
+        <v>480.5711364746094</v>
       </c>
       <c r="D165" t="n">
         <v>312.3923034667969</v>
@@ -6696,10 +6696,10 @@
         <v>186.0646057128906</v>
       </c>
       <c r="G165" t="n">
-        <v>658.3950805664062</v>
+        <v>658.39501953125</v>
       </c>
       <c r="H165" t="n">
-        <v>119520.53125</v>
+        <v>214.1600036621094</v>
       </c>
       <c r="I165" t="n">
         <v>449.7200012207031</v>
@@ -6708,7 +6708,7 @@
         <v>36.90000152587891</v>
       </c>
       <c r="K165" t="n">
-        <v>592.1014404296875</v>
+        <v>344.2030029296875</v>
       </c>
       <c r="L165" t="n">
         <v>6845.5</v>
@@ -6719,7 +6719,7 @@
         <v>46023</v>
       </c>
       <c r="B166" t="n">
-        <v>258.775634765625</v>
+        <v>258.7756652832031</v>
       </c>
       <c r="C166" t="n">
         <v>427.577392578125</v>
@@ -6734,10 +6734,10 @@
         <v>190.6838073730469</v>
       </c>
       <c r="G166" t="n">
-        <v>714.66015625</v>
+        <v>714.6602172851562</v>
       </c>
       <c r="H166" t="n">
-        <v>159992.03125</v>
+        <v>236.7299957275391</v>
       </c>
       <c r="I166" t="n">
         <v>430.4100036621094</v>
@@ -6746,7 +6746,7 @@
         <v>46.47000122070312</v>
       </c>
       <c r="K166" t="n">
-        <v>599.0208740234375</v>
+        <v>329.4840698242188</v>
       </c>
       <c r="L166" t="n">
         <v>6939.02978515625</v>
@@ -6757,7 +6757,7 @@
         <v>46054</v>
       </c>
       <c r="B167" t="n">
-        <v>263.7094116210938</v>
+        <v>263.7093811035156</v>
       </c>
       <c r="C167" t="n">
         <v>391.1548461914062</v>
@@ -6775,7 +6775,7 @@
         <v>646.515625</v>
       </c>
       <c r="H167" t="n">
-        <v>215814.796875</v>
+        <v>200.2100067138672</v>
       </c>
       <c r="I167" t="n">
         <v>402.510009765625</v>
@@ -6784,7 +6784,7 @@
         <v>45.61000061035156</v>
       </c>
       <c r="K167" t="n">
-        <v>512.0343017578125</v>
+        <v>317.7984924316406</v>
       </c>
       <c r="L167" t="n">
         <v>6878.8798828125</v>
@@ -6795,7 +6795,7 @@
         <v>46082</v>
       </c>
       <c r="B168" t="n">
-        <v>253.3379058837891</v>
+        <v>253.337890625</v>
       </c>
       <c r="C168" t="n">
         <v>368.6759643554688</v>
@@ -6813,7 +6813,7 @@
         <v>571.1494750976562</v>
       </c>
       <c r="H168" t="n">
-        <v>167015.8125</v>
+        <v>203.4299926757812</v>
       </c>
       <c r="I168" t="n">
         <v>371.75</v>
@@ -6822,7 +6822,7 @@
         <v>44.13000106811523</v>
       </c>
       <c r="K168" t="n">
-        <v>478.4259033203125</v>
+        <v>308.4592590332031</v>
       </c>
       <c r="L168" t="n">
         <v>6528.52001953125</v>
@@ -6851,7 +6851,7 @@
         <v>610.8612670898438</v>
       </c>
       <c r="H169" t="n">
-        <v>220257.09375</v>
+        <v>354.489990234375</v>
       </c>
       <c r="I169" t="n">
         <v>381.6300048828125</v>
@@ -6860,7 +6860,7 @@
         <v>94.48000335693359</v>
       </c>
       <c r="K169" t="n">
-        <v>462.4124450683594</v>
+        <v>416.0128479003906</v>
       </c>
       <c r="L169" t="n">
         <v>7209.009765625</v>
@@ -6889,7 +6889,7 @@
         <v>631.426025390625</v>
       </c>
       <c r="H170" t="n">
-        <v>316650.78125</v>
+        <v>516.0999755859375</v>
       </c>
       <c r="I170" t="n">
         <v>435.7900085449219</v>
@@ -6898,7 +6898,7 @@
         <v>114.6800003051758</v>
       </c>
       <c r="K170" t="n">
-        <v>427.2000122070312</v>
+        <v>445.2532348632812</v>
       </c>
       <c r="L170" t="n">
         <v>7580.06005859375</v>
@@ -6927,7 +6927,7 @@
         <v>562.8457641601562</v>
       </c>
       <c r="H171" t="n">
-        <v>334000</v>
+        <v>580.9099731445312</v>
       </c>
       <c r="I171" t="n">
         <v>420.6000061035156</v>
@@ -6936,7 +6936,7 @@
         <v>139.6300048828125</v>
       </c>
       <c r="K171" t="n">
-        <v>429.7999877929688</v>
+        <v>377.0633850097656</v>
       </c>
       <c r="L171" t="n">
         <v>7499.35986328125</v>
@@ -6965,7 +6965,7 @@
         <v>556.27099609375</v>
       </c>
       <c r="H172" t="n">
-        <v>262500</v>
+        <v>476.1499938964844</v>
       </c>
       <c r="I172" t="n">
         <v>311.2099914550781</v>
@@ -6974,7 +6974,7 @@
         <v>90.19999694824219</v>
       </c>
       <c r="K172" t="n">
-        <v>475.2000122070312</v>
+        <v>388.5724182128906</v>
       </c>
       <c r="L172" t="n">
         <v>7489.72021484375</v>
@@ -7003,7 +7003,7 @@
         <v>571.888671875</v>
       </c>
       <c r="H173" t="n">
-        <v>260000</v>
+        <v>470.7200012207031</v>
       </c>
       <c r="I173" t="n">
         <v>367.9500122070312</v>
@@ -7012,7 +7012,7 @@
         <v>89.51000213623047</v>
       </c>
       <c r="K173" t="n">
-        <v>453</v>
+        <v>369.6668395996094</v>
       </c>
       <c r="L173" t="n">
         <v>7686.14013671875</v>
@@ -7041,7 +7041,7 @@
         <v>725.1799926757812</v>
       </c>
       <c r="H174" t="n">
-        <v>268500</v>
+        <v>611.760009765625</v>
       </c>
       <c r="I174" t="n">
         <v>354.8099975585938</v>
@@ -7050,7 +7050,7 @@
         <v>120.2300033569336</v>
       </c>
       <c r="K174" t="n">
-        <v>431</v>
+        <v>351.1900024414062</v>
       </c>
       <c r="L174" t="n">
         <v>7651.5400390625</v>
@@ -7061,37 +7061,37 @@
         <v>46296</v>
       </c>
       <c r="B175" t="n">
-        <v>337.6900024414062</v>
+        <v>342.9599914550781</v>
       </c>
       <c r="C175" t="n">
-        <v>530.22998046875</v>
+        <v>533.6900024414062</v>
       </c>
       <c r="D175" t="n">
-        <v>350.2749938964844</v>
+        <v>347.6400146484375</v>
       </c>
       <c r="E175" t="n">
-        <v>258.3299865722656</v>
+        <v>254.0800018310547</v>
       </c>
       <c r="F175" t="n">
-        <v>236.0399932861328</v>
+        <v>221.3000030517578</v>
       </c>
       <c r="G175" t="n">
-        <v>721.5449829101562</v>
+        <v>737.5399780273438</v>
       </c>
       <c r="H175" t="n">
-        <v>262000</v>
+        <v>570.8200073242188</v>
       </c>
       <c r="I175" t="n">
-        <v>372.3150024414062</v>
+        <v>367.1600036621094</v>
       </c>
       <c r="J175" t="n">
-        <v>109.5</v>
+        <v>98.12000274658203</v>
       </c>
       <c r="K175" t="n">
-        <v>411.3999938964844</v>
+        <v>346.25</v>
       </c>
       <c r="L175" t="n">
-        <v>7772.490234375</v>
+        <v>7718.93994140625</v>
       </c>
     </row>
   </sheetData>

--- a/monthly.xlsx
+++ b/monthly.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L175"/>
+  <dimension ref="A1:L174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,22 +487,22 @@
         <v>41030</v>
       </c>
       <c r="B2" t="n">
-        <v>17.27969551086426</v>
+        <v>17.27969360351562</v>
       </c>
       <c r="C2" t="n">
         <v>23.01618003845215</v>
       </c>
       <c r="D2" t="n">
-        <v>14.39901828765869</v>
+        <v>14.39902019500732</v>
       </c>
       <c r="E2" t="n">
         <v>10.64550018310547</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2842411696910858</v>
+        <v>0.2842412889003754</v>
       </c>
       <c r="G2" t="n">
-        <v>29.31919097900391</v>
+        <v>29.31918907165527</v>
       </c>
       <c r="H2" t="n">
         <v>6.079999923706055</v>
@@ -511,7 +511,7 @@
         <v>1.966667056083679</v>
       </c>
       <c r="J2" t="n">
-        <v>18.13142967224121</v>
+        <v>18.13143730163574</v>
       </c>
       <c r="K2" t="n">
         <v>2.36237907409668</v>
@@ -525,19 +525,19 @@
         <v>41061</v>
       </c>
       <c r="B3" t="n">
-        <v>17.46722412109375</v>
+        <v>17.46722602844238</v>
       </c>
       <c r="C3" t="n">
-        <v>24.12006950378418</v>
+        <v>24.12006568908691</v>
       </c>
       <c r="D3" t="n">
-        <v>14.37943458557129</v>
+        <v>14.37943553924561</v>
       </c>
       <c r="E3" t="n">
         <v>11.41749954223633</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3160269558429718</v>
+        <v>0.3160266876220703</v>
       </c>
       <c r="G3" t="n">
         <v>30.80496025085449</v>
@@ -549,10 +549,10 @@
         <v>2.085999965667725</v>
       </c>
       <c r="J3" t="n">
-        <v>18.69979476928711</v>
+        <v>18.69979286193848</v>
       </c>
       <c r="K3" t="n">
-        <v>2.57355809211731</v>
+        <v>2.573558568954468</v>
       </c>
       <c r="L3" t="n">
         <v>1362.160034179688</v>
@@ -563,13 +563,13 @@
         <v>41091</v>
       </c>
       <c r="B4" t="n">
-        <v>18.26760864257812</v>
+        <v>18.26760673522949</v>
       </c>
       <c r="C4" t="n">
-        <v>23.23695945739746</v>
+        <v>23.23695755004883</v>
       </c>
       <c r="D4" t="n">
-        <v>15.69077968597412</v>
+        <v>15.69078063964844</v>
       </c>
       <c r="E4" t="n">
         <v>11.66499996185303</v>
@@ -578,7 +578,7 @@
         <v>0.3096239864826202</v>
       </c>
       <c r="G4" t="n">
-        <v>21.50403785705566</v>
+        <v>21.50404167175293</v>
       </c>
       <c r="H4" t="n">
         <v>4.059999942779541</v>
@@ -587,10 +587,10 @@
         <v>1.827999949455261</v>
       </c>
       <c r="J4" t="n">
-        <v>18.0331974029541</v>
+        <v>18.03319931030273</v>
       </c>
       <c r="K4" t="n">
-        <v>2.64524507522583</v>
+        <v>2.645245552062988</v>
       </c>
       <c r="L4" t="n">
         <v>1379.319946289062</v>
@@ -613,10 +613,10 @@
         <v>12.41349983215332</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3208289742469788</v>
+        <v>0.3208289444446564</v>
       </c>
       <c r="G5" t="n">
-        <v>17.8886661529541</v>
+        <v>17.88866806030273</v>
       </c>
       <c r="H5" t="n">
         <v>3.720000028610229</v>
@@ -625,10 +625,10 @@
         <v>1.901332974433899</v>
       </c>
       <c r="J5" t="n">
-        <v>17.57535743713379</v>
+        <v>17.57536315917969</v>
       </c>
       <c r="K5" t="n">
-        <v>2.621588468551636</v>
+        <v>2.621588706970215</v>
       </c>
       <c r="L5" t="n">
         <v>1406.579956054688</v>
@@ -639,22 +639,22 @@
         <v>41153</v>
       </c>
       <c r="B6" t="n">
-        <v>20.03838157653809</v>
+        <v>20.03837776184082</v>
       </c>
       <c r="C6" t="n">
-        <v>23.62106895446777</v>
+        <v>23.62107276916504</v>
       </c>
       <c r="D6" t="n">
-        <v>18.70340538024902</v>
+        <v>18.70340347290039</v>
       </c>
       <c r="E6" t="n">
         <v>12.71599960327148</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3050503730773926</v>
+        <v>0.3050504624843597</v>
       </c>
       <c r="G6" t="n">
-        <v>21.45451736450195</v>
+        <v>21.45451545715332</v>
       </c>
       <c r="H6" t="n">
         <v>3.369999885559082</v>
@@ -663,10 +663,10 @@
         <v>1.952000021934509</v>
       </c>
       <c r="J6" t="n">
-        <v>16.03936767578125</v>
+        <v>16.03937530517578</v>
       </c>
       <c r="K6" t="n">
-        <v>2.511109113693237</v>
+        <v>2.5111083984375</v>
       </c>
       <c r="L6" t="n">
         <v>1440.670043945312</v>
@@ -677,22 +677,22 @@
         <v>41183</v>
       </c>
       <c r="B7" t="n">
-        <v>17.88224411010742</v>
+        <v>17.88224792480469</v>
       </c>
       <c r="C7" t="n">
-        <v>22.65273094177246</v>
+        <v>22.65273475646973</v>
       </c>
       <c r="D7" t="n">
-        <v>16.86405372619629</v>
+        <v>16.86404991149902</v>
       </c>
       <c r="E7" t="n">
         <v>11.64449977874756</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2739508748054504</v>
+        <v>0.2739508450031281</v>
       </c>
       <c r="G7" t="n">
-        <v>20.90973091125488</v>
+        <v>20.90973281860352</v>
       </c>
       <c r="H7" t="n">
         <v>2.049999952316284</v>
@@ -701,10 +701,10 @@
         <v>1.875332951545715</v>
       </c>
       <c r="J7" t="n">
-        <v>15.31031227111816</v>
+        <v>15.31030750274658</v>
       </c>
       <c r="K7" t="n">
-        <v>2.378604173660278</v>
+        <v>2.378604888916016</v>
       </c>
       <c r="L7" t="n">
         <v>1412.160034179688</v>
@@ -715,10 +715,10 @@
         <v>41214</v>
       </c>
       <c r="B8" t="n">
-        <v>17.66096305847168</v>
+        <v>17.66097068786621</v>
       </c>
       <c r="C8" t="n">
-        <v>21.30241012573242</v>
+        <v>21.30241966247559</v>
       </c>
       <c r="D8" t="n">
         <v>17.31199073791504</v>
@@ -727,10 +727,10 @@
         <v>12.60249996185303</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2754880785942078</v>
+        <v>0.2754881680011749</v>
       </c>
       <c r="G8" t="n">
-        <v>27.73436546325684</v>
+        <v>27.7343692779541</v>
       </c>
       <c r="H8" t="n">
         <v>2.200000047683716</v>
@@ -739,10 +739,10 @@
         <v>2.254667043685913</v>
       </c>
       <c r="J8" t="n">
-        <v>13.99492454528809</v>
+        <v>13.99492359161377</v>
       </c>
       <c r="K8" t="n">
-        <v>2.527671813964844</v>
+        <v>2.527672529220581</v>
       </c>
       <c r="L8" t="n">
         <v>1416.180053710938</v>
@@ -756,19 +756,19 @@
         <v>16.0583610534668</v>
       </c>
       <c r="C9" t="n">
-        <v>21.37444114685059</v>
+        <v>21.37443351745605</v>
       </c>
       <c r="D9" t="n">
-        <v>17.53534507751465</v>
+        <v>17.53534126281738</v>
       </c>
       <c r="E9" t="n">
         <v>12.54349994659424</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2821624577045441</v>
+        <v>0.2821624875068665</v>
       </c>
       <c r="G9" t="n">
-        <v>26.36746025085449</v>
+        <v>26.36746215820312</v>
       </c>
       <c r="H9" t="n">
         <v>2.400000095367432</v>
@@ -780,7 +780,7 @@
         <v>14.74580383300781</v>
       </c>
       <c r="K9" t="n">
-        <v>2.290489673614502</v>
+        <v>2.290488958358765</v>
       </c>
       <c r="L9" t="n">
         <v>1426.18994140625</v>
@@ -791,19 +791,19 @@
         <v>41275</v>
       </c>
       <c r="B10" t="n">
-        <v>13.74452495574951</v>
+        <v>13.74452018737793</v>
       </c>
       <c r="C10" t="n">
-        <v>21.96661186218262</v>
+        <v>21.96661758422852</v>
       </c>
       <c r="D10" t="n">
-        <v>18.73290824890137</v>
+        <v>18.73290634155273</v>
       </c>
       <c r="E10" t="n">
         <v>13.27499961853027</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2821624577045441</v>
+        <v>0.2821624875068665</v>
       </c>
       <c r="G10" t="n">
         <v>30.68609619140625</v>
@@ -815,10 +815,10 @@
         <v>2.500667095184326</v>
       </c>
       <c r="J10" t="n">
-        <v>15.04615306854248</v>
+        <v>15.0461597442627</v>
       </c>
       <c r="K10" t="n">
-        <v>2.588650941848755</v>
+        <v>2.588650703430176</v>
       </c>
       <c r="L10" t="n">
         <v>1498.109985351562</v>
@@ -829,13 +829,13 @@
         <v>41306</v>
       </c>
       <c r="B11" t="n">
-        <v>13.39697742462158</v>
+        <v>13.3969841003418</v>
       </c>
       <c r="C11" t="n">
-        <v>22.43089294433594</v>
+        <v>22.4308910369873</v>
       </c>
       <c r="D11" t="n">
-        <v>19.86106300354004</v>
+        <v>19.86106109619141</v>
       </c>
       <c r="E11" t="n">
         <v>13.21350002288818</v>
@@ -844,7 +844,7 @@
         <v>0.2931560277938843</v>
       </c>
       <c r="G11" t="n">
-        <v>26.99148368835449</v>
+        <v>26.99148559570312</v>
       </c>
       <c r="H11" t="n">
         <v>2.490000009536743</v>
@@ -853,10 +853,10 @@
         <v>2.322000026702881</v>
       </c>
       <c r="J11" t="n">
-        <v>15.092209815979</v>
+        <v>15.09221172332764</v>
       </c>
       <c r="K11" t="n">
-        <v>2.476478099822998</v>
+        <v>2.476478576660156</v>
       </c>
       <c r="L11" t="n">
         <v>1514.680053710938</v>
@@ -867,22 +867,22 @@
         <v>41334</v>
       </c>
       <c r="B12" t="n">
-        <v>13.43521976470947</v>
+        <v>13.43521785736084</v>
       </c>
       <c r="C12" t="n">
-        <v>23.08444595336914</v>
+        <v>23.08444976806641</v>
       </c>
       <c r="D12" t="n">
-        <v>19.68728446960449</v>
+        <v>19.68728828430176</v>
       </c>
       <c r="E12" t="n">
         <v>13.32450008392334</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2970924973487854</v>
+        <v>0.297092467546463</v>
       </c>
       <c r="G12" t="n">
-        <v>25.33732414245605</v>
+        <v>25.33732795715332</v>
       </c>
       <c r="H12" t="n">
         <v>2.549999952316284</v>
@@ -891,10 +891,10 @@
         <v>2.526000022888184</v>
       </c>
       <c r="J12" t="n">
-        <v>15.78610801696777</v>
+        <v>15.78610992431641</v>
       </c>
       <c r="K12" t="n">
-        <v>2.613325595855713</v>
+        <v>2.613326072692871</v>
       </c>
       <c r="L12" t="n">
         <v>1569.18994140625</v>
@@ -905,7 +905,7 @@
         <v>41365</v>
       </c>
       <c r="B13" t="n">
-        <v>13.43886184692383</v>
+        <v>13.43886566162109</v>
       </c>
       <c r="C13" t="n">
         <v>26.70728302001953</v>
@@ -917,10 +917,10 @@
         <v>12.69050025939941</v>
       </c>
       <c r="F13" t="n">
-        <v>0.318859189748764</v>
+        <v>0.3188591301441193</v>
       </c>
       <c r="G13" t="n">
-        <v>27.50654792785645</v>
+        <v>27.50655364990234</v>
       </c>
       <c r="H13" t="n">
         <v>2.819999933242798</v>
@@ -929,10 +929,10 @@
         <v>3.599333047866821</v>
       </c>
       <c r="J13" t="n">
-        <v>17.31123542785645</v>
+        <v>17.31123161315918</v>
       </c>
       <c r="K13" t="n">
-        <v>2.325219631195068</v>
+        <v>2.325219869613647</v>
       </c>
       <c r="L13" t="n">
         <v>1597.569946289062</v>
@@ -949,16 +949,16 @@
         <v>28.35710334777832</v>
       </c>
       <c r="D14" t="n">
-        <v>21.5967960357666</v>
+        <v>21.5967903137207</v>
       </c>
       <c r="E14" t="n">
         <v>13.46000003814697</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3367703557014465</v>
+        <v>0.3367704749107361</v>
       </c>
       <c r="G14" t="n">
-        <v>24.11899757385254</v>
+        <v>24.11899566650391</v>
       </c>
       <c r="H14" t="n">
         <v>4</v>
@@ -967,7 +967,7 @@
         <v>6.517333030700684</v>
       </c>
       <c r="J14" t="n">
-        <v>17.71508598327637</v>
+        <v>17.71508407592773</v>
       </c>
       <c r="K14" t="n">
         <v>2.745010375976562</v>
@@ -981,19 +981,19 @@
         <v>41426</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11478710174561</v>
+        <v>12.11478805541992</v>
       </c>
       <c r="C15" t="n">
-        <v>28.0645923614502</v>
+        <v>28.06458854675293</v>
       </c>
       <c r="D15" t="n">
-        <v>21.8236141204834</v>
+        <v>21.82361221313477</v>
       </c>
       <c r="E15" t="n">
         <v>13.88449954986572</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3267627358436584</v>
+        <v>0.3267628252506256</v>
       </c>
       <c r="G15" t="n">
         <v>24.64396667480469</v>
@@ -1008,7 +1008,7 @@
         <v>17.67859840393066</v>
       </c>
       <c r="K15" t="n">
-        <v>2.735513687133789</v>
+        <v>2.735512971878052</v>
       </c>
       <c r="L15" t="n">
         <v>1606.280029296875</v>
@@ -1019,22 +1019,22 @@
         <v>41456</v>
       </c>
       <c r="B16" t="n">
-        <v>13.82569789886475</v>
+        <v>13.82569980621338</v>
       </c>
       <c r="C16" t="n">
-        <v>25.87077140808105</v>
+        <v>25.87077713012695</v>
       </c>
       <c r="D16" t="n">
-        <v>22.00655364990234</v>
+        <v>22.00655746459961</v>
       </c>
       <c r="E16" t="n">
         <v>15.06099987030029</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3360722959041595</v>
+        <v>0.3360723555088043</v>
       </c>
       <c r="G16" t="n">
-        <v>36.45087814331055</v>
+        <v>36.45088195800781</v>
       </c>
       <c r="H16" t="n">
         <v>3.769999980926514</v>
@@ -1046,7 +1046,7 @@
         <v>17.02924156188965</v>
       </c>
       <c r="K16" t="n">
-        <v>2.684286594390869</v>
+        <v>2.68428635597229</v>
       </c>
       <c r="L16" t="n">
         <v>1685.72998046875</v>
@@ -1057,19 +1057,19 @@
         <v>41487</v>
       </c>
       <c r="B17" t="n">
-        <v>14.98383045196533</v>
+        <v>14.9838342666626</v>
       </c>
       <c r="C17" t="n">
         <v>27.32955169677734</v>
       </c>
       <c r="D17" t="n">
-        <v>20.99392318725586</v>
+        <v>20.99391937255859</v>
       </c>
       <c r="E17" t="n">
         <v>14.04899978637695</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3450179696083069</v>
+        <v>0.3450179398059845</v>
       </c>
       <c r="G17" t="n">
         <v>40.89829254150391</v>
@@ -1081,10 +1081,10 @@
         <v>11.26666736602783</v>
       </c>
       <c r="J17" t="n">
-        <v>16.19388008117676</v>
+        <v>16.19388198852539</v>
       </c>
       <c r="K17" t="n">
-        <v>2.818207025527954</v>
+        <v>2.818206787109375</v>
       </c>
       <c r="L17" t="n">
         <v>1632.969970703125</v>
@@ -1095,10 +1095,10 @@
         <v>41518</v>
       </c>
       <c r="B18" t="n">
-        <v>14.66184329986572</v>
+        <v>14.66183948516846</v>
       </c>
       <c r="C18" t="n">
-        <v>27.23135375976562</v>
+        <v>27.23135757446289</v>
       </c>
       <c r="D18" t="n">
         <v>21.71305465698242</v>
@@ -1107,10 +1107,10 @@
         <v>15.63199996948242</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3639648258686066</v>
+        <v>0.3639647364616394</v>
       </c>
       <c r="G18" t="n">
-        <v>49.75347137451172</v>
+        <v>49.75347900390625</v>
       </c>
       <c r="H18" t="n">
         <v>3.809999942779541</v>
@@ -1119,10 +1119,10 @@
         <v>12.89133262634277</v>
       </c>
       <c r="J18" t="n">
-        <v>16.88643455505371</v>
+        <v>16.88643264770508</v>
       </c>
       <c r="K18" t="n">
-        <v>3.171213865280151</v>
+        <v>3.17121410369873</v>
       </c>
       <c r="L18" t="n">
         <v>1681.550048828125</v>
@@ -1133,10 +1133,10 @@
         <v>41548</v>
       </c>
       <c r="B19" t="n">
-        <v>16.07497406005859</v>
+        <v>16.07497596740723</v>
       </c>
       <c r="C19" t="n">
-        <v>28.97422218322754</v>
+        <v>28.97422981262207</v>
       </c>
       <c r="D19" t="n">
         <v>25.54719161987305</v>
@@ -1145,10 +1145,10 @@
         <v>18.20149993896484</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3553101420402527</v>
+        <v>0.3553100228309631</v>
       </c>
       <c r="G19" t="n">
-        <v>49.73366546630859</v>
+        <v>49.73366165161133</v>
       </c>
       <c r="H19" t="n">
         <v>3.339999914169312</v>
@@ -1157,10 +1157,10 @@
         <v>10.6626672744751</v>
       </c>
       <c r="J19" t="n">
-        <v>18.02840614318848</v>
+        <v>18.02840232849121</v>
       </c>
       <c r="K19" t="n">
-        <v>3.344204664230347</v>
+        <v>3.344202995300293</v>
       </c>
       <c r="L19" t="n">
         <v>1756.5400390625</v>
@@ -1171,19 +1171,19 @@
         <v>41579</v>
       </c>
       <c r="B20" t="n">
-        <v>17.20107460021973</v>
+        <v>17.2010669708252</v>
       </c>
       <c r="C20" t="n">
-        <v>31.43649673461914</v>
+        <v>31.43648529052734</v>
       </c>
       <c r="D20" t="n">
-        <v>26.26632118225098</v>
+        <v>26.26632308959961</v>
       </c>
       <c r="E20" t="n">
         <v>19.68099975585938</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3668766021728516</v>
+        <v>0.3668765723705292</v>
       </c>
       <c r="G20" t="n">
         <v>46.56401824951172</v>
@@ -1195,7 +1195,7 @@
         <v>8.485333442687988</v>
       </c>
       <c r="J20" t="n">
-        <v>17.72867012023926</v>
+        <v>17.72867202758789</v>
       </c>
       <c r="K20" t="n">
         <v>3.292674541473389</v>
@@ -1209,10 +1209,10 @@
         <v>41609</v>
       </c>
       <c r="B21" t="n">
-        <v>17.35419654846191</v>
+        <v>17.35419082641602</v>
       </c>
       <c r="C21" t="n">
-        <v>30.84288215637207</v>
+        <v>30.84289169311523</v>
       </c>
       <c r="D21" t="n">
         <v>27.78143501281738</v>
@@ -1221,10 +1221,10 @@
         <v>19.93950080871582</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3767539858818054</v>
+        <v>0.3767540156841278</v>
       </c>
       <c r="G21" t="n">
-        <v>54.13155364990234</v>
+        <v>54.13154983520508</v>
       </c>
       <c r="H21" t="n">
         <v>3.869999885559082</v>
@@ -1233,10 +1233,10 @@
         <v>10.02866744995117</v>
       </c>
       <c r="J21" t="n">
-        <v>19.30521583557129</v>
+        <v>19.30521392822266</v>
       </c>
       <c r="K21" t="n">
-        <v>3.910868883132935</v>
+        <v>3.910867214202881</v>
       </c>
       <c r="L21" t="n">
         <v>1848.359985351562</v>
@@ -1247,19 +1247,19 @@
         <v>41640</v>
       </c>
       <c r="B22" t="n">
-        <v>15.48520755767822</v>
+        <v>15.48520183563232</v>
       </c>
       <c r="C22" t="n">
-        <v>31.19738578796387</v>
+        <v>31.19739723205566</v>
       </c>
       <c r="D22" t="n">
-        <v>29.27523422241211</v>
+        <v>29.27523231506348</v>
       </c>
       <c r="E22" t="n">
         <v>17.93449974060059</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3692283034324646</v>
+        <v>0.3692282438278198</v>
       </c>
       <c r="G22" t="n">
         <v>61.97641372680664</v>
@@ -1271,10 +1271,10 @@
         <v>12.0939998626709</v>
       </c>
       <c r="J22" t="n">
-        <v>18.24923324584961</v>
+        <v>18.24922370910645</v>
       </c>
       <c r="K22" t="n">
-        <v>4.041032314300537</v>
+        <v>4.041033744812012</v>
       </c>
       <c r="L22" t="n">
         <v>1782.589965820312</v>
@@ -1288,16 +1288,16 @@
         <v>16.37577247619629</v>
       </c>
       <c r="C23" t="n">
-        <v>31.82174301147461</v>
+        <v>31.82173728942871</v>
       </c>
       <c r="D23" t="n">
-        <v>30.13492012023926</v>
+        <v>30.13491630554199</v>
       </c>
       <c r="E23" t="n">
         <v>18.10499954223633</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4342075288295746</v>
+        <v>0.4342076480388641</v>
       </c>
       <c r="G23" t="n">
         <v>67.81053161621094</v>
@@ -1309,10 +1309,10 @@
         <v>16.3206672668457</v>
       </c>
       <c r="J23" t="n">
-        <v>18.58841896057129</v>
+        <v>18.58840942382812</v>
       </c>
       <c r="K23" t="n">
-        <v>4.56317138671875</v>
+        <v>4.563173294067383</v>
       </c>
       <c r="L23" t="n">
         <v>1859.449951171875</v>
@@ -1323,22 +1323,22 @@
         <v>41699</v>
       </c>
       <c r="B24" t="n">
-        <v>16.70252227783203</v>
+        <v>16.70251655578613</v>
       </c>
       <c r="C24" t="n">
-        <v>34.04784393310547</v>
+        <v>34.0478515625</v>
       </c>
       <c r="D24" t="n">
-        <v>27.62774276733398</v>
+        <v>27.62774085998535</v>
       </c>
       <c r="E24" t="n">
         <v>16.81850051879883</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4231044054031372</v>
+        <v>0.4231042265892029</v>
       </c>
       <c r="G24" t="n">
-        <v>59.66851806640625</v>
+        <v>59.66851425170898</v>
       </c>
       <c r="H24" t="n">
         <v>4.010000228881836</v>
@@ -1350,7 +1350,7 @@
         <v>19.37669563293457</v>
       </c>
       <c r="K24" t="n">
-        <v>4.783967018127441</v>
+        <v>4.783966064453125</v>
       </c>
       <c r="L24" t="n">
         <v>1872.339965820312</v>
@@ -1361,22 +1361,22 @@
         <v>41730</v>
       </c>
       <c r="B25" t="n">
-        <v>18.36268615722656</v>
+        <v>18.3626823425293</v>
       </c>
       <c r="C25" t="n">
-        <v>33.55777359008789</v>
+        <v>33.55775451660156</v>
       </c>
       <c r="D25" t="n">
-        <v>26.49191284179688</v>
+        <v>26.49191093444824</v>
       </c>
       <c r="E25" t="n">
         <v>15.20650005340576</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4363337755203247</v>
+        <v>0.4363337159156799</v>
       </c>
       <c r="G25" t="n">
-        <v>59.21287536621094</v>
+        <v>59.2128791809082</v>
       </c>
       <c r="H25" t="n">
         <v>4.090000152587891</v>
@@ -1385,10 +1385,10 @@
         <v>13.85933303833008</v>
       </c>
       <c r="J25" t="n">
-        <v>20.037353515625</v>
+        <v>20.03735160827637</v>
       </c>
       <c r="K25" t="n">
-        <v>4.716379642486572</v>
+        <v>4.716378211975098</v>
       </c>
       <c r="L25" t="n">
         <v>1883.949951171875</v>
@@ -1399,22 +1399,22 @@
         <v>41760</v>
       </c>
       <c r="B26" t="n">
-        <v>19.8080005645752</v>
+        <v>19.80800247192383</v>
       </c>
       <c r="C26" t="n">
-        <v>34.24621200561523</v>
+        <v>34.24623107910156</v>
       </c>
       <c r="D26" t="n">
-        <v>28.31307983398438</v>
+        <v>28.31308364868164</v>
       </c>
       <c r="E26" t="n">
         <v>15.6274995803833</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4509217441082001</v>
+        <v>0.4509217143058777</v>
       </c>
       <c r="G26" t="n">
-        <v>62.69948196411133</v>
+        <v>62.69947814941406</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
@@ -1423,10 +1423,10 @@
         <v>13.85133266448975</v>
       </c>
       <c r="J26" t="n">
-        <v>20.68655967712402</v>
+        <v>20.68655395507812</v>
       </c>
       <c r="K26" t="n">
-        <v>5.248920440673828</v>
+        <v>5.248920917510986</v>
       </c>
       <c r="L26" t="n">
         <v>1923.569946289062</v>
@@ -1437,19 +1437,19 @@
         <v>41791</v>
       </c>
       <c r="B27" t="n">
-        <v>20.35592842102051</v>
+        <v>20.35592269897461</v>
       </c>
       <c r="C27" t="n">
-        <v>34.88196182250977</v>
+        <v>34.88196563720703</v>
       </c>
       <c r="D27" t="n">
-        <v>28.95794486999512</v>
+        <v>28.95794677734375</v>
       </c>
       <c r="E27" t="n">
         <v>16.23900032043457</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4400047361850739</v>
+        <v>0.4400046169757843</v>
       </c>
       <c r="G27" t="n">
         <v>66.65163421630859</v>
@@ -1461,10 +1461,10 @@
         <v>16.00399971008301</v>
       </c>
       <c r="J27" t="n">
-        <v>23.39731407165527</v>
+        <v>23.39731025695801</v>
       </c>
       <c r="K27" t="n">
-        <v>5.374894142150879</v>
+        <v>5.374895572662354</v>
       </c>
       <c r="L27" t="n">
         <v>1960.22998046875</v>
@@ -1475,13 +1475,13 @@
         <v>41821</v>
       </c>
       <c r="B28" t="n">
-        <v>20.94077491760254</v>
+        <v>20.94077301025391</v>
       </c>
       <c r="C28" t="n">
-        <v>36.10324096679688</v>
+        <v>36.10324478149414</v>
       </c>
       <c r="D28" t="n">
-        <v>28.70435905456543</v>
+        <v>28.7043571472168</v>
       </c>
       <c r="E28" t="n">
         <v>15.64949989318848</v>
@@ -1490,7 +1490,7 @@
         <v>0.4153226613998413</v>
       </c>
       <c r="G28" t="n">
-        <v>71.96079254150391</v>
+        <v>71.96078491210938</v>
       </c>
       <c r="H28" t="n">
         <v>3.910000085830688</v>
@@ -1499,10 +1499,10 @@
         <v>14.88666725158691</v>
       </c>
       <c r="J28" t="n">
-        <v>25.66132736206055</v>
+        <v>25.66132354736328</v>
       </c>
       <c r="K28" t="n">
-        <v>5.174277782440186</v>
+        <v>5.174279689788818</v>
       </c>
       <c r="L28" t="n">
         <v>1930.670043945312</v>
@@ -1513,22 +1513,22 @@
         <v>41852</v>
       </c>
       <c r="B29" t="n">
-        <v>22.56386947631836</v>
+        <v>22.56387901306152</v>
       </c>
       <c r="C29" t="n">
         <v>38.23945236206055</v>
       </c>
       <c r="D29" t="n">
-        <v>28.84353446960449</v>
+        <v>28.84353065490723</v>
       </c>
       <c r="E29" t="n">
         <v>16.95199966430664</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4636433124542236</v>
+        <v>0.4636434018611908</v>
       </c>
       <c r="G29" t="n">
-        <v>74.11019897460938</v>
+        <v>74.11019134521484</v>
       </c>
       <c r="H29" t="n">
         <v>4.170000076293945</v>
@@ -1537,10 +1537,10 @@
         <v>17.97999954223633</v>
       </c>
       <c r="J29" t="n">
-        <v>26.61711692810059</v>
+        <v>26.61712265014648</v>
       </c>
       <c r="K29" t="n">
-        <v>6.122174263000488</v>
+        <v>6.122176647186279</v>
       </c>
       <c r="L29" t="n">
         <v>2003.369995117188</v>
@@ -1551,22 +1551,22 @@
         <v>41883</v>
       </c>
       <c r="B30" t="n">
-        <v>22.17863464355469</v>
+        <v>22.17864036560059</v>
       </c>
       <c r="C30" t="n">
-        <v>39.02224731445312</v>
+        <v>39.02224349975586</v>
       </c>
       <c r="D30" t="n">
-        <v>29.14318084716797</v>
+        <v>29.14318466186523</v>
       </c>
       <c r="E30" t="n">
         <v>16.12199974060059</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4398056268692017</v>
+        <v>0.4398057758808136</v>
       </c>
       <c r="G30" t="n">
-        <v>78.29017639160156</v>
+        <v>78.29016876220703</v>
       </c>
       <c r="H30" t="n">
         <v>3.410000085830688</v>
@@ -1575,10 +1575,10 @@
         <v>16.17866706848145</v>
       </c>
       <c r="J30" t="n">
-        <v>26.54090690612793</v>
+        <v>26.5408935546875</v>
       </c>
       <c r="K30" t="n">
-        <v>6.512059688568115</v>
+        <v>6.512059211730957</v>
       </c>
       <c r="L30" t="n">
         <v>1972.2900390625</v>
@@ -1589,22 +1589,22 @@
         <v>41913</v>
       </c>
       <c r="B31" t="n">
-        <v>23.77462196350098</v>
+        <v>23.77462387084961</v>
       </c>
       <c r="C31" t="n">
-        <v>39.51885604858398</v>
+        <v>39.51887512207031</v>
       </c>
       <c r="D31" t="n">
-        <v>28.12586212158203</v>
+        <v>28.1258602142334</v>
       </c>
       <c r="E31" t="n">
         <v>15.27299976348877</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4657887518405914</v>
+        <v>0.465788722038269</v>
       </c>
       <c r="G31" t="n">
-        <v>74.27857971191406</v>
+        <v>74.27857208251953</v>
       </c>
       <c r="H31" t="n">
         <v>2.799999952316284</v>
@@ -1613,10 +1613,10 @@
         <v>16.11333274841309</v>
       </c>
       <c r="J31" t="n">
-        <v>25.92349624633789</v>
+        <v>25.92348670959473</v>
       </c>
       <c r="K31" t="n">
-        <v>6.455920696258545</v>
+        <v>6.455919742584229</v>
       </c>
       <c r="L31" t="n">
         <v>2018.050048828125</v>
@@ -1627,10 +1627,10 @@
         <v>41944</v>
       </c>
       <c r="B32" t="n">
-        <v>26.29421615600586</v>
+        <v>26.29421997070312</v>
       </c>
       <c r="C32" t="n">
-        <v>40.49656677246094</v>
+        <v>40.4965705871582</v>
       </c>
       <c r="D32" t="n">
         <v>27.19522094726562</v>
@@ -1639,10 +1639,10 @@
         <v>16.93199920654297</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5019922256469727</v>
+        <v>0.5019921064376831</v>
       </c>
       <c r="G32" t="n">
-        <v>76.96287536621094</v>
+        <v>76.96286773681641</v>
       </c>
       <c r="H32" t="n">
         <v>2.789999961853027</v>
@@ -1651,10 +1651,10 @@
         <v>16.30133247375488</v>
       </c>
       <c r="J32" t="n">
-        <v>28.57929801940918</v>
+        <v>28.57929611206055</v>
       </c>
       <c r="K32" t="n">
-        <v>6.991106033325195</v>
+        <v>6.991106986999512</v>
       </c>
       <c r="L32" t="n">
         <v>2067.56005859375</v>
@@ -1665,7 +1665,7 @@
         <v>41974</v>
       </c>
       <c r="B33" t="n">
-        <v>24.40390014648438</v>
+        <v>24.40389633178711</v>
       </c>
       <c r="C33" t="n">
         <v>39.3446044921875</v>
@@ -1680,7 +1680,7 @@
         <v>0.4799687266349792</v>
       </c>
       <c r="G33" t="n">
-        <v>77.27982330322266</v>
+        <v>77.27983856201172</v>
       </c>
       <c r="H33" t="n">
         <v>2.670000076293945</v>
@@ -1689,7 +1689,7 @@
         <v>14.82733345031738</v>
       </c>
       <c r="J33" t="n">
-        <v>27.84275054931641</v>
+        <v>27.84275245666504</v>
       </c>
       <c r="K33" t="n">
         <v>7.556460380554199</v>
@@ -1703,19 +1703,19 @@
         <v>42005</v>
       </c>
       <c r="B34" t="n">
-        <v>25.90289497375488</v>
+        <v>25.90288925170898</v>
       </c>
       <c r="C34" t="n">
-        <v>34.22006988525391</v>
+        <v>34.22006607055664</v>
       </c>
       <c r="D34" t="n">
-        <v>26.62415313720703</v>
+        <v>26.62415504455566</v>
       </c>
       <c r="E34" t="n">
         <v>17.72649955749512</v>
       </c>
       <c r="F34" t="n">
-        <v>0.459620863199234</v>
+        <v>0.4596209228038788</v>
       </c>
       <c r="G34" t="n">
         <v>75.18985748291016</v>
@@ -1730,7 +1730,7 @@
         <v>25.34925270080566</v>
       </c>
       <c r="K34" t="n">
-        <v>7.728487491607666</v>
+        <v>7.72848653793335</v>
       </c>
       <c r="L34" t="n">
         <v>1994.989990234375</v>
@@ -1741,13 +1741,13 @@
         <v>42036</v>
       </c>
       <c r="B35" t="n">
-        <v>28.51329231262207</v>
+        <v>28.51329803466797</v>
       </c>
       <c r="C35" t="n">
-        <v>37.40665435791016</v>
+        <v>37.40664291381836</v>
       </c>
       <c r="D35" t="n">
-        <v>27.86633110046387</v>
+        <v>27.86633491516113</v>
       </c>
       <c r="E35" t="n">
         <v>19.00799942016602</v>
@@ -1756,7 +1756,7 @@
         <v>0.5301187038421631</v>
       </c>
       <c r="G35" t="n">
-        <v>78.2208251953125</v>
+        <v>78.22081756591797</v>
       </c>
       <c r="H35" t="n">
         <v>3.109999895095825</v>
@@ -1765,10 +1765,10 @@
         <v>13.55599975585938</v>
       </c>
       <c r="J35" t="n">
-        <v>25.69335746765137</v>
+        <v>25.69335556030273</v>
       </c>
       <c r="K35" t="n">
-        <v>9.586992263793945</v>
+        <v>9.586993217468262</v>
       </c>
       <c r="L35" t="n">
         <v>2104.5</v>
@@ -1779,19 +1779,19 @@
         <v>42064</v>
       </c>
       <c r="B36" t="n">
-        <v>27.61878395080566</v>
+        <v>27.6187858581543</v>
       </c>
       <c r="C36" t="n">
-        <v>34.68539810180664</v>
+        <v>34.68538665771484</v>
       </c>
       <c r="D36" t="n">
-        <v>27.47357177734375</v>
+        <v>27.47356986999512</v>
       </c>
       <c r="E36" t="n">
         <v>18.60499954223633</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5029639601707458</v>
+        <v>0.5029637813568115</v>
       </c>
       <c r="G36" t="n">
         <v>81.43998718261719</v>
@@ -1803,10 +1803,10 @@
         <v>12.58466720581055</v>
       </c>
       <c r="J36" t="n">
-        <v>24.16334533691406</v>
+        <v>24.1633415222168</v>
       </c>
       <c r="K36" t="n">
-        <v>9.567073822021484</v>
+        <v>9.567071914672852</v>
       </c>
       <c r="L36" t="n">
         <v>2067.889892578125</v>
@@ -1817,19 +1817,19 @@
         <v>42095</v>
       </c>
       <c r="B37" t="n">
-        <v>27.77860260009766</v>
+        <v>27.77859878540039</v>
       </c>
       <c r="C37" t="n">
-        <v>41.4928092956543</v>
+        <v>41.49280548095703</v>
       </c>
       <c r="D37" t="n">
-        <v>27.17986297607422</v>
+        <v>27.17986488342285</v>
       </c>
       <c r="E37" t="n">
         <v>21.0890007019043</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5334831476211548</v>
+        <v>0.5334829688072205</v>
       </c>
       <c r="G37" t="n">
         <v>78.02272033691406</v>
@@ -1841,10 +1841,10 @@
         <v>15.06999969482422</v>
       </c>
       <c r="J37" t="n">
-        <v>25.15243911743164</v>
+        <v>25.15244102478027</v>
       </c>
       <c r="K37" t="n">
-        <v>8.806108474731445</v>
+        <v>8.806105613708496</v>
       </c>
       <c r="L37" t="n">
         <v>2085.510009765625</v>
@@ -1855,10 +1855,10 @@
         <v>42125</v>
       </c>
       <c r="B38" t="n">
-        <v>29.03805541992188</v>
+        <v>29.03806495666504</v>
       </c>
       <c r="C38" t="n">
-        <v>40.23413467407227</v>
+        <v>40.23414611816406</v>
       </c>
       <c r="D38" t="n">
         <v>27.00899124145508</v>
@@ -1867,10 +1867,10 @@
         <v>21.46150016784668</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5342625379562378</v>
+        <v>0.534262478351593</v>
       </c>
       <c r="G38" t="n">
-        <v>78.43873596191406</v>
+        <v>78.43874359130859</v>
       </c>
       <c r="H38" t="n">
         <v>2.279999971389771</v>
@@ -1879,10 +1879,10 @@
         <v>16.71999931335449</v>
       </c>
       <c r="J38" t="n">
-        <v>26.8209056854248</v>
+        <v>26.8209114074707</v>
       </c>
       <c r="K38" t="n">
-        <v>11.15606212615967</v>
+        <v>11.15606021881104</v>
       </c>
       <c r="L38" t="n">
         <v>2107.389892578125</v>
@@ -1893,22 +1893,22 @@
         <v>42156</v>
       </c>
       <c r="B39" t="n">
-        <v>27.95703506469727</v>
+        <v>27.9570484161377</v>
       </c>
       <c r="C39" t="n">
-        <v>37.90732955932617</v>
+        <v>37.90733337402344</v>
       </c>
       <c r="D39" t="n">
-        <v>26.74747848510742</v>
+        <v>26.74748039245605</v>
       </c>
       <c r="E39" t="n">
         <v>21.70450019836426</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4854955077171326</v>
+        <v>0.4854954779148102</v>
       </c>
       <c r="G39" t="n">
-        <v>84.95632171630859</v>
+        <v>84.95631408691406</v>
       </c>
       <c r="H39" t="n">
         <v>2.400000095367432</v>
@@ -1917,10 +1917,10 @@
         <v>17.88400077819824</v>
       </c>
       <c r="J39" t="n">
-        <v>23.67650604248047</v>
+        <v>23.67649841308594</v>
       </c>
       <c r="K39" t="n">
-        <v>10.04366016387939</v>
+        <v>10.04365730285645</v>
       </c>
       <c r="L39" t="n">
         <v>2063.110107421875</v>
@@ -1931,19 +1931,19 @@
         <v>42186</v>
       </c>
       <c r="B40" t="n">
-        <v>27.0365104675293</v>
+        <v>27.0365047454834</v>
       </c>
       <c r="C40" t="n">
-        <v>40.09676361083984</v>
+        <v>40.09677124023438</v>
       </c>
       <c r="D40" t="n">
-        <v>32.56511688232422</v>
+        <v>32.56512451171875</v>
       </c>
       <c r="E40" t="n">
         <v>26.8075008392334</v>
       </c>
       <c r="F40" t="n">
-        <v>0.481632798910141</v>
+        <v>0.4816328585147858</v>
       </c>
       <c r="G40" t="n">
         <v>93.11813354492188</v>
@@ -1958,7 +1958,7 @@
         <v>22.53236961364746</v>
       </c>
       <c r="K40" t="n">
-        <v>9.455080032348633</v>
+        <v>9.455074310302734</v>
       </c>
       <c r="L40" t="n">
         <v>2103.840087890625</v>
@@ -1969,19 +1969,19 @@
         <v>42217</v>
       </c>
       <c r="B41" t="n">
-        <v>25.24678611755371</v>
+        <v>25.24679374694824</v>
       </c>
       <c r="C41" t="n">
-        <v>37.61282348632812</v>
+        <v>37.61281967163086</v>
       </c>
       <c r="D41" t="n">
-        <v>32.08567810058594</v>
+        <v>32.08568572998047</v>
       </c>
       <c r="E41" t="n">
         <v>25.64450073242188</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5449955463409424</v>
+        <v>0.5449956059455872</v>
       </c>
       <c r="G41" t="n">
         <v>88.58158874511719</v>
@@ -1993,10 +1993,10 @@
         <v>16.60400009155273</v>
       </c>
       <c r="J41" t="n">
-        <v>22.39778900146484</v>
+        <v>22.39779663085938</v>
       </c>
       <c r="K41" t="n">
-        <v>9.517791748046875</v>
+        <v>9.517788887023926</v>
       </c>
       <c r="L41" t="n">
         <v>1972.180053710938</v>
@@ -2007,22 +2007,22 @@
         <v>42248</v>
       </c>
       <c r="B42" t="n">
-        <v>24.69600296020508</v>
+        <v>24.69600677490234</v>
       </c>
       <c r="C42" t="n">
-        <v>38.25237655639648</v>
+        <v>38.25236129760742</v>
       </c>
       <c r="D42" t="n">
-        <v>31.61763763427734</v>
+        <v>31.61763572692871</v>
       </c>
       <c r="E42" t="n">
         <v>25.5944995880127</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5976040959358215</v>
+        <v>0.5976042151451111</v>
       </c>
       <c r="G42" t="n">
-        <v>89.04713439941406</v>
+        <v>89.04714202880859</v>
       </c>
       <c r="H42" t="n">
         <v>1.720000028610229</v>
@@ -2031,10 +2031,10 @@
         <v>16.55999946594238</v>
       </c>
       <c r="J42" t="n">
-        <v>23.6534481048584</v>
+        <v>23.65344619750977</v>
       </c>
       <c r="K42" t="n">
-        <v>9.474867820739746</v>
+        <v>9.47486686706543</v>
       </c>
       <c r="L42" t="n">
         <v>1920.030029296875</v>
@@ -2045,19 +2045,19 @@
         <v>42278</v>
       </c>
       <c r="B43" t="n">
-        <v>26.7558650970459</v>
+        <v>26.7558765411377</v>
       </c>
       <c r="C43" t="n">
-        <v>45.49492645263672</v>
+        <v>45.49491882324219</v>
       </c>
       <c r="D43" t="n">
-        <v>36.52197265625</v>
+        <v>36.52196884155273</v>
       </c>
       <c r="E43" t="n">
         <v>31.29500007629395</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6877902746200562</v>
+        <v>0.6877900958061218</v>
       </c>
       <c r="G43" t="n">
         <v>101.0026321411133</v>
@@ -2069,10 +2069,10 @@
         <v>13.79533290863037</v>
       </c>
       <c r="J43" t="n">
-        <v>26.57285118103027</v>
+        <v>26.57285499572754</v>
       </c>
       <c r="K43" t="n">
-        <v>9.332377433776855</v>
+        <v>9.332378387451172</v>
       </c>
       <c r="L43" t="n">
         <v>2079.360107421875</v>
@@ -2083,13 +2083,13 @@
         <v>42309</v>
       </c>
       <c r="B44" t="n">
-        <v>26.60057258605957</v>
+        <v>26.6005744934082</v>
       </c>
       <c r="C44" t="n">
         <v>47.28942108154297</v>
       </c>
       <c r="D44" t="n">
-        <v>37.7829704284668</v>
+        <v>37.78297424316406</v>
       </c>
       <c r="E44" t="n">
         <v>33.2400016784668</v>
@@ -2098,7 +2098,7 @@
         <v>0.7719262838363647</v>
       </c>
       <c r="G44" t="n">
-        <v>103.2510833740234</v>
+        <v>103.2510757446289</v>
       </c>
       <c r="H44" t="n">
         <v>2.359999895095825</v>
@@ -2107,10 +2107,10 @@
         <v>15.35066699981689</v>
       </c>
       <c r="J44" t="n">
-        <v>27.47922706604004</v>
+        <v>27.47922897338867</v>
       </c>
       <c r="K44" t="n">
-        <v>9.887185096740723</v>
+        <v>9.887184143066406</v>
       </c>
       <c r="L44" t="n">
         <v>2080.409912109375</v>
@@ -2121,22 +2121,22 @@
         <v>42339</v>
       </c>
       <c r="B45" t="n">
-        <v>23.66843605041504</v>
+        <v>23.66843414306641</v>
       </c>
       <c r="C45" t="n">
-        <v>48.27262496948242</v>
+        <v>48.27261734008789</v>
       </c>
       <c r="D45" t="n">
-        <v>38.53382873535156</v>
+        <v>38.53383255004883</v>
       </c>
       <c r="E45" t="n">
         <v>33.79449844360352</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8021023869514465</v>
+        <v>0.8021025061607361</v>
       </c>
       <c r="G45" t="n">
-        <v>103.667106628418</v>
+        <v>103.667121887207</v>
       </c>
       <c r="H45" t="n">
         <v>2.869999885559082</v>
@@ -2145,10 +2145,10 @@
         <v>16.00066757202148</v>
       </c>
       <c r="J45" t="n">
-        <v>27.22632598876953</v>
+        <v>27.22631645202637</v>
       </c>
       <c r="K45" t="n">
-        <v>11.03522872924805</v>
+        <v>11.03522968292236</v>
       </c>
       <c r="L45" t="n">
         <v>2043.93994140625</v>
@@ -2159,22 +2159,22 @@
         <v>42370</v>
       </c>
       <c r="B46" t="n">
-        <v>21.88756370544434</v>
+        <v>21.8875617980957</v>
       </c>
       <c r="C46" t="n">
         <v>47.93329238891602</v>
       </c>
       <c r="D46" t="n">
-        <v>37.70867538452148</v>
+        <v>37.70866775512695</v>
       </c>
       <c r="E46" t="n">
         <v>29.35000038146973</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7127906084060669</v>
+        <v>0.7127907872200012</v>
       </c>
       <c r="G46" t="n">
-        <v>111.1454772949219</v>
+        <v>111.1454849243164</v>
       </c>
       <c r="H46" t="n">
         <v>2.200000047683716</v>
@@ -2183,10 +2183,10 @@
         <v>12.74666690826416</v>
       </c>
       <c r="J46" t="n">
-        <v>24.51554489135742</v>
+        <v>24.51554870605469</v>
       </c>
       <c r="K46" t="n">
-        <v>10.16548919677734</v>
+        <v>10.16548442840576</v>
       </c>
       <c r="L46" t="n">
         <v>1940.239990234375</v>
@@ -2197,10 +2197,10 @@
         <v>42401</v>
       </c>
       <c r="B47" t="n">
-        <v>21.8593864440918</v>
+        <v>21.85938262939453</v>
       </c>
       <c r="C47" t="n">
-        <v>44.58806610107422</v>
+        <v>44.58807373046875</v>
       </c>
       <c r="D47" t="n">
         <v>35.52297592163086</v>
@@ -2209,10 +2209,10 @@
         <v>27.62599945068359</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7659458518028259</v>
+        <v>0.7659459114074707</v>
       </c>
       <c r="G47" t="n">
-        <v>105.9056625366211</v>
+        <v>105.9056701660156</v>
       </c>
       <c r="H47" t="n">
         <v>2.140000104904175</v>
@@ -2221,10 +2221,10 @@
         <v>12.79533290863037</v>
       </c>
       <c r="J47" t="n">
-        <v>23.59122276306152</v>
+        <v>23.59122467041016</v>
       </c>
       <c r="K47" t="n">
-        <v>10.18525505065918</v>
+        <v>10.18525409698486</v>
       </c>
       <c r="L47" t="n">
         <v>1932.22998046875</v>
@@ -2235,19 +2235,19 @@
         <v>42430</v>
       </c>
       <c r="B48" t="n">
-        <v>24.64013671875</v>
+        <v>24.64013481140137</v>
       </c>
       <c r="C48" t="n">
         <v>48.4001350402832</v>
       </c>
       <c r="D48" t="n">
-        <v>37.78543853759766</v>
+        <v>37.78544235229492</v>
       </c>
       <c r="E48" t="n">
         <v>29.68199920654297</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8702375292778015</v>
+        <v>0.8702373504638672</v>
       </c>
       <c r="G48" t="n">
         <v>113.0175552368164</v>
@@ -2259,10 +2259,10 @@
         <v>15.31799983978271</v>
       </c>
       <c r="J48" t="n">
-        <v>25.79169273376465</v>
+        <v>25.79168701171875</v>
       </c>
       <c r="K48" t="n">
-        <v>11.78496742248535</v>
+        <v>11.7849702835083</v>
       </c>
       <c r="L48" t="n">
         <v>2059.739990234375</v>
@@ -2273,22 +2273,22 @@
         <v>42461</v>
       </c>
       <c r="B49" t="n">
-        <v>21.19246292114258</v>
+        <v>21.19245910644531</v>
       </c>
       <c r="C49" t="n">
-        <v>43.70296478271484</v>
+        <v>43.70296096801758</v>
       </c>
       <c r="D49" t="n">
-        <v>35.06038284301758</v>
+        <v>35.06037902832031</v>
       </c>
       <c r="E49" t="n">
         <v>32.97949981689453</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8677949905395508</v>
+        <v>0.8677952885627747</v>
       </c>
       <c r="G49" t="n">
-        <v>116.4645385742188</v>
+        <v>116.4645309448242</v>
       </c>
       <c r="H49" t="n">
         <v>3.549999952316284</v>
@@ -2297,10 +2297,10 @@
         <v>16.05066680908203</v>
       </c>
       <c r="J49" t="n">
-        <v>24.14133834838867</v>
+        <v>24.14134407043457</v>
       </c>
       <c r="K49" t="n">
-        <v>11.11753463745117</v>
+        <v>11.11753177642822</v>
       </c>
       <c r="L49" t="n">
         <v>2065.300048828125</v>
@@ -2311,22 +2311,22 @@
         <v>42491</v>
       </c>
       <c r="B50" t="n">
-        <v>22.7135066986084</v>
+        <v>22.71350479125977</v>
       </c>
       <c r="C50" t="n">
-        <v>46.770751953125</v>
+        <v>46.77075958251953</v>
       </c>
       <c r="D50" t="n">
-        <v>37.08956527709961</v>
+        <v>37.08956909179688</v>
       </c>
       <c r="E50" t="n">
         <v>36.13949966430664</v>
       </c>
       <c r="F50" t="n">
-        <v>1.144066214561462</v>
+        <v>1.144066095352173</v>
       </c>
       <c r="G50" t="n">
-        <v>117.682861328125</v>
+        <v>117.6828689575195</v>
       </c>
       <c r="H50" t="n">
         <v>4.570000171661377</v>
@@ -2335,7 +2335,7 @@
         <v>14.88199996948242</v>
       </c>
       <c r="J50" t="n">
-        <v>25.40332221984863</v>
+        <v>25.4033260345459</v>
       </c>
       <c r="K50" t="n">
         <v>11.77429103851318</v>
@@ -2349,19 +2349,19 @@
         <v>42522</v>
       </c>
       <c r="B51" t="n">
-        <v>21.74455451965332</v>
+        <v>21.74455261230469</v>
       </c>
       <c r="C51" t="n">
-        <v>45.15584945678711</v>
+        <v>45.15583801269531</v>
       </c>
       <c r="D51" t="n">
-        <v>34.84492492675781</v>
+        <v>34.84492111206055</v>
       </c>
       <c r="E51" t="n">
         <v>35.78099822998047</v>
       </c>
       <c r="F51" t="n">
-        <v>1.151167750358582</v>
+        <v>1.151167631149292</v>
       </c>
       <c r="G51" t="n">
         <v>113.1958465576172</v>
@@ -2373,10 +2373,10 @@
         <v>14.15200042724609</v>
       </c>
       <c r="J51" t="n">
-        <v>26.37635040283203</v>
+        <v>26.37634468078613</v>
       </c>
       <c r="K51" t="n">
-        <v>11.89101409912109</v>
+        <v>11.89101791381836</v>
       </c>
       <c r="L51" t="n">
         <v>2098.860107421875</v>
@@ -2387,10 +2387,10 @@
         <v>42552</v>
       </c>
       <c r="B52" t="n">
-        <v>23.70293235778809</v>
+        <v>23.70292663574219</v>
       </c>
       <c r="C52" t="n">
-        <v>50.01823425292969</v>
+        <v>50.01824188232422</v>
       </c>
       <c r="D52" t="n">
         <v>39.19403839111328</v>
@@ -2399,10 +2399,10 @@
         <v>37.94049835205078</v>
       </c>
       <c r="F52" t="n">
-        <v>1.398248672485352</v>
+        <v>1.398248553276062</v>
       </c>
       <c r="G52" t="n">
-        <v>122.7641906738281</v>
+        <v>122.7642059326172</v>
       </c>
       <c r="H52" t="n">
         <v>6.860000133514404</v>
@@ -2411,10 +2411,10 @@
         <v>15.65266704559326</v>
       </c>
       <c r="J52" t="n">
-        <v>28.03290939331055</v>
+        <v>28.03291320800781</v>
       </c>
       <c r="K52" t="n">
-        <v>12.39450931549072</v>
+        <v>12.39450836181641</v>
       </c>
       <c r="L52" t="n">
         <v>2173.60009765625</v>
@@ -2425,22 +2425,22 @@
         <v>42583</v>
       </c>
       <c r="B53" t="n">
-        <v>24.26355171203613</v>
+        <v>24.26354217529297</v>
       </c>
       <c r="C53" t="n">
-        <v>51.02258682250977</v>
+        <v>51.0225944519043</v>
       </c>
       <c r="D53" t="n">
-        <v>39.12024307250977</v>
+        <v>39.12025451660156</v>
       </c>
       <c r="E53" t="n">
         <v>38.45800018310547</v>
       </c>
       <c r="F53" t="n">
-        <v>1.504844546318054</v>
+        <v>1.504844903945923</v>
       </c>
       <c r="G53" t="n">
-        <v>124.9235229492188</v>
+        <v>124.9235305786133</v>
       </c>
       <c r="H53" t="n">
         <v>7.400000095367432</v>
@@ -2449,10 +2449,10 @@
         <v>14.13399982452393</v>
       </c>
       <c r="J53" t="n">
-        <v>29.07996368408203</v>
+        <v>29.0799732208252</v>
       </c>
       <c r="K53" t="n">
-        <v>13.49943923950195</v>
+        <v>13.49944114685059</v>
       </c>
       <c r="L53" t="n">
         <v>2170.949951171875</v>
@@ -2463,7 +2463,7 @@
         <v>42614</v>
       </c>
       <c r="B54" t="n">
-        <v>25.85290908813477</v>
+        <v>25.85291290283203</v>
       </c>
       <c r="C54" t="n">
         <v>51.14691162109375</v>
@@ -2475,10 +2475,10 @@
         <v>41.86550140380859</v>
       </c>
       <c r="F54" t="n">
-        <v>1.680990815162659</v>
+        <v>1.68099045753479</v>
       </c>
       <c r="G54" t="n">
-        <v>127.0531158447266</v>
+        <v>127.0531234741211</v>
       </c>
       <c r="H54" t="n">
         <v>6.909999847412109</v>
@@ -2487,10 +2487,10 @@
         <v>13.60200023651123</v>
       </c>
       <c r="J54" t="n">
-        <v>30.58703804016113</v>
+        <v>30.5870361328125</v>
       </c>
       <c r="K54" t="n">
-        <v>13.2408275604248</v>
+        <v>13.24083137512207</v>
       </c>
       <c r="L54" t="n">
         <v>2168.27001953125</v>
@@ -2501,7 +2501,7 @@
         <v>42644</v>
       </c>
       <c r="B55" t="n">
-        <v>25.9649658203125</v>
+        <v>25.9649715423584</v>
       </c>
       <c r="C55" t="n">
         <v>53.20700073242188</v>
@@ -2516,7 +2516,7 @@
         <v>1.745757460594177</v>
       </c>
       <c r="G55" t="n">
-        <v>129.747314453125</v>
+        <v>129.7473297119141</v>
       </c>
       <c r="H55" t="n">
         <v>7.230000019073486</v>
@@ -2525,10 +2525,10 @@
         <v>13.18200016021729</v>
       </c>
       <c r="J55" t="n">
-        <v>28.25351142883301</v>
+        <v>28.25350761413574</v>
       </c>
       <c r="K55" t="n">
-        <v>13.06891059875488</v>
+        <v>13.06891345977783</v>
       </c>
       <c r="L55" t="n">
         <v>2126.14990234375</v>
@@ -2539,19 +2539,19 @@
         <v>42675</v>
       </c>
       <c r="B56" t="n">
-        <v>25.40409660339355</v>
+        <v>25.40410232543945</v>
       </c>
       <c r="C56" t="n">
-        <v>53.87038421630859</v>
+        <v>53.87038803100586</v>
       </c>
       <c r="D56" t="n">
-        <v>38.42832183837891</v>
+        <v>38.42832946777344</v>
       </c>
       <c r="E56" t="n">
         <v>37.52849960327148</v>
       </c>
       <c r="F56" t="n">
-        <v>2.265315055847168</v>
+        <v>2.265315294265747</v>
       </c>
       <c r="G56" t="n">
         <v>117.2965698242188</v>
@@ -2563,10 +2563,10 @@
         <v>12.62666702270508</v>
       </c>
       <c r="J56" t="n">
-        <v>28.32863807678223</v>
+        <v>28.32863616943359</v>
       </c>
       <c r="K56" t="n">
-        <v>13.08502674102783</v>
+        <v>13.0850305557251</v>
       </c>
       <c r="L56" t="n">
         <v>2198.81005859375</v>
@@ -2577,10 +2577,10 @@
         <v>42705</v>
       </c>
       <c r="B57" t="n">
-        <v>26.62235260009766</v>
+        <v>26.62235641479492</v>
       </c>
       <c r="C57" t="n">
-        <v>55.55105209350586</v>
+        <v>55.55104827880859</v>
       </c>
       <c r="D57" t="n">
         <v>39.24901962280273</v>
@@ -2589,10 +2589,10 @@
         <v>37.49349975585938</v>
       </c>
       <c r="F57" t="n">
-        <v>2.62255597114563</v>
+        <v>2.622557163238525</v>
       </c>
       <c r="G57" t="n">
-        <v>113.9585571289062</v>
+        <v>113.9585494995117</v>
       </c>
       <c r="H57" t="n">
         <v>11.34000015258789</v>
@@ -2601,10 +2601,10 @@
         <v>14.24600028991699</v>
       </c>
       <c r="J57" t="n">
-        <v>29.6103687286377</v>
+        <v>29.6103630065918</v>
       </c>
       <c r="K57" t="n">
-        <v>13.64457893371582</v>
+        <v>13.64457702636719</v>
       </c>
       <c r="L57" t="n">
         <v>2238.830078125</v>
@@ -2618,16 +2618,16 @@
         <v>27.89348602294922</v>
       </c>
       <c r="C58" t="n">
-        <v>57.79491424560547</v>
+        <v>57.79490661621094</v>
       </c>
       <c r="D58" t="n">
-        <v>40.6229362487793</v>
+        <v>40.62294006347656</v>
       </c>
       <c r="E58" t="n">
         <v>41.17399978637695</v>
       </c>
       <c r="F58" t="n">
-        <v>2.68250560760498</v>
+        <v>2.682506322860718</v>
       </c>
       <c r="G58" t="n">
         <v>129.0836944580078</v>
@@ -2639,10 +2639,10 @@
         <v>16.79533386230469</v>
       </c>
       <c r="J58" t="n">
-        <v>30.05938148498535</v>
+        <v>30.05938720703125</v>
       </c>
       <c r="K58" t="n">
-        <v>15.39906978607178</v>
+        <v>15.39906883239746</v>
       </c>
       <c r="L58" t="n">
         <v>2278.8701171875</v>
@@ -2653,7 +2653,7 @@
         <v>42767</v>
       </c>
       <c r="B59" t="n">
-        <v>31.62500953674316</v>
+        <v>31.62501525878906</v>
       </c>
       <c r="C59" t="n">
         <v>57.54269790649414</v>
@@ -2665,7 +2665,7 @@
         <v>42.25199890136719</v>
       </c>
       <c r="F59" t="n">
-        <v>2.496467351913452</v>
+        <v>2.496467113494873</v>
       </c>
       <c r="G59" t="n">
         <v>134.2541656494141</v>
@@ -2677,7 +2677,7 @@
         <v>16.66600036621094</v>
       </c>
       <c r="J59" t="n">
-        <v>29.76419258117676</v>
+        <v>29.76419639587402</v>
       </c>
       <c r="K59" t="n">
         <v>16.28133201599121</v>
@@ -2691,13 +2691,13 @@
         <v>42795</v>
       </c>
       <c r="B60" t="n">
-        <v>33.16482162475586</v>
+        <v>33.16482925415039</v>
       </c>
       <c r="C60" t="n">
         <v>59.23354339599609</v>
       </c>
       <c r="D60" t="n">
-        <v>41.99044036865234</v>
+        <v>41.99043655395508</v>
       </c>
       <c r="E60" t="n">
         <v>44.32699966430664</v>
@@ -2706,7 +2706,7 @@
         <v>2.679741144180298</v>
       </c>
       <c r="G60" t="n">
-        <v>140.7023773193359</v>
+        <v>140.7024078369141</v>
       </c>
       <c r="H60" t="n">
         <v>14.55000019073486</v>
@@ -2715,10 +2715,10 @@
         <v>18.5533332824707</v>
       </c>
       <c r="J60" t="n">
-        <v>29.65730857849121</v>
+        <v>29.65730476379395</v>
       </c>
       <c r="K60" t="n">
-        <v>16.97779846191406</v>
+        <v>16.97780609130859</v>
       </c>
       <c r="L60" t="n">
         <v>2362.719970703125</v>
@@ -2729,22 +2729,22 @@
         <v>42826</v>
       </c>
       <c r="B61" t="n">
-        <v>33.16250610351562</v>
+        <v>33.16251373291016</v>
       </c>
       <c r="C61" t="n">
-        <v>61.57194900512695</v>
+        <v>61.57193374633789</v>
       </c>
       <c r="D61" t="n">
-        <v>45.79027557373047</v>
+        <v>45.7902717590332</v>
       </c>
       <c r="E61" t="n">
         <v>46.2495002746582</v>
       </c>
       <c r="F61" t="n">
-        <v>2.565840244293213</v>
+        <v>2.565840482711792</v>
       </c>
       <c r="G61" t="n">
-        <v>148.8246154785156</v>
+        <v>148.8245697021484</v>
       </c>
       <c r="H61" t="n">
         <v>13.30000019073486</v>
@@ -2753,10 +2753,10 @@
         <v>20.9379997253418</v>
       </c>
       <c r="J61" t="n">
-        <v>29.72309684753418</v>
+        <v>29.72308158874512</v>
       </c>
       <c r="K61" t="n">
-        <v>17.12124824523926</v>
+        <v>17.12124443054199</v>
       </c>
       <c r="L61" t="n">
         <v>2384.199951171875</v>
@@ -2767,10 +2767,10 @@
         <v>42856</v>
       </c>
       <c r="B62" t="n">
-        <v>35.41117095947266</v>
+        <v>35.41117858886719</v>
       </c>
       <c r="C62" t="n">
-        <v>63.17313003540039</v>
+        <v>63.17313766479492</v>
       </c>
       <c r="D62" t="n">
         <v>48.8892822265625</v>
@@ -2779,10 +2779,10 @@
         <v>49.73099899291992</v>
       </c>
       <c r="F62" t="n">
-        <v>3.554834365844727</v>
+        <v>3.554834604263306</v>
       </c>
       <c r="G62" t="n">
-        <v>150.0231323242188</v>
+        <v>150.0231475830078</v>
       </c>
       <c r="H62" t="n">
         <v>11.1899995803833</v>
@@ -2791,10 +2791,10 @@
         <v>22.73399925231934</v>
       </c>
       <c r="J62" t="n">
-        <v>29.91107177734375</v>
+        <v>29.91107749938965</v>
       </c>
       <c r="K62" t="n">
-        <v>18.56888771057129</v>
+        <v>18.56889343261719</v>
       </c>
       <c r="L62" t="n">
         <v>2411.800048828125</v>
@@ -2805,10 +2805,10 @@
         <v>42887</v>
       </c>
       <c r="B63" t="n">
-        <v>33.38515472412109</v>
+        <v>33.38517379760742</v>
       </c>
       <c r="C63" t="n">
-        <v>62.34999847412109</v>
+        <v>62.35000228881836</v>
       </c>
       <c r="D63" t="n">
         <v>46.04583740234375</v>
@@ -2817,7 +2817,7 @@
         <v>48.40000152587891</v>
       </c>
       <c r="F63" t="n">
-        <v>3.560005903244019</v>
+        <v>3.560005664825439</v>
       </c>
       <c r="G63" t="n">
         <v>149.5476837158203</v>
@@ -2829,10 +2829,10 @@
         <v>24.10733222961426</v>
       </c>
       <c r="J63" t="n">
-        <v>27.94792938232422</v>
+        <v>27.94792366027832</v>
       </c>
       <c r="K63" t="n">
-        <v>18.14727783203125</v>
+        <v>18.14726638793945</v>
       </c>
       <c r="L63" t="n">
         <v>2423.409912109375</v>
@@ -2843,13 +2843,13 @@
         <v>42917</v>
       </c>
       <c r="B64" t="n">
-        <v>34.47698974609375</v>
+        <v>34.47697448730469</v>
       </c>
       <c r="C64" t="n">
         <v>65.76011657714844</v>
       </c>
       <c r="D64" t="n">
-        <v>46.82938385009766</v>
+        <v>46.82939147949219</v>
       </c>
       <c r="E64" t="n">
         <v>49.38899993896484</v>
@@ -2858,7 +2858,7 @@
         <v>4.002050876617432</v>
       </c>
       <c r="G64" t="n">
-        <v>167.6443786621094</v>
+        <v>167.6443328857422</v>
       </c>
       <c r="H64" t="n">
         <v>13.60999965667725</v>
@@ -2867,10 +2867,10 @@
         <v>21.56466674804688</v>
       </c>
       <c r="J64" t="n">
-        <v>29.38093948364258</v>
+        <v>29.38094329833984</v>
       </c>
       <c r="K64" t="n">
-        <v>19.20706367492676</v>
+        <v>19.20705986022949</v>
       </c>
       <c r="L64" t="n">
         <v>2470.300048828125</v>
@@ -2881,10 +2881,10 @@
         <v>42948</v>
       </c>
       <c r="B65" t="n">
-        <v>38.16600799560547</v>
+        <v>38.16600036621094</v>
       </c>
       <c r="C65" t="n">
-        <v>67.99285888671875</v>
+        <v>67.99284362792969</v>
       </c>
       <c r="D65" t="n">
         <v>47.31179809570312</v>
@@ -2893,10 +2893,10 @@
         <v>49.02999877929688</v>
       </c>
       <c r="F65" t="n">
-        <v>4.176387786865234</v>
+        <v>4.176384925842285</v>
       </c>
       <c r="G65" t="n">
-        <v>170.3385314941406</v>
+        <v>170.3385467529297</v>
       </c>
       <c r="H65" t="n">
         <v>13</v>
@@ -2905,10 +2905,10 @@
         <v>23.7266674041748</v>
       </c>
       <c r="J65" t="n">
-        <v>29.26767730712891</v>
+        <v>29.26767349243164</v>
       </c>
       <c r="K65" t="n">
-        <v>19.62832832336426</v>
+        <v>19.62833023071289</v>
       </c>
       <c r="L65" t="n">
         <v>2471.64990234375</v>
@@ -2919,13 +2919,13 @@
         <v>42979</v>
       </c>
       <c r="B66" t="n">
-        <v>35.86673355102539</v>
+        <v>35.86674499511719</v>
       </c>
       <c r="C66" t="n">
-        <v>67.73822784423828</v>
+        <v>67.73824310302734</v>
       </c>
       <c r="D66" t="n">
-        <v>48.22708892822266</v>
+        <v>48.22708129882812</v>
       </c>
       <c r="E66" t="n">
         <v>48.06750106811523</v>
@@ -2934,7 +2934,7 @@
         <v>4.406355857849121</v>
       </c>
       <c r="G66" t="n">
-        <v>169.2489776611328</v>
+        <v>169.2490081787109</v>
       </c>
       <c r="H66" t="n">
         <v>12.75</v>
@@ -2943,10 +2943,10 @@
         <v>22.73999977111816</v>
       </c>
       <c r="J66" t="n">
-        <v>31.7796688079834</v>
+        <v>31.7796745300293</v>
       </c>
       <c r="K66" t="n">
-        <v>18.96344757080078</v>
+        <v>18.96344566345215</v>
       </c>
       <c r="L66" t="n">
         <v>2519.360107421875</v>
@@ -2957,22 +2957,22 @@
         <v>43009</v>
       </c>
       <c r="B67" t="n">
-        <v>39.33891296386719</v>
+        <v>39.33892440795898</v>
       </c>
       <c r="C67" t="n">
-        <v>75.64057922363281</v>
+        <v>75.64060211181641</v>
       </c>
       <c r="D67" t="n">
-        <v>51.16512680053711</v>
+        <v>51.16513061523438</v>
       </c>
       <c r="E67" t="n">
         <v>55.26399993896484</v>
       </c>
       <c r="F67" t="n">
-        <v>5.097490310668945</v>
+        <v>5.097489356994629</v>
       </c>
       <c r="G67" t="n">
-        <v>178.351806640625</v>
+        <v>178.3517913818359</v>
       </c>
       <c r="H67" t="n">
         <v>10.98999977111816</v>
@@ -2981,10 +2981,10 @@
         <v>22.10199928283691</v>
       </c>
       <c r="J67" t="n">
-        <v>37.96368789672852</v>
+        <v>37.96369552612305</v>
       </c>
       <c r="K67" t="n">
-        <v>20.63430023193359</v>
+        <v>20.63429832458496</v>
       </c>
       <c r="L67" t="n">
         <v>2575.260009765625</v>
@@ -2995,22 +2995,22 @@
         <v>43040</v>
       </c>
       <c r="B68" t="n">
-        <v>40.13661575317383</v>
+        <v>40.13662719726562</v>
       </c>
       <c r="C68" t="n">
-        <v>76.92524719238281</v>
+        <v>76.92522430419922</v>
       </c>
       <c r="D68" t="n">
-        <v>51.32015228271484</v>
+        <v>51.32014846801758</v>
       </c>
       <c r="E68" t="n">
         <v>58.83750152587891</v>
       </c>
       <c r="F68" t="n">
-        <v>4.950572967529297</v>
+        <v>4.950571537017822</v>
       </c>
       <c r="G68" t="n">
-        <v>175.4991302490234</v>
+        <v>175.4991149902344</v>
       </c>
       <c r="H68" t="n">
         <v>10.89000034332275</v>
@@ -3019,7 +3019,7 @@
         <v>20.59000015258789</v>
       </c>
       <c r="J68" t="n">
-        <v>37.64299774169922</v>
+        <v>37.64299392700195</v>
       </c>
       <c r="K68" t="n">
         <v>21.73125839233398</v>
@@ -3033,10 +3033,10 @@
         <v>43070</v>
       </c>
       <c r="B69" t="n">
-        <v>39.52470779418945</v>
+        <v>39.52470397949219</v>
       </c>
       <c r="C69" t="n">
-        <v>78.17732238769531</v>
+        <v>78.17731475830078</v>
       </c>
       <c r="D69" t="n">
         <v>52.17352676391602</v>
@@ -3045,7 +3045,7 @@
         <v>58.4734992980957</v>
       </c>
       <c r="F69" t="n">
-        <v>4.772736072540283</v>
+        <v>4.772734642028809</v>
       </c>
       <c r="G69" t="n">
         <v>174.7859649658203</v>
@@ -3057,10 +3057,10 @@
         <v>20.75666618347168</v>
       </c>
       <c r="J69" t="n">
-        <v>38.75113677978516</v>
+        <v>38.75113296508789</v>
       </c>
       <c r="K69" t="n">
-        <v>20.21936225891113</v>
+        <v>20.21936416625977</v>
       </c>
       <c r="L69" t="n">
         <v>2673.610107421875</v>
@@ -3071,22 +3071,22 @@
         <v>43101</v>
       </c>
       <c r="B70" t="n">
-        <v>39.10429000854492</v>
+        <v>39.10430526733398</v>
       </c>
       <c r="C70" t="n">
-        <v>86.83221435546875</v>
+        <v>86.83222198486328</v>
       </c>
       <c r="D70" t="n">
-        <v>58.55382537841797</v>
+        <v>58.5538215637207</v>
       </c>
       <c r="E70" t="n">
         <v>72.54450225830078</v>
       </c>
       <c r="F70" t="n">
-        <v>6.062728404998779</v>
+        <v>6.062729835510254</v>
       </c>
       <c r="G70" t="n">
-        <v>185.1170043945312</v>
+        <v>185.1169891357422</v>
       </c>
       <c r="H70" t="n">
         <v>13.73999977111816</v>
@@ -3098,7 +3098,7 @@
         <v>40.4133415222168</v>
       </c>
       <c r="K70" t="n">
-        <v>19.5212459564209</v>
+        <v>19.52124786376953</v>
       </c>
       <c r="L70" t="n">
         <v>2823.81005859375</v>
@@ -3112,19 +3112,19 @@
         <v>41.7706298828125</v>
       </c>
       <c r="C71" t="n">
-        <v>86.10150909423828</v>
+        <v>86.10148620605469</v>
       </c>
       <c r="D71" t="n">
-        <v>54.67573165893555</v>
+        <v>54.67572784423828</v>
       </c>
       <c r="E71" t="n">
         <v>75.62249755859375</v>
       </c>
       <c r="F71" t="n">
-        <v>5.972712516784668</v>
+        <v>5.972711563110352</v>
       </c>
       <c r="G71" t="n">
-        <v>176.6283111572266</v>
+        <v>176.6282958984375</v>
       </c>
       <c r="H71" t="n">
         <v>12.10999965667725</v>
@@ -3136,7 +3136,7 @@
         <v>41.65947723388672</v>
       </c>
       <c r="K71" t="n">
-        <v>19.39768028259277</v>
+        <v>19.39768409729004</v>
       </c>
       <c r="L71" t="n">
         <v>2713.830078125</v>
@@ -3150,19 +3150,19 @@
         <v>39.34581756591797</v>
       </c>
       <c r="C72" t="n">
-        <v>83.80594635009766</v>
+        <v>83.80596923828125</v>
       </c>
       <c r="D72" t="n">
-        <v>51.36819076538086</v>
+        <v>51.36819839477539</v>
       </c>
       <c r="E72" t="n">
         <v>72.36699676513672</v>
       </c>
       <c r="F72" t="n">
-        <v>5.715787410736084</v>
+        <v>5.715786457061768</v>
       </c>
       <c r="G72" t="n">
-        <v>158.2740936279297</v>
+        <v>158.2741088867188</v>
       </c>
       <c r="H72" t="n">
         <v>10.05000019073486</v>
@@ -3171,10 +3171,10 @@
         <v>17.74200057983398</v>
       </c>
       <c r="J72" t="n">
-        <v>44.0175666809082</v>
+        <v>44.01756286621094</v>
       </c>
       <c r="K72" t="n">
-        <v>18.81864738464355</v>
+        <v>18.81864356994629</v>
       </c>
       <c r="L72" t="n">
         <v>2640.8701171875</v>
@@ -3185,22 +3185,22 @@
         <v>43191</v>
       </c>
       <c r="B73" t="n">
-        <v>38.75485610961914</v>
+        <v>38.75485229492188</v>
       </c>
       <c r="C73" t="n">
-        <v>85.87196350097656</v>
+        <v>85.87197113037109</v>
       </c>
       <c r="D73" t="n">
-        <v>50.44894027709961</v>
+        <v>50.44894790649414</v>
       </c>
       <c r="E73" t="n">
         <v>78.30650329589844</v>
       </c>
       <c r="F73" t="n">
-        <v>5.550673007965088</v>
+        <v>5.550672054290771</v>
       </c>
       <c r="G73" t="n">
-        <v>170.3682708740234</v>
+        <v>170.3682556152344</v>
       </c>
       <c r="H73" t="n">
         <v>10.88000011444092</v>
@@ -3212,7 +3212,7 @@
         <v>43.62877655029297</v>
       </c>
       <c r="K73" t="n">
-        <v>18.32112503051758</v>
+        <v>18.32112884521484</v>
       </c>
       <c r="L73" t="n">
         <v>2648.050048828125</v>
@@ -3226,16 +3226,16 @@
         <v>43.9915657043457</v>
       </c>
       <c r="C74" t="n">
-        <v>91.1502685546875</v>
+        <v>91.15024566650391</v>
       </c>
       <c r="D74" t="n">
-        <v>54.4815673828125</v>
+        <v>54.48156356811523</v>
       </c>
       <c r="E74" t="n">
         <v>81.48100280761719</v>
       </c>
       <c r="F74" t="n">
-        <v>6.228055477142334</v>
+        <v>6.228056907653809</v>
       </c>
       <c r="G74" t="n">
         <v>189.9606170654297</v>
@@ -3247,7 +3247,7 @@
         <v>18.98200035095215</v>
       </c>
       <c r="J74" t="n">
-        <v>46.92382431030273</v>
+        <v>46.923828125</v>
       </c>
       <c r="K74" t="n">
         <v>20.12992095947266</v>
@@ -3261,22 +3261,22 @@
         <v>43252</v>
       </c>
       <c r="B75" t="n">
-        <v>43.57723236083984</v>
+        <v>43.57724380493164</v>
       </c>
       <c r="C75" t="n">
-        <v>90.93814086914062</v>
+        <v>90.93815612792969</v>
       </c>
       <c r="D75" t="n">
-        <v>55.92730712890625</v>
+        <v>55.92731094360352</v>
       </c>
       <c r="E75" t="n">
         <v>84.98999786376953</v>
       </c>
       <c r="F75" t="n">
-        <v>5.850456714630127</v>
+        <v>5.850456237792969</v>
       </c>
       <c r="G75" t="n">
-        <v>192.4765319824219</v>
+        <v>192.4765167236328</v>
       </c>
       <c r="H75" t="n">
         <v>14.98999977111816</v>
@@ -3288,7 +3288,7 @@
         <v>42.2569465637207</v>
       </c>
       <c r="K75" t="n">
-        <v>19.6367015838623</v>
+        <v>19.63669967651367</v>
       </c>
       <c r="L75" t="n">
         <v>2718.3701171875</v>
@@ -3299,19 +3299,19 @@
         <v>43282</v>
       </c>
       <c r="B76" t="n">
-        <v>44.79666900634766</v>
+        <v>44.79666137695312</v>
       </c>
       <c r="C76" t="n">
-        <v>97.82698822021484</v>
+        <v>97.82697296142578</v>
       </c>
       <c r="D76" t="n">
-        <v>60.78260803222656</v>
+        <v>60.78261566162109</v>
       </c>
       <c r="E76" t="n">
         <v>88.87200164794922</v>
       </c>
       <c r="F76" t="n">
-        <v>6.047035217285156</v>
+        <v>6.047035694122314</v>
       </c>
       <c r="G76" t="n">
         <v>170.9427642822266</v>
@@ -3323,10 +3323,10 @@
         <v>19.87599945068359</v>
       </c>
       <c r="J76" t="n">
-        <v>40.88832092285156</v>
+        <v>40.88833236694336</v>
       </c>
       <c r="K76" t="n">
-        <v>17.94770240783691</v>
+        <v>17.94770431518555</v>
       </c>
       <c r="L76" t="n">
         <v>2816.2900390625</v>
@@ -3340,10 +3340,10 @@
         <v>53.77492141723633</v>
       </c>
       <c r="C77" t="n">
-        <v>103.9893951416016</v>
+        <v>103.989387512207</v>
       </c>
       <c r="D77" t="n">
-        <v>61.00945663452148</v>
+        <v>61.00945281982422</v>
       </c>
       <c r="E77" t="n">
         <v>100.635498046875</v>
@@ -3352,7 +3352,7 @@
         <v>6.935434341430664</v>
       </c>
       <c r="G77" t="n">
-        <v>174.0628509521484</v>
+        <v>174.0628814697266</v>
       </c>
       <c r="H77" t="n">
         <v>25.17000007629395</v>
@@ -3361,10 +3361,10 @@
         <v>20.11066627502441</v>
       </c>
       <c r="J77" t="n">
-        <v>41.41922760009766</v>
+        <v>41.41922378540039</v>
       </c>
       <c r="K77" t="n">
-        <v>17.72595405578613</v>
+        <v>17.7259521484375</v>
       </c>
       <c r="L77" t="n">
         <v>2901.52001953125</v>
@@ -3378,19 +3378,19 @@
         <v>53.32843399047852</v>
       </c>
       <c r="C78" t="n">
-        <v>105.8779220581055</v>
+        <v>105.8779296875</v>
       </c>
       <c r="D78" t="n">
-        <v>59.78510665893555</v>
+        <v>59.78510284423828</v>
       </c>
       <c r="E78" t="n">
         <v>100.1500015258789</v>
       </c>
       <c r="F78" t="n">
-        <v>6.943834781646729</v>
+        <v>6.943835258483887</v>
       </c>
       <c r="G78" t="n">
-        <v>162.8997802734375</v>
+        <v>162.8997955322266</v>
       </c>
       <c r="H78" t="n">
         <v>30.88999938964844</v>
@@ -3402,7 +3402,7 @@
         <v>40.44425201416016</v>
       </c>
       <c r="K78" t="n">
-        <v>20.11761665344238</v>
+        <v>20.11762046813965</v>
       </c>
       <c r="L78" t="n">
         <v>2913.97998046875</v>
@@ -3413,22 +3413,22 @@
         <v>43374</v>
       </c>
       <c r="B79" t="n">
-        <v>51.70310592651367</v>
+        <v>51.70311737060547</v>
       </c>
       <c r="C79" t="n">
-        <v>98.87925720214844</v>
+        <v>98.87924194335938</v>
       </c>
       <c r="D79" t="n">
-        <v>54.01501083374023</v>
+        <v>54.0150146484375</v>
       </c>
       <c r="E79" t="n">
         <v>79.90049743652344</v>
       </c>
       <c r="F79" t="n">
-        <v>5.209482192993164</v>
+        <v>5.20948314666748</v>
       </c>
       <c r="G79" t="n">
-        <v>150.3499603271484</v>
+        <v>150.3500061035156</v>
       </c>
       <c r="H79" t="n">
         <v>18.20999908447266</v>
@@ -3437,7 +3437,7 @@
         <v>22.48800086975098</v>
       </c>
       <c r="J79" t="n">
-        <v>40.09360504150391</v>
+        <v>40.09361267089844</v>
       </c>
       <c r="K79" t="n">
         <v>18.22270011901855</v>
@@ -3457,16 +3457,16 @@
         <v>103.0997848510742</v>
       </c>
       <c r="D80" t="n">
-        <v>54.95952224731445</v>
+        <v>54.95951843261719</v>
       </c>
       <c r="E80" t="n">
         <v>84.50849914550781</v>
       </c>
       <c r="F80" t="n">
-        <v>4.04229736328125</v>
+        <v>4.042297840118408</v>
       </c>
       <c r="G80" t="n">
-        <v>139.2760467529297</v>
+        <v>139.2760620117188</v>
       </c>
       <c r="H80" t="n">
         <v>21.29999923706055</v>
@@ -3475,10 +3475,10 @@
         <v>23.36533355712891</v>
       </c>
       <c r="J80" t="n">
-        <v>42.43722915649414</v>
+        <v>42.43723297119141</v>
       </c>
       <c r="K80" t="n">
-        <v>19.35769653320312</v>
+        <v>19.35769462585449</v>
       </c>
       <c r="L80" t="n">
         <v>2760.169921875</v>
@@ -3489,22 +3489,22 @@
         <v>43435</v>
       </c>
       <c r="B81" t="n">
-        <v>37.39424133300781</v>
+        <v>37.39424514770508</v>
       </c>
       <c r="C81" t="n">
-        <v>94.43453979492188</v>
+        <v>94.43452453613281</v>
       </c>
       <c r="D81" t="n">
-        <v>51.75551605224609</v>
+        <v>51.75551223754883</v>
       </c>
       <c r="E81" t="n">
         <v>75.09850311279297</v>
       </c>
       <c r="F81" t="n">
-        <v>3.302005529403687</v>
+        <v>3.302005290985107</v>
       </c>
       <c r="G81" t="n">
-        <v>129.8463897705078</v>
+        <v>129.8463592529297</v>
       </c>
       <c r="H81" t="n">
         <v>18.45999908447266</v>
@@ -3513,10 +3513,10 @@
         <v>22.18666648864746</v>
       </c>
       <c r="J81" t="n">
-        <v>40.38895797729492</v>
+        <v>40.38894271850586</v>
       </c>
       <c r="K81" t="n">
-        <v>20.95170402526855</v>
+        <v>20.95170021057129</v>
       </c>
       <c r="L81" t="n">
         <v>2506.85009765625</v>
@@ -3530,19 +3530,19 @@
         <v>39.45669555664062</v>
       </c>
       <c r="C82" t="n">
-        <v>97.09359741210938</v>
+        <v>97.09362030029297</v>
       </c>
       <c r="D82" t="n">
-        <v>55.76386260986328</v>
+        <v>55.76387405395508</v>
       </c>
       <c r="E82" t="n">
         <v>85.93650054931641</v>
       </c>
       <c r="F82" t="n">
-        <v>3.555529594421387</v>
+        <v>3.555530309677124</v>
       </c>
       <c r="G82" t="n">
-        <v>165.108642578125</v>
+        <v>165.1086578369141</v>
       </c>
       <c r="H82" t="n">
         <v>24.40999984741211</v>
@@ -3551,7 +3551,7 @@
         <v>20.4680004119873</v>
       </c>
       <c r="J82" t="n">
-        <v>40.55246353149414</v>
+        <v>40.55247116088867</v>
       </c>
       <c r="K82" t="n">
         <v>22.102783203125</v>
@@ -3565,10 +3565,10 @@
         <v>43497</v>
       </c>
       <c r="B83" t="n">
-        <v>41.22341537475586</v>
+        <v>41.22343826293945</v>
       </c>
       <c r="C83" t="n">
-        <v>104.6045455932617</v>
+        <v>104.6045379638672</v>
       </c>
       <c r="D83" t="n">
         <v>55.79655838012695</v>
@@ -3580,7 +3580,7 @@
         <v>3.819417476654053</v>
       </c>
       <c r="G83" t="n">
-        <v>159.9183502197266</v>
+        <v>159.9183349609375</v>
       </c>
       <c r="H83" t="n">
         <v>23.53000068664551</v>
@@ -3589,10 +3589,10 @@
         <v>21.32533264160156</v>
       </c>
       <c r="J83" t="n">
-        <v>45.86740112304688</v>
+        <v>45.86740875244141</v>
       </c>
       <c r="K83" t="n">
-        <v>22.68861389160156</v>
+        <v>22.68861198425293</v>
       </c>
       <c r="L83" t="n">
         <v>2784.489990234375</v>
@@ -3603,10 +3603,10 @@
         <v>43525</v>
       </c>
       <c r="B84" t="n">
-        <v>45.22315216064453</v>
+        <v>45.22314834594727</v>
       </c>
       <c r="C84" t="n">
-        <v>110.1228103637695</v>
+        <v>110.1228179931641</v>
       </c>
       <c r="D84" t="n">
         <v>58.28983688354492</v>
@@ -3618,7 +3618,7 @@
         <v>4.445836067199707</v>
       </c>
       <c r="G84" t="n">
-        <v>165.108642578125</v>
+        <v>165.1086578369141</v>
       </c>
       <c r="H84" t="n">
         <v>25.52000045776367</v>
@@ -3641,22 +3641,22 @@
         <v>43556</v>
       </c>
       <c r="B85" t="n">
-        <v>47.77536773681641</v>
+        <v>47.77536010742188</v>
       </c>
       <c r="C85" t="n">
-        <v>121.9437026977539</v>
+        <v>121.943717956543</v>
       </c>
       <c r="D85" t="n">
-        <v>59.38293075561523</v>
+        <v>59.3829345703125</v>
       </c>
       <c r="E85" t="n">
         <v>96.32599639892578</v>
       </c>
       <c r="F85" t="n">
-        <v>4.481489181518555</v>
+        <v>4.481490612030029</v>
       </c>
       <c r="G85" t="n">
-        <v>191.5652465820312</v>
+        <v>191.5652313232422</v>
       </c>
       <c r="H85" t="n">
         <v>27.6299991607666</v>
@@ -3665,10 +3665,10 @@
         <v>15.9126672744751</v>
       </c>
       <c r="J85" t="n">
-        <v>44.20453643798828</v>
+        <v>44.20453262329102</v>
       </c>
       <c r="K85" t="n">
-        <v>26.46929931640625</v>
+        <v>26.46929550170898</v>
       </c>
       <c r="L85" t="n">
         <v>2945.830078125</v>
@@ -3679,19 +3679,19 @@
         <v>43586</v>
       </c>
       <c r="B86" t="n">
-        <v>41.84104156494141</v>
+        <v>41.84104537963867</v>
       </c>
       <c r="C86" t="n">
-        <v>115.9098434448242</v>
+        <v>115.9098205566406</v>
       </c>
       <c r="D86" t="n">
-        <v>54.80350112915039</v>
+        <v>54.80350875854492</v>
       </c>
       <c r="E86" t="n">
         <v>88.75350189208984</v>
       </c>
       <c r="F86" t="n">
-        <v>3.357765674591064</v>
+        <v>3.357764720916748</v>
       </c>
       <c r="G86" t="n">
         <v>175.786376953125</v>
@@ -3703,10 +3703,10 @@
         <v>12.3439998626709</v>
       </c>
       <c r="J86" t="n">
-        <v>38.37558746337891</v>
+        <v>38.37559127807617</v>
       </c>
       <c r="K86" t="n">
-        <v>20.91939163208008</v>
+        <v>20.91938972473145</v>
       </c>
       <c r="L86" t="n">
         <v>2752.06005859375</v>
@@ -3717,19 +3717,19 @@
         <v>43617</v>
       </c>
       <c r="B87" t="n">
-        <v>47.30210876464844</v>
+        <v>47.3021125793457</v>
       </c>
       <c r="C87" t="n">
-        <v>125.5440216064453</v>
+        <v>125.5440139770508</v>
       </c>
       <c r="D87" t="n">
-        <v>53.62967300415039</v>
+        <v>53.62967681884766</v>
       </c>
       <c r="E87" t="n">
         <v>94.68150329589844</v>
       </c>
       <c r="F87" t="n">
-        <v>4.07091236114502</v>
+        <v>4.070912837982178</v>
       </c>
       <c r="G87" t="n">
         <v>191.1690368652344</v>
@@ -3741,7 +3741,7 @@
         <v>14.8973331451416</v>
       </c>
       <c r="J87" t="n">
-        <v>41.71298217773438</v>
+        <v>41.71298599243164</v>
       </c>
       <c r="K87" t="n">
         <v>24.15987205505371</v>
@@ -3758,16 +3758,16 @@
         <v>50.91572189331055</v>
       </c>
       <c r="C88" t="n">
-        <v>127.7088241577148</v>
+        <v>127.7088470458984</v>
       </c>
       <c r="D88" t="n">
-        <v>60.33585739135742</v>
+        <v>60.33586120605469</v>
       </c>
       <c r="E88" t="n">
         <v>93.33899688720703</v>
       </c>
       <c r="F88" t="n">
-        <v>4.182209491729736</v>
+        <v>4.182209014892578</v>
       </c>
       <c r="G88" t="n">
         <v>192.3873748779297</v>
@@ -3782,7 +3782,7 @@
         <v>44.04828262329102</v>
       </c>
       <c r="K88" t="n">
-        <v>24.33864593505859</v>
+        <v>24.33864212036133</v>
       </c>
       <c r="L88" t="n">
         <v>2980.3798828125</v>
@@ -3796,19 +3796,19 @@
         <v>50.07759857177734</v>
       </c>
       <c r="C89" t="n">
-        <v>129.6291656494141</v>
+        <v>129.6292419433594</v>
       </c>
       <c r="D89" t="n">
-        <v>58.96540451049805</v>
+        <v>58.96540069580078</v>
       </c>
       <c r="E89" t="n">
         <v>88.81449890136719</v>
       </c>
       <c r="F89" t="n">
-        <v>4.156328678131104</v>
+        <v>4.156327724456787</v>
       </c>
       <c r="G89" t="n">
-        <v>183.9085845947266</v>
+        <v>183.9085540771484</v>
       </c>
       <c r="H89" t="n">
         <v>31.45000076293945</v>
@@ -3817,10 +3817,10 @@
         <v>15.0406665802002</v>
       </c>
       <c r="J89" t="n">
-        <v>41.59106826782227</v>
+        <v>41.591064453125</v>
       </c>
       <c r="K89" t="n">
-        <v>23.72176170349121</v>
+        <v>23.72175979614258</v>
       </c>
       <c r="L89" t="n">
         <v>2926.4599609375</v>
@@ -3831,22 +3831,22 @@
         <v>43709</v>
       </c>
       <c r="B90" t="n">
-        <v>53.73132705688477</v>
+        <v>53.73131942749023</v>
       </c>
       <c r="C90" t="n">
-        <v>130.7293701171875</v>
+        <v>130.7293395996094</v>
       </c>
       <c r="D90" t="n">
-        <v>60.48147583007812</v>
+        <v>60.48147201538086</v>
       </c>
       <c r="E90" t="n">
         <v>86.79550170898438</v>
       </c>
       <c r="F90" t="n">
-        <v>4.319097518920898</v>
+        <v>4.31909704208374</v>
       </c>
       <c r="G90" t="n">
-        <v>176.3905944824219</v>
+        <v>176.3905792236328</v>
       </c>
       <c r="H90" t="n">
         <v>28.98999977111816</v>
@@ -3855,10 +3855,10 @@
         <v>16.0580005645752</v>
       </c>
       <c r="J90" t="n">
-        <v>45.20539474487305</v>
+        <v>45.20540237426758</v>
       </c>
       <c r="K90" t="n">
-        <v>23.38355445861816</v>
+        <v>23.3835563659668</v>
       </c>
       <c r="L90" t="n">
         <v>2976.739990234375</v>
@@ -3869,7 +3869,7 @@
         <v>43739</v>
       </c>
       <c r="B91" t="n">
-        <v>59.67855834960938</v>
+        <v>59.67855072021484</v>
       </c>
       <c r="C91" t="n">
         <v>134.8102264404297</v>
@@ -3881,10 +3881,10 @@
         <v>88.83300018310547</v>
       </c>
       <c r="F91" t="n">
-        <v>4.987790107727051</v>
+        <v>4.987790584564209</v>
       </c>
       <c r="G91" t="n">
-        <v>189.8318634033203</v>
+        <v>189.8318481445312</v>
       </c>
       <c r="H91" t="n">
         <v>33.93000030517578</v>
@@ -3893,10 +3893,10 @@
         <v>20.99466705322266</v>
       </c>
       <c r="J91" t="n">
-        <v>49.59171676635742</v>
+        <v>49.59172058105469</v>
       </c>
       <c r="K91" t="n">
-        <v>24.80484390258789</v>
+        <v>24.80484580993652</v>
       </c>
       <c r="L91" t="n">
         <v>3037.56005859375</v>
@@ -3907,22 +3907,22 @@
         <v>43770</v>
       </c>
       <c r="B92" t="n">
-        <v>64.30685424804688</v>
+        <v>64.306884765625</v>
       </c>
       <c r="C92" t="n">
-        <v>142.8263854980469</v>
+        <v>142.826416015625</v>
       </c>
       <c r="D92" t="n">
-        <v>64.58987426757812</v>
+        <v>64.58986663818359</v>
       </c>
       <c r="E92" t="n">
         <v>90.04000091552734</v>
       </c>
       <c r="F92" t="n">
-        <v>5.381809234619141</v>
+        <v>5.381809711456299</v>
       </c>
       <c r="G92" t="n">
-        <v>199.7270812988281</v>
+        <v>199.7270660400391</v>
       </c>
       <c r="H92" t="n">
         <v>39.15000152587891</v>
@@ -3931,7 +3931,7 @@
         <v>21.99600028991699</v>
       </c>
       <c r="J92" t="n">
-        <v>51.20542907714844</v>
+        <v>51.20542526245117</v>
       </c>
       <c r="K92" t="n">
         <v>26.78347778320312</v>
@@ -3945,19 +3945,19 @@
         <v>43800</v>
       </c>
       <c r="B93" t="n">
-        <v>70.65937042236328</v>
+        <v>70.65935516357422</v>
       </c>
       <c r="C93" t="n">
-        <v>148.7892761230469</v>
+        <v>148.7892608642578</v>
       </c>
       <c r="D93" t="n">
-        <v>66.33824157714844</v>
+        <v>66.33824920654297</v>
       </c>
       <c r="E93" t="n">
         <v>92.39199829101562</v>
       </c>
       <c r="F93" t="n">
-        <v>5.842668533325195</v>
+        <v>5.842668056488037</v>
       </c>
       <c r="G93" t="n">
         <v>203.3028259277344</v>
@@ -3969,10 +3969,10 @@
         <v>27.8886661529541</v>
       </c>
       <c r="J93" t="n">
-        <v>52.79319763183594</v>
+        <v>52.79320526123047</v>
       </c>
       <c r="K93" t="n">
-        <v>27.03851890563965</v>
+        <v>27.03851699829102</v>
       </c>
       <c r="L93" t="n">
         <v>3230.780029296875</v>
@@ -3983,22 +3983,22 @@
         <v>43831</v>
       </c>
       <c r="B94" t="n">
-        <v>74.47563171386719</v>
+        <v>74.47566986083984</v>
       </c>
       <c r="C94" t="n">
-        <v>160.6112670898438</v>
+        <v>160.6112518310547</v>
       </c>
       <c r="D94" t="n">
-        <v>70.96372222900391</v>
+        <v>70.96372985839844</v>
       </c>
       <c r="E94" t="n">
         <v>100.4359970092773</v>
       </c>
       <c r="F94" t="n">
-        <v>5.870727062225342</v>
+        <v>5.8707275390625</v>
       </c>
       <c r="G94" t="n">
-        <v>199.9945220947266</v>
+        <v>199.9945068359375</v>
       </c>
       <c r="H94" t="n">
         <v>47</v>
@@ -4010,7 +4010,7 @@
         <v>56.39213180541992</v>
       </c>
       <c r="K94" t="n">
-        <v>26.10933876037598</v>
+        <v>26.10934066772461</v>
       </c>
       <c r="L94" t="n">
         <v>3225.52001953125</v>
@@ -4021,10 +4021,10 @@
         <v>43862</v>
       </c>
       <c r="B95" t="n">
-        <v>65.93319702148438</v>
+        <v>65.93321228027344</v>
       </c>
       <c r="C95" t="n">
-        <v>153.2732391357422</v>
+        <v>153.2732086181641</v>
       </c>
       <c r="D95" t="n">
         <v>66.33131408691406</v>
@@ -4033,10 +4033,10 @@
         <v>94.1875</v>
       </c>
       <c r="F95" t="n">
-        <v>6.710043430328369</v>
+        <v>6.710044384002686</v>
       </c>
       <c r="G95" t="n">
-        <v>190.6441040039062</v>
+        <v>190.6440734863281</v>
       </c>
       <c r="H95" t="n">
         <v>45.47999954223633</v>
@@ -4045,10 +4045,10 @@
         <v>44.53266525268555</v>
       </c>
       <c r="J95" t="n">
-        <v>49.21491241455078</v>
+        <v>49.21491622924805</v>
       </c>
       <c r="K95" t="n">
-        <v>23.32523536682129</v>
+        <v>23.32523345947266</v>
       </c>
       <c r="L95" t="n">
         <v>2954.219970703125</v>
@@ -4059,10 +4059,10 @@
         <v>43891</v>
       </c>
       <c r="B96" t="n">
-        <v>61.33359909057617</v>
+        <v>61.33359146118164</v>
       </c>
       <c r="C96" t="n">
-        <v>149.2051391601562</v>
+        <v>149.2051239013672</v>
       </c>
       <c r="D96" t="n">
         <v>57.54987335205078</v>
@@ -4071,10 +4071,10 @@
         <v>97.48600006103516</v>
       </c>
       <c r="F96" t="n">
-        <v>6.54929256439209</v>
+        <v>6.549293041229248</v>
       </c>
       <c r="G96" t="n">
-        <v>165.2176208496094</v>
+        <v>165.2176055908203</v>
       </c>
       <c r="H96" t="n">
         <v>45.47999954223633</v>
@@ -4083,10 +4083,10 @@
         <v>34.93333435058594</v>
       </c>
       <c r="J96" t="n">
-        <v>47.97390365600586</v>
+        <v>47.97391128540039</v>
       </c>
       <c r="K96" t="n">
-        <v>20.63097953796387</v>
+        <v>20.6309814453125</v>
       </c>
       <c r="L96" t="n">
         <v>2584.590087890625</v>
@@ -4097,19 +4097,19 @@
         <v>43922</v>
       </c>
       <c r="B97" t="n">
-        <v>70.86322784423828</v>
+        <v>70.86325073242188</v>
       </c>
       <c r="C97" t="n">
-        <v>169.545654296875</v>
+        <v>169.5457305908203</v>
       </c>
       <c r="D97" t="n">
-        <v>66.70030212402344</v>
+        <v>66.70029449462891</v>
       </c>
       <c r="E97" t="n">
         <v>123.6999969482422</v>
       </c>
       <c r="F97" t="n">
-        <v>7.261862277984619</v>
+        <v>7.261863231658936</v>
       </c>
       <c r="G97" t="n">
         <v>202.7679443359375</v>
@@ -4121,10 +4121,10 @@
         <v>52.12533187866211</v>
       </c>
       <c r="J97" t="n">
-        <v>53.16842269897461</v>
+        <v>53.16841888427734</v>
       </c>
       <c r="K97" t="n">
-        <v>23.63470077514648</v>
+        <v>23.63469696044922</v>
       </c>
       <c r="L97" t="n">
         <v>2912.429931640625</v>
@@ -4135,22 +4135,22 @@
         <v>43952</v>
       </c>
       <c r="B98" t="n">
-        <v>76.89329528808594</v>
+        <v>76.89328002929688</v>
       </c>
       <c r="C98" t="n">
-        <v>173.8506774902344</v>
+        <v>173.8506622314453</v>
       </c>
       <c r="D98" t="n">
-        <v>71.00037384033203</v>
+        <v>71.00038909912109</v>
       </c>
       <c r="E98" t="n">
         <v>122.1184997558594</v>
       </c>
       <c r="F98" t="n">
-        <v>8.820676803588867</v>
+        <v>8.820675849914551</v>
       </c>
       <c r="G98" t="n">
-        <v>222.9546051025391</v>
+        <v>222.9546203613281</v>
       </c>
       <c r="H98" t="n">
         <v>53.79999923706055</v>
@@ -4159,10 +4159,10 @@
         <v>55.66666793823242</v>
       </c>
       <c r="J98" t="n">
-        <v>56.09851837158203</v>
+        <v>56.0985107421875</v>
       </c>
       <c r="K98" t="n">
-        <v>25.34452247619629</v>
+        <v>25.34451675415039</v>
       </c>
       <c r="L98" t="n">
         <v>3044.31005859375</v>
@@ -4173,19 +4173,19 @@
         <v>43983</v>
       </c>
       <c r="B99" t="n">
-        <v>88.22629547119141</v>
+        <v>88.22631072998047</v>
       </c>
       <c r="C99" t="n">
-        <v>193.0714721679688</v>
+        <v>193.0714874267578</v>
       </c>
       <c r="D99" t="n">
-        <v>70.23418426513672</v>
+        <v>70.23416137695312</v>
       </c>
       <c r="E99" t="n">
         <v>137.9409942626953</v>
       </c>
       <c r="F99" t="n">
-        <v>9.443388938903809</v>
+        <v>9.443389892578125</v>
       </c>
       <c r="G99" t="n">
         <v>224.9158325195312</v>
@@ -4200,7 +4200,7 @@
         <v>53.33504486083984</v>
       </c>
       <c r="K99" t="n">
-        <v>27.74537086486816</v>
+        <v>27.745361328125</v>
       </c>
       <c r="L99" t="n">
         <v>3100.2900390625</v>
@@ -4214,19 +4214,19 @@
         <v>102.7952575683594</v>
       </c>
       <c r="C100" t="n">
-        <v>194.4945526123047</v>
+        <v>194.4945373535156</v>
       </c>
       <c r="D100" t="n">
-        <v>73.69622802734375</v>
+        <v>73.69623565673828</v>
       </c>
       <c r="E100" t="n">
         <v>158.2339935302734</v>
       </c>
       <c r="F100" t="n">
-        <v>10.55399608612061</v>
+        <v>10.55399894714355</v>
       </c>
       <c r="G100" t="n">
-        <v>251.2634887695312</v>
+        <v>251.2634735107422</v>
       </c>
       <c r="H100" t="n">
         <v>77.43000030517578</v>
@@ -4235,10 +4235,10 @@
         <v>95.38400268554688</v>
       </c>
       <c r="J100" t="n">
-        <v>42.54858016967773</v>
+        <v>42.54857635498047</v>
       </c>
       <c r="K100" t="n">
-        <v>27.84558868408203</v>
+        <v>27.84558296203613</v>
       </c>
       <c r="L100" t="n">
         <v>3271.1201171875</v>
@@ -4261,10 +4261,10 @@
         <v>172.5480041503906</v>
       </c>
       <c r="F101" t="n">
-        <v>13.29795169830322</v>
+        <v>13.29795360565186</v>
       </c>
       <c r="G101" t="n">
-        <v>290.4183959960938</v>
+        <v>290.4184875488281</v>
       </c>
       <c r="H101" t="n">
         <v>90.81999969482422</v>
@@ -4287,22 +4287,22 @@
         <v>44075</v>
       </c>
       <c r="B102" t="n">
-        <v>112.2358322143555</v>
+        <v>112.23583984375</v>
       </c>
       <c r="C102" t="n">
         <v>200.0240173339844</v>
       </c>
       <c r="D102" t="n">
-        <v>72.58924865722656</v>
+        <v>72.58927154541016</v>
       </c>
       <c r="E102" t="n">
         <v>157.4364929199219</v>
       </c>
       <c r="F102" t="n">
-        <v>13.4570837020874</v>
+        <v>13.45708084106445</v>
       </c>
       <c r="G102" t="n">
-        <v>259.4153747558594</v>
+        <v>259.4154052734375</v>
       </c>
       <c r="H102" t="n">
         <v>81.98999786376953</v>
@@ -4314,7 +4314,7 @@
         <v>46.47240829467773</v>
       </c>
       <c r="K102" t="n">
-        <v>32.3194694519043</v>
+        <v>32.31946182250977</v>
       </c>
       <c r="L102" t="n">
         <v>3363</v>
@@ -4325,22 +4325,22 @@
         <v>44105</v>
       </c>
       <c r="B103" t="n">
-        <v>105.5003509521484</v>
+        <v>105.5003356933594</v>
       </c>
       <c r="C103" t="n">
-        <v>192.5491485595703</v>
+        <v>192.5491638183594</v>
       </c>
       <c r="D103" t="n">
-        <v>80.0438232421875</v>
+        <v>80.04381561279297</v>
       </c>
       <c r="E103" t="n">
         <v>151.8074951171875</v>
       </c>
       <c r="F103" t="n">
-        <v>12.46599102020264</v>
+        <v>12.465989112854</v>
       </c>
       <c r="G103" t="n">
-        <v>260.6139526367188</v>
+        <v>260.6138610839844</v>
       </c>
       <c r="H103" t="n">
         <v>75.29000091552734</v>
@@ -4349,10 +4349,10 @@
         <v>129.3466644287109</v>
       </c>
       <c r="J103" t="n">
-        <v>39.74118804931641</v>
+        <v>39.74118423461914</v>
       </c>
       <c r="K103" t="n">
-        <v>31.01629447937012</v>
+        <v>31.01629829406738</v>
       </c>
       <c r="L103" t="n">
         <v>3269.9599609375</v>
@@ -4375,10 +4375,10 @@
         <v>158.4019927978516</v>
       </c>
       <c r="F104" t="n">
-        <v>13.32878494262695</v>
+        <v>13.32878112792969</v>
       </c>
       <c r="G104" t="n">
-        <v>274.3424377441406</v>
+        <v>274.3424682617188</v>
       </c>
       <c r="H104" t="n">
         <v>92.66000366210938</v>
@@ -4390,7 +4390,7 @@
         <v>43.70962142944336</v>
       </c>
       <c r="K104" t="n">
-        <v>35.6248779296875</v>
+        <v>35.62487030029297</v>
       </c>
       <c r="L104" t="n">
         <v>3621.6298828125</v>
@@ -4401,22 +4401,22 @@
         <v>44166</v>
       </c>
       <c r="B105" t="n">
-        <v>128.8167572021484</v>
+        <v>128.8167419433594</v>
       </c>
       <c r="C105" t="n">
-        <v>212.0753936767578</v>
+        <v>212.0753479003906</v>
       </c>
       <c r="D105" t="n">
-        <v>86.80597686767578</v>
+        <v>86.80598449707031</v>
       </c>
       <c r="E105" t="n">
         <v>162.8464965820312</v>
       </c>
       <c r="F105" t="n">
-        <v>12.98799705505371</v>
+        <v>12.98799896240234</v>
       </c>
       <c r="G105" t="n">
-        <v>270.5685424804688</v>
+        <v>270.5685729980469</v>
       </c>
       <c r="H105" t="n">
         <v>91.70999908447266</v>
@@ -4425,7 +4425,7 @@
         <v>235.2233276367188</v>
       </c>
       <c r="J105" t="n">
-        <v>45.03853988647461</v>
+        <v>45.03854370117188</v>
       </c>
       <c r="K105" t="n">
         <v>39.17340850830078</v>
@@ -4439,22 +4439,22 @@
         <v>44197</v>
       </c>
       <c r="B106" t="n">
-        <v>128.1080780029297</v>
+        <v>128.1080932617188</v>
       </c>
       <c r="C106" t="n">
         <v>221.1716766357422</v>
       </c>
       <c r="D106" t="n">
-        <v>90.50676727294922</v>
+        <v>90.50675964355469</v>
       </c>
       <c r="E106" t="n">
         <v>160.3099975585938</v>
       </c>
       <c r="F106" t="n">
-        <v>12.92308330535889</v>
+        <v>12.92308139801025</v>
       </c>
       <c r="G106" t="n">
-        <v>255.8792419433594</v>
+        <v>255.8792572021484</v>
       </c>
       <c r="H106" t="n">
         <v>85.63999938964844</v>
@@ -4463,10 +4463,10 @@
         <v>264.510009765625</v>
       </c>
       <c r="J106" t="n">
-        <v>50.18243789672852</v>
+        <v>50.18244171142578</v>
       </c>
       <c r="K106" t="n">
-        <v>40.3051872253418</v>
+        <v>40.30517196655273</v>
       </c>
       <c r="L106" t="n">
         <v>3714.239990234375</v>
@@ -4483,13 +4483,13 @@
         <v>222.0824890136719</v>
       </c>
       <c r="D107" t="n">
-        <v>100.1425628662109</v>
+        <v>100.1425704956055</v>
       </c>
       <c r="E107" t="n">
         <v>154.6464996337891</v>
       </c>
       <c r="F107" t="n">
-        <v>13.64411067962646</v>
+        <v>13.6441125869751</v>
       </c>
       <c r="G107" t="n">
         <v>255.1760101318359</v>
@@ -4501,10 +4501,10 @@
         <v>225.1666717529297</v>
       </c>
       <c r="J107" t="n">
-        <v>55.28017807006836</v>
+        <v>55.28018188476562</v>
       </c>
       <c r="K107" t="n">
-        <v>42.03816986083984</v>
+        <v>42.03816604614258</v>
       </c>
       <c r="L107" t="n">
         <v>3811.14990234375</v>
@@ -4515,10 +4515,10 @@
         <v>44256</v>
       </c>
       <c r="B108" t="n">
-        <v>118.7616348266602</v>
+        <v>118.7616195678711</v>
       </c>
       <c r="C108" t="n">
-        <v>225.3222503662109</v>
+        <v>225.3222808837891</v>
       </c>
       <c r="D108" t="n">
         <v>102.153938293457</v>
@@ -4527,10 +4527,10 @@
         <v>154.7039947509766</v>
       </c>
       <c r="F108" t="n">
-        <v>13.28432750701904</v>
+        <v>13.28432655334473</v>
       </c>
       <c r="G108" t="n">
-        <v>291.7358093261719</v>
+        <v>291.7358703613281</v>
       </c>
       <c r="H108" t="n">
         <v>78.5</v>
@@ -4539,10 +4539,10 @@
         <v>222.6433258056641</v>
       </c>
       <c r="J108" t="n">
-        <v>58.20881271362305</v>
+        <v>58.20880889892578</v>
       </c>
       <c r="K108" t="n">
-        <v>41.80682754516602</v>
+        <v>41.80683135986328</v>
       </c>
       <c r="L108" t="n">
         <v>3972.889892578125</v>
@@ -4553,22 +4553,22 @@
         <v>44287</v>
       </c>
       <c r="B109" t="n">
-        <v>127.8133773803711</v>
+        <v>127.8134155273438</v>
       </c>
       <c r="C109" t="n">
         <v>241.0050506591797</v>
       </c>
       <c r="D109" t="n">
-        <v>116.5657958984375</v>
+        <v>116.565803527832</v>
       </c>
       <c r="E109" t="n">
         <v>173.3710021972656</v>
       </c>
       <c r="F109" t="n">
-        <v>14.93762111663818</v>
+        <v>14.93761825561523</v>
       </c>
       <c r="G109" t="n">
-        <v>321.9960327148438</v>
+        <v>321.9959411621094</v>
       </c>
       <c r="H109" t="n">
         <v>81.62000274658203</v>
@@ -4577,7 +4577,7 @@
         <v>236.4799957275391</v>
       </c>
       <c r="J109" t="n">
-        <v>52.32425689697266</v>
+        <v>52.32426834106445</v>
       </c>
       <c r="K109" t="n">
         <v>41.13418579101562</v>
@@ -4591,19 +4591,19 @@
         <v>44317</v>
       </c>
       <c r="B110" t="n">
-        <v>121.3591690063477</v>
+        <v>121.3591842651367</v>
       </c>
       <c r="C110" t="n">
         <v>239.1668395996094</v>
       </c>
       <c r="D110" t="n">
-        <v>116.7317123413086</v>
+        <v>116.7317199707031</v>
       </c>
       <c r="E110" t="n">
         <v>161.1535034179688</v>
       </c>
       <c r="F110" t="n">
-        <v>16.16670036315918</v>
+        <v>16.16670799255371</v>
       </c>
       <c r="G110" t="n">
         <v>325.6113891601562</v>
@@ -4618,7 +4618,7 @@
         <v>52.27133941650391</v>
       </c>
       <c r="K110" t="n">
-        <v>42.58858489990234</v>
+        <v>42.58858108520508</v>
       </c>
       <c r="L110" t="n">
         <v>4204.10986328125</v>
@@ -4629,22 +4629,22 @@
         <v>44348</v>
       </c>
       <c r="B111" t="n">
-        <v>133.386962890625</v>
+        <v>133.3869934082031</v>
       </c>
       <c r="C111" t="n">
-        <v>259.4933166503906</v>
+        <v>259.4933776855469</v>
       </c>
       <c r="D111" t="n">
-        <v>120.9386901855469</v>
+        <v>120.9386825561523</v>
       </c>
       <c r="E111" t="n">
         <v>172.0079956054688</v>
       </c>
       <c r="F111" t="n">
-        <v>19.91127014160156</v>
+        <v>19.91127586364746</v>
       </c>
       <c r="G111" t="n">
-        <v>344.4113159179688</v>
+        <v>344.4113464355469</v>
       </c>
       <c r="H111" t="n">
         <v>93.93000030517578</v>
@@ -4653,10 +4653,10 @@
         <v>226.5666656494141</v>
       </c>
       <c r="J111" t="n">
-        <v>51.37451934814453</v>
+        <v>51.3745231628418</v>
       </c>
       <c r="K111" t="n">
-        <v>43.331787109375</v>
+        <v>43.33178329467773</v>
       </c>
       <c r="L111" t="n">
         <v>4297.5</v>
@@ -4673,13 +4673,13 @@
         <v>272.9134521484375</v>
       </c>
       <c r="D112" t="n">
-        <v>133.4565887451172</v>
+        <v>133.4565734863281</v>
       </c>
       <c r="E112" t="n">
         <v>166.3795013427734</v>
       </c>
       <c r="F112" t="n">
-        <v>19.41006278991699</v>
+        <v>19.41007041931152</v>
       </c>
       <c r="G112" t="n">
         <v>352.9198303222656</v>
@@ -4691,7 +4691,7 @@
         <v>229.0666656494141</v>
       </c>
       <c r="J112" t="n">
-        <v>49.15994262695312</v>
+        <v>49.15995025634766</v>
       </c>
       <c r="K112" t="n">
         <v>44.10965728759766</v>
@@ -4708,7 +4708,7 @@
         <v>148.0905914306641</v>
       </c>
       <c r="C113" t="n">
-        <v>289.7224731445312</v>
+        <v>289.722412109375</v>
       </c>
       <c r="D113" t="n">
         <v>143.3335723876953</v>
@@ -4717,10 +4717,10 @@
         <v>173.5395050048828</v>
       </c>
       <c r="F113" t="n">
-        <v>22.28683471679688</v>
+        <v>22.28683280944824</v>
       </c>
       <c r="G113" t="n">
-        <v>375.7809448242188</v>
+        <v>375.7808837890625</v>
       </c>
       <c r="H113" t="n">
         <v>110.7200012207031</v>
@@ -4729,10 +4729,10 @@
         <v>245.2400054931641</v>
       </c>
       <c r="J113" t="n">
-        <v>49.79256057739258</v>
+        <v>49.79256439208984</v>
       </c>
       <c r="K113" t="n">
-        <v>45.18286514282227</v>
+        <v>45.1828727722168</v>
       </c>
       <c r="L113" t="n">
         <v>4522.68017578125</v>
@@ -4743,7 +4743,7 @@
         <v>44440</v>
       </c>
       <c r="B114" t="n">
-        <v>138.0150146484375</v>
+        <v>138.0150299072266</v>
       </c>
       <c r="C114" t="n">
         <v>270.5663146972656</v>
@@ -4755,10 +4755,10 @@
         <v>164.2519989013672</v>
       </c>
       <c r="F114" t="n">
-        <v>20.62515068054199</v>
+        <v>20.62516021728516</v>
       </c>
       <c r="G114" t="n">
-        <v>336.1702575683594</v>
+        <v>336.1703186035156</v>
       </c>
       <c r="H114" t="n">
         <v>102.9000015258789</v>
@@ -4767,10 +4767,10 @@
         <v>258.4933471679688</v>
       </c>
       <c r="J114" t="n">
-        <v>49.07413482666016</v>
+        <v>49.07413864135742</v>
       </c>
       <c r="K114" t="n">
-        <v>44.38990020751953</v>
+        <v>44.389892578125</v>
       </c>
       <c r="L114" t="n">
         <v>4307.5400390625</v>
@@ -4781,22 +4781,22 @@
         <v>44470</v>
       </c>
       <c r="B115" t="n">
-        <v>146.110595703125</v>
+        <v>146.1105804443359</v>
       </c>
       <c r="C115" t="n">
-        <v>318.2646789550781</v>
+        <v>318.2647705078125</v>
       </c>
       <c r="D115" t="n">
-        <v>146.6505279541016</v>
+        <v>146.6505432128906</v>
       </c>
       <c r="E115" t="n">
         <v>168.6215057373047</v>
       </c>
       <c r="F115" t="n">
-        <v>25.45488548278809</v>
+        <v>25.45488166809082</v>
       </c>
       <c r="G115" t="n">
-        <v>320.5003662109375</v>
+        <v>320.5003356933594</v>
       </c>
       <c r="H115" t="n">
         <v>120.2300033569336</v>
@@ -4805,10 +4805,10 @@
         <v>371.3333435058594</v>
       </c>
       <c r="J115" t="n">
-        <v>45.13200378417969</v>
+        <v>45.13199234008789</v>
       </c>
       <c r="K115" t="n">
-        <v>48.66841506958008</v>
+        <v>48.66841888427734</v>
       </c>
       <c r="L115" t="n">
         <v>4605.3798828125</v>
@@ -4819,22 +4819,22 @@
         <v>44501</v>
       </c>
       <c r="B116" t="n">
-        <v>161.4641418457031</v>
+        <v>161.4641571044922</v>
       </c>
       <c r="C116" t="n">
-        <v>317.8566589355469</v>
+        <v>317.8567199707031</v>
       </c>
       <c r="D116" t="n">
-        <v>140.5599822998047</v>
+        <v>140.5599670410156</v>
       </c>
       <c r="E116" t="n">
         <v>175.3535003662109</v>
       </c>
       <c r="F116" t="n">
-        <v>32.53269958496094</v>
+        <v>32.53269577026367</v>
       </c>
       <c r="G116" t="n">
-        <v>321.3819274902344</v>
+        <v>321.3818664550781</v>
       </c>
       <c r="H116" t="n">
         <v>158.3699951171875</v>
@@ -4846,7 +4846,7 @@
         <v>45.63135147094727</v>
       </c>
       <c r="K116" t="n">
-        <v>50.68319702148438</v>
+        <v>50.68319320678711</v>
       </c>
       <c r="L116" t="n">
         <v>4567</v>
@@ -4857,13 +4857,13 @@
         <v>44531</v>
       </c>
       <c r="B117" t="n">
-        <v>173.4494476318359</v>
+        <v>173.449462890625</v>
       </c>
       <c r="C117" t="n">
-        <v>323.365966796875</v>
+        <v>323.3659362792969</v>
       </c>
       <c r="D117" t="n">
-        <v>143.4866333007812</v>
+        <v>143.4866485595703</v>
       </c>
       <c r="E117" t="n">
         <v>166.7169952392578</v>
@@ -4872,7 +4872,7 @@
         <v>29.28560829162598</v>
       </c>
       <c r="G117" t="n">
-        <v>333.1590881347656</v>
+        <v>333.1590576171875</v>
       </c>
       <c r="H117" t="n">
         <v>143.8999938964844</v>
@@ -4881,10 +4881,10 @@
         <v>352.260009765625</v>
       </c>
       <c r="J117" t="n">
-        <v>47.76452255249023</v>
+        <v>47.76451873779297</v>
       </c>
       <c r="K117" t="n">
-        <v>61.30045700073242</v>
+        <v>61.30046844482422</v>
       </c>
       <c r="L117" t="n">
         <v>4766.18017578125</v>
@@ -4895,10 +4895,10 @@
         <v>44562</v>
       </c>
       <c r="B118" t="n">
-        <v>170.7241668701172</v>
+        <v>170.7241363525391</v>
       </c>
       <c r="C118" t="n">
-        <v>299.001953125</v>
+        <v>299.0020751953125</v>
       </c>
       <c r="D118" t="n">
         <v>134.0281219482422</v>
@@ -4907,10 +4907,10 @@
         <v>149.5735015869141</v>
       </c>
       <c r="F118" t="n">
-        <v>24.38160514831543</v>
+        <v>24.3816089630127</v>
       </c>
       <c r="G118" t="n">
-        <v>310.2881469726562</v>
+        <v>310.2881774902344</v>
       </c>
       <c r="H118" t="n">
         <v>114.25</v>
@@ -4919,10 +4919,10 @@
         <v>312.239990234375</v>
       </c>
       <c r="J118" t="n">
-        <v>45.27891159057617</v>
+        <v>45.27890396118164</v>
       </c>
       <c r="K118" t="n">
-        <v>53.97382736206055</v>
+        <v>53.97382354736328</v>
       </c>
       <c r="L118" t="n">
         <v>4515.5498046875</v>
@@ -4936,10 +4936,10 @@
         <v>161.4937896728516</v>
       </c>
       <c r="C119" t="n">
-        <v>287.8755187988281</v>
+        <v>287.87548828125</v>
       </c>
       <c r="D119" t="n">
-        <v>133.7839660644531</v>
+        <v>133.783935546875</v>
       </c>
       <c r="E119" t="n">
         <v>153.5630035400391</v>
@@ -4948,7 +4948,7 @@
         <v>24.28103637695312</v>
       </c>
       <c r="G119" t="n">
-        <v>209.0279693603516</v>
+        <v>209.0279998779297</v>
       </c>
       <c r="H119" t="n">
         <v>123.3399963378906</v>
@@ -4957,7 +4957,7 @@
         <v>290.1433410644531</v>
       </c>
       <c r="J119" t="n">
-        <v>44.5771484375</v>
+        <v>44.57715606689453</v>
       </c>
       <c r="K119" t="n">
         <v>54.11753463745117</v>
@@ -4971,22 +4971,22 @@
         <v>44621</v>
       </c>
       <c r="B120" t="n">
-        <v>170.7754516601562</v>
+        <v>170.7754211425781</v>
       </c>
       <c r="C120" t="n">
         <v>297.0478210449219</v>
       </c>
       <c r="D120" t="n">
-        <v>137.7566375732422</v>
+        <v>137.7566528320312</v>
       </c>
       <c r="E120" t="n">
         <v>162.9974975585938</v>
       </c>
       <c r="F120" t="n">
-        <v>27.17430114746094</v>
+        <v>27.1742992401123</v>
       </c>
       <c r="G120" t="n">
-        <v>220.2505035400391</v>
+        <v>220.2505340576172</v>
       </c>
       <c r="H120" t="n">
         <v>109.3399963378906</v>
@@ -4995,10 +4995,10 @@
         <v>359.2000122070312</v>
       </c>
       <c r="J120" t="n">
-        <v>46.31538391113281</v>
+        <v>46.31538009643555</v>
       </c>
       <c r="K120" t="n">
-        <v>58.40113067626953</v>
+        <v>58.4011344909668</v>
       </c>
       <c r="L120" t="n">
         <v>4530.41015625</v>
@@ -5012,7 +5012,7 @@
         <v>154.1878509521484</v>
       </c>
       <c r="C121" t="n">
-        <v>267.3824768066406</v>
+        <v>267.3825988769531</v>
       </c>
       <c r="D121" t="n">
         <v>113.0339050292969</v>
@@ -5021,7 +5021,7 @@
         <v>124.2815017700195</v>
       </c>
       <c r="F121" t="n">
-        <v>18.47107315063477</v>
+        <v>18.47107696533203</v>
       </c>
       <c r="G121" t="n">
         <v>198.5681762695312</v>
@@ -5033,10 +5033,10 @@
         <v>290.2533264160156</v>
       </c>
       <c r="J121" t="n">
-        <v>40.73623275756836</v>
+        <v>40.73622131347656</v>
       </c>
       <c r="K121" t="n">
-        <v>51.41817855834961</v>
+        <v>51.41819000244141</v>
       </c>
       <c r="L121" t="n">
         <v>4131.93017578125</v>
@@ -5047,7 +5047,7 @@
         <v>44682</v>
       </c>
       <c r="B122" t="n">
-        <v>145.7852172851562</v>
+        <v>145.7852020263672</v>
       </c>
       <c r="C122" t="n">
         <v>262.5490112304688</v>
@@ -5059,10 +5059,10 @@
         <v>120.2095031738281</v>
       </c>
       <c r="F122" t="n">
-        <v>18.59556198120117</v>
+        <v>18.59556579589844</v>
       </c>
       <c r="G122" t="n">
-        <v>191.8029479980469</v>
+        <v>191.802978515625</v>
       </c>
       <c r="H122" t="n">
         <v>101.8600006103516</v>
@@ -5074,7 +5074,7 @@
         <v>41.84002685546875</v>
       </c>
       <c r="K122" t="n">
-        <v>53.80550384521484</v>
+        <v>53.80549621582031</v>
       </c>
       <c r="L122" t="n">
         <v>4132.14990234375</v>
@@ -5088,7 +5088,7 @@
         <v>133.9139709472656</v>
       </c>
       <c r="C123" t="n">
-        <v>248.0245971679688</v>
+        <v>248.0246429443359</v>
       </c>
       <c r="D123" t="n">
         <v>107.9359130859375</v>
@@ -5097,10 +5097,10 @@
         <v>106.2099990844727</v>
       </c>
       <c r="F123" t="n">
-        <v>15.10013580322266</v>
+        <v>15.10013294219971</v>
       </c>
       <c r="G123" t="n">
-        <v>159.7202606201172</v>
+        <v>159.72021484375</v>
       </c>
       <c r="H123" t="n">
         <v>76.47000122070312</v>
@@ -5109,10 +5109,10 @@
         <v>224.4733276367188</v>
       </c>
       <c r="J123" t="n">
-        <v>35.23717880249023</v>
+        <v>35.23718643188477</v>
       </c>
       <c r="K123" t="n">
-        <v>45.43112564086914</v>
+        <v>45.43112182617188</v>
       </c>
       <c r="L123" t="n">
         <v>3785.3798828125</v>
@@ -5123,22 +5123,22 @@
         <v>44743</v>
       </c>
       <c r="B124" t="n">
-        <v>159.1746520996094</v>
+        <v>159.1746826171875</v>
       </c>
       <c r="C124" t="n">
-        <v>271.1148986816406</v>
+        <v>271.1148681640625</v>
       </c>
       <c r="D124" t="n">
-        <v>115.2235565185547</v>
+        <v>115.2235717773438</v>
       </c>
       <c r="E124" t="n">
         <v>134.9499969482422</v>
       </c>
       <c r="F124" t="n">
-        <v>18.09247398376465</v>
+        <v>18.09246635437012</v>
       </c>
       <c r="G124" t="n">
-        <v>157.5906524658203</v>
+        <v>157.5906677246094</v>
       </c>
       <c r="H124" t="n">
         <v>94.47000122070312</v>
@@ -5147,10 +5147,10 @@
         <v>297.1499938964844</v>
       </c>
       <c r="J124" t="n">
-        <v>34.20106506347656</v>
+        <v>34.20107269287109</v>
       </c>
       <c r="K124" t="n">
-        <v>50.07607269287109</v>
+        <v>50.07607650756836</v>
       </c>
       <c r="L124" t="n">
         <v>4130.2900390625</v>
@@ -5161,22 +5161,22 @@
         <v>44774</v>
       </c>
       <c r="B125" t="n">
-        <v>154.2071380615234</v>
+        <v>154.2071685791016</v>
       </c>
       <c r="C125" t="n">
-        <v>253.0415344238281</v>
+        <v>253.0414886474609</v>
       </c>
       <c r="D125" t="n">
-        <v>107.1999206542969</v>
+        <v>107.1999130249023</v>
       </c>
       <c r="E125" t="n">
         <v>126.7699966430664</v>
       </c>
       <c r="F125" t="n">
-        <v>15.0353889465332</v>
+        <v>15.03538513183594</v>
       </c>
       <c r="G125" t="n">
-        <v>161.3842926025391</v>
+        <v>161.3843231201172</v>
       </c>
       <c r="H125" t="n">
         <v>84.87000274658203</v>
@@ -5185,10 +5185,10 @@
         <v>275.6099853515625</v>
       </c>
       <c r="J125" t="n">
-        <v>30.36957359313965</v>
+        <v>30.36957550048828</v>
       </c>
       <c r="K125" t="n">
-        <v>46.67488098144531</v>
+        <v>46.67489242553711</v>
       </c>
       <c r="L125" t="n">
         <v>3955</v>
@@ -5199,19 +5199,19 @@
         <v>44805</v>
       </c>
       <c r="B126" t="n">
-        <v>135.5516510009766</v>
+        <v>135.5515747070312</v>
       </c>
       <c r="C126" t="n">
-        <v>225.3924560546875</v>
+        <v>225.3924713134766</v>
       </c>
       <c r="D126" t="n">
-        <v>94.74839782714844</v>
+        <v>94.7484130859375</v>
       </c>
       <c r="E126" t="n">
         <v>113</v>
       </c>
       <c r="F126" t="n">
-        <v>12.09545612335205</v>
+        <v>12.09545516967773</v>
       </c>
       <c r="G126" t="n">
         <v>134.3928375244141</v>
@@ -5223,10 +5223,10 @@
         <v>265.25</v>
       </c>
       <c r="J126" t="n">
-        <v>24.51829719543457</v>
+        <v>24.5182933807373</v>
       </c>
       <c r="K126" t="n">
-        <v>41.87031173706055</v>
+        <v>41.87030410766602</v>
       </c>
       <c r="L126" t="n">
         <v>3585.6201171875</v>
@@ -5237,10 +5237,10 @@
         <v>44835</v>
       </c>
       <c r="B127" t="n">
-        <v>150.4014892578125</v>
+        <v>150.4015045166016</v>
       </c>
       <c r="C127" t="n">
-        <v>224.6472930908203</v>
+        <v>224.6473083496094</v>
       </c>
       <c r="D127" t="n">
         <v>93.61915588378906</v>
@@ -5261,10 +5261,10 @@
         <v>227.5399932861328</v>
       </c>
       <c r="J127" t="n">
-        <v>27.04909515380859</v>
+        <v>27.04909133911133</v>
       </c>
       <c r="K127" t="n">
-        <v>44.33249664306641</v>
+        <v>44.33249282836914</v>
       </c>
       <c r="L127" t="n">
         <v>3871.97998046875</v>
@@ -5275,22 +5275,22 @@
         <v>44866</v>
       </c>
       <c r="B128" t="n">
-        <v>145.4341430664062</v>
+        <v>145.4340972900391</v>
       </c>
       <c r="C128" t="n">
-        <v>247.6114044189453</v>
+        <v>247.6114196777344</v>
       </c>
       <c r="D128" t="n">
-        <v>100.0380706787109</v>
+        <v>100.0380630493164</v>
       </c>
       <c r="E128" t="n">
         <v>96.54000091552734</v>
       </c>
       <c r="F128" t="n">
-        <v>16.86660575866699</v>
+        <v>16.86660766601562</v>
       </c>
       <c r="G128" t="n">
-        <v>116.9795913696289</v>
+        <v>116.9795989990234</v>
       </c>
       <c r="H128" t="n">
         <v>77.62999725341797</v>
@@ -5299,7 +5299,7 @@
         <v>194.6999969482422</v>
       </c>
       <c r="J128" t="n">
-        <v>28.99583053588867</v>
+        <v>28.9958324432373</v>
       </c>
       <c r="K128" t="n">
         <v>51.96234130859375</v>
@@ -5316,7 +5316,7 @@
         <v>127.6515045166016</v>
       </c>
       <c r="C129" t="n">
-        <v>232.7435150146484</v>
+        <v>232.7434844970703</v>
       </c>
       <c r="D129" t="n">
         <v>87.39835357666016</v>
@@ -5325,7 +5325,7 @@
         <v>84</v>
       </c>
       <c r="F129" t="n">
-        <v>14.5653018951416</v>
+        <v>14.56530094146729</v>
       </c>
       <c r="G129" t="n">
         <v>119.1983489990234</v>
@@ -5337,10 +5337,10 @@
         <v>123.1800003051758</v>
       </c>
       <c r="J129" t="n">
-        <v>25.48586273193359</v>
+        <v>25.48586082458496</v>
       </c>
       <c r="K129" t="n">
-        <v>53.16610717773438</v>
+        <v>53.16610336303711</v>
       </c>
       <c r="L129" t="n">
         <v>3839.5</v>
@@ -5351,13 +5351,13 @@
         <v>44927</v>
       </c>
       <c r="B130" t="n">
-        <v>141.7596740722656</v>
+        <v>141.7597045898438</v>
       </c>
       <c r="C130" t="n">
         <v>240.4977416992188</v>
       </c>
       <c r="D130" t="n">
-        <v>97.90831756591797</v>
+        <v>97.9083251953125</v>
       </c>
       <c r="E130" t="n">
         <v>103.129997253418</v>
@@ -5378,7 +5378,7 @@
         <v>27.25048828125</v>
       </c>
       <c r="K130" t="n">
-        <v>55.62696075439453</v>
+        <v>55.6269645690918</v>
       </c>
       <c r="L130" t="n">
         <v>4076.60009765625</v>
@@ -5389,10 +5389,10 @@
         <v>44958</v>
       </c>
       <c r="B131" t="n">
-        <v>145.0460968017578</v>
+        <v>145.0461120605469</v>
       </c>
       <c r="C131" t="n">
-        <v>242.66650390625</v>
+        <v>242.6664886474609</v>
       </c>
       <c r="D131" t="n">
         <v>89.21108245849609</v>
@@ -5404,7 +5404,7 @@
         <v>23.13863945007324</v>
       </c>
       <c r="G131" t="n">
-        <v>173.2803649902344</v>
+        <v>173.2803802490234</v>
       </c>
       <c r="H131" t="n">
         <v>78.58000183105469</v>
@@ -5413,10 +5413,10 @@
         <v>205.7100067138672</v>
       </c>
       <c r="J131" t="n">
-        <v>24.33236312866211</v>
+        <v>24.33236503601074</v>
       </c>
       <c r="K131" t="n">
-        <v>56.50937652587891</v>
+        <v>56.50938415527344</v>
       </c>
       <c r="L131" t="n">
         <v>3970.14990234375</v>
@@ -5427,19 +5427,19 @@
         <v>44986</v>
       </c>
       <c r="B132" t="n">
-        <v>162.2556304931641</v>
+        <v>162.2556457519531</v>
       </c>
       <c r="C132" t="n">
-        <v>280.4937133789062</v>
+        <v>280.4937438964844</v>
       </c>
       <c r="D132" t="n">
-        <v>102.7522354125977</v>
+        <v>102.7522277832031</v>
       </c>
       <c r="E132" t="n">
         <v>103.2900009155273</v>
       </c>
       <c r="F132" t="n">
-        <v>27.68914413452148</v>
+        <v>27.68914031982422</v>
       </c>
       <c r="G132" t="n">
         <v>209.9293518066406</v>
@@ -5451,10 +5451,10 @@
         <v>207.4600067138672</v>
       </c>
       <c r="J132" t="n">
-        <v>31.88681030273438</v>
+        <v>31.88681411743164</v>
       </c>
       <c r="K132" t="n">
-        <v>61.44130325317383</v>
+        <v>61.44130706787109</v>
       </c>
       <c r="L132" t="n">
         <v>4109.31005859375</v>
@@ -5465,22 +5465,22 @@
         <v>45017</v>
       </c>
       <c r="B133" t="n">
-        <v>166.9589691162109</v>
+        <v>166.958984375</v>
       </c>
       <c r="C133" t="n">
-        <v>298.9403686523438</v>
+        <v>298.9403381347656</v>
       </c>
       <c r="D133" t="n">
-        <v>106.3282089233398</v>
+        <v>106.3282012939453</v>
       </c>
       <c r="E133" t="n">
         <v>105.4499969482422</v>
       </c>
       <c r="F133" t="n">
-        <v>27.66123580932617</v>
+        <v>27.66123008728027</v>
       </c>
       <c r="G133" t="n">
-        <v>238.0401153564453</v>
+        <v>238.0401306152344</v>
       </c>
       <c r="H133" t="n">
         <v>89.37000274658203</v>
@@ -5489,10 +5489,10 @@
         <v>164.3099975585938</v>
       </c>
       <c r="J133" t="n">
-        <v>30.3154125213623</v>
+        <v>30.31541061401367</v>
       </c>
       <c r="K133" t="n">
-        <v>60.00090789794922</v>
+        <v>60.00090408325195</v>
       </c>
       <c r="L133" t="n">
         <v>4169.47998046875</v>
@@ -5509,16 +5509,16 @@
         <v>320.1966857910156</v>
       </c>
       <c r="D134" t="n">
-        <v>121.7118301391602</v>
+        <v>121.7118377685547</v>
       </c>
       <c r="E134" t="n">
         <v>120.5800018310547</v>
       </c>
       <c r="F134" t="n">
-        <v>37.71432495117188</v>
+        <v>37.71433258056641</v>
       </c>
       <c r="G134" t="n">
-        <v>262.2086181640625</v>
+        <v>262.2086486816406</v>
       </c>
       <c r="H134" t="n">
         <v>118.2099990844727</v>
@@ -5527,10 +5527,10 @@
         <v>203.9299926757812</v>
       </c>
       <c r="J134" t="n">
-        <v>30.81196212768555</v>
+        <v>30.81196403503418</v>
       </c>
       <c r="K134" t="n">
-        <v>77.37961578369141</v>
+        <v>77.37960815429688</v>
       </c>
       <c r="L134" t="n">
         <v>4179.830078125</v>
@@ -5541,22 +5541,22 @@
         <v>45078</v>
       </c>
       <c r="B135" t="n">
-        <v>191.1234588623047</v>
+        <v>191.1234741210938</v>
       </c>
       <c r="C135" t="n">
         <v>332.0434875488281</v>
       </c>
       <c r="D135" t="n">
-        <v>118.5717086791992</v>
+        <v>118.5717010498047</v>
       </c>
       <c r="E135" t="n">
         <v>130.3600006103516</v>
       </c>
       <c r="F135" t="n">
-        <v>42.17255783081055</v>
+        <v>42.17256927490234</v>
       </c>
       <c r="G135" t="n">
-        <v>284.2575378417969</v>
+        <v>284.2574462890625</v>
       </c>
       <c r="H135" t="n">
         <v>113.9100036621094</v>
@@ -5565,10 +5565,10 @@
         <v>261.7699890136719</v>
       </c>
       <c r="J135" t="n">
-        <v>32.77201080322266</v>
+        <v>32.77200698852539</v>
       </c>
       <c r="K135" t="n">
-        <v>83.51773834228516</v>
+        <v>83.51774597167969</v>
       </c>
       <c r="L135" t="n">
         <v>4450.3798828125</v>
@@ -5579,10 +5579,10 @@
         <v>45108</v>
       </c>
       <c r="B136" t="n">
-        <v>193.5670471191406</v>
+        <v>193.5670623779297</v>
       </c>
       <c r="C136" t="n">
-        <v>327.5388793945312</v>
+        <v>327.5388488769531</v>
       </c>
       <c r="D136" t="n">
         <v>131.4689788818359</v>
@@ -5591,10 +5591,10 @@
         <v>133.6799926757812</v>
       </c>
       <c r="F136" t="n">
-        <v>46.58601379394531</v>
+        <v>46.58601760864258</v>
       </c>
       <c r="G136" t="n">
-        <v>315.5775146484375</v>
+        <v>315.5774841308594</v>
       </c>
       <c r="H136" t="n">
         <v>114.4000015258789</v>
@@ -5606,7 +5606,7 @@
         <v>35.05546951293945</v>
       </c>
       <c r="K136" t="n">
-        <v>86.52365875244141</v>
+        <v>86.52366638183594</v>
       </c>
       <c r="L136" t="n">
         <v>4588.9599609375</v>
@@ -5623,16 +5623,16 @@
         <v>320.259033203125</v>
       </c>
       <c r="D137" t="n">
-        <v>134.886474609375</v>
+        <v>134.8864593505859</v>
       </c>
       <c r="E137" t="n">
         <v>138.0099945068359</v>
       </c>
       <c r="F137" t="n">
-        <v>49.20398330688477</v>
+        <v>49.20397567749023</v>
       </c>
       <c r="G137" t="n">
-        <v>293.0830078125</v>
+        <v>293.0829772949219</v>
       </c>
       <c r="H137" t="n">
         <v>105.7200012207031</v>
@@ -5655,22 +5655,22 @@
         <v>45170</v>
       </c>
       <c r="B138" t="n">
-        <v>168.92529296875</v>
+        <v>168.9252777099609</v>
       </c>
       <c r="C138" t="n">
-        <v>308.5238647460938</v>
+        <v>308.5238342285156</v>
       </c>
       <c r="D138" t="n">
-        <v>129.6264953613281</v>
+        <v>129.6265106201172</v>
       </c>
       <c r="E138" t="n">
         <v>127.120002746582</v>
       </c>
       <c r="F138" t="n">
-        <v>43.36946868896484</v>
+        <v>43.36948013305664</v>
       </c>
       <c r="G138" t="n">
-        <v>297.3619689941406</v>
+        <v>297.3619995117188</v>
       </c>
       <c r="H138" t="n">
         <v>102.8199996948242</v>
@@ -5679,10 +5679,10 @@
         <v>250.2200012207031</v>
       </c>
       <c r="J138" t="n">
-        <v>34.96520614624023</v>
+        <v>34.96520233154297</v>
       </c>
       <c r="K138" t="n">
-        <v>80.40529632568359</v>
+        <v>80.40530395507812</v>
       </c>
       <c r="L138" t="n">
         <v>4288.0498046875</v>
@@ -5693,13 +5693,13 @@
         <v>45200</v>
       </c>
       <c r="B139" t="n">
-        <v>168.4911499023438</v>
+        <v>168.4911346435547</v>
       </c>
       <c r="C139" t="n">
         <v>330.3721313476562</v>
       </c>
       <c r="D139" t="n">
-        <v>122.9104156494141</v>
+        <v>122.9104309082031</v>
       </c>
       <c r="E139" t="n">
         <v>133.0899963378906</v>
@@ -5708,7 +5708,7 @@
         <v>40.65856552124023</v>
       </c>
       <c r="G139" t="n">
-        <v>298.4118957519531</v>
+        <v>298.4118347167969</v>
       </c>
       <c r="H139" t="n">
         <v>98.5</v>
@@ -5731,22 +5731,22 @@
         <v>45231</v>
       </c>
       <c r="B140" t="n">
-        <v>187.6620635986328</v>
+        <v>187.6620941162109</v>
       </c>
       <c r="C140" t="n">
         <v>370.9898986816406</v>
       </c>
       <c r="D140" t="n">
-        <v>131.28076171875</v>
+        <v>131.2807769775391</v>
       </c>
       <c r="E140" t="n">
         <v>146.0899963378906</v>
       </c>
       <c r="F140" t="n">
-        <v>46.63072204589844</v>
+        <v>46.63073348999023</v>
       </c>
       <c r="G140" t="n">
-        <v>324.0464477539062</v>
+        <v>324.0463562011719</v>
       </c>
       <c r="H140" t="n">
         <v>121.1600036621094</v>
@@ -5769,13 +5769,13 @@
         <v>45261</v>
       </c>
       <c r="B141" t="n">
-        <v>190.2110290527344</v>
+        <v>190.2110443115234</v>
       </c>
       <c r="C141" t="n">
-        <v>368.1799011230469</v>
+        <v>368.1798706054688</v>
       </c>
       <c r="D141" t="n">
-        <v>138.3732757568359</v>
+        <v>138.373291015625</v>
       </c>
       <c r="E141" t="n">
         <v>151.9400024414062</v>
@@ -5784,7 +5784,7 @@
         <v>49.37887573242188</v>
       </c>
       <c r="G141" t="n">
-        <v>350.6020202636719</v>
+        <v>350.6019897460938</v>
       </c>
       <c r="H141" t="n">
         <v>147.4100036621094</v>
@@ -5796,7 +5796,7 @@
         <v>49.58590316772461</v>
       </c>
       <c r="K141" t="n">
-        <v>108.5568161010742</v>
+        <v>108.5568084716797</v>
       </c>
       <c r="L141" t="n">
         <v>4769.830078125</v>
@@ -5807,13 +5807,13 @@
         <v>45292</v>
       </c>
       <c r="B142" t="n">
-        <v>182.1789245605469</v>
+        <v>182.178955078125</v>
       </c>
       <c r="C142" t="n">
-        <v>389.2697143554688</v>
+        <v>389.2696228027344</v>
       </c>
       <c r="D142" t="n">
-        <v>138.7794189453125</v>
+        <v>138.7794342041016</v>
       </c>
       <c r="E142" t="n">
         <v>155.1999969482422</v>
@@ -5834,7 +5834,7 @@
         <v>42.51066207885742</v>
       </c>
       <c r="K142" t="n">
-        <v>114.7565765380859</v>
+        <v>114.7565841674805</v>
       </c>
       <c r="L142" t="n">
         <v>4845.64990234375</v>
@@ -5845,22 +5845,22 @@
         <v>45323</v>
       </c>
       <c r="B143" t="n">
-        <v>178.80078125</v>
+        <v>178.8007659912109</v>
       </c>
       <c r="C143" t="n">
         <v>405.7428588867188</v>
       </c>
       <c r="D143" t="n">
-        <v>137.1548919677734</v>
+        <v>137.1548767089844</v>
       </c>
       <c r="E143" t="n">
         <v>176.7599945068359</v>
       </c>
       <c r="F143" t="n">
-        <v>78.88335418701172</v>
+        <v>78.88334655761719</v>
       </c>
       <c r="G143" t="n">
-        <v>485.9953002929688</v>
+        <v>485.9953308105469</v>
       </c>
       <c r="H143" t="n">
         <v>192.5299987792969</v>
@@ -5872,7 +5872,7 @@
         <v>42.60557556152344</v>
       </c>
       <c r="K143" t="n">
-        <v>126.4744033813477</v>
+        <v>126.4743957519531</v>
       </c>
       <c r="L143" t="n">
         <v>5096.27001953125</v>
@@ -5889,7 +5889,7 @@
         <v>412.6877136230469</v>
       </c>
       <c r="D144" t="n">
-        <v>149.5073394775391</v>
+        <v>149.50732421875</v>
       </c>
       <c r="E144" t="n">
         <v>180.3800048828125</v>
@@ -5898,7 +5898,7 @@
         <v>90.09910583496094</v>
       </c>
       <c r="G144" t="n">
-        <v>481.4837036132812</v>
+        <v>481.4836730957031</v>
       </c>
       <c r="H144" t="n">
         <v>180.4900054931641</v>
@@ -5910,7 +5910,7 @@
         <v>43.71401214599609</v>
       </c>
       <c r="K144" t="n">
-        <v>129.4468231201172</v>
+        <v>129.4468536376953</v>
       </c>
       <c r="L144" t="n">
         <v>5254.35009765625</v>
@@ -5924,19 +5924,19 @@
         <v>168.4931488037109</v>
       </c>
       <c r="C145" t="n">
-        <v>381.8969421386719</v>
+        <v>381.89697265625</v>
       </c>
       <c r="D145" t="n">
-        <v>161.2456359863281</v>
+        <v>161.2456207275391</v>
       </c>
       <c r="E145" t="n">
         <v>175</v>
       </c>
       <c r="F145" t="n">
-        <v>86.15634155273438</v>
+        <v>86.15633392333984</v>
       </c>
       <c r="G145" t="n">
-        <v>426.5411376953125</v>
+        <v>426.5411682128906</v>
       </c>
       <c r="H145" t="n">
         <v>158.3800048828125</v>
@@ -5948,7 +5948,7 @@
         <v>30.15544509887695</v>
       </c>
       <c r="K145" t="n">
-        <v>126.9915237426758</v>
+        <v>126.9915161132812</v>
       </c>
       <c r="L145" t="n">
         <v>5035.68994140625</v>
@@ -5959,13 +5959,13 @@
         <v>45413</v>
       </c>
       <c r="B146" t="n">
-        <v>190.4347229003906</v>
+        <v>190.4347076416016</v>
       </c>
       <c r="C146" t="n">
         <v>407.9389343261719</v>
       </c>
       <c r="D146" t="n">
-        <v>170.8740234375</v>
+        <v>170.8740081787109</v>
       </c>
       <c r="E146" t="n">
         <v>176.4400024414062</v>
@@ -5974,7 +5974,7 @@
         <v>109.3212966918945</v>
       </c>
       <c r="G146" t="n">
-        <v>462.891845703125</v>
+        <v>462.8918151855469</v>
       </c>
       <c r="H146" t="n">
         <v>166.8999938964844</v>
@@ -5986,7 +5986,7 @@
         <v>30.6555347442627</v>
       </c>
       <c r="K146" t="n">
-        <v>129.7534942626953</v>
+        <v>129.7535247802734</v>
       </c>
       <c r="L146" t="n">
         <v>5277.509765625</v>
@@ -6003,16 +6003,16 @@
         <v>439.2077026367188</v>
       </c>
       <c r="D147" t="n">
-        <v>180.6401519775391</v>
+        <v>180.64013671875</v>
       </c>
       <c r="E147" t="n">
         <v>193.25</v>
       </c>
       <c r="F147" t="n">
-        <v>123.1988754272461</v>
+        <v>123.198860168457</v>
       </c>
       <c r="G147" t="n">
-        <v>500.4628295898438</v>
+        <v>500.4628601074219</v>
       </c>
       <c r="H147" t="n">
         <v>162.2100067138672</v>
@@ -6024,7 +6024,7 @@
         <v>30.77477645874023</v>
       </c>
       <c r="K147" t="n">
-        <v>157.3028106689453</v>
+        <v>157.3027954101562</v>
       </c>
       <c r="L147" t="n">
         <v>5460.47998046875</v>
@@ -6038,19 +6038,19 @@
         <v>219.9830474853516</v>
       </c>
       <c r="C148" t="n">
-        <v>411.1031188964844</v>
+        <v>411.1031494140625</v>
       </c>
       <c r="D148" t="n">
-        <v>170.1180877685547</v>
+        <v>170.1180572509766</v>
       </c>
       <c r="E148" t="n">
         <v>186.9799957275391</v>
       </c>
       <c r="F148" t="n">
-        <v>116.6968536376953</v>
+        <v>116.6968612670898</v>
       </c>
       <c r="G148" t="n">
-        <v>471.2918701171875</v>
+        <v>471.2918395996094</v>
       </c>
       <c r="H148" t="n">
         <v>144.4799957275391</v>
@@ -6079,16 +6079,16 @@
         <v>410.6529235839844</v>
       </c>
       <c r="D149" t="n">
-        <v>162.0257263183594</v>
+        <v>162.0257415771484</v>
       </c>
       <c r="E149" t="n">
         <v>178.5</v>
       </c>
       <c r="F149" t="n">
-        <v>119.0403747558594</v>
+        <v>119.0403823852539</v>
       </c>
       <c r="G149" t="n">
-        <v>517.4255981445312</v>
+        <v>517.4254760742188</v>
       </c>
       <c r="H149" t="n">
         <v>148.5599975585938</v>
@@ -6100,7 +6100,7 @@
         <v>22.04000091552734</v>
       </c>
       <c r="K149" t="n">
-        <v>159.5239410400391</v>
+        <v>159.52392578125</v>
       </c>
       <c r="L149" t="n">
         <v>5648.39990234375</v>
@@ -6111,19 +6111,19 @@
         <v>45536</v>
       </c>
       <c r="B150" t="n">
-        <v>231.0670776367188</v>
+        <v>231.0670471191406</v>
       </c>
       <c r="C150" t="n">
         <v>423.6082458496094</v>
       </c>
       <c r="D150" t="n">
-        <v>164.6934967041016</v>
+        <v>164.6935119628906</v>
       </c>
       <c r="E150" t="n">
         <v>186.3300018310547</v>
       </c>
       <c r="F150" t="n">
-        <v>121.1150360107422</v>
+        <v>121.1150207519531</v>
       </c>
       <c r="G150" t="n">
         <v>568.716552734375</v>
@@ -6149,19 +6149,19 @@
         <v>45566</v>
       </c>
       <c r="B151" t="n">
-        <v>224.0359039306641</v>
+        <v>224.035888671875</v>
       </c>
       <c r="C151" t="n">
-        <v>400.0307312011719</v>
+        <v>400.0306701660156</v>
       </c>
       <c r="D151" t="n">
-        <v>169.9168090820312</v>
+        <v>169.9168395996094</v>
       </c>
       <c r="E151" t="n">
         <v>186.3999938964844</v>
       </c>
       <c r="F151" t="n">
-        <v>132.4047088623047</v>
+        <v>132.4047241210938</v>
       </c>
       <c r="G151" t="n">
         <v>563.88818359375</v>
@@ -6176,7 +6176,7 @@
         <v>21.52000045776367</v>
       </c>
       <c r="K151" t="n">
-        <v>166.8802947998047</v>
+        <v>166.8803100585938</v>
       </c>
       <c r="L151" t="n">
         <v>5705.4501953125</v>
@@ -6214,7 +6214,7 @@
         <v>24.04999923706055</v>
       </c>
       <c r="K152" t="n">
-        <v>159.3211975097656</v>
+        <v>159.3212127685547</v>
       </c>
       <c r="L152" t="n">
         <v>6032.3798828125</v>
@@ -6231,16 +6231,16 @@
         <v>415.7757263183594</v>
       </c>
       <c r="D153" t="n">
-        <v>188.1954040527344</v>
+        <v>188.1954345703125</v>
       </c>
       <c r="E153" t="n">
         <v>219.3899993896484</v>
       </c>
       <c r="F153" t="n">
-        <v>133.9398651123047</v>
+        <v>133.9398345947266</v>
       </c>
       <c r="G153" t="n">
-        <v>582.1707763671875</v>
+        <v>582.1708374023438</v>
       </c>
       <c r="H153" t="n">
         <v>120.7900009155273</v>
@@ -6252,7 +6252,7 @@
         <v>20.04999923706055</v>
       </c>
       <c r="K153" t="n">
-        <v>228.5044097900391</v>
+        <v>228.50439453125</v>
       </c>
       <c r="L153" t="n">
         <v>5881.6298828125</v>
@@ -6263,19 +6263,19 @@
         <v>45658</v>
       </c>
       <c r="B154" t="n">
-        <v>234.2996826171875</v>
+        <v>234.2996673583984</v>
       </c>
       <c r="C154" t="n">
-        <v>409.4231872558594</v>
+        <v>409.4231262207031</v>
       </c>
       <c r="D154" t="n">
-        <v>202.8295288085938</v>
+        <v>202.8295135498047</v>
       </c>
       <c r="E154" t="n">
         <v>237.6799926757812</v>
       </c>
       <c r="F154" t="n">
-        <v>119.7569351196289</v>
+        <v>119.7569427490234</v>
       </c>
       <c r="G154" t="n">
         <v>685.24951171875</v>
@@ -6301,22 +6301,22 @@
         <v>45689</v>
       </c>
       <c r="B155" t="n">
-        <v>240.361572265625</v>
+        <v>240.3615875244141</v>
       </c>
       <c r="C155" t="n">
-        <v>392.3837280273438</v>
+        <v>392.3837585449219</v>
       </c>
       <c r="D155" t="n">
-        <v>169.2864074707031</v>
+        <v>169.2863922119141</v>
       </c>
       <c r="E155" t="n">
         <v>212.2799987792969</v>
       </c>
       <c r="F155" t="n">
-        <v>124.5942993164062</v>
+        <v>124.5942916870117</v>
       </c>
       <c r="G155" t="n">
-        <v>664.3892211914062</v>
+        <v>664.38916015625</v>
       </c>
       <c r="H155" t="n">
         <v>99.86000061035156</v>
@@ -6328,7 +6328,7 @@
         <v>23.72999954223633</v>
       </c>
       <c r="K155" t="n">
-        <v>196.5606994628906</v>
+        <v>196.5606842041016</v>
       </c>
       <c r="L155" t="n">
         <v>5954.5</v>
@@ -6342,16 +6342,16 @@
         <v>220.7720947265625</v>
       </c>
       <c r="C156" t="n">
-        <v>371.0343933105469</v>
+        <v>371.0344543457031</v>
       </c>
       <c r="D156" t="n">
-        <v>153.9147033691406</v>
+        <v>153.9147186279297</v>
       </c>
       <c r="E156" t="n">
         <v>190.2599945068359</v>
       </c>
       <c r="F156" t="n">
-        <v>108.1073608398438</v>
+        <v>108.1073532104492</v>
       </c>
       <c r="G156" t="n">
         <v>573.5827026367188</v>
@@ -6366,7 +6366,7 @@
         <v>22.70999908447266</v>
       </c>
       <c r="K156" t="n">
-        <v>165.5204620361328</v>
+        <v>165.5204467773438</v>
       </c>
       <c r="L156" t="n">
         <v>5611.85009765625</v>
@@ -6377,13 +6377,13 @@
         <v>45748</v>
       </c>
       <c r="B157" t="n">
-        <v>211.2009429931641</v>
+        <v>211.2009582519531</v>
       </c>
       <c r="C157" t="n">
-        <v>390.6738891601562</v>
+        <v>390.673828125</v>
       </c>
       <c r="D157" t="n">
-        <v>158.0552062988281</v>
+        <v>158.0552215576172</v>
       </c>
       <c r="E157" t="n">
         <v>184.4199981689453</v>
@@ -6392,7 +6392,7 @@
         <v>108.64599609375</v>
       </c>
       <c r="G157" t="n">
-        <v>546.3545532226562</v>
+        <v>546.3546142578125</v>
       </c>
       <c r="H157" t="n">
         <v>97.34999847412109</v>
@@ -6415,22 +6415,22 @@
         <v>45778</v>
       </c>
       <c r="B158" t="n">
-        <v>199.8839416503906</v>
+        <v>199.8839569091797</v>
       </c>
       <c r="C158" t="n">
         <v>455.8537902832031</v>
       </c>
       <c r="D158" t="n">
-        <v>170.9345245361328</v>
+        <v>170.9345397949219</v>
       </c>
       <c r="E158" t="n">
         <v>205.0099945068359</v>
       </c>
       <c r="F158" t="n">
-        <v>134.7900848388672</v>
+        <v>134.7900695800781</v>
       </c>
       <c r="G158" t="n">
-        <v>644.3699951171875</v>
+        <v>644.3700561523438</v>
       </c>
       <c r="H158" t="n">
         <v>110.7300033569336</v>
@@ -6442,7 +6442,7 @@
         <v>19.54999923706055</v>
       </c>
       <c r="K158" t="n">
-        <v>239.3091735839844</v>
+        <v>239.3091888427734</v>
       </c>
       <c r="L158" t="n">
         <v>5911.68994140625</v>
@@ -6459,13 +6459,13 @@
         <v>492.5411682128906</v>
       </c>
       <c r="D159" t="n">
-        <v>175.6157989501953</v>
+        <v>175.6158142089844</v>
       </c>
       <c r="E159" t="n">
         <v>219.3899993896484</v>
       </c>
       <c r="F159" t="n">
-        <v>157.603515625</v>
+        <v>157.6035003662109</v>
       </c>
       <c r="G159" t="n">
         <v>735.0987548828125</v>
@@ -6503,7 +6503,7 @@
         <v>234.1100006103516</v>
       </c>
       <c r="F160" t="n">
-        <v>177.4348754882812</v>
+        <v>177.4348602294922</v>
       </c>
       <c r="G160" t="n">
         <v>770.305419921875</v>
@@ -6535,7 +6535,7 @@
         <v>502.5551147460938</v>
       </c>
       <c r="D161" t="n">
-        <v>212.1679534912109</v>
+        <v>212.1679840087891</v>
       </c>
       <c r="E161" t="n">
         <v>229</v>
@@ -6544,7 +6544,7 @@
         <v>173.7538909912109</v>
       </c>
       <c r="G161" t="n">
-        <v>735.7062377929688</v>
+        <v>735.7061767578125</v>
       </c>
       <c r="H161" t="n">
         <v>162.6300048828125</v>
@@ -6567,13 +6567,13 @@
         <v>45901</v>
       </c>
       <c r="B162" t="n">
-        <v>253.69287109375</v>
+        <v>253.6928863525391</v>
       </c>
       <c r="C162" t="n">
         <v>513.7232666015625</v>
       </c>
       <c r="D162" t="n">
-        <v>242.4694366455078</v>
+        <v>242.4694213867188</v>
       </c>
       <c r="E162" t="n">
         <v>219.5700073242188</v>
@@ -6582,7 +6582,7 @@
         <v>186.1340637207031</v>
       </c>
       <c r="G162" t="n">
-        <v>731.8973388671875</v>
+        <v>731.8973999023438</v>
       </c>
       <c r="H162" t="n">
         <v>161.7899932861328</v>
@@ -6605,7 +6605,7 @@
         <v>45931</v>
       </c>
       <c r="B163" t="n">
-        <v>269.3749084472656</v>
+        <v>269.3749389648438</v>
       </c>
       <c r="C163" t="n">
         <v>513.5843505859375</v>
@@ -6617,7 +6617,7 @@
         <v>244.2200012207031</v>
       </c>
       <c r="F163" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060577392578</v>
       </c>
       <c r="G163" t="n">
         <v>646.1581420898438</v>
@@ -6632,7 +6632,7 @@
         <v>39.9900016784668</v>
       </c>
       <c r="K163" t="n">
-        <v>366.9019470214844</v>
+        <v>366.9019775390625</v>
       </c>
       <c r="L163" t="n">
         <v>6840.2001953125</v>
@@ -6670,7 +6670,7 @@
         <v>40.56000137329102</v>
       </c>
       <c r="K164" t="n">
-        <v>399.9859619140625</v>
+        <v>399.9859313964844</v>
       </c>
       <c r="L164" t="n">
         <v>6849.08984375</v>
@@ -6696,7 +6696,7 @@
         <v>186.0646057128906</v>
       </c>
       <c r="G165" t="n">
-        <v>658.39501953125</v>
+        <v>658.3950805664062</v>
       </c>
       <c r="H165" t="n">
         <v>214.1600036621094</v>
@@ -6769,10 +6769,10 @@
         <v>210</v>
       </c>
       <c r="F167" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="G167" t="n">
-        <v>646.515625</v>
+        <v>646.5156860351562</v>
       </c>
       <c r="H167" t="n">
         <v>200.2100067138672</v>
@@ -6807,7 +6807,7 @@
         <v>208.2700042724609</v>
       </c>
       <c r="F168" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="G168" t="n">
         <v>571.1494750976562</v>
@@ -6845,7 +6845,7 @@
         <v>265.0599975585938</v>
       </c>
       <c r="F169" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="G169" t="n">
         <v>610.8612670898438</v>
@@ -7054,44 +7054,6 @@
       </c>
       <c r="L174" t="n">
         <v>7651.5400390625</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B175" t="n">
-        <v>342.9599914550781</v>
-      </c>
-      <c r="C175" t="n">
-        <v>533.6900024414062</v>
-      </c>
-      <c r="D175" t="n">
-        <v>347.6400146484375</v>
-      </c>
-      <c r="E175" t="n">
-        <v>254.0800018310547</v>
-      </c>
-      <c r="F175" t="n">
-        <v>221.3000030517578</v>
-      </c>
-      <c r="G175" t="n">
-        <v>737.5399780273438</v>
-      </c>
-      <c r="H175" t="n">
-        <v>570.8200073242188</v>
-      </c>
-      <c r="I175" t="n">
-        <v>367.1600036621094</v>
-      </c>
-      <c r="J175" t="n">
-        <v>98.12000274658203</v>
-      </c>
-      <c r="K175" t="n">
-        <v>346.25</v>
-      </c>
-      <c r="L175" t="n">
-        <v>7718.93994140625</v>
       </c>
     </row>
   </sheetData>

--- a/monthly.xlsx
+++ b/monthly.xlsx
@@ -487,22 +487,22 @@
         <v>41030</v>
       </c>
       <c r="B2" t="n">
-        <v>17.27969360351562</v>
+        <v>17.27968978881836</v>
       </c>
       <c r="C2" t="n">
-        <v>23.01618003845215</v>
+        <v>23.01618385314941</v>
       </c>
       <c r="D2" t="n">
-        <v>14.39902019500732</v>
+        <v>14.39901924133301</v>
       </c>
       <c r="E2" t="n">
         <v>10.64550018310547</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2842412889003754</v>
+        <v>0.2842412292957306</v>
       </c>
       <c r="G2" t="n">
-        <v>29.31918907165527</v>
+        <v>29.31919097900391</v>
       </c>
       <c r="H2" t="n">
         <v>6.079999923706055</v>
@@ -514,7 +514,7 @@
         <v>18.13143730163574</v>
       </c>
       <c r="K2" t="n">
-        <v>2.36237907409668</v>
+        <v>2.362378120422363</v>
       </c>
       <c r="L2" t="n">
         <v>1310.329956054688</v>
@@ -525,22 +525,22 @@
         <v>41061</v>
       </c>
       <c r="B3" t="n">
-        <v>17.46722602844238</v>
+        <v>17.46722793579102</v>
       </c>
       <c r="C3" t="n">
-        <v>24.12006568908691</v>
+        <v>24.12006950378418</v>
       </c>
       <c r="D3" t="n">
-        <v>14.37943553924561</v>
+        <v>14.37943458557129</v>
       </c>
       <c r="E3" t="n">
         <v>11.41749954223633</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3160266876220703</v>
+        <v>0.3160268068313599</v>
       </c>
       <c r="G3" t="n">
-        <v>30.80496025085449</v>
+        <v>30.80496215820312</v>
       </c>
       <c r="H3" t="n">
         <v>5.730000019073486</v>
@@ -549,7 +549,7 @@
         <v>2.085999965667725</v>
       </c>
       <c r="J3" t="n">
-        <v>18.69979286193848</v>
+        <v>18.69979858398438</v>
       </c>
       <c r="K3" t="n">
         <v>2.573558568954468</v>
@@ -566,7 +566,7 @@
         <v>18.26760673522949</v>
       </c>
       <c r="C4" t="n">
-        <v>23.23695755004883</v>
+        <v>23.23695945739746</v>
       </c>
       <c r="D4" t="n">
         <v>15.69078063964844</v>
@@ -575,10 +575,10 @@
         <v>11.66499996185303</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3096239864826202</v>
+        <v>0.3096239566802979</v>
       </c>
       <c r="G4" t="n">
-        <v>21.50404167175293</v>
+        <v>21.5040397644043</v>
       </c>
       <c r="H4" t="n">
         <v>4.059999942779541</v>
@@ -587,10 +587,10 @@
         <v>1.827999949455261</v>
       </c>
       <c r="J4" t="n">
-        <v>18.03319931030273</v>
+        <v>18.03319549560547</v>
       </c>
       <c r="K4" t="n">
-        <v>2.645245552062988</v>
+        <v>2.64524507522583</v>
       </c>
       <c r="L4" t="n">
         <v>1379.319946289062</v>
@@ -601,13 +601,13 @@
         <v>41122</v>
       </c>
       <c r="B5" t="n">
-        <v>19.98250961303711</v>
+        <v>19.98251342773438</v>
       </c>
       <c r="C5" t="n">
-        <v>24.4624137878418</v>
+        <v>24.46241188049316</v>
       </c>
       <c r="D5" t="n">
-        <v>16.98279190063477</v>
+        <v>16.9827938079834</v>
       </c>
       <c r="E5" t="n">
         <v>12.41349983215332</v>
@@ -628,7 +628,7 @@
         <v>17.57536315917969</v>
       </c>
       <c r="K5" t="n">
-        <v>2.621588706970215</v>
+        <v>2.621588468551636</v>
       </c>
       <c r="L5" t="n">
         <v>1406.579956054688</v>
@@ -642,19 +642,19 @@
         <v>20.03837776184082</v>
       </c>
       <c r="C6" t="n">
-        <v>23.62107276916504</v>
+        <v>23.62106895446777</v>
       </c>
       <c r="D6" t="n">
-        <v>18.70340347290039</v>
+        <v>18.70340538024902</v>
       </c>
       <c r="E6" t="n">
         <v>12.71599960327148</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3050504624843597</v>
+        <v>0.3050505220890045</v>
       </c>
       <c r="G6" t="n">
-        <v>21.45451545715332</v>
+        <v>21.45451354980469</v>
       </c>
       <c r="H6" t="n">
         <v>3.369999885559082</v>
@@ -663,10 +663,10 @@
         <v>1.952000021934509</v>
       </c>
       <c r="J6" t="n">
-        <v>16.03937530517578</v>
+        <v>16.03937339782715</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5111083984375</v>
+        <v>2.511108636856079</v>
       </c>
       <c r="L6" t="n">
         <v>1440.670043945312</v>
@@ -677,13 +677,13 @@
         <v>41183</v>
       </c>
       <c r="B7" t="n">
-        <v>17.88224792480469</v>
+        <v>17.88224601745605</v>
       </c>
       <c r="C7" t="n">
         <v>22.65273475646973</v>
       </c>
       <c r="D7" t="n">
-        <v>16.86404991149902</v>
+        <v>16.86405563354492</v>
       </c>
       <c r="E7" t="n">
         <v>11.64449977874756</v>
@@ -692,7 +692,7 @@
         <v>0.2739508450031281</v>
       </c>
       <c r="G7" t="n">
-        <v>20.90973281860352</v>
+        <v>20.90973472595215</v>
       </c>
       <c r="H7" t="n">
         <v>2.049999952316284</v>
@@ -701,7 +701,7 @@
         <v>1.875332951545715</v>
       </c>
       <c r="J7" t="n">
-        <v>15.31030750274658</v>
+        <v>15.31030941009521</v>
       </c>
       <c r="K7" t="n">
         <v>2.378604888916016</v>
@@ -718,7 +718,7 @@
         <v>17.66097068786621</v>
       </c>
       <c r="C8" t="n">
-        <v>21.30241966247559</v>
+        <v>21.30241584777832</v>
       </c>
       <c r="D8" t="n">
         <v>17.31199073791504</v>
@@ -727,10 +727,10 @@
         <v>12.60249996185303</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2754881680011749</v>
+        <v>0.2754881978034973</v>
       </c>
       <c r="G8" t="n">
-        <v>27.7343692779541</v>
+        <v>27.73437118530273</v>
       </c>
       <c r="H8" t="n">
         <v>2.200000047683716</v>
@@ -739,10 +739,10 @@
         <v>2.254667043685913</v>
       </c>
       <c r="J8" t="n">
-        <v>13.99492359161377</v>
+        <v>13.99492931365967</v>
       </c>
       <c r="K8" t="n">
-        <v>2.527672529220581</v>
+        <v>2.527672290802002</v>
       </c>
       <c r="L8" t="n">
         <v>1416.180053710938</v>
@@ -759,16 +759,16 @@
         <v>21.37443351745605</v>
       </c>
       <c r="D9" t="n">
-        <v>17.53534126281738</v>
+        <v>17.53533935546875</v>
       </c>
       <c r="E9" t="n">
         <v>12.54349994659424</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2821624875068665</v>
+        <v>0.2821624279022217</v>
       </c>
       <c r="G9" t="n">
-        <v>26.36746215820312</v>
+        <v>26.36745834350586</v>
       </c>
       <c r="H9" t="n">
         <v>2.400000095367432</v>
@@ -777,7 +777,7 @@
         <v>2.257999897003174</v>
       </c>
       <c r="J9" t="n">
-        <v>14.74580383300781</v>
+        <v>14.74580764770508</v>
       </c>
       <c r="K9" t="n">
         <v>2.290488958358765</v>
@@ -791,22 +791,22 @@
         <v>41275</v>
       </c>
       <c r="B10" t="n">
-        <v>13.74452018737793</v>
+        <v>13.74452114105225</v>
       </c>
       <c r="C10" t="n">
-        <v>21.96661758422852</v>
+        <v>21.96661949157715</v>
       </c>
       <c r="D10" t="n">
-        <v>18.73290634155273</v>
+        <v>18.7329044342041</v>
       </c>
       <c r="E10" t="n">
         <v>13.27499961853027</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2821624875068665</v>
+        <v>0.2821624279022217</v>
       </c>
       <c r="G10" t="n">
-        <v>30.68609619140625</v>
+        <v>30.68609809875488</v>
       </c>
       <c r="H10" t="n">
         <v>2.599999904632568</v>
@@ -815,10 +815,10 @@
         <v>2.500667095184326</v>
       </c>
       <c r="J10" t="n">
-        <v>15.0461597442627</v>
+        <v>15.0461540222168</v>
       </c>
       <c r="K10" t="n">
-        <v>2.588650703430176</v>
+        <v>2.588651418685913</v>
       </c>
       <c r="L10" t="n">
         <v>1498.109985351562</v>
@@ -829,22 +829,22 @@
         <v>41306</v>
       </c>
       <c r="B11" t="n">
-        <v>13.3969841003418</v>
+        <v>13.39697742462158</v>
       </c>
       <c r="C11" t="n">
-        <v>22.4308910369873</v>
+        <v>22.43088912963867</v>
       </c>
       <c r="D11" t="n">
-        <v>19.86106109619141</v>
+        <v>19.86105918884277</v>
       </c>
       <c r="E11" t="n">
         <v>13.21350002288818</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2931560277938843</v>
+        <v>0.2931559681892395</v>
       </c>
       <c r="G11" t="n">
-        <v>26.99148559570312</v>
+        <v>26.99148178100586</v>
       </c>
       <c r="H11" t="n">
         <v>2.490000009536743</v>
@@ -853,10 +853,10 @@
         <v>2.322000026702881</v>
       </c>
       <c r="J11" t="n">
-        <v>15.09221172332764</v>
+        <v>15.09221363067627</v>
       </c>
       <c r="K11" t="n">
-        <v>2.476478576660156</v>
+        <v>2.476478815078735</v>
       </c>
       <c r="L11" t="n">
         <v>1514.680053710938</v>
@@ -867,22 +867,22 @@
         <v>41334</v>
       </c>
       <c r="B12" t="n">
-        <v>13.43521785736084</v>
+        <v>13.43522548675537</v>
       </c>
       <c r="C12" t="n">
         <v>23.08444976806641</v>
       </c>
       <c r="D12" t="n">
-        <v>19.68728828430176</v>
+        <v>19.68728637695312</v>
       </c>
       <c r="E12" t="n">
         <v>13.32450008392334</v>
       </c>
       <c r="F12" t="n">
-        <v>0.297092467546463</v>
+        <v>0.2970924973487854</v>
       </c>
       <c r="G12" t="n">
-        <v>25.33732795715332</v>
+        <v>25.33732223510742</v>
       </c>
       <c r="H12" t="n">
         <v>2.549999952316284</v>
@@ -891,10 +891,10 @@
         <v>2.526000022888184</v>
       </c>
       <c r="J12" t="n">
-        <v>15.78610992431641</v>
+        <v>15.78611183166504</v>
       </c>
       <c r="K12" t="n">
-        <v>2.613326072692871</v>
+        <v>2.613325357437134</v>
       </c>
       <c r="L12" t="n">
         <v>1569.18994140625</v>
@@ -905,13 +905,13 @@
         <v>41365</v>
       </c>
       <c r="B13" t="n">
-        <v>13.43886566162109</v>
+        <v>13.43886375427246</v>
       </c>
       <c r="C13" t="n">
-        <v>26.70728302001953</v>
+        <v>26.70728874206543</v>
       </c>
       <c r="D13" t="n">
-        <v>20.44038200378418</v>
+        <v>20.44038009643555</v>
       </c>
       <c r="E13" t="n">
         <v>12.69050025939941</v>
@@ -932,7 +932,7 @@
         <v>17.31123161315918</v>
       </c>
       <c r="K13" t="n">
-        <v>2.325219869613647</v>
+        <v>2.325220346450806</v>
       </c>
       <c r="L13" t="n">
         <v>1597.569946289062</v>
@@ -943,19 +943,19 @@
         <v>41395</v>
       </c>
       <c r="B14" t="n">
-        <v>13.74015045166016</v>
+        <v>13.74015235900879</v>
       </c>
       <c r="C14" t="n">
-        <v>28.35710334777832</v>
+        <v>28.35709571838379</v>
       </c>
       <c r="D14" t="n">
-        <v>21.5967903137207</v>
+        <v>21.59679222106934</v>
       </c>
       <c r="E14" t="n">
         <v>13.46000003814697</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3367704749107361</v>
+        <v>0.3367704153060913</v>
       </c>
       <c r="G14" t="n">
         <v>24.11899566650391</v>
@@ -967,10 +967,10 @@
         <v>6.517333030700684</v>
       </c>
       <c r="J14" t="n">
-        <v>17.71508407592773</v>
+        <v>17.71508026123047</v>
       </c>
       <c r="K14" t="n">
-        <v>2.745010375976562</v>
+        <v>2.745010614395142</v>
       </c>
       <c r="L14" t="n">
         <v>1630.739990234375</v>
@@ -981,22 +981,22 @@
         <v>41426</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11478805541992</v>
+        <v>12.11478710174561</v>
       </c>
       <c r="C15" t="n">
-        <v>28.06458854675293</v>
+        <v>28.06459426879883</v>
       </c>
       <c r="D15" t="n">
-        <v>21.82361221313477</v>
+        <v>21.8236141204834</v>
       </c>
       <c r="E15" t="n">
         <v>13.88449954986572</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3267628252506256</v>
+        <v>0.326762855052948</v>
       </c>
       <c r="G15" t="n">
-        <v>24.64396667480469</v>
+        <v>24.64396476745605</v>
       </c>
       <c r="H15" t="n">
         <v>4.079999923706055</v>
@@ -1005,10 +1005,10 @@
         <v>7.157332897186279</v>
       </c>
       <c r="J15" t="n">
-        <v>17.67859840393066</v>
+        <v>17.67860412597656</v>
       </c>
       <c r="K15" t="n">
-        <v>2.735512971878052</v>
+        <v>2.735512733459473</v>
       </c>
       <c r="L15" t="n">
         <v>1606.280029296875</v>
@@ -1019,10 +1019,10 @@
         <v>41456</v>
       </c>
       <c r="B16" t="n">
-        <v>13.82569980621338</v>
+        <v>13.82569885253906</v>
       </c>
       <c r="C16" t="n">
-        <v>25.87077713012695</v>
+        <v>25.87077522277832</v>
       </c>
       <c r="D16" t="n">
         <v>22.00655746459961</v>
@@ -1031,10 +1031,10 @@
         <v>15.06099987030029</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3360723555088043</v>
+        <v>0.3360723257064819</v>
       </c>
       <c r="G16" t="n">
-        <v>36.45088195800781</v>
+        <v>36.45088577270508</v>
       </c>
       <c r="H16" t="n">
         <v>3.769999980926514</v>
@@ -1043,10 +1043,10 @@
         <v>8.951999664306641</v>
       </c>
       <c r="J16" t="n">
-        <v>17.02924156188965</v>
+        <v>17.02923774719238</v>
       </c>
       <c r="K16" t="n">
-        <v>2.68428635597229</v>
+        <v>2.684286117553711</v>
       </c>
       <c r="L16" t="n">
         <v>1685.72998046875</v>
@@ -1057,10 +1057,10 @@
         <v>41487</v>
       </c>
       <c r="B17" t="n">
-        <v>14.9838342666626</v>
+        <v>14.98383235931396</v>
       </c>
       <c r="C17" t="n">
-        <v>27.32955169677734</v>
+        <v>27.32954406738281</v>
       </c>
       <c r="D17" t="n">
         <v>20.99391937255859</v>
@@ -1069,7 +1069,7 @@
         <v>14.04899978637695</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3450179398059845</v>
+        <v>0.3450179100036621</v>
       </c>
       <c r="G17" t="n">
         <v>40.89829254150391</v>
@@ -1084,7 +1084,7 @@
         <v>16.19388198852539</v>
       </c>
       <c r="K17" t="n">
-        <v>2.818206787109375</v>
+        <v>2.818207502365112</v>
       </c>
       <c r="L17" t="n">
         <v>1632.969970703125</v>
@@ -1095,22 +1095,22 @@
         <v>41518</v>
       </c>
       <c r="B18" t="n">
-        <v>14.66183948516846</v>
+        <v>14.66184043884277</v>
       </c>
       <c r="C18" t="n">
-        <v>27.23135757446289</v>
+        <v>27.23136138916016</v>
       </c>
       <c r="D18" t="n">
-        <v>21.71305465698242</v>
+        <v>21.71305656433105</v>
       </c>
       <c r="E18" t="n">
         <v>15.63199996948242</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3639647364616394</v>
+        <v>0.3639645874500275</v>
       </c>
       <c r="G18" t="n">
-        <v>49.75347900390625</v>
+        <v>49.75347137451172</v>
       </c>
       <c r="H18" t="n">
         <v>3.809999942779541</v>
@@ -1119,10 +1119,10 @@
         <v>12.89133262634277</v>
       </c>
       <c r="J18" t="n">
-        <v>16.88643264770508</v>
+        <v>16.88643074035645</v>
       </c>
       <c r="K18" t="n">
-        <v>3.17121410369873</v>
+        <v>3.171213388442993</v>
       </c>
       <c r="L18" t="n">
         <v>1681.550048828125</v>
@@ -1136,7 +1136,7 @@
         <v>16.07497596740723</v>
       </c>
       <c r="C19" t="n">
-        <v>28.97422981262207</v>
+        <v>28.97423553466797</v>
       </c>
       <c r="D19" t="n">
         <v>25.54719161987305</v>
@@ -1145,7 +1145,7 @@
         <v>18.20149993896484</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3553100228309631</v>
+        <v>0.3553099632263184</v>
       </c>
       <c r="G19" t="n">
         <v>49.73366165161133</v>
@@ -1157,10 +1157,10 @@
         <v>10.6626672744751</v>
       </c>
       <c r="J19" t="n">
-        <v>18.02840232849121</v>
+        <v>18.02840423583984</v>
       </c>
       <c r="K19" t="n">
-        <v>3.344202995300293</v>
+        <v>3.34420371055603</v>
       </c>
       <c r="L19" t="n">
         <v>1756.5400390625</v>
@@ -1171,22 +1171,22 @@
         <v>41579</v>
       </c>
       <c r="B20" t="n">
-        <v>17.2010669708252</v>
+        <v>17.20107650756836</v>
       </c>
       <c r="C20" t="n">
-        <v>31.43648529052734</v>
+        <v>31.43650245666504</v>
       </c>
       <c r="D20" t="n">
-        <v>26.26632308959961</v>
+        <v>26.26632118225098</v>
       </c>
       <c r="E20" t="n">
         <v>19.68099975585938</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3668765723705292</v>
+        <v>0.3668765425682068</v>
       </c>
       <c r="G20" t="n">
-        <v>46.56401824951172</v>
+        <v>46.56402969360352</v>
       </c>
       <c r="H20" t="n">
         <v>3.640000104904175</v>
@@ -1195,10 +1195,10 @@
         <v>8.485333442687988</v>
       </c>
       <c r="J20" t="n">
-        <v>17.72867202758789</v>
+        <v>17.72867393493652</v>
       </c>
       <c r="K20" t="n">
-        <v>3.292674541473389</v>
+        <v>3.292673587799072</v>
       </c>
       <c r="L20" t="n">
         <v>1805.81005859375</v>
@@ -1209,13 +1209,13 @@
         <v>41609</v>
       </c>
       <c r="B21" t="n">
-        <v>17.35419082641602</v>
+        <v>17.35419273376465</v>
       </c>
       <c r="C21" t="n">
-        <v>30.84289169311523</v>
+        <v>30.84288597106934</v>
       </c>
       <c r="D21" t="n">
-        <v>27.78143501281738</v>
+        <v>27.78143692016602</v>
       </c>
       <c r="E21" t="n">
         <v>19.93950080871582</v>
@@ -1233,10 +1233,10 @@
         <v>10.02866744995117</v>
       </c>
       <c r="J21" t="n">
-        <v>19.30521392822266</v>
+        <v>19.30521583557129</v>
       </c>
       <c r="K21" t="n">
-        <v>3.910867214202881</v>
+        <v>3.910869836807251</v>
       </c>
       <c r="L21" t="n">
         <v>1848.359985351562</v>
@@ -1247,19 +1247,19 @@
         <v>41640</v>
       </c>
       <c r="B22" t="n">
-        <v>15.48520183563232</v>
+        <v>15.48520946502686</v>
       </c>
       <c r="C22" t="n">
-        <v>31.19739723205566</v>
+        <v>31.19739532470703</v>
       </c>
       <c r="D22" t="n">
-        <v>29.27523231506348</v>
+        <v>29.27522850036621</v>
       </c>
       <c r="E22" t="n">
         <v>17.93449974060059</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3692282438278198</v>
+        <v>0.3692282736301422</v>
       </c>
       <c r="G22" t="n">
         <v>61.97641372680664</v>
@@ -1271,10 +1271,10 @@
         <v>12.0939998626709</v>
       </c>
       <c r="J22" t="n">
-        <v>18.24922370910645</v>
+        <v>18.24923706054688</v>
       </c>
       <c r="K22" t="n">
-        <v>4.041033744812012</v>
+        <v>4.041032791137695</v>
       </c>
       <c r="L22" t="n">
         <v>1782.589965820312</v>
@@ -1285,22 +1285,22 @@
         <v>41671</v>
       </c>
       <c r="B23" t="n">
-        <v>16.37577247619629</v>
+        <v>16.37577438354492</v>
       </c>
       <c r="C23" t="n">
-        <v>31.82173728942871</v>
+        <v>31.82172775268555</v>
       </c>
       <c r="D23" t="n">
-        <v>30.13491630554199</v>
+        <v>30.13492012023926</v>
       </c>
       <c r="E23" t="n">
         <v>18.10499954223633</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4342076480388641</v>
+        <v>0.4342077672481537</v>
       </c>
       <c r="G23" t="n">
-        <v>67.81053161621094</v>
+        <v>67.81053924560547</v>
       </c>
       <c r="H23" t="n">
         <v>3.710000038146973</v>
@@ -1309,10 +1309,10 @@
         <v>16.3206672668457</v>
       </c>
       <c r="J23" t="n">
-        <v>18.58840942382812</v>
+        <v>18.58842086791992</v>
       </c>
       <c r="K23" t="n">
-        <v>4.563173294067383</v>
+        <v>4.563174724578857</v>
       </c>
       <c r="L23" t="n">
         <v>1859.449951171875</v>
@@ -1323,22 +1323,22 @@
         <v>41699</v>
       </c>
       <c r="B24" t="n">
-        <v>16.70251655578613</v>
+        <v>16.7025146484375</v>
       </c>
       <c r="C24" t="n">
-        <v>34.0478515625</v>
+        <v>34.04784393310547</v>
       </c>
       <c r="D24" t="n">
-        <v>27.62774085998535</v>
+        <v>27.62774276733398</v>
       </c>
       <c r="E24" t="n">
         <v>16.81850051879883</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4231042265892029</v>
+        <v>0.423104465007782</v>
       </c>
       <c r="G24" t="n">
-        <v>59.66851425170898</v>
+        <v>59.66852188110352</v>
       </c>
       <c r="H24" t="n">
         <v>4.010000228881836</v>
@@ -1347,10 +1347,10 @@
         <v>13.89666652679443</v>
       </c>
       <c r="J24" t="n">
-        <v>19.37669563293457</v>
+        <v>19.37668800354004</v>
       </c>
       <c r="K24" t="n">
-        <v>4.783966064453125</v>
+        <v>4.783967018127441</v>
       </c>
       <c r="L24" t="n">
         <v>1872.339965820312</v>
@@ -1361,22 +1361,22 @@
         <v>41730</v>
       </c>
       <c r="B25" t="n">
-        <v>18.3626823425293</v>
+        <v>18.36268424987793</v>
       </c>
       <c r="C25" t="n">
-        <v>33.55775451660156</v>
+        <v>33.55776596069336</v>
       </c>
       <c r="D25" t="n">
-        <v>26.49191093444824</v>
+        <v>26.49191284179688</v>
       </c>
       <c r="E25" t="n">
         <v>15.20650005340576</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4363337159156799</v>
+        <v>0.4363337755203247</v>
       </c>
       <c r="G25" t="n">
-        <v>59.2128791809082</v>
+        <v>59.21287155151367</v>
       </c>
       <c r="H25" t="n">
         <v>4.090000152587891</v>
@@ -1385,10 +1385,10 @@
         <v>13.85933303833008</v>
       </c>
       <c r="J25" t="n">
-        <v>20.03735160827637</v>
+        <v>20.03735733032227</v>
       </c>
       <c r="K25" t="n">
-        <v>4.716378211975098</v>
+        <v>4.716377735137939</v>
       </c>
       <c r="L25" t="n">
         <v>1883.949951171875</v>
@@ -1399,10 +1399,10 @@
         <v>41760</v>
       </c>
       <c r="B26" t="n">
-        <v>19.80800247192383</v>
+        <v>19.80799865722656</v>
       </c>
       <c r="C26" t="n">
-        <v>34.24623107910156</v>
+        <v>34.2462158203125</v>
       </c>
       <c r="D26" t="n">
         <v>28.31308364868164</v>
@@ -1411,10 +1411,10 @@
         <v>15.6274995803833</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4509217143058777</v>
+        <v>0.4509216845035553</v>
       </c>
       <c r="G26" t="n">
-        <v>62.69947814941406</v>
+        <v>62.69948196411133</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
@@ -1423,10 +1423,10 @@
         <v>13.85133266448975</v>
       </c>
       <c r="J26" t="n">
-        <v>20.68655395507812</v>
+        <v>20.68655204772949</v>
       </c>
       <c r="K26" t="n">
-        <v>5.248920917510986</v>
+        <v>5.248920440673828</v>
       </c>
       <c r="L26" t="n">
         <v>1923.569946289062</v>
@@ -1437,10 +1437,10 @@
         <v>41791</v>
       </c>
       <c r="B27" t="n">
-        <v>20.35592269897461</v>
+        <v>20.35592842102051</v>
       </c>
       <c r="C27" t="n">
-        <v>34.88196563720703</v>
+        <v>34.88195419311523</v>
       </c>
       <c r="D27" t="n">
         <v>28.95794677734375</v>
@@ -1449,10 +1449,10 @@
         <v>16.23900032043457</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4400046169757843</v>
+        <v>0.4400047063827515</v>
       </c>
       <c r="G27" t="n">
-        <v>66.65163421630859</v>
+        <v>66.65164184570312</v>
       </c>
       <c r="H27" t="n">
         <v>4.190000057220459</v>
@@ -1461,10 +1461,10 @@
         <v>16.00399971008301</v>
       </c>
       <c r="J27" t="n">
-        <v>23.39731025695801</v>
+        <v>23.39731407165527</v>
       </c>
       <c r="K27" t="n">
-        <v>5.374895572662354</v>
+        <v>5.374893665313721</v>
       </c>
       <c r="L27" t="n">
         <v>1960.22998046875</v>
@@ -1475,22 +1475,22 @@
         <v>41821</v>
       </c>
       <c r="B28" t="n">
-        <v>20.94077301025391</v>
+        <v>20.94077491760254</v>
       </c>
       <c r="C28" t="n">
-        <v>36.10324478149414</v>
+        <v>36.10322570800781</v>
       </c>
       <c r="D28" t="n">
-        <v>28.7043571472168</v>
+        <v>28.70435905456543</v>
       </c>
       <c r="E28" t="n">
         <v>15.64949989318848</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4153226613998413</v>
+        <v>0.4153226912021637</v>
       </c>
       <c r="G28" t="n">
-        <v>71.96078491210938</v>
+        <v>71.96079254150391</v>
       </c>
       <c r="H28" t="n">
         <v>3.910000085830688</v>
@@ -1499,10 +1499,10 @@
         <v>14.88666725158691</v>
       </c>
       <c r="J28" t="n">
-        <v>25.66132354736328</v>
+        <v>25.66133117675781</v>
       </c>
       <c r="K28" t="n">
-        <v>5.174279689788818</v>
+        <v>5.174277782440186</v>
       </c>
       <c r="L28" t="n">
         <v>1930.670043945312</v>
@@ -1513,7 +1513,7 @@
         <v>41852</v>
       </c>
       <c r="B29" t="n">
-        <v>22.56387901306152</v>
+        <v>22.56387138366699</v>
       </c>
       <c r="C29" t="n">
         <v>38.23945236206055</v>
@@ -1525,7 +1525,7 @@
         <v>16.95199966430664</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4636434018611908</v>
+        <v>0.463643491268158</v>
       </c>
       <c r="G29" t="n">
         <v>74.11019134521484</v>
@@ -1537,10 +1537,10 @@
         <v>17.97999954223633</v>
       </c>
       <c r="J29" t="n">
-        <v>26.61712265014648</v>
+        <v>26.61712074279785</v>
       </c>
       <c r="K29" t="n">
-        <v>6.122176647186279</v>
+        <v>6.122175693511963</v>
       </c>
       <c r="L29" t="n">
         <v>2003.369995117188</v>
@@ -1551,22 +1551,22 @@
         <v>41883</v>
       </c>
       <c r="B30" t="n">
-        <v>22.17864036560059</v>
+        <v>22.17863464355469</v>
       </c>
       <c r="C30" t="n">
         <v>39.02224349975586</v>
       </c>
       <c r="D30" t="n">
-        <v>29.14318466186523</v>
+        <v>29.1431827545166</v>
       </c>
       <c r="E30" t="n">
         <v>16.12199974060059</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4398057758808136</v>
+        <v>0.4398057460784912</v>
       </c>
       <c r="G30" t="n">
-        <v>78.29016876220703</v>
+        <v>78.2901611328125</v>
       </c>
       <c r="H30" t="n">
         <v>3.410000085830688</v>
@@ -1575,10 +1575,10 @@
         <v>16.17866706848145</v>
       </c>
       <c r="J30" t="n">
-        <v>26.5408935546875</v>
+        <v>26.5408878326416</v>
       </c>
       <c r="K30" t="n">
-        <v>6.512059211730957</v>
+        <v>6.512058258056641</v>
       </c>
       <c r="L30" t="n">
         <v>1972.2900390625</v>
@@ -1589,22 +1589,22 @@
         <v>41913</v>
       </c>
       <c r="B31" t="n">
-        <v>23.77462387084961</v>
+        <v>23.77461242675781</v>
       </c>
       <c r="C31" t="n">
-        <v>39.51887512207031</v>
+        <v>39.51885223388672</v>
       </c>
       <c r="D31" t="n">
-        <v>28.1258602142334</v>
+        <v>28.12586402893066</v>
       </c>
       <c r="E31" t="n">
         <v>15.27299976348877</v>
       </c>
       <c r="F31" t="n">
-        <v>0.465788722038269</v>
+        <v>0.4657888412475586</v>
       </c>
       <c r="G31" t="n">
-        <v>74.27857208251953</v>
+        <v>74.27858734130859</v>
       </c>
       <c r="H31" t="n">
         <v>2.799999952316284</v>
@@ -1613,7 +1613,7 @@
         <v>16.11333274841309</v>
       </c>
       <c r="J31" t="n">
-        <v>25.92348670959473</v>
+        <v>25.92348480224609</v>
       </c>
       <c r="K31" t="n">
         <v>6.455919742584229</v>
@@ -1627,19 +1627,19 @@
         <v>41944</v>
       </c>
       <c r="B32" t="n">
-        <v>26.29421997070312</v>
+        <v>26.29421806335449</v>
       </c>
       <c r="C32" t="n">
-        <v>40.4965705871582</v>
+        <v>40.49655914306641</v>
       </c>
       <c r="D32" t="n">
-        <v>27.19522094726562</v>
+        <v>27.19521522521973</v>
       </c>
       <c r="E32" t="n">
         <v>16.93199920654297</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5019921064376831</v>
+        <v>0.5019920468330383</v>
       </c>
       <c r="G32" t="n">
         <v>76.96286773681641</v>
@@ -1651,7 +1651,7 @@
         <v>16.30133247375488</v>
       </c>
       <c r="J32" t="n">
-        <v>28.57929611206055</v>
+        <v>28.57929420471191</v>
       </c>
       <c r="K32" t="n">
         <v>6.991106986999512</v>
@@ -1665,10 +1665,10 @@
         <v>41974</v>
       </c>
       <c r="B33" t="n">
-        <v>24.40389633178711</v>
+        <v>24.40390396118164</v>
       </c>
       <c r="C33" t="n">
-        <v>39.3446044921875</v>
+        <v>39.34459686279297</v>
       </c>
       <c r="D33" t="n">
         <v>26.28290176391602</v>
@@ -1677,10 +1677,10 @@
         <v>15.51749992370605</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4799687266349792</v>
+        <v>0.4799687564373016</v>
       </c>
       <c r="G33" t="n">
-        <v>77.27983856201172</v>
+        <v>77.27983093261719</v>
       </c>
       <c r="H33" t="n">
         <v>2.670000076293945</v>
@@ -1689,10 +1689,10 @@
         <v>14.82733345031738</v>
       </c>
       <c r="J33" t="n">
-        <v>27.84275245666504</v>
+        <v>27.84275054931641</v>
       </c>
       <c r="K33" t="n">
-        <v>7.556460380554199</v>
+        <v>7.556458950042725</v>
       </c>
       <c r="L33" t="n">
         <v>2058.89990234375</v>
@@ -1703,13 +1703,13 @@
         <v>42005</v>
       </c>
       <c r="B34" t="n">
-        <v>25.90288925170898</v>
+        <v>25.90288543701172</v>
       </c>
       <c r="C34" t="n">
-        <v>34.22006607055664</v>
+        <v>34.22007369995117</v>
       </c>
       <c r="D34" t="n">
-        <v>26.62415504455566</v>
+        <v>26.62415313720703</v>
       </c>
       <c r="E34" t="n">
         <v>17.72649955749512</v>
@@ -1727,10 +1727,10 @@
         <v>13.57333278656006</v>
       </c>
       <c r="J34" t="n">
-        <v>25.34925270080566</v>
+        <v>25.34926223754883</v>
       </c>
       <c r="K34" t="n">
-        <v>7.72848653793335</v>
+        <v>7.728487014770508</v>
       </c>
       <c r="L34" t="n">
         <v>1994.989990234375</v>
@@ -1741,19 +1741,19 @@
         <v>42036</v>
       </c>
       <c r="B35" t="n">
-        <v>28.51329803466797</v>
+        <v>28.51329612731934</v>
       </c>
       <c r="C35" t="n">
-        <v>37.40664291381836</v>
+        <v>37.40663528442383</v>
       </c>
       <c r="D35" t="n">
-        <v>27.86633491516113</v>
+        <v>27.86633110046387</v>
       </c>
       <c r="E35" t="n">
         <v>19.00799942016602</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5301187038421631</v>
+        <v>0.530118465423584</v>
       </c>
       <c r="G35" t="n">
         <v>78.22081756591797</v>
@@ -1765,10 +1765,10 @@
         <v>13.55599975585938</v>
       </c>
       <c r="J35" t="n">
-        <v>25.69335556030273</v>
+        <v>25.693359375</v>
       </c>
       <c r="K35" t="n">
-        <v>9.586993217468262</v>
+        <v>9.586991310119629</v>
       </c>
       <c r="L35" t="n">
         <v>2104.5</v>
@@ -1779,22 +1779,22 @@
         <v>42064</v>
       </c>
       <c r="B36" t="n">
-        <v>27.6187858581543</v>
+        <v>27.61878395080566</v>
       </c>
       <c r="C36" t="n">
-        <v>34.68538665771484</v>
+        <v>34.68537521362305</v>
       </c>
       <c r="D36" t="n">
-        <v>27.47356986999512</v>
+        <v>27.47357177734375</v>
       </c>
       <c r="E36" t="n">
         <v>18.60499954223633</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5029637813568115</v>
+        <v>0.5029640197753906</v>
       </c>
       <c r="G36" t="n">
-        <v>81.43998718261719</v>
+        <v>81.44001007080078</v>
       </c>
       <c r="H36" t="n">
         <v>2.680000066757202</v>
@@ -1806,7 +1806,7 @@
         <v>24.1633415222168</v>
       </c>
       <c r="K36" t="n">
-        <v>9.567071914672852</v>
+        <v>9.567074775695801</v>
       </c>
       <c r="L36" t="n">
         <v>2067.889892578125</v>
@@ -1820,10 +1820,10 @@
         <v>27.77859878540039</v>
       </c>
       <c r="C37" t="n">
-        <v>41.49280548095703</v>
+        <v>41.49278259277344</v>
       </c>
       <c r="D37" t="n">
-        <v>27.17986488342285</v>
+        <v>27.17986679077148</v>
       </c>
       <c r="E37" t="n">
         <v>21.0890007019043</v>
@@ -1832,7 +1832,7 @@
         <v>0.5334829688072205</v>
       </c>
       <c r="G37" t="n">
-        <v>78.02272033691406</v>
+        <v>78.022705078125</v>
       </c>
       <c r="H37" t="n">
         <v>2.259999990463257</v>
@@ -1841,10 +1841,10 @@
         <v>15.06999969482422</v>
       </c>
       <c r="J37" t="n">
-        <v>25.15244102478027</v>
+        <v>25.15244293212891</v>
       </c>
       <c r="K37" t="n">
-        <v>8.806105613708496</v>
+        <v>8.806107521057129</v>
       </c>
       <c r="L37" t="n">
         <v>2085.510009765625</v>
@@ -1855,10 +1855,10 @@
         <v>42125</v>
       </c>
       <c r="B38" t="n">
-        <v>29.03806495666504</v>
+        <v>29.03805541992188</v>
       </c>
       <c r="C38" t="n">
-        <v>40.23414611816406</v>
+        <v>40.2341423034668</v>
       </c>
       <c r="D38" t="n">
         <v>27.00899124145508</v>
@@ -1867,7 +1867,7 @@
         <v>21.46150016784668</v>
       </c>
       <c r="F38" t="n">
-        <v>0.534262478351593</v>
+        <v>0.5342624187469482</v>
       </c>
       <c r="G38" t="n">
         <v>78.43874359130859</v>
@@ -1879,7 +1879,7 @@
         <v>16.71999931335449</v>
       </c>
       <c r="J38" t="n">
-        <v>26.8209114074707</v>
+        <v>26.82090759277344</v>
       </c>
       <c r="K38" t="n">
         <v>11.15606021881104</v>
@@ -1893,22 +1893,22 @@
         <v>42156</v>
       </c>
       <c r="B39" t="n">
-        <v>27.9570484161377</v>
+        <v>27.95704078674316</v>
       </c>
       <c r="C39" t="n">
         <v>37.90733337402344</v>
       </c>
       <c r="D39" t="n">
-        <v>26.74748039245605</v>
+        <v>26.74748229980469</v>
       </c>
       <c r="E39" t="n">
         <v>21.70450019836426</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4854954779148102</v>
+        <v>0.4854956567287445</v>
       </c>
       <c r="G39" t="n">
-        <v>84.95631408691406</v>
+        <v>84.95630645751953</v>
       </c>
       <c r="H39" t="n">
         <v>2.400000095367432</v>
@@ -1920,7 +1920,7 @@
         <v>23.67649841308594</v>
       </c>
       <c r="K39" t="n">
-        <v>10.04365730285645</v>
+        <v>10.04366016387939</v>
       </c>
       <c r="L39" t="n">
         <v>2063.110107421875</v>
@@ -1931,22 +1931,22 @@
         <v>42186</v>
       </c>
       <c r="B40" t="n">
-        <v>27.0365047454834</v>
+        <v>27.03650856018066</v>
       </c>
       <c r="C40" t="n">
-        <v>40.09677124023438</v>
+        <v>40.09676742553711</v>
       </c>
       <c r="D40" t="n">
-        <v>32.56512451171875</v>
+        <v>32.56511688232422</v>
       </c>
       <c r="E40" t="n">
         <v>26.8075008392334</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4816328585147858</v>
+        <v>0.4816329479217529</v>
       </c>
       <c r="G40" t="n">
-        <v>93.11813354492188</v>
+        <v>93.11814880371094</v>
       </c>
       <c r="H40" t="n">
         <v>1.929999947547913</v>
@@ -1955,10 +1955,10 @@
         <v>17.74333381652832</v>
       </c>
       <c r="J40" t="n">
-        <v>22.53236961364746</v>
+        <v>22.5323657989502</v>
       </c>
       <c r="K40" t="n">
-        <v>9.455074310302734</v>
+        <v>9.455079078674316</v>
       </c>
       <c r="L40" t="n">
         <v>2103.840087890625</v>
@@ -1972,19 +1972,19 @@
         <v>25.24679374694824</v>
       </c>
       <c r="C41" t="n">
-        <v>37.61281967163086</v>
+        <v>37.61282348632812</v>
       </c>
       <c r="D41" t="n">
-        <v>32.08568572998047</v>
+        <v>32.08567810058594</v>
       </c>
       <c r="E41" t="n">
         <v>25.64450073242188</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5449956059455872</v>
+        <v>0.5449955463409424</v>
       </c>
       <c r="G41" t="n">
-        <v>88.58158874511719</v>
+        <v>88.58161163330078</v>
       </c>
       <c r="H41" t="n">
         <v>1.809999942779541</v>
@@ -1993,10 +1993,10 @@
         <v>16.60400009155273</v>
       </c>
       <c r="J41" t="n">
-        <v>22.39779663085938</v>
+        <v>22.39779281616211</v>
       </c>
       <c r="K41" t="n">
-        <v>9.517788887023926</v>
+        <v>9.517789840698242</v>
       </c>
       <c r="L41" t="n">
         <v>1972.180053710938</v>
@@ -2007,22 +2007,22 @@
         <v>42248</v>
       </c>
       <c r="B42" t="n">
-        <v>24.69600677490234</v>
+        <v>24.69600296020508</v>
       </c>
       <c r="C42" t="n">
-        <v>38.25236129760742</v>
+        <v>38.25237274169922</v>
       </c>
       <c r="D42" t="n">
-        <v>31.61763572692871</v>
+        <v>31.61763954162598</v>
       </c>
       <c r="E42" t="n">
         <v>25.5944995880127</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5976042151451111</v>
+        <v>0.5976041555404663</v>
       </c>
       <c r="G42" t="n">
-        <v>89.04714202880859</v>
+        <v>89.04713439941406</v>
       </c>
       <c r="H42" t="n">
         <v>1.720000028610229</v>
@@ -2031,10 +2031,10 @@
         <v>16.55999946594238</v>
       </c>
       <c r="J42" t="n">
-        <v>23.65344619750977</v>
+        <v>23.6534481048584</v>
       </c>
       <c r="K42" t="n">
-        <v>9.47486686706543</v>
+        <v>9.474868774414062</v>
       </c>
       <c r="L42" t="n">
         <v>1920.030029296875</v>
@@ -2045,7 +2045,7 @@
         <v>42278</v>
       </c>
       <c r="B43" t="n">
-        <v>26.7558765411377</v>
+        <v>26.75586891174316</v>
       </c>
       <c r="C43" t="n">
         <v>45.49491882324219</v>
@@ -2057,10 +2057,10 @@
         <v>31.29500007629395</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6877900958061218</v>
+        <v>0.6877901554107666</v>
       </c>
       <c r="G43" t="n">
-        <v>101.0026321411133</v>
+        <v>101.0026397705078</v>
       </c>
       <c r="H43" t="n">
         <v>2.119999885559082</v>
@@ -2072,7 +2072,7 @@
         <v>26.57285499572754</v>
       </c>
       <c r="K43" t="n">
-        <v>9.332378387451172</v>
+        <v>9.332379341125488</v>
       </c>
       <c r="L43" t="n">
         <v>2079.360107421875</v>
@@ -2083,22 +2083,22 @@
         <v>42309</v>
       </c>
       <c r="B44" t="n">
-        <v>26.6005744934082</v>
+        <v>26.60057258605957</v>
       </c>
       <c r="C44" t="n">
-        <v>47.28942108154297</v>
+        <v>47.28943634033203</v>
       </c>
       <c r="D44" t="n">
-        <v>37.78297424316406</v>
+        <v>37.7829704284668</v>
       </c>
       <c r="E44" t="n">
         <v>33.2400016784668</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7719262838363647</v>
+        <v>0.7719261050224304</v>
       </c>
       <c r="G44" t="n">
-        <v>103.2510757446289</v>
+        <v>103.2510833740234</v>
       </c>
       <c r="H44" t="n">
         <v>2.359999895095825</v>
@@ -2107,10 +2107,10 @@
         <v>15.35066699981689</v>
       </c>
       <c r="J44" t="n">
-        <v>27.47922897338867</v>
+        <v>27.47922325134277</v>
       </c>
       <c r="K44" t="n">
-        <v>9.887184143066406</v>
+        <v>9.887182235717773</v>
       </c>
       <c r="L44" t="n">
         <v>2080.409912109375</v>
@@ -2121,22 +2121,22 @@
         <v>42339</v>
       </c>
       <c r="B45" t="n">
-        <v>23.66843414306641</v>
+        <v>23.66844177246094</v>
       </c>
       <c r="C45" t="n">
-        <v>48.27261734008789</v>
+        <v>48.27263259887695</v>
       </c>
       <c r="D45" t="n">
-        <v>38.53383255004883</v>
+        <v>38.53382873535156</v>
       </c>
       <c r="E45" t="n">
         <v>33.79449844360352</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8021025061607361</v>
+        <v>0.8021024465560913</v>
       </c>
       <c r="G45" t="n">
-        <v>103.667121887207</v>
+        <v>103.667106628418</v>
       </c>
       <c r="H45" t="n">
         <v>2.869999885559082</v>
@@ -2145,7 +2145,7 @@
         <v>16.00066757202148</v>
       </c>
       <c r="J45" t="n">
-        <v>27.22631645202637</v>
+        <v>27.22632217407227</v>
       </c>
       <c r="K45" t="n">
         <v>11.03522968292236</v>
@@ -2159,19 +2159,19 @@
         <v>42370</v>
       </c>
       <c r="B46" t="n">
-        <v>21.8875617980957</v>
+        <v>21.88756942749023</v>
       </c>
       <c r="C46" t="n">
-        <v>47.93329238891602</v>
+        <v>47.93328475952148</v>
       </c>
       <c r="D46" t="n">
-        <v>37.70866775512695</v>
+        <v>37.70867919921875</v>
       </c>
       <c r="E46" t="n">
         <v>29.35000038146973</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7127907872200012</v>
+        <v>0.7127904295921326</v>
       </c>
       <c r="G46" t="n">
         <v>111.1454849243164</v>
@@ -2183,10 +2183,10 @@
         <v>12.74666690826416</v>
       </c>
       <c r="J46" t="n">
-        <v>24.51554870605469</v>
+        <v>24.51554298400879</v>
       </c>
       <c r="K46" t="n">
-        <v>10.16548442840576</v>
+        <v>10.16548633575439</v>
       </c>
       <c r="L46" t="n">
         <v>1940.239990234375</v>
@@ -2197,19 +2197,19 @@
         <v>42401</v>
       </c>
       <c r="B47" t="n">
-        <v>21.85938262939453</v>
+        <v>21.85939025878906</v>
       </c>
       <c r="C47" t="n">
-        <v>44.58807373046875</v>
+        <v>44.58806991577148</v>
       </c>
       <c r="D47" t="n">
-        <v>35.52297592163086</v>
+        <v>35.52297973632812</v>
       </c>
       <c r="E47" t="n">
         <v>27.62599945068359</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7659459114074707</v>
+        <v>0.7659457921981812</v>
       </c>
       <c r="G47" t="n">
         <v>105.9056701660156</v>
@@ -2221,10 +2221,10 @@
         <v>12.79533290863037</v>
       </c>
       <c r="J47" t="n">
-        <v>23.59122467041016</v>
+        <v>23.59122848510742</v>
       </c>
       <c r="K47" t="n">
-        <v>10.18525409698486</v>
+        <v>10.18525314331055</v>
       </c>
       <c r="L47" t="n">
         <v>1932.22998046875</v>
@@ -2235,19 +2235,19 @@
         <v>42430</v>
       </c>
       <c r="B48" t="n">
-        <v>24.64013481140137</v>
+        <v>24.6401309967041</v>
       </c>
       <c r="C48" t="n">
-        <v>48.4001350402832</v>
+        <v>48.400146484375</v>
       </c>
       <c r="D48" t="n">
-        <v>37.78544235229492</v>
+        <v>37.78544616699219</v>
       </c>
       <c r="E48" t="n">
         <v>29.68199920654297</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8702373504638672</v>
+        <v>0.8702375292778015</v>
       </c>
       <c r="G48" t="n">
         <v>113.0175552368164</v>
@@ -2259,10 +2259,10 @@
         <v>15.31799983978271</v>
       </c>
       <c r="J48" t="n">
-        <v>25.79168701171875</v>
+        <v>25.79169082641602</v>
       </c>
       <c r="K48" t="n">
-        <v>11.7849702835083</v>
+        <v>11.78496932983398</v>
       </c>
       <c r="L48" t="n">
         <v>2059.739990234375</v>
@@ -2285,10 +2285,10 @@
         <v>32.97949981689453</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8677952885627747</v>
+        <v>0.8677951097488403</v>
       </c>
       <c r="G49" t="n">
-        <v>116.4645309448242</v>
+        <v>116.4645385742188</v>
       </c>
       <c r="H49" t="n">
         <v>3.549999952316284</v>
@@ -2300,7 +2300,7 @@
         <v>24.14134407043457</v>
       </c>
       <c r="K49" t="n">
-        <v>11.11753177642822</v>
+        <v>11.1175365447998</v>
       </c>
       <c r="L49" t="n">
         <v>2065.300048828125</v>
@@ -2314,7 +2314,7 @@
         <v>22.71350479125977</v>
       </c>
       <c r="C50" t="n">
-        <v>46.77075958251953</v>
+        <v>46.7707405090332</v>
       </c>
       <c r="D50" t="n">
         <v>37.08956909179688</v>
@@ -2326,7 +2326,7 @@
         <v>1.144066095352173</v>
       </c>
       <c r="G50" t="n">
-        <v>117.6828689575195</v>
+        <v>117.6828765869141</v>
       </c>
       <c r="H50" t="n">
         <v>4.570000171661377</v>
@@ -2335,10 +2335,10 @@
         <v>14.88199996948242</v>
       </c>
       <c r="J50" t="n">
-        <v>25.4033260345459</v>
+        <v>25.40332221984863</v>
       </c>
       <c r="K50" t="n">
-        <v>11.77429103851318</v>
+        <v>11.77429389953613</v>
       </c>
       <c r="L50" t="n">
         <v>2096.949951171875</v>
@@ -2352,19 +2352,19 @@
         <v>21.74455261230469</v>
       </c>
       <c r="C51" t="n">
-        <v>45.15583801269531</v>
+        <v>45.15584564208984</v>
       </c>
       <c r="D51" t="n">
-        <v>34.84492111206055</v>
+        <v>34.84492874145508</v>
       </c>
       <c r="E51" t="n">
         <v>35.78099822998047</v>
       </c>
       <c r="F51" t="n">
-        <v>1.151167631149292</v>
+        <v>1.15116810798645</v>
       </c>
       <c r="G51" t="n">
-        <v>113.1958465576172</v>
+        <v>113.1958389282227</v>
       </c>
       <c r="H51" t="n">
         <v>5.139999866485596</v>
@@ -2373,7 +2373,7 @@
         <v>14.15200042724609</v>
       </c>
       <c r="J51" t="n">
-        <v>26.37634468078613</v>
+        <v>26.3763484954834</v>
       </c>
       <c r="K51" t="n">
         <v>11.89101791381836</v>
@@ -2390,19 +2390,19 @@
         <v>23.70292663574219</v>
       </c>
       <c r="C52" t="n">
-        <v>50.01824188232422</v>
+        <v>50.01823425292969</v>
       </c>
       <c r="D52" t="n">
-        <v>39.19403839111328</v>
+        <v>39.19404220581055</v>
       </c>
       <c r="E52" t="n">
         <v>37.94049835205078</v>
       </c>
       <c r="F52" t="n">
-        <v>1.398248553276062</v>
+        <v>1.398248434066772</v>
       </c>
       <c r="G52" t="n">
-        <v>122.7642059326172</v>
+        <v>122.7641983032227</v>
       </c>
       <c r="H52" t="n">
         <v>6.860000133514404</v>
@@ -2411,10 +2411,10 @@
         <v>15.65266704559326</v>
       </c>
       <c r="J52" t="n">
-        <v>28.03291320800781</v>
+        <v>28.03291702270508</v>
       </c>
       <c r="K52" t="n">
-        <v>12.39450836181641</v>
+        <v>12.39451026916504</v>
       </c>
       <c r="L52" t="n">
         <v>2173.60009765625</v>
@@ -2425,22 +2425,22 @@
         <v>42583</v>
       </c>
       <c r="B53" t="n">
-        <v>24.26354217529297</v>
+        <v>24.2635383605957</v>
       </c>
       <c r="C53" t="n">
         <v>51.0225944519043</v>
       </c>
       <c r="D53" t="n">
-        <v>39.12025451660156</v>
+        <v>39.12024688720703</v>
       </c>
       <c r="E53" t="n">
         <v>38.45800018310547</v>
       </c>
       <c r="F53" t="n">
-        <v>1.504844903945923</v>
+        <v>1.504844307899475</v>
       </c>
       <c r="G53" t="n">
-        <v>124.9235305786133</v>
+        <v>124.9235153198242</v>
       </c>
       <c r="H53" t="n">
         <v>7.400000095367432</v>
@@ -2449,10 +2449,10 @@
         <v>14.13399982452393</v>
       </c>
       <c r="J53" t="n">
-        <v>29.0799732208252</v>
+        <v>29.07995986938477</v>
       </c>
       <c r="K53" t="n">
-        <v>13.49944114685059</v>
+        <v>13.49943828582764</v>
       </c>
       <c r="L53" t="n">
         <v>2170.949951171875</v>
@@ -2463,22 +2463,22 @@
         <v>42614</v>
       </c>
       <c r="B54" t="n">
-        <v>25.85291290283203</v>
+        <v>25.85290718078613</v>
       </c>
       <c r="C54" t="n">
-        <v>51.14691162109375</v>
+        <v>51.14691543579102</v>
       </c>
       <c r="D54" t="n">
-        <v>39.82404708862305</v>
+        <v>39.82404327392578</v>
       </c>
       <c r="E54" t="n">
         <v>41.86550140380859</v>
       </c>
       <c r="F54" t="n">
-        <v>1.68099045753479</v>
+        <v>1.680990815162659</v>
       </c>
       <c r="G54" t="n">
-        <v>127.0531234741211</v>
+        <v>127.0531463623047</v>
       </c>
       <c r="H54" t="n">
         <v>6.909999847412109</v>
@@ -2487,10 +2487,10 @@
         <v>13.60200023651123</v>
       </c>
       <c r="J54" t="n">
-        <v>30.5870361328125</v>
+        <v>30.58703804016113</v>
       </c>
       <c r="K54" t="n">
-        <v>13.24083137512207</v>
+        <v>13.24082851409912</v>
       </c>
       <c r="L54" t="n">
         <v>2168.27001953125</v>
@@ -2501,22 +2501,22 @@
         <v>42644</v>
       </c>
       <c r="B55" t="n">
-        <v>25.9649715423584</v>
+        <v>25.96496391296387</v>
       </c>
       <c r="C55" t="n">
-        <v>53.20700073242188</v>
+        <v>53.20698547363281</v>
       </c>
       <c r="D55" t="n">
-        <v>40.11328887939453</v>
+        <v>40.11329650878906</v>
       </c>
       <c r="E55" t="n">
         <v>39.49100112915039</v>
       </c>
       <c r="F55" t="n">
-        <v>1.745757460594177</v>
+        <v>1.745756983757019</v>
       </c>
       <c r="G55" t="n">
-        <v>129.7473297119141</v>
+        <v>129.747314453125</v>
       </c>
       <c r="H55" t="n">
         <v>7.230000019073486</v>
@@ -2539,19 +2539,19 @@
         <v>42675</v>
       </c>
       <c r="B56" t="n">
-        <v>25.40410232543945</v>
+        <v>25.40409851074219</v>
       </c>
       <c r="C56" t="n">
-        <v>53.87038803100586</v>
+        <v>53.87038421630859</v>
       </c>
       <c r="D56" t="n">
-        <v>38.42832946777344</v>
+        <v>38.42832565307617</v>
       </c>
       <c r="E56" t="n">
         <v>37.52849960327148</v>
       </c>
       <c r="F56" t="n">
-        <v>2.265315294265747</v>
+        <v>2.26531457901001</v>
       </c>
       <c r="G56" t="n">
         <v>117.2965698242188</v>
@@ -2563,10 +2563,10 @@
         <v>12.62666702270508</v>
       </c>
       <c r="J56" t="n">
-        <v>28.32863616943359</v>
+        <v>28.32864379882812</v>
       </c>
       <c r="K56" t="n">
-        <v>13.0850305557251</v>
+        <v>13.08503150939941</v>
       </c>
       <c r="L56" t="n">
         <v>2198.81005859375</v>
@@ -2577,10 +2577,10 @@
         <v>42705</v>
       </c>
       <c r="B57" t="n">
-        <v>26.62235641479492</v>
+        <v>26.62236022949219</v>
       </c>
       <c r="C57" t="n">
-        <v>55.55104827880859</v>
+        <v>55.55104064941406</v>
       </c>
       <c r="D57" t="n">
         <v>39.24901962280273</v>
@@ -2589,7 +2589,7 @@
         <v>37.49349975585938</v>
       </c>
       <c r="F57" t="n">
-        <v>2.622557163238525</v>
+        <v>2.622556447982788</v>
       </c>
       <c r="G57" t="n">
         <v>113.9585494995117</v>
@@ -2601,7 +2601,7 @@
         <v>14.24600028991699</v>
       </c>
       <c r="J57" t="n">
-        <v>29.6103630065918</v>
+        <v>29.61036682128906</v>
       </c>
       <c r="K57" t="n">
         <v>13.64457702636719</v>
@@ -2615,10 +2615,10 @@
         <v>42736</v>
       </c>
       <c r="B58" t="n">
-        <v>27.89348602294922</v>
+        <v>27.89348411560059</v>
       </c>
       <c r="C58" t="n">
-        <v>57.79490661621094</v>
+        <v>57.79489898681641</v>
       </c>
       <c r="D58" t="n">
         <v>40.62294006347656</v>
@@ -2627,10 +2627,10 @@
         <v>41.17399978637695</v>
       </c>
       <c r="F58" t="n">
-        <v>2.682506322860718</v>
+        <v>2.68250560760498</v>
       </c>
       <c r="G58" t="n">
-        <v>129.0836944580078</v>
+        <v>129.0836791992188</v>
       </c>
       <c r="H58" t="n">
         <v>10.36999988555908</v>
@@ -2639,10 +2639,10 @@
         <v>16.79533386230469</v>
       </c>
       <c r="J58" t="n">
-        <v>30.05938720703125</v>
+        <v>30.05937194824219</v>
       </c>
       <c r="K58" t="n">
-        <v>15.39906883239746</v>
+        <v>15.3990650177002</v>
       </c>
       <c r="L58" t="n">
         <v>2278.8701171875</v>
@@ -2665,10 +2665,10 @@
         <v>42.25199890136719</v>
       </c>
       <c r="F59" t="n">
-        <v>2.496467113494873</v>
+        <v>2.496466636657715</v>
       </c>
       <c r="G59" t="n">
-        <v>134.2541656494141</v>
+        <v>134.2541351318359</v>
       </c>
       <c r="H59" t="n">
         <v>14.46000003814697</v>
@@ -2677,10 +2677,10 @@
         <v>16.66600036621094</v>
       </c>
       <c r="J59" t="n">
-        <v>29.76419639587402</v>
+        <v>29.76420021057129</v>
       </c>
       <c r="K59" t="n">
-        <v>16.28133201599121</v>
+        <v>16.28133010864258</v>
       </c>
       <c r="L59" t="n">
         <v>2363.639892578125</v>
@@ -2691,13 +2691,13 @@
         <v>42795</v>
       </c>
       <c r="B60" t="n">
-        <v>33.16482925415039</v>
+        <v>33.16482543945312</v>
       </c>
       <c r="C60" t="n">
         <v>59.23354339599609</v>
       </c>
       <c r="D60" t="n">
-        <v>41.99043655395508</v>
+        <v>41.99043273925781</v>
       </c>
       <c r="E60" t="n">
         <v>44.32699966430664</v>
@@ -2706,7 +2706,7 @@
         <v>2.679741144180298</v>
       </c>
       <c r="G60" t="n">
-        <v>140.7024078369141</v>
+        <v>140.702392578125</v>
       </c>
       <c r="H60" t="n">
         <v>14.55000019073486</v>
@@ -2715,10 +2715,10 @@
         <v>18.5533332824707</v>
       </c>
       <c r="J60" t="n">
-        <v>29.65730476379395</v>
+        <v>29.65730285644531</v>
       </c>
       <c r="K60" t="n">
-        <v>16.97780609130859</v>
+        <v>16.97780227661133</v>
       </c>
       <c r="L60" t="n">
         <v>2362.719970703125</v>
@@ -2729,10 +2729,10 @@
         <v>42826</v>
       </c>
       <c r="B61" t="n">
-        <v>33.16251373291016</v>
+        <v>33.16250610351562</v>
       </c>
       <c r="C61" t="n">
-        <v>61.57193374633789</v>
+        <v>61.57194137573242</v>
       </c>
       <c r="D61" t="n">
         <v>45.7902717590332</v>
@@ -2741,10 +2741,10 @@
         <v>46.2495002746582</v>
       </c>
       <c r="F61" t="n">
-        <v>2.565840482711792</v>
+        <v>2.565840721130371</v>
       </c>
       <c r="G61" t="n">
-        <v>148.8245697021484</v>
+        <v>148.8245849609375</v>
       </c>
       <c r="H61" t="n">
         <v>13.30000019073486</v>
@@ -2753,10 +2753,10 @@
         <v>20.9379997253418</v>
       </c>
       <c r="J61" t="n">
-        <v>29.72308158874512</v>
+        <v>29.72308731079102</v>
       </c>
       <c r="K61" t="n">
-        <v>17.12124443054199</v>
+        <v>17.12124061584473</v>
       </c>
       <c r="L61" t="n">
         <v>2384.199951171875</v>
@@ -2770,10 +2770,10 @@
         <v>35.41117858886719</v>
       </c>
       <c r="C62" t="n">
-        <v>63.17313766479492</v>
+        <v>63.17313385009766</v>
       </c>
       <c r="D62" t="n">
-        <v>48.8892822265625</v>
+        <v>48.88928604125977</v>
       </c>
       <c r="E62" t="n">
         <v>49.73099899291992</v>
@@ -2782,7 +2782,7 @@
         <v>3.554834604263306</v>
       </c>
       <c r="G62" t="n">
-        <v>150.0231475830078</v>
+        <v>150.0231323242188</v>
       </c>
       <c r="H62" t="n">
         <v>11.1899995803833</v>
@@ -2791,7 +2791,7 @@
         <v>22.73399925231934</v>
       </c>
       <c r="J62" t="n">
-        <v>29.91107749938965</v>
+        <v>29.91107368469238</v>
       </c>
       <c r="K62" t="n">
         <v>18.56889343261719</v>
@@ -2805,22 +2805,22 @@
         <v>42887</v>
       </c>
       <c r="B63" t="n">
-        <v>33.38517379760742</v>
+        <v>33.38516235351562</v>
       </c>
       <c r="C63" t="n">
-        <v>62.35000228881836</v>
+        <v>62.35000991821289</v>
       </c>
       <c r="D63" t="n">
-        <v>46.04583740234375</v>
+        <v>46.04584884643555</v>
       </c>
       <c r="E63" t="n">
         <v>48.40000152587891</v>
       </c>
       <c r="F63" t="n">
-        <v>3.560005664825439</v>
+        <v>3.560005903244019</v>
       </c>
       <c r="G63" t="n">
-        <v>149.5476837158203</v>
+        <v>149.5476684570312</v>
       </c>
       <c r="H63" t="n">
         <v>12.47999954223633</v>
@@ -2829,10 +2829,10 @@
         <v>24.10733222961426</v>
       </c>
       <c r="J63" t="n">
-        <v>27.94792366027832</v>
+        <v>27.94792747497559</v>
       </c>
       <c r="K63" t="n">
-        <v>18.14726638793945</v>
+        <v>18.14726829528809</v>
       </c>
       <c r="L63" t="n">
         <v>2423.409912109375</v>
@@ -2843,13 +2843,13 @@
         <v>42917</v>
       </c>
       <c r="B64" t="n">
-        <v>34.47697448730469</v>
+        <v>34.47698593139648</v>
       </c>
       <c r="C64" t="n">
         <v>65.76011657714844</v>
       </c>
       <c r="D64" t="n">
-        <v>46.82939147949219</v>
+        <v>46.82938766479492</v>
       </c>
       <c r="E64" t="n">
         <v>49.38899993896484</v>
@@ -2867,7 +2867,7 @@
         <v>21.56466674804688</v>
       </c>
       <c r="J64" t="n">
-        <v>29.38094329833984</v>
+        <v>29.38094711303711</v>
       </c>
       <c r="K64" t="n">
         <v>19.20705986022949</v>
@@ -2881,10 +2881,10 @@
         <v>42948</v>
       </c>
       <c r="B65" t="n">
-        <v>38.16600036621094</v>
+        <v>38.16600799560547</v>
       </c>
       <c r="C65" t="n">
-        <v>67.99284362792969</v>
+        <v>67.99286651611328</v>
       </c>
       <c r="D65" t="n">
         <v>47.31179809570312</v>
@@ -2893,10 +2893,10 @@
         <v>49.02999877929688</v>
       </c>
       <c r="F65" t="n">
-        <v>4.176384925842285</v>
+        <v>4.176385879516602</v>
       </c>
       <c r="G65" t="n">
-        <v>170.3385467529297</v>
+        <v>170.3385620117188</v>
       </c>
       <c r="H65" t="n">
         <v>13</v>
@@ -2905,10 +2905,10 @@
         <v>23.7266674041748</v>
       </c>
       <c r="J65" t="n">
-        <v>29.26767349243164</v>
+        <v>29.26767730712891</v>
       </c>
       <c r="K65" t="n">
-        <v>19.62833023071289</v>
+        <v>19.62832641601562</v>
       </c>
       <c r="L65" t="n">
         <v>2471.64990234375</v>
@@ -2925,7 +2925,7 @@
         <v>67.73824310302734</v>
       </c>
       <c r="D66" t="n">
-        <v>48.22708129882812</v>
+        <v>48.22708892822266</v>
       </c>
       <c r="E66" t="n">
         <v>48.06750106811523</v>
@@ -2934,7 +2934,7 @@
         <v>4.406355857849121</v>
       </c>
       <c r="G66" t="n">
-        <v>169.2490081787109</v>
+        <v>169.2489929199219</v>
       </c>
       <c r="H66" t="n">
         <v>12.75</v>
@@ -2943,10 +2943,10 @@
         <v>22.73999977111816</v>
       </c>
       <c r="J66" t="n">
-        <v>31.7796745300293</v>
+        <v>31.77967643737793</v>
       </c>
       <c r="K66" t="n">
-        <v>18.96344566345215</v>
+        <v>18.96344757080078</v>
       </c>
       <c r="L66" t="n">
         <v>2519.360107421875</v>
@@ -2957,13 +2957,13 @@
         <v>43009</v>
       </c>
       <c r="B67" t="n">
-        <v>39.33892440795898</v>
+        <v>39.33890914916992</v>
       </c>
       <c r="C67" t="n">
-        <v>75.64060211181641</v>
+        <v>75.64057159423828</v>
       </c>
       <c r="D67" t="n">
-        <v>51.16513061523438</v>
+        <v>51.16512680053711</v>
       </c>
       <c r="E67" t="n">
         <v>55.26399993896484</v>
@@ -2981,10 +2981,10 @@
         <v>22.10199928283691</v>
       </c>
       <c r="J67" t="n">
-        <v>37.96369552612305</v>
+        <v>37.96369171142578</v>
       </c>
       <c r="K67" t="n">
-        <v>20.63429832458496</v>
+        <v>20.63429641723633</v>
       </c>
       <c r="L67" t="n">
         <v>2575.260009765625</v>
@@ -2995,10 +2995,10 @@
         <v>43040</v>
       </c>
       <c r="B68" t="n">
-        <v>40.13662719726562</v>
+        <v>40.13662338256836</v>
       </c>
       <c r="C68" t="n">
-        <v>76.92522430419922</v>
+        <v>76.92520904541016</v>
       </c>
       <c r="D68" t="n">
         <v>51.32014846801758</v>
@@ -3007,7 +3007,7 @@
         <v>58.83750152587891</v>
       </c>
       <c r="F68" t="n">
-        <v>4.950571537017822</v>
+        <v>4.950571060180664</v>
       </c>
       <c r="G68" t="n">
         <v>175.4991149902344</v>
@@ -3019,7 +3019,7 @@
         <v>20.59000015258789</v>
       </c>
       <c r="J68" t="n">
-        <v>37.64299392700195</v>
+        <v>37.64299774169922</v>
       </c>
       <c r="K68" t="n">
         <v>21.73125839233398</v>
@@ -3036,7 +3036,7 @@
         <v>39.52470397949219</v>
       </c>
       <c r="C69" t="n">
-        <v>78.17731475830078</v>
+        <v>78.17733764648438</v>
       </c>
       <c r="D69" t="n">
         <v>52.17352676391602</v>
@@ -3045,7 +3045,7 @@
         <v>58.4734992980957</v>
       </c>
       <c r="F69" t="n">
-        <v>4.772734642028809</v>
+        <v>4.772736549377441</v>
       </c>
       <c r="G69" t="n">
         <v>174.7859649658203</v>
@@ -3057,10 +3057,10 @@
         <v>20.75666618347168</v>
       </c>
       <c r="J69" t="n">
-        <v>38.75113296508789</v>
+        <v>38.75112915039062</v>
       </c>
       <c r="K69" t="n">
-        <v>20.21936416625977</v>
+        <v>20.21936798095703</v>
       </c>
       <c r="L69" t="n">
         <v>2673.610107421875</v>
@@ -3071,10 +3071,10 @@
         <v>43101</v>
       </c>
       <c r="B70" t="n">
-        <v>39.10430526733398</v>
+        <v>39.10430145263672</v>
       </c>
       <c r="C70" t="n">
-        <v>86.83222198486328</v>
+        <v>86.83221435546875</v>
       </c>
       <c r="D70" t="n">
         <v>58.5538215637207</v>
@@ -3083,7 +3083,7 @@
         <v>72.54450225830078</v>
       </c>
       <c r="F70" t="n">
-        <v>6.062729835510254</v>
+        <v>6.062730312347412</v>
       </c>
       <c r="G70" t="n">
         <v>185.1169891357422</v>
@@ -3095,10 +3095,10 @@
         <v>23.62066650390625</v>
       </c>
       <c r="J70" t="n">
-        <v>40.4133415222168</v>
+        <v>40.41333389282227</v>
       </c>
       <c r="K70" t="n">
-        <v>19.52124786376953</v>
+        <v>19.52124977111816</v>
       </c>
       <c r="L70" t="n">
         <v>2823.81005859375</v>
@@ -3109,22 +3109,22 @@
         <v>43132</v>
       </c>
       <c r="B71" t="n">
-        <v>41.7706298828125</v>
+        <v>41.77062606811523</v>
       </c>
       <c r="C71" t="n">
-        <v>86.10148620605469</v>
+        <v>86.10150146484375</v>
       </c>
       <c r="D71" t="n">
-        <v>54.67572784423828</v>
+        <v>54.67572021484375</v>
       </c>
       <c r="E71" t="n">
         <v>75.62249755859375</v>
       </c>
       <c r="F71" t="n">
-        <v>5.972711563110352</v>
+        <v>5.97271203994751</v>
       </c>
       <c r="G71" t="n">
-        <v>176.6282958984375</v>
+        <v>176.6283111572266</v>
       </c>
       <c r="H71" t="n">
         <v>12.10999965667725</v>
@@ -3133,10 +3133,10 @@
         <v>22.87066650390625</v>
       </c>
       <c r="J71" t="n">
-        <v>41.65947723388672</v>
+        <v>41.65947341918945</v>
       </c>
       <c r="K71" t="n">
-        <v>19.39768409729004</v>
+        <v>19.39767837524414</v>
       </c>
       <c r="L71" t="n">
         <v>2713.830078125</v>
@@ -3150,19 +3150,19 @@
         <v>39.34581756591797</v>
       </c>
       <c r="C72" t="n">
-        <v>83.80596923828125</v>
+        <v>83.80594635009766</v>
       </c>
       <c r="D72" t="n">
-        <v>51.36819839477539</v>
+        <v>51.36819458007812</v>
       </c>
       <c r="E72" t="n">
         <v>72.36699676513672</v>
       </c>
       <c r="F72" t="n">
-        <v>5.715786457061768</v>
+        <v>5.7157883644104</v>
       </c>
       <c r="G72" t="n">
-        <v>158.2741088867188</v>
+        <v>158.2740783691406</v>
       </c>
       <c r="H72" t="n">
         <v>10.05000019073486</v>
@@ -3171,10 +3171,10 @@
         <v>17.74200057983398</v>
       </c>
       <c r="J72" t="n">
-        <v>44.01756286621094</v>
+        <v>44.01757049560547</v>
       </c>
       <c r="K72" t="n">
-        <v>18.81864356994629</v>
+        <v>18.81864547729492</v>
       </c>
       <c r="L72" t="n">
         <v>2640.8701171875</v>
@@ -3188,19 +3188,19 @@
         <v>38.75485229492188</v>
       </c>
       <c r="C73" t="n">
-        <v>85.87197113037109</v>
+        <v>85.87193298339844</v>
       </c>
       <c r="D73" t="n">
-        <v>50.44894790649414</v>
+        <v>50.44894409179688</v>
       </c>
       <c r="E73" t="n">
         <v>78.30650329589844</v>
       </c>
       <c r="F73" t="n">
-        <v>5.550672054290771</v>
+        <v>5.550673007965088</v>
       </c>
       <c r="G73" t="n">
-        <v>170.3682556152344</v>
+        <v>170.3682861328125</v>
       </c>
       <c r="H73" t="n">
         <v>10.88000011444092</v>
@@ -3209,10 +3209,10 @@
         <v>19.59333229064941</v>
       </c>
       <c r="J73" t="n">
-        <v>43.62877655029297</v>
+        <v>43.62878036499023</v>
       </c>
       <c r="K73" t="n">
-        <v>18.32112884521484</v>
+        <v>18.32112693786621</v>
       </c>
       <c r="L73" t="n">
         <v>2648.050048828125</v>
@@ -3223,22 +3223,22 @@
         <v>43221</v>
       </c>
       <c r="B74" t="n">
-        <v>43.9915657043457</v>
+        <v>43.99156951904297</v>
       </c>
       <c r="C74" t="n">
-        <v>91.15024566650391</v>
+        <v>91.15025329589844</v>
       </c>
       <c r="D74" t="n">
-        <v>54.48156356811523</v>
+        <v>54.48157119750977</v>
       </c>
       <c r="E74" t="n">
         <v>81.48100280761719</v>
       </c>
       <c r="F74" t="n">
-        <v>6.228056907653809</v>
+        <v>6.228055000305176</v>
       </c>
       <c r="G74" t="n">
-        <v>189.9606170654297</v>
+        <v>189.9606018066406</v>
       </c>
       <c r="H74" t="n">
         <v>13.72999954223633</v>
@@ -3250,7 +3250,7 @@
         <v>46.923828125</v>
       </c>
       <c r="K74" t="n">
-        <v>20.12992095947266</v>
+        <v>20.12992668151855</v>
       </c>
       <c r="L74" t="n">
         <v>2705.27001953125</v>
@@ -3261,22 +3261,22 @@
         <v>43252</v>
       </c>
       <c r="B75" t="n">
-        <v>43.57724380493164</v>
+        <v>43.57723236083984</v>
       </c>
       <c r="C75" t="n">
-        <v>90.93815612792969</v>
+        <v>90.93814849853516</v>
       </c>
       <c r="D75" t="n">
-        <v>55.92731094360352</v>
+        <v>55.92730712890625</v>
       </c>
       <c r="E75" t="n">
         <v>84.98999786376953</v>
       </c>
       <c r="F75" t="n">
-        <v>5.850456237792969</v>
+        <v>5.850454807281494</v>
       </c>
       <c r="G75" t="n">
-        <v>192.4765167236328</v>
+        <v>192.4765319824219</v>
       </c>
       <c r="H75" t="n">
         <v>14.98999977111816</v>
@@ -3285,10 +3285,10 @@
         <v>22.86333274841309</v>
       </c>
       <c r="J75" t="n">
-        <v>42.2569465637207</v>
+        <v>42.25693511962891</v>
       </c>
       <c r="K75" t="n">
-        <v>19.63669967651367</v>
+        <v>19.63669776916504</v>
       </c>
       <c r="L75" t="n">
         <v>2718.3701171875</v>
@@ -3299,19 +3299,19 @@
         <v>43282</v>
       </c>
       <c r="B76" t="n">
-        <v>44.79666137695312</v>
+        <v>44.79666519165039</v>
       </c>
       <c r="C76" t="n">
-        <v>97.82697296142578</v>
+        <v>97.82700347900391</v>
       </c>
       <c r="D76" t="n">
-        <v>60.78261566162109</v>
+        <v>60.78261184692383</v>
       </c>
       <c r="E76" t="n">
         <v>88.87200164794922</v>
       </c>
       <c r="F76" t="n">
-        <v>6.047035694122314</v>
+        <v>6.047036170959473</v>
       </c>
       <c r="G76" t="n">
         <v>170.9427642822266</v>
@@ -3323,10 +3323,10 @@
         <v>19.87599945068359</v>
       </c>
       <c r="J76" t="n">
-        <v>40.88833236694336</v>
+        <v>40.88832855224609</v>
       </c>
       <c r="K76" t="n">
-        <v>17.94770431518555</v>
+        <v>17.94770622253418</v>
       </c>
       <c r="L76" t="n">
         <v>2816.2900390625</v>
@@ -3340,7 +3340,7 @@
         <v>53.77492141723633</v>
       </c>
       <c r="C77" t="n">
-        <v>103.989387512207</v>
+        <v>103.9894027709961</v>
       </c>
       <c r="D77" t="n">
         <v>61.00945281982422</v>
@@ -3349,7 +3349,7 @@
         <v>100.635498046875</v>
       </c>
       <c r="F77" t="n">
-        <v>6.935434341430664</v>
+        <v>6.935433387756348</v>
       </c>
       <c r="G77" t="n">
         <v>174.0628814697266</v>
@@ -3361,7 +3361,7 @@
         <v>20.11066627502441</v>
       </c>
       <c r="J77" t="n">
-        <v>41.41922378540039</v>
+        <v>41.41922760009766</v>
       </c>
       <c r="K77" t="n">
         <v>17.7259521484375</v>
@@ -3375,22 +3375,22 @@
         <v>43344</v>
       </c>
       <c r="B78" t="n">
-        <v>53.32843399047852</v>
+        <v>53.32843017578125</v>
       </c>
       <c r="C78" t="n">
-        <v>105.8779296875</v>
+        <v>105.8779067993164</v>
       </c>
       <c r="D78" t="n">
-        <v>59.78510284423828</v>
+        <v>59.78511047363281</v>
       </c>
       <c r="E78" t="n">
         <v>100.1500015258789</v>
       </c>
       <c r="F78" t="n">
-        <v>6.943835258483887</v>
+        <v>6.943833351135254</v>
       </c>
       <c r="G78" t="n">
-        <v>162.8997955322266</v>
+        <v>162.8998107910156</v>
       </c>
       <c r="H78" t="n">
         <v>30.88999938964844</v>
@@ -3399,10 +3399,10 @@
         <v>17.65133285522461</v>
       </c>
       <c r="J78" t="n">
-        <v>40.44425201416016</v>
+        <v>40.44425582885742</v>
       </c>
       <c r="K78" t="n">
-        <v>20.11762046813965</v>
+        <v>20.11762237548828</v>
       </c>
       <c r="L78" t="n">
         <v>2913.97998046875</v>
@@ -3413,22 +3413,22 @@
         <v>43374</v>
       </c>
       <c r="B79" t="n">
-        <v>51.70311737060547</v>
+        <v>51.70310974121094</v>
       </c>
       <c r="C79" t="n">
-        <v>98.87924194335938</v>
+        <v>98.87924957275391</v>
       </c>
       <c r="D79" t="n">
-        <v>54.0150146484375</v>
+        <v>54.01501083374023</v>
       </c>
       <c r="E79" t="n">
         <v>79.90049743652344</v>
       </c>
       <c r="F79" t="n">
-        <v>5.20948314666748</v>
+        <v>5.209482669830322</v>
       </c>
       <c r="G79" t="n">
-        <v>150.3500061035156</v>
+        <v>150.3499908447266</v>
       </c>
       <c r="H79" t="n">
         <v>18.20999908447266</v>
@@ -3437,10 +3437,10 @@
         <v>22.48800086975098</v>
       </c>
       <c r="J79" t="n">
-        <v>40.09361267089844</v>
+        <v>40.09360122680664</v>
       </c>
       <c r="K79" t="n">
-        <v>18.22270011901855</v>
+        <v>18.22270202636719</v>
       </c>
       <c r="L79" t="n">
         <v>2711.739990234375</v>
@@ -3451,19 +3451,19 @@
         <v>43405</v>
       </c>
       <c r="B80" t="n">
-        <v>42.33462905883789</v>
+        <v>42.33464050292969</v>
       </c>
       <c r="C80" t="n">
         <v>103.0997848510742</v>
       </c>
       <c r="D80" t="n">
-        <v>54.95951843261719</v>
+        <v>54.95952606201172</v>
       </c>
       <c r="E80" t="n">
         <v>84.50849914550781</v>
       </c>
       <c r="F80" t="n">
-        <v>4.042297840118408</v>
+        <v>4.042298316955566</v>
       </c>
       <c r="G80" t="n">
         <v>139.2760620117188</v>
@@ -3489,19 +3489,19 @@
         <v>43435</v>
       </c>
       <c r="B81" t="n">
-        <v>37.39424514770508</v>
+        <v>37.39424133300781</v>
       </c>
       <c r="C81" t="n">
         <v>94.43452453613281</v>
       </c>
       <c r="D81" t="n">
-        <v>51.75551223754883</v>
+        <v>51.75550842285156</v>
       </c>
       <c r="E81" t="n">
         <v>75.09850311279297</v>
       </c>
       <c r="F81" t="n">
-        <v>3.302005290985107</v>
+        <v>3.302006006240845</v>
       </c>
       <c r="G81" t="n">
         <v>129.8463592529297</v>
@@ -3516,7 +3516,7 @@
         <v>40.38894271850586</v>
       </c>
       <c r="K81" t="n">
-        <v>20.95170021057129</v>
+        <v>20.95170211791992</v>
       </c>
       <c r="L81" t="n">
         <v>2506.85009765625</v>
@@ -3527,19 +3527,19 @@
         <v>43466</v>
       </c>
       <c r="B82" t="n">
-        <v>39.45669555664062</v>
+        <v>39.45668029785156</v>
       </c>
       <c r="C82" t="n">
         <v>97.09362030029297</v>
       </c>
       <c r="D82" t="n">
-        <v>55.76387405395508</v>
+        <v>55.76386260986328</v>
       </c>
       <c r="E82" t="n">
         <v>85.93650054931641</v>
       </c>
       <c r="F82" t="n">
-        <v>3.555530309677124</v>
+        <v>3.555529356002808</v>
       </c>
       <c r="G82" t="n">
         <v>165.1086578369141</v>
@@ -3551,10 +3551,10 @@
         <v>20.4680004119873</v>
       </c>
       <c r="J82" t="n">
-        <v>40.55247116088867</v>
+        <v>40.55246734619141</v>
       </c>
       <c r="K82" t="n">
-        <v>22.102783203125</v>
+        <v>22.10277557373047</v>
       </c>
       <c r="L82" t="n">
         <v>2704.10009765625</v>
@@ -3565,22 +3565,22 @@
         <v>43497</v>
       </c>
       <c r="B83" t="n">
-        <v>41.22343826293945</v>
+        <v>41.22342681884766</v>
       </c>
       <c r="C83" t="n">
-        <v>104.6045379638672</v>
+        <v>104.6045455932617</v>
       </c>
       <c r="D83" t="n">
-        <v>55.79655838012695</v>
+        <v>55.79656219482422</v>
       </c>
       <c r="E83" t="n">
         <v>81.99150085449219</v>
       </c>
       <c r="F83" t="n">
-        <v>3.819417476654053</v>
+        <v>3.819417953491211</v>
       </c>
       <c r="G83" t="n">
-        <v>159.9183349609375</v>
+        <v>159.9183502197266</v>
       </c>
       <c r="H83" t="n">
         <v>23.53000068664551</v>
@@ -3592,7 +3592,7 @@
         <v>45.86740875244141</v>
       </c>
       <c r="K83" t="n">
-        <v>22.68861198425293</v>
+        <v>22.6886100769043</v>
       </c>
       <c r="L83" t="n">
         <v>2784.489990234375</v>
@@ -3603,19 +3603,19 @@
         <v>43525</v>
       </c>
       <c r="B84" t="n">
-        <v>45.22314834594727</v>
+        <v>45.22315979003906</v>
       </c>
       <c r="C84" t="n">
-        <v>110.1228179931641</v>
+        <v>110.1228256225586</v>
       </c>
       <c r="D84" t="n">
-        <v>58.28983688354492</v>
+        <v>58.28982925415039</v>
       </c>
       <c r="E84" t="n">
         <v>89.03749847412109</v>
       </c>
       <c r="F84" t="n">
-        <v>4.445836067199707</v>
+        <v>4.445835590362549</v>
       </c>
       <c r="G84" t="n">
         <v>165.1086578369141</v>
@@ -3644,7 +3644,7 @@
         <v>47.77536010742188</v>
       </c>
       <c r="C85" t="n">
-        <v>121.943717956543</v>
+        <v>121.9436874389648</v>
       </c>
       <c r="D85" t="n">
         <v>59.3829345703125</v>
@@ -3656,7 +3656,7 @@
         <v>4.481490612030029</v>
       </c>
       <c r="G85" t="n">
-        <v>191.5652313232422</v>
+        <v>191.5652465820312</v>
       </c>
       <c r="H85" t="n">
         <v>27.6299991607666</v>
@@ -3665,10 +3665,10 @@
         <v>15.9126672744751</v>
       </c>
       <c r="J85" t="n">
-        <v>44.20453262329102</v>
+        <v>44.20454025268555</v>
       </c>
       <c r="K85" t="n">
-        <v>26.46929550170898</v>
+        <v>26.46929359436035</v>
       </c>
       <c r="L85" t="n">
         <v>2945.830078125</v>
@@ -3679,22 +3679,22 @@
         <v>43586</v>
       </c>
       <c r="B86" t="n">
-        <v>41.84104537963867</v>
+        <v>41.8410530090332</v>
       </c>
       <c r="C86" t="n">
-        <v>115.9098205566406</v>
+        <v>115.9098587036133</v>
       </c>
       <c r="D86" t="n">
-        <v>54.80350875854492</v>
+        <v>54.80350494384766</v>
       </c>
       <c r="E86" t="n">
         <v>88.75350189208984</v>
       </c>
       <c r="F86" t="n">
-        <v>3.357764720916748</v>
+        <v>3.357764959335327</v>
       </c>
       <c r="G86" t="n">
-        <v>175.786376953125</v>
+        <v>175.7863616943359</v>
       </c>
       <c r="H86" t="n">
         <v>27.40999984741211</v>
@@ -3706,7 +3706,7 @@
         <v>38.37559127807617</v>
       </c>
       <c r="K86" t="n">
-        <v>20.91938972473145</v>
+        <v>20.91939163208008</v>
       </c>
       <c r="L86" t="n">
         <v>2752.06005859375</v>
@@ -3717,7 +3717,7 @@
         <v>43617</v>
       </c>
       <c r="B87" t="n">
-        <v>47.3021125793457</v>
+        <v>47.30210494995117</v>
       </c>
       <c r="C87" t="n">
         <v>125.5440139770508</v>
@@ -3729,7 +3729,7 @@
         <v>94.68150329589844</v>
       </c>
       <c r="F87" t="n">
-        <v>4.070912837982178</v>
+        <v>4.07091236114502</v>
       </c>
       <c r="G87" t="n">
         <v>191.1690368652344</v>
@@ -3741,10 +3741,10 @@
         <v>14.8973331451416</v>
       </c>
       <c r="J87" t="n">
-        <v>41.71298599243164</v>
+        <v>41.71298217773438</v>
       </c>
       <c r="K87" t="n">
-        <v>24.15987205505371</v>
+        <v>24.15987777709961</v>
       </c>
       <c r="L87" t="n">
         <v>2941.760009765625</v>
@@ -3755,19 +3755,19 @@
         <v>43647</v>
       </c>
       <c r="B88" t="n">
-        <v>50.91572189331055</v>
+        <v>50.91572570800781</v>
       </c>
       <c r="C88" t="n">
-        <v>127.7088470458984</v>
+        <v>127.7088851928711</v>
       </c>
       <c r="D88" t="n">
-        <v>60.33586120605469</v>
+        <v>60.33586502075195</v>
       </c>
       <c r="E88" t="n">
         <v>93.33899688720703</v>
       </c>
       <c r="F88" t="n">
-        <v>4.182209014892578</v>
+        <v>4.182210445404053</v>
       </c>
       <c r="G88" t="n">
         <v>192.3873748779297</v>
@@ -3779,10 +3779,10 @@
         <v>16.10733222961426</v>
       </c>
       <c r="J88" t="n">
-        <v>44.04828262329102</v>
+        <v>44.04827499389648</v>
       </c>
       <c r="K88" t="n">
-        <v>24.33864212036133</v>
+        <v>24.33864402770996</v>
       </c>
       <c r="L88" t="n">
         <v>2980.3798828125</v>
@@ -3793,10 +3793,10 @@
         <v>43678</v>
       </c>
       <c r="B89" t="n">
-        <v>50.07759857177734</v>
+        <v>50.07759475708008</v>
       </c>
       <c r="C89" t="n">
-        <v>129.6292419433594</v>
+        <v>129.6292114257812</v>
       </c>
       <c r="D89" t="n">
         <v>58.96540069580078</v>
@@ -3805,10 +3805,10 @@
         <v>88.81449890136719</v>
       </c>
       <c r="F89" t="n">
-        <v>4.156327724456787</v>
+        <v>4.156326770782471</v>
       </c>
       <c r="G89" t="n">
-        <v>183.9085540771484</v>
+        <v>183.9085845947266</v>
       </c>
       <c r="H89" t="n">
         <v>31.45000076293945</v>
@@ -3817,10 +3817,10 @@
         <v>15.0406665802002</v>
       </c>
       <c r="J89" t="n">
-        <v>41.591064453125</v>
+        <v>41.59106826782227</v>
       </c>
       <c r="K89" t="n">
-        <v>23.72175979614258</v>
+        <v>23.72176170349121</v>
       </c>
       <c r="L89" t="n">
         <v>2926.4599609375</v>
@@ -3831,19 +3831,19 @@
         <v>43709</v>
       </c>
       <c r="B90" t="n">
-        <v>53.73131942749023</v>
+        <v>53.7313232421875</v>
       </c>
       <c r="C90" t="n">
-        <v>130.7293395996094</v>
+        <v>130.7294006347656</v>
       </c>
       <c r="D90" t="n">
-        <v>60.48147201538086</v>
+        <v>60.48147583007812</v>
       </c>
       <c r="E90" t="n">
         <v>86.79550170898438</v>
       </c>
       <c r="F90" t="n">
-        <v>4.31909704208374</v>
+        <v>4.319095134735107</v>
       </c>
       <c r="G90" t="n">
         <v>176.3905792236328</v>
@@ -3855,10 +3855,10 @@
         <v>16.0580005645752</v>
       </c>
       <c r="J90" t="n">
-        <v>45.20540237426758</v>
+        <v>45.20539474487305</v>
       </c>
       <c r="K90" t="n">
-        <v>23.3835563659668</v>
+        <v>23.38355255126953</v>
       </c>
       <c r="L90" t="n">
         <v>2976.739990234375</v>
@@ -3869,19 +3869,19 @@
         <v>43739</v>
       </c>
       <c r="B91" t="n">
-        <v>59.67855072021484</v>
+        <v>59.67854690551758</v>
       </c>
       <c r="C91" t="n">
         <v>134.8102264404297</v>
       </c>
       <c r="D91" t="n">
-        <v>62.34672546386719</v>
+        <v>62.34672927856445</v>
       </c>
       <c r="E91" t="n">
         <v>88.83300018310547</v>
       </c>
       <c r="F91" t="n">
-        <v>4.987790584564209</v>
+        <v>4.987791538238525</v>
       </c>
       <c r="G91" t="n">
         <v>189.8318481445312</v>
@@ -3896,7 +3896,7 @@
         <v>49.59172058105469</v>
       </c>
       <c r="K91" t="n">
-        <v>24.80484580993652</v>
+        <v>24.80484008789062</v>
       </c>
       <c r="L91" t="n">
         <v>3037.56005859375</v>
@@ -3907,13 +3907,13 @@
         <v>43770</v>
       </c>
       <c r="B92" t="n">
-        <v>64.306884765625</v>
+        <v>64.30687713623047</v>
       </c>
       <c r="C92" t="n">
-        <v>142.826416015625</v>
+        <v>142.8263549804688</v>
       </c>
       <c r="D92" t="n">
-        <v>64.58986663818359</v>
+        <v>64.58988952636719</v>
       </c>
       <c r="E92" t="n">
         <v>90.04000091552734</v>
@@ -3922,7 +3922,7 @@
         <v>5.381809711456299</v>
       </c>
       <c r="G92" t="n">
-        <v>199.7270660400391</v>
+        <v>199.7270812988281</v>
       </c>
       <c r="H92" t="n">
         <v>39.15000152587891</v>
@@ -3931,10 +3931,10 @@
         <v>21.99600028991699</v>
       </c>
       <c r="J92" t="n">
-        <v>51.20542526245117</v>
+        <v>51.20542907714844</v>
       </c>
       <c r="K92" t="n">
-        <v>26.78347778320312</v>
+        <v>26.78347396850586</v>
       </c>
       <c r="L92" t="n">
         <v>3140.97998046875</v>
@@ -3948,16 +3948,16 @@
         <v>70.65935516357422</v>
       </c>
       <c r="C93" t="n">
-        <v>148.7892608642578</v>
+        <v>148.7892303466797</v>
       </c>
       <c r="D93" t="n">
-        <v>66.33824920654297</v>
+        <v>66.33824157714844</v>
       </c>
       <c r="E93" t="n">
         <v>92.39199829101562</v>
       </c>
       <c r="F93" t="n">
-        <v>5.842668056488037</v>
+        <v>5.842667102813721</v>
       </c>
       <c r="G93" t="n">
         <v>203.3028259277344</v>
@@ -3969,10 +3969,10 @@
         <v>27.8886661529541</v>
       </c>
       <c r="J93" t="n">
-        <v>52.79320526123047</v>
+        <v>52.79319381713867</v>
       </c>
       <c r="K93" t="n">
-        <v>27.03851699829102</v>
+        <v>27.03851318359375</v>
       </c>
       <c r="L93" t="n">
         <v>3230.780029296875</v>
@@ -3986,16 +3986,16 @@
         <v>74.47566986083984</v>
       </c>
       <c r="C94" t="n">
-        <v>160.6112518310547</v>
+        <v>160.6112365722656</v>
       </c>
       <c r="D94" t="n">
-        <v>70.96372985839844</v>
+        <v>70.96373748779297</v>
       </c>
       <c r="E94" t="n">
         <v>100.4359970092773</v>
       </c>
       <c r="F94" t="n">
-        <v>5.8707275390625</v>
+        <v>5.870728015899658</v>
       </c>
       <c r="G94" t="n">
         <v>199.9945068359375</v>
@@ -4007,7 +4007,7 @@
         <v>43.37133407592773</v>
       </c>
       <c r="J94" t="n">
-        <v>56.39213180541992</v>
+        <v>56.39212417602539</v>
       </c>
       <c r="K94" t="n">
         <v>26.10934066772461</v>
@@ -4021,22 +4021,22 @@
         <v>43862</v>
       </c>
       <c r="B95" t="n">
-        <v>65.93321228027344</v>
+        <v>65.93318939208984</v>
       </c>
       <c r="C95" t="n">
-        <v>153.2732086181641</v>
+        <v>153.2732543945312</v>
       </c>
       <c r="D95" t="n">
-        <v>66.33131408691406</v>
+        <v>66.33130645751953</v>
       </c>
       <c r="E95" t="n">
         <v>94.1875</v>
       </c>
       <c r="F95" t="n">
-        <v>6.710044384002686</v>
+        <v>6.710041999816895</v>
       </c>
       <c r="G95" t="n">
-        <v>190.6440734863281</v>
+        <v>190.6440582275391</v>
       </c>
       <c r="H95" t="n">
         <v>45.47999954223633</v>
@@ -4045,7 +4045,7 @@
         <v>44.53266525268555</v>
       </c>
       <c r="J95" t="n">
-        <v>49.21491622924805</v>
+        <v>49.21492004394531</v>
       </c>
       <c r="K95" t="n">
         <v>23.32523345947266</v>
@@ -4059,22 +4059,22 @@
         <v>43891</v>
       </c>
       <c r="B96" t="n">
-        <v>61.33359146118164</v>
+        <v>61.33360290527344</v>
       </c>
       <c r="C96" t="n">
         <v>149.2051239013672</v>
       </c>
       <c r="D96" t="n">
-        <v>57.54987335205078</v>
+        <v>57.54987716674805</v>
       </c>
       <c r="E96" t="n">
         <v>97.48600006103516</v>
       </c>
       <c r="F96" t="n">
-        <v>6.549293041229248</v>
+        <v>6.549292087554932</v>
       </c>
       <c r="G96" t="n">
-        <v>165.2176055908203</v>
+        <v>165.2176208496094</v>
       </c>
       <c r="H96" t="n">
         <v>45.47999954223633</v>
@@ -4083,10 +4083,10 @@
         <v>34.93333435058594</v>
       </c>
       <c r="J96" t="n">
-        <v>47.97391128540039</v>
+        <v>47.97390747070312</v>
       </c>
       <c r="K96" t="n">
-        <v>20.6309814453125</v>
+        <v>20.63098335266113</v>
       </c>
       <c r="L96" t="n">
         <v>2584.590087890625</v>
@@ -4097,22 +4097,22 @@
         <v>43922</v>
       </c>
       <c r="B97" t="n">
-        <v>70.86325073242188</v>
+        <v>70.86322021484375</v>
       </c>
       <c r="C97" t="n">
-        <v>169.5457305908203</v>
+        <v>169.5456695556641</v>
       </c>
       <c r="D97" t="n">
-        <v>66.70029449462891</v>
+        <v>66.70030212402344</v>
       </c>
       <c r="E97" t="n">
         <v>123.6999969482422</v>
       </c>
       <c r="F97" t="n">
-        <v>7.261863231658936</v>
+        <v>7.261863708496094</v>
       </c>
       <c r="G97" t="n">
-        <v>202.7679443359375</v>
+        <v>202.7679901123047</v>
       </c>
       <c r="H97" t="n">
         <v>52.38999938964844</v>
@@ -4124,7 +4124,7 @@
         <v>53.16841888427734</v>
       </c>
       <c r="K97" t="n">
-        <v>23.63469696044922</v>
+        <v>23.63469886779785</v>
       </c>
       <c r="L97" t="n">
         <v>2912.429931640625</v>
@@ -4135,7 +4135,7 @@
         <v>43952</v>
       </c>
       <c r="B98" t="n">
-        <v>76.89328002929688</v>
+        <v>76.89328765869141</v>
       </c>
       <c r="C98" t="n">
         <v>173.8506622314453</v>
@@ -4147,10 +4147,10 @@
         <v>122.1184997558594</v>
       </c>
       <c r="F98" t="n">
-        <v>8.820675849914551</v>
+        <v>8.820673942565918</v>
       </c>
       <c r="G98" t="n">
-        <v>222.9546203613281</v>
+        <v>222.9546051025391</v>
       </c>
       <c r="H98" t="n">
         <v>53.79999923706055</v>
@@ -4162,7 +4162,7 @@
         <v>56.0985107421875</v>
       </c>
       <c r="K98" t="n">
-        <v>25.34451675415039</v>
+        <v>25.34452247619629</v>
       </c>
       <c r="L98" t="n">
         <v>3044.31005859375</v>
@@ -4176,19 +4176,19 @@
         <v>88.22631072998047</v>
       </c>
       <c r="C99" t="n">
-        <v>193.0714874267578</v>
+        <v>193.0714569091797</v>
       </c>
       <c r="D99" t="n">
-        <v>70.23416137695312</v>
+        <v>70.23415374755859</v>
       </c>
       <c r="E99" t="n">
         <v>137.9409942626953</v>
       </c>
       <c r="F99" t="n">
-        <v>9.443389892578125</v>
+        <v>9.443387985229492</v>
       </c>
       <c r="G99" t="n">
-        <v>224.9158325195312</v>
+        <v>224.9158477783203</v>
       </c>
       <c r="H99" t="n">
         <v>52.61000061035156</v>
@@ -4197,10 +4197,10 @@
         <v>71.98733520507812</v>
       </c>
       <c r="J99" t="n">
-        <v>53.33504486083984</v>
+        <v>53.33504104614258</v>
       </c>
       <c r="K99" t="n">
-        <v>27.745361328125</v>
+        <v>27.7453670501709</v>
       </c>
       <c r="L99" t="n">
         <v>3100.2900390625</v>
@@ -4211,22 +4211,22 @@
         <v>44013</v>
       </c>
       <c r="B100" t="n">
-        <v>102.7952575683594</v>
+        <v>102.7952346801758</v>
       </c>
       <c r="C100" t="n">
-        <v>194.4945373535156</v>
+        <v>194.4944915771484</v>
       </c>
       <c r="D100" t="n">
-        <v>73.69623565673828</v>
+        <v>73.69622802734375</v>
       </c>
       <c r="E100" t="n">
         <v>158.2339935302734</v>
       </c>
       <c r="F100" t="n">
-        <v>10.55399894714355</v>
+        <v>10.55399608612061</v>
       </c>
       <c r="G100" t="n">
-        <v>251.2634735107422</v>
+        <v>251.2634582519531</v>
       </c>
       <c r="H100" t="n">
         <v>77.43000030517578</v>
@@ -4235,10 +4235,10 @@
         <v>95.38400268554688</v>
       </c>
       <c r="J100" t="n">
-        <v>42.54857635498047</v>
+        <v>42.54858016967773</v>
       </c>
       <c r="K100" t="n">
-        <v>27.84558296203613</v>
+        <v>27.8455867767334</v>
       </c>
       <c r="L100" t="n">
         <v>3271.1201171875</v>
@@ -4249,10 +4249,10 @@
         <v>44044</v>
       </c>
       <c r="B101" t="n">
-        <v>125.0575485229492</v>
+        <v>125.0575332641602</v>
       </c>
       <c r="C101" t="n">
-        <v>214.4792327880859</v>
+        <v>214.4792175292969</v>
       </c>
       <c r="D101" t="n">
         <v>80.70850372314453</v>
@@ -4261,7 +4261,7 @@
         <v>172.5480041503906</v>
       </c>
       <c r="F101" t="n">
-        <v>13.29795360565186</v>
+        <v>13.29794883728027</v>
       </c>
       <c r="G101" t="n">
         <v>290.4184875488281</v>
@@ -4273,10 +4273,10 @@
         <v>166.1066741943359</v>
       </c>
       <c r="J101" t="n">
-        <v>45.72748947143555</v>
+        <v>45.72749710083008</v>
       </c>
       <c r="K101" t="n">
-        <v>30.51805686950684</v>
+        <v>30.51805877685547</v>
       </c>
       <c r="L101" t="n">
         <v>3500.31005859375</v>
@@ -4287,22 +4287,22 @@
         <v>44075</v>
       </c>
       <c r="B102" t="n">
-        <v>112.23583984375</v>
+        <v>112.2358474731445</v>
       </c>
       <c r="C102" t="n">
-        <v>200.0240173339844</v>
+        <v>200.0240325927734</v>
       </c>
       <c r="D102" t="n">
-        <v>72.58927154541016</v>
+        <v>72.58926391601562</v>
       </c>
       <c r="E102" t="n">
         <v>157.4364929199219</v>
       </c>
       <c r="F102" t="n">
-        <v>13.45708084106445</v>
+        <v>13.45708179473877</v>
       </c>
       <c r="G102" t="n">
-        <v>259.4154052734375</v>
+        <v>259.4154357910156</v>
       </c>
       <c r="H102" t="n">
         <v>81.98999786376953</v>
@@ -4311,10 +4311,10 @@
         <v>143.0033264160156</v>
       </c>
       <c r="J102" t="n">
-        <v>46.47240829467773</v>
+        <v>46.472412109375</v>
       </c>
       <c r="K102" t="n">
-        <v>32.31946182250977</v>
+        <v>32.3194580078125</v>
       </c>
       <c r="L102" t="n">
         <v>3363</v>
@@ -4328,10 +4328,10 @@
         <v>105.5003356933594</v>
       </c>
       <c r="C103" t="n">
-        <v>192.5491638183594</v>
+        <v>192.5491180419922</v>
       </c>
       <c r="D103" t="n">
-        <v>80.04381561279297</v>
+        <v>80.0438232421875</v>
       </c>
       <c r="E103" t="n">
         <v>151.8074951171875</v>
@@ -4340,7 +4340,7 @@
         <v>12.465989112854</v>
       </c>
       <c r="G103" t="n">
-        <v>260.6138610839844</v>
+        <v>260.6138916015625</v>
       </c>
       <c r="H103" t="n">
         <v>75.29000091552734</v>
@@ -4349,10 +4349,10 @@
         <v>129.3466644287109</v>
       </c>
       <c r="J103" t="n">
-        <v>39.74118423461914</v>
+        <v>39.74118041992188</v>
       </c>
       <c r="K103" t="n">
-        <v>31.01629829406738</v>
+        <v>31.01629257202148</v>
       </c>
       <c r="L103" t="n">
         <v>3269.9599609375</v>
@@ -4363,10 +4363,10 @@
         <v>44136</v>
       </c>
       <c r="B104" t="n">
-        <v>115.5749359130859</v>
+        <v>115.5749130249023</v>
       </c>
       <c r="C104" t="n">
-        <v>204.1137084960938</v>
+        <v>204.1137237548828</v>
       </c>
       <c r="D104" t="n">
         <v>86.89315032958984</v>
@@ -4375,10 +4375,10 @@
         <v>158.4019927978516</v>
       </c>
       <c r="F104" t="n">
-        <v>13.32878112792969</v>
+        <v>13.32877922058105</v>
       </c>
       <c r="G104" t="n">
-        <v>274.3424682617188</v>
+        <v>274.3424377441406</v>
       </c>
       <c r="H104" t="n">
         <v>92.66000366210938</v>
@@ -4401,19 +4401,19 @@
         <v>44166</v>
       </c>
       <c r="B105" t="n">
-        <v>128.8167419433594</v>
+        <v>128.8167724609375</v>
       </c>
       <c r="C105" t="n">
-        <v>212.0753479003906</v>
+        <v>212.0753936767578</v>
       </c>
       <c r="D105" t="n">
-        <v>86.80598449707031</v>
+        <v>86.80597686767578</v>
       </c>
       <c r="E105" t="n">
         <v>162.8464965820312</v>
       </c>
       <c r="F105" t="n">
-        <v>12.98799896240234</v>
+        <v>12.98800086975098</v>
       </c>
       <c r="G105" t="n">
         <v>270.5685729980469</v>
@@ -4428,7 +4428,7 @@
         <v>45.03854370117188</v>
       </c>
       <c r="K105" t="n">
-        <v>39.17340850830078</v>
+        <v>39.17341613769531</v>
       </c>
       <c r="L105" t="n">
         <v>3756.070068359375</v>
@@ -4439,22 +4439,22 @@
         <v>44197</v>
       </c>
       <c r="B106" t="n">
-        <v>128.1080932617188</v>
+        <v>128.1080627441406</v>
       </c>
       <c r="C106" t="n">
-        <v>221.1716766357422</v>
+        <v>221.1717376708984</v>
       </c>
       <c r="D106" t="n">
-        <v>90.50675964355469</v>
+        <v>90.50675201416016</v>
       </c>
       <c r="E106" t="n">
         <v>160.3099975585938</v>
       </c>
       <c r="F106" t="n">
-        <v>12.92308139801025</v>
+        <v>12.92308235168457</v>
       </c>
       <c r="G106" t="n">
-        <v>255.8792572021484</v>
+        <v>255.8793334960938</v>
       </c>
       <c r="H106" t="n">
         <v>85.63999938964844</v>
@@ -4463,7 +4463,7 @@
         <v>264.510009765625</v>
       </c>
       <c r="J106" t="n">
-        <v>50.18244171142578</v>
+        <v>50.18245315551758</v>
       </c>
       <c r="K106" t="n">
         <v>40.30517196655273</v>
@@ -4477,22 +4477,22 @@
         <v>44228</v>
       </c>
       <c r="B107" t="n">
-        <v>117.8963165283203</v>
+        <v>117.8963012695312</v>
       </c>
       <c r="C107" t="n">
-        <v>222.0824890136719</v>
+        <v>222.0824737548828</v>
       </c>
       <c r="D107" t="n">
-        <v>100.1425704956055</v>
+        <v>100.142578125</v>
       </c>
       <c r="E107" t="n">
         <v>154.6464996337891</v>
       </c>
       <c r="F107" t="n">
-        <v>13.6441125869751</v>
+        <v>13.64411354064941</v>
       </c>
       <c r="G107" t="n">
-        <v>255.1760101318359</v>
+        <v>255.1759796142578</v>
       </c>
       <c r="H107" t="n">
         <v>84.51000213623047</v>
@@ -4504,7 +4504,7 @@
         <v>55.28018188476562</v>
       </c>
       <c r="K107" t="n">
-        <v>42.03816604614258</v>
+        <v>42.03816223144531</v>
       </c>
       <c r="L107" t="n">
         <v>3811.14990234375</v>
@@ -4515,13 +4515,13 @@
         <v>44256</v>
       </c>
       <c r="B108" t="n">
-        <v>118.7616195678711</v>
+        <v>118.7616271972656</v>
       </c>
       <c r="C108" t="n">
-        <v>225.3222808837891</v>
+        <v>225.3222503662109</v>
       </c>
       <c r="D108" t="n">
-        <v>102.153938293457</v>
+        <v>102.1539459228516</v>
       </c>
       <c r="E108" t="n">
         <v>154.7039947509766</v>
@@ -4530,7 +4530,7 @@
         <v>13.28432655334473</v>
       </c>
       <c r="G108" t="n">
-        <v>291.7358703613281</v>
+        <v>291.7358093261719</v>
       </c>
       <c r="H108" t="n">
         <v>78.5</v>
@@ -4542,7 +4542,7 @@
         <v>58.20880889892578</v>
       </c>
       <c r="K108" t="n">
-        <v>41.80683135986328</v>
+        <v>41.80683898925781</v>
       </c>
       <c r="L108" t="n">
         <v>3972.889892578125</v>
@@ -4553,22 +4553,22 @@
         <v>44287</v>
       </c>
       <c r="B109" t="n">
-        <v>127.8134155273438</v>
+        <v>127.8133850097656</v>
       </c>
       <c r="C109" t="n">
         <v>241.0050506591797</v>
       </c>
       <c r="D109" t="n">
-        <v>116.565803527832</v>
+        <v>116.565788269043</v>
       </c>
       <c r="E109" t="n">
         <v>173.3710021972656</v>
       </c>
       <c r="F109" t="n">
-        <v>14.93761825561523</v>
+        <v>14.93762016296387</v>
       </c>
       <c r="G109" t="n">
-        <v>321.9959411621094</v>
+        <v>321.9960327148438</v>
       </c>
       <c r="H109" t="n">
         <v>81.62000274658203</v>
@@ -4577,10 +4577,10 @@
         <v>236.4799957275391</v>
       </c>
       <c r="J109" t="n">
-        <v>52.32426834106445</v>
+        <v>52.32426071166992</v>
       </c>
       <c r="K109" t="n">
-        <v>41.13418579101562</v>
+        <v>41.13419723510742</v>
       </c>
       <c r="L109" t="n">
         <v>4181.169921875</v>
@@ -4591,13 +4591,13 @@
         <v>44317</v>
       </c>
       <c r="B110" t="n">
-        <v>121.3591842651367</v>
+        <v>121.3591766357422</v>
       </c>
       <c r="C110" t="n">
         <v>239.1668395996094</v>
       </c>
       <c r="D110" t="n">
-        <v>116.7317199707031</v>
+        <v>116.7317123413086</v>
       </c>
       <c r="E110" t="n">
         <v>161.1535034179688</v>
@@ -4615,10 +4615,10 @@
         <v>208.4066619873047</v>
       </c>
       <c r="J110" t="n">
-        <v>52.27133941650391</v>
+        <v>52.27133560180664</v>
       </c>
       <c r="K110" t="n">
-        <v>42.58858108520508</v>
+        <v>42.58857345581055</v>
       </c>
       <c r="L110" t="n">
         <v>4204.10986328125</v>
@@ -4632,16 +4632,16 @@
         <v>133.3869934082031</v>
       </c>
       <c r="C111" t="n">
-        <v>259.4933776855469</v>
+        <v>259.4932861328125</v>
       </c>
       <c r="D111" t="n">
-        <v>120.9386825561523</v>
+        <v>120.9386901855469</v>
       </c>
       <c r="E111" t="n">
         <v>172.0079956054688</v>
       </c>
       <c r="F111" t="n">
-        <v>19.91127586364746</v>
+        <v>19.9112720489502</v>
       </c>
       <c r="G111" t="n">
         <v>344.4113464355469</v>
@@ -4667,10 +4667,10 @@
         <v>44378</v>
       </c>
       <c r="B112" t="n">
-        <v>142.0547790527344</v>
+        <v>142.0547943115234</v>
       </c>
       <c r="C112" t="n">
-        <v>272.9134521484375</v>
+        <v>272.9133605957031</v>
       </c>
       <c r="D112" t="n">
         <v>133.4565734863281</v>
@@ -4691,10 +4691,10 @@
         <v>229.0666656494141</v>
       </c>
       <c r="J112" t="n">
-        <v>49.15995025634766</v>
+        <v>49.15995407104492</v>
       </c>
       <c r="K112" t="n">
-        <v>44.10965728759766</v>
+        <v>44.10966110229492</v>
       </c>
       <c r="L112" t="n">
         <v>4395.259765625</v>
@@ -4705,19 +4705,19 @@
         <v>44409</v>
       </c>
       <c r="B113" t="n">
-        <v>148.0905914306641</v>
+        <v>148.090576171875</v>
       </c>
       <c r="C113" t="n">
-        <v>289.722412109375</v>
+        <v>289.7225036621094</v>
       </c>
       <c r="D113" t="n">
-        <v>143.3335723876953</v>
+        <v>143.3335876464844</v>
       </c>
       <c r="E113" t="n">
         <v>173.5395050048828</v>
       </c>
       <c r="F113" t="n">
-        <v>22.28683280944824</v>
+        <v>22.28683471679688</v>
       </c>
       <c r="G113" t="n">
         <v>375.7808837890625</v>
@@ -4729,10 +4729,10 @@
         <v>245.2400054931641</v>
       </c>
       <c r="J113" t="n">
-        <v>49.79256439208984</v>
+        <v>49.79257202148438</v>
       </c>
       <c r="K113" t="n">
-        <v>45.1828727722168</v>
+        <v>45.18286895751953</v>
       </c>
       <c r="L113" t="n">
         <v>4522.68017578125</v>
@@ -4743,7 +4743,7 @@
         <v>44440</v>
       </c>
       <c r="B114" t="n">
-        <v>138.0150299072266</v>
+        <v>138.0149688720703</v>
       </c>
       <c r="C114" t="n">
         <v>270.5663146972656</v>
@@ -4755,10 +4755,10 @@
         <v>164.2519989013672</v>
       </c>
       <c r="F114" t="n">
-        <v>20.62516021728516</v>
+        <v>20.62515449523926</v>
       </c>
       <c r="G114" t="n">
-        <v>336.1703186035156</v>
+        <v>336.1702880859375</v>
       </c>
       <c r="H114" t="n">
         <v>102.9000015258789</v>
@@ -4767,10 +4767,10 @@
         <v>258.4933471679688</v>
       </c>
       <c r="J114" t="n">
-        <v>49.07413864135742</v>
+        <v>49.07413482666016</v>
       </c>
       <c r="K114" t="n">
-        <v>44.389892578125</v>
+        <v>44.3899040222168</v>
       </c>
       <c r="L114" t="n">
         <v>4307.5400390625</v>
@@ -4781,22 +4781,22 @@
         <v>44470</v>
       </c>
       <c r="B115" t="n">
-        <v>146.1105804443359</v>
+        <v>146.1106109619141</v>
       </c>
       <c r="C115" t="n">
-        <v>318.2647705078125</v>
+        <v>318.2647399902344</v>
       </c>
       <c r="D115" t="n">
-        <v>146.6505432128906</v>
+        <v>146.6505279541016</v>
       </c>
       <c r="E115" t="n">
         <v>168.6215057373047</v>
       </c>
       <c r="F115" t="n">
-        <v>25.45488166809082</v>
+        <v>25.45487785339355</v>
       </c>
       <c r="G115" t="n">
-        <v>320.5003356933594</v>
+        <v>320.5003051757812</v>
       </c>
       <c r="H115" t="n">
         <v>120.2300033569336</v>
@@ -4805,10 +4805,10 @@
         <v>371.3333435058594</v>
       </c>
       <c r="J115" t="n">
-        <v>45.13199234008789</v>
+        <v>45.13199615478516</v>
       </c>
       <c r="K115" t="n">
-        <v>48.66841888427734</v>
+        <v>48.66843032836914</v>
       </c>
       <c r="L115" t="n">
         <v>4605.3798828125</v>
@@ -4822,19 +4822,19 @@
         <v>161.4641571044922</v>
       </c>
       <c r="C116" t="n">
-        <v>317.8567199707031</v>
+        <v>317.8567504882812</v>
       </c>
       <c r="D116" t="n">
-        <v>140.5599670410156</v>
+        <v>140.5599822998047</v>
       </c>
       <c r="E116" t="n">
         <v>175.3535003662109</v>
       </c>
       <c r="F116" t="n">
-        <v>32.53269577026367</v>
+        <v>32.5327033996582</v>
       </c>
       <c r="G116" t="n">
-        <v>321.3818664550781</v>
+        <v>321.3818969726562</v>
       </c>
       <c r="H116" t="n">
         <v>158.3699951171875</v>
@@ -4846,7 +4846,7 @@
         <v>45.63135147094727</v>
       </c>
       <c r="K116" t="n">
-        <v>50.68319320678711</v>
+        <v>50.68319702148438</v>
       </c>
       <c r="L116" t="n">
         <v>4567</v>
@@ -4857,22 +4857,22 @@
         <v>44531</v>
       </c>
       <c r="B117" t="n">
-        <v>173.449462890625</v>
+        <v>173.4494171142578</v>
       </c>
       <c r="C117" t="n">
         <v>323.3659362792969</v>
       </c>
       <c r="D117" t="n">
-        <v>143.4866485595703</v>
+        <v>143.4866333007812</v>
       </c>
       <c r="E117" t="n">
         <v>166.7169952392578</v>
       </c>
       <c r="F117" t="n">
-        <v>29.28560829162598</v>
+        <v>29.28561210632324</v>
       </c>
       <c r="G117" t="n">
-        <v>333.1590576171875</v>
+        <v>333.1591186523438</v>
       </c>
       <c r="H117" t="n">
         <v>143.8999938964844</v>
@@ -4881,10 +4881,10 @@
         <v>352.260009765625</v>
       </c>
       <c r="J117" t="n">
-        <v>47.76451873779297</v>
+        <v>47.7645149230957</v>
       </c>
       <c r="K117" t="n">
-        <v>61.30046844482422</v>
+        <v>61.30047607421875</v>
       </c>
       <c r="L117" t="n">
         <v>4766.18017578125</v>
@@ -4895,13 +4895,13 @@
         <v>44562</v>
       </c>
       <c r="B118" t="n">
-        <v>170.7241363525391</v>
+        <v>170.7241973876953</v>
       </c>
       <c r="C118" t="n">
-        <v>299.0020751953125</v>
+        <v>299.0020446777344</v>
       </c>
       <c r="D118" t="n">
-        <v>134.0281219482422</v>
+        <v>134.0281372070312</v>
       </c>
       <c r="E118" t="n">
         <v>149.5735015869141</v>
@@ -4910,7 +4910,7 @@
         <v>24.3816089630127</v>
       </c>
       <c r="G118" t="n">
-        <v>310.2881774902344</v>
+        <v>310.2881469726562</v>
       </c>
       <c r="H118" t="n">
         <v>114.25</v>
@@ -4922,7 +4922,7 @@
         <v>45.27890396118164</v>
       </c>
       <c r="K118" t="n">
-        <v>53.97382354736328</v>
+        <v>53.97381973266602</v>
       </c>
       <c r="L118" t="n">
         <v>4515.5498046875</v>
@@ -4933,22 +4933,22 @@
         <v>44593</v>
       </c>
       <c r="B119" t="n">
-        <v>161.4937896728516</v>
+        <v>161.4938354492188</v>
       </c>
       <c r="C119" t="n">
-        <v>287.87548828125</v>
+        <v>287.8755493164062</v>
       </c>
       <c r="D119" t="n">
-        <v>133.783935546875</v>
+        <v>133.7839660644531</v>
       </c>
       <c r="E119" t="n">
         <v>153.5630035400391</v>
       </c>
       <c r="F119" t="n">
-        <v>24.28103637695312</v>
+        <v>24.28104209899902</v>
       </c>
       <c r="G119" t="n">
-        <v>209.0279998779297</v>
+        <v>209.0279693603516</v>
       </c>
       <c r="H119" t="n">
         <v>123.3399963378906</v>
@@ -4957,10 +4957,10 @@
         <v>290.1433410644531</v>
       </c>
       <c r="J119" t="n">
-        <v>44.57715606689453</v>
+        <v>44.57715225219727</v>
       </c>
       <c r="K119" t="n">
-        <v>54.11753463745117</v>
+        <v>54.11753082275391</v>
       </c>
       <c r="L119" t="n">
         <v>4373.93994140625</v>
@@ -4971,22 +4971,22 @@
         <v>44621</v>
       </c>
       <c r="B120" t="n">
-        <v>170.7754211425781</v>
+        <v>170.7754058837891</v>
       </c>
       <c r="C120" t="n">
-        <v>297.0478210449219</v>
+        <v>297.0477294921875</v>
       </c>
       <c r="D120" t="n">
-        <v>137.7566528320312</v>
+        <v>137.7566375732422</v>
       </c>
       <c r="E120" t="n">
         <v>162.9974975585938</v>
       </c>
       <c r="F120" t="n">
-        <v>27.1742992401123</v>
+        <v>27.17429733276367</v>
       </c>
       <c r="G120" t="n">
-        <v>220.2505340576172</v>
+        <v>220.2505493164062</v>
       </c>
       <c r="H120" t="n">
         <v>109.3399963378906</v>
@@ -4995,10 +4995,10 @@
         <v>359.2000122070312</v>
       </c>
       <c r="J120" t="n">
-        <v>46.31538009643555</v>
+        <v>46.31539154052734</v>
       </c>
       <c r="K120" t="n">
-        <v>58.4011344909668</v>
+        <v>58.40113067626953</v>
       </c>
       <c r="L120" t="n">
         <v>4530.41015625</v>
@@ -5012,16 +5012,16 @@
         <v>154.1878509521484</v>
       </c>
       <c r="C121" t="n">
-        <v>267.3825988769531</v>
+        <v>267.3824768066406</v>
       </c>
       <c r="D121" t="n">
-        <v>113.0339050292969</v>
+        <v>113.0338897705078</v>
       </c>
       <c r="E121" t="n">
         <v>124.2815017700195</v>
       </c>
       <c r="F121" t="n">
-        <v>18.47107696533203</v>
+        <v>18.47107887268066</v>
       </c>
       <c r="G121" t="n">
         <v>198.5681762695312</v>
@@ -5033,7 +5033,7 @@
         <v>290.2533264160156</v>
       </c>
       <c r="J121" t="n">
-        <v>40.73622131347656</v>
+        <v>40.73622894287109</v>
       </c>
       <c r="K121" t="n">
         <v>51.41819000244141</v>
@@ -5047,19 +5047,19 @@
         <v>44682</v>
       </c>
       <c r="B122" t="n">
-        <v>145.7852020263672</v>
+        <v>145.7852478027344</v>
       </c>
       <c r="C122" t="n">
-        <v>262.5490112304688</v>
+        <v>262.5489501953125</v>
       </c>
       <c r="D122" t="n">
-        <v>112.6896820068359</v>
+        <v>112.6896743774414</v>
       </c>
       <c r="E122" t="n">
         <v>120.2095031738281</v>
       </c>
       <c r="F122" t="n">
-        <v>18.59556579589844</v>
+        <v>18.5955638885498</v>
       </c>
       <c r="G122" t="n">
         <v>191.802978515625</v>
@@ -5071,10 +5071,10 @@
         <v>252.7533264160156</v>
       </c>
       <c r="J122" t="n">
-        <v>41.84002685546875</v>
+        <v>41.84003067016602</v>
       </c>
       <c r="K122" t="n">
-        <v>53.80549621582031</v>
+        <v>53.80550384521484</v>
       </c>
       <c r="L122" t="n">
         <v>4132.14990234375</v>
@@ -5085,10 +5085,10 @@
         <v>44713</v>
       </c>
       <c r="B123" t="n">
-        <v>133.9139709472656</v>
+        <v>133.9140167236328</v>
       </c>
       <c r="C123" t="n">
-        <v>248.0246429443359</v>
+        <v>248.0246276855469</v>
       </c>
       <c r="D123" t="n">
         <v>107.9359130859375</v>
@@ -5097,10 +5097,10 @@
         <v>106.2099990844727</v>
       </c>
       <c r="F123" t="n">
-        <v>15.10013294219971</v>
+        <v>15.10013580322266</v>
       </c>
       <c r="G123" t="n">
-        <v>159.72021484375</v>
+        <v>159.7202606201172</v>
       </c>
       <c r="H123" t="n">
         <v>76.47000122070312</v>
@@ -5109,7 +5109,7 @@
         <v>224.4733276367188</v>
       </c>
       <c r="J123" t="n">
-        <v>35.23718643188477</v>
+        <v>35.23717498779297</v>
       </c>
       <c r="K123" t="n">
         <v>45.43112182617188</v>
@@ -5123,10 +5123,10 @@
         <v>44743</v>
       </c>
       <c r="B124" t="n">
-        <v>159.1746826171875</v>
+        <v>159.1746368408203</v>
       </c>
       <c r="C124" t="n">
-        <v>271.1148681640625</v>
+        <v>271.1148376464844</v>
       </c>
       <c r="D124" t="n">
         <v>115.2235717773438</v>
@@ -5135,10 +5135,10 @@
         <v>134.9499969482422</v>
       </c>
       <c r="F124" t="n">
-        <v>18.09246635437012</v>
+        <v>18.09247016906738</v>
       </c>
       <c r="G124" t="n">
-        <v>157.5906677246094</v>
+        <v>157.5906372070312</v>
       </c>
       <c r="H124" t="n">
         <v>94.47000122070312</v>
@@ -5147,10 +5147,10 @@
         <v>297.1499938964844</v>
       </c>
       <c r="J124" t="n">
-        <v>34.20107269287109</v>
+        <v>34.20106887817383</v>
       </c>
       <c r="K124" t="n">
-        <v>50.07607650756836</v>
+        <v>50.07607269287109</v>
       </c>
       <c r="L124" t="n">
         <v>4130.2900390625</v>
@@ -5161,22 +5161,22 @@
         <v>44774</v>
       </c>
       <c r="B125" t="n">
-        <v>154.2071685791016</v>
+        <v>154.2071380615234</v>
       </c>
       <c r="C125" t="n">
-        <v>253.0414886474609</v>
+        <v>253.0414733886719</v>
       </c>
       <c r="D125" t="n">
-        <v>107.1999130249023</v>
+        <v>107.1999053955078</v>
       </c>
       <c r="E125" t="n">
         <v>126.7699966430664</v>
       </c>
       <c r="F125" t="n">
-        <v>15.03538513183594</v>
+        <v>15.03538703918457</v>
       </c>
       <c r="G125" t="n">
-        <v>161.3843231201172</v>
+        <v>161.3843078613281</v>
       </c>
       <c r="H125" t="n">
         <v>84.87000274658203</v>
@@ -5185,7 +5185,7 @@
         <v>275.6099853515625</v>
       </c>
       <c r="J125" t="n">
-        <v>30.36957550048828</v>
+        <v>30.36957359313965</v>
       </c>
       <c r="K125" t="n">
         <v>46.67489242553711</v>
@@ -5199,13 +5199,13 @@
         <v>44805</v>
       </c>
       <c r="B126" t="n">
-        <v>135.5515747070312</v>
+        <v>135.5516357421875</v>
       </c>
       <c r="C126" t="n">
-        <v>225.3924713134766</v>
+        <v>225.3924560546875</v>
       </c>
       <c r="D126" t="n">
-        <v>94.7484130859375</v>
+        <v>94.74840545654297</v>
       </c>
       <c r="E126" t="n">
         <v>113</v>
@@ -5214,7 +5214,7 @@
         <v>12.09545516967773</v>
       </c>
       <c r="G126" t="n">
-        <v>134.3928375244141</v>
+        <v>134.3927917480469</v>
       </c>
       <c r="H126" t="n">
         <v>63.36000061035156</v>
@@ -5223,10 +5223,10 @@
         <v>265.25</v>
       </c>
       <c r="J126" t="n">
-        <v>24.5182933807373</v>
+        <v>24.51829528808594</v>
       </c>
       <c r="K126" t="n">
-        <v>41.87030410766602</v>
+        <v>41.87031555175781</v>
       </c>
       <c r="L126" t="n">
         <v>3585.6201171875</v>
@@ -5237,13 +5237,13 @@
         <v>44835</v>
       </c>
       <c r="B127" t="n">
-        <v>150.4015045166016</v>
+        <v>150.4014739990234</v>
       </c>
       <c r="C127" t="n">
-        <v>224.6473083496094</v>
+        <v>224.6473236083984</v>
       </c>
       <c r="D127" t="n">
-        <v>93.61915588378906</v>
+        <v>93.61914825439453</v>
       </c>
       <c r="E127" t="n">
         <v>102.4400024414062</v>
@@ -5261,7 +5261,7 @@
         <v>227.5399932861328</v>
       </c>
       <c r="J127" t="n">
-        <v>27.04909133911133</v>
+        <v>27.04909324645996</v>
       </c>
       <c r="K127" t="n">
         <v>44.33249282836914</v>
@@ -5278,19 +5278,19 @@
         <v>145.4340972900391</v>
       </c>
       <c r="C128" t="n">
-        <v>247.6114196777344</v>
+        <v>247.6114044189453</v>
       </c>
       <c r="D128" t="n">
-        <v>100.0380630493164</v>
+        <v>100.0380706787109</v>
       </c>
       <c r="E128" t="n">
         <v>96.54000091552734</v>
       </c>
       <c r="F128" t="n">
-        <v>16.86660766601562</v>
+        <v>16.86661148071289</v>
       </c>
       <c r="G128" t="n">
-        <v>116.9795989990234</v>
+        <v>116.979606628418</v>
       </c>
       <c r="H128" t="n">
         <v>77.62999725341797</v>
@@ -5302,7 +5302,7 @@
         <v>28.9958324432373</v>
       </c>
       <c r="K128" t="n">
-        <v>51.96234130859375</v>
+        <v>51.96233749389648</v>
       </c>
       <c r="L128" t="n">
         <v>4080.110107421875</v>
@@ -5313,13 +5313,13 @@
         <v>44896</v>
       </c>
       <c r="B129" t="n">
-        <v>127.6515045166016</v>
+        <v>127.6515121459961</v>
       </c>
       <c r="C129" t="n">
-        <v>232.7434844970703</v>
+        <v>232.7434997558594</v>
       </c>
       <c r="D129" t="n">
-        <v>87.39835357666016</v>
+        <v>87.39834594726562</v>
       </c>
       <c r="E129" t="n">
         <v>84</v>
@@ -5328,7 +5328,7 @@
         <v>14.56530094146729</v>
       </c>
       <c r="G129" t="n">
-        <v>119.1983489990234</v>
+        <v>119.198356628418</v>
       </c>
       <c r="H129" t="n">
         <v>64.76999664306641</v>
@@ -5337,7 +5337,7 @@
         <v>123.1800003051758</v>
       </c>
       <c r="J129" t="n">
-        <v>25.48586082458496</v>
+        <v>25.48585891723633</v>
       </c>
       <c r="K129" t="n">
         <v>53.16610336303711</v>
@@ -5351,19 +5351,19 @@
         <v>44927</v>
       </c>
       <c r="B130" t="n">
-        <v>141.7597045898438</v>
+        <v>141.7596740722656</v>
       </c>
       <c r="C130" t="n">
-        <v>240.4977416992188</v>
+        <v>240.4976959228516</v>
       </c>
       <c r="D130" t="n">
-        <v>97.9083251953125</v>
+        <v>97.90833282470703</v>
       </c>
       <c r="E130" t="n">
         <v>103.129997253418</v>
       </c>
       <c r="F130" t="n">
-        <v>19.47189712524414</v>
+        <v>19.47190093994141</v>
       </c>
       <c r="G130" t="n">
         <v>147.5567474365234</v>
@@ -5378,7 +5378,7 @@
         <v>27.25048828125</v>
       </c>
       <c r="K130" t="n">
-        <v>55.6269645690918</v>
+        <v>55.62695693969727</v>
       </c>
       <c r="L130" t="n">
         <v>4076.60009765625</v>
@@ -5389,22 +5389,22 @@
         <v>44958</v>
       </c>
       <c r="B131" t="n">
-        <v>145.0461120605469</v>
+        <v>145.0460815429688</v>
       </c>
       <c r="C131" t="n">
-        <v>242.6664886474609</v>
+        <v>242.6664581298828</v>
       </c>
       <c r="D131" t="n">
-        <v>89.21108245849609</v>
+        <v>89.21109008789062</v>
       </c>
       <c r="E131" t="n">
         <v>94.23000335693359</v>
       </c>
       <c r="F131" t="n">
-        <v>23.13863945007324</v>
+        <v>23.13863563537598</v>
       </c>
       <c r="G131" t="n">
-        <v>173.2803802490234</v>
+        <v>173.2803497314453</v>
       </c>
       <c r="H131" t="n">
         <v>78.58000183105469</v>
@@ -5416,7 +5416,7 @@
         <v>24.33236503601074</v>
       </c>
       <c r="K131" t="n">
-        <v>56.50938415527344</v>
+        <v>56.50938034057617</v>
       </c>
       <c r="L131" t="n">
         <v>3970.14990234375</v>
@@ -5427,22 +5427,22 @@
         <v>44986</v>
       </c>
       <c r="B132" t="n">
-        <v>162.2556457519531</v>
+        <v>162.2556304931641</v>
       </c>
       <c r="C132" t="n">
         <v>280.4937438964844</v>
       </c>
       <c r="D132" t="n">
-        <v>102.7522277832031</v>
+        <v>102.7522430419922</v>
       </c>
       <c r="E132" t="n">
         <v>103.2900009155273</v>
       </c>
       <c r="F132" t="n">
-        <v>27.68914031982422</v>
+        <v>27.68913841247559</v>
       </c>
       <c r="G132" t="n">
-        <v>209.9293518066406</v>
+        <v>209.9293823242188</v>
       </c>
       <c r="H132" t="n">
         <v>98.01000213623047</v>
@@ -5454,7 +5454,7 @@
         <v>31.88681411743164</v>
       </c>
       <c r="K132" t="n">
-        <v>61.44130706787109</v>
+        <v>61.44131469726562</v>
       </c>
       <c r="L132" t="n">
         <v>4109.31005859375</v>
@@ -5465,19 +5465,19 @@
         <v>45017</v>
       </c>
       <c r="B133" t="n">
-        <v>166.958984375</v>
+        <v>166.9589385986328</v>
       </c>
       <c r="C133" t="n">
-        <v>298.9403381347656</v>
+        <v>298.9404296875</v>
       </c>
       <c r="D133" t="n">
-        <v>106.3282012939453</v>
+        <v>106.3282089233398</v>
       </c>
       <c r="E133" t="n">
         <v>105.4499969482422</v>
       </c>
       <c r="F133" t="n">
-        <v>27.66123008728027</v>
+        <v>27.66123390197754</v>
       </c>
       <c r="G133" t="n">
         <v>238.0401306152344</v>
@@ -5489,10 +5489,10 @@
         <v>164.3099975585938</v>
       </c>
       <c r="J133" t="n">
-        <v>30.31541061401367</v>
+        <v>30.3154125213623</v>
       </c>
       <c r="K133" t="n">
-        <v>60.00090408325195</v>
+        <v>60.00090026855469</v>
       </c>
       <c r="L133" t="n">
         <v>4169.47998046875</v>
@@ -5503,7 +5503,7 @@
         <v>45047</v>
       </c>
       <c r="B134" t="n">
-        <v>174.6488342285156</v>
+        <v>174.6488189697266</v>
       </c>
       <c r="C134" t="n">
         <v>320.1966857910156</v>
@@ -5515,7 +5515,7 @@
         <v>120.5800018310547</v>
       </c>
       <c r="F134" t="n">
-        <v>37.71433258056641</v>
+        <v>37.71432876586914</v>
       </c>
       <c r="G134" t="n">
         <v>262.2086486816406</v>
@@ -5527,10 +5527,10 @@
         <v>203.9299926757812</v>
       </c>
       <c r="J134" t="n">
-        <v>30.81196403503418</v>
+        <v>30.81196212768555</v>
       </c>
       <c r="K134" t="n">
-        <v>77.37960815429688</v>
+        <v>77.37961578369141</v>
       </c>
       <c r="L134" t="n">
         <v>4179.830078125</v>
@@ -5541,10 +5541,10 @@
         <v>45078</v>
       </c>
       <c r="B135" t="n">
-        <v>191.1234741210938</v>
+        <v>191.1234436035156</v>
       </c>
       <c r="C135" t="n">
-        <v>332.0434875488281</v>
+        <v>332.0435180664062</v>
       </c>
       <c r="D135" t="n">
         <v>118.5717010498047</v>
@@ -5553,10 +5553,10 @@
         <v>130.3600006103516</v>
       </c>
       <c r="F135" t="n">
-        <v>42.17256927490234</v>
+        <v>42.17255401611328</v>
       </c>
       <c r="G135" t="n">
-        <v>284.2574462890625</v>
+        <v>284.2575073242188</v>
       </c>
       <c r="H135" t="n">
         <v>113.9100036621094</v>
@@ -5565,10 +5565,10 @@
         <v>261.7699890136719</v>
       </c>
       <c r="J135" t="n">
-        <v>32.77200698852539</v>
+        <v>32.77201080322266</v>
       </c>
       <c r="K135" t="n">
-        <v>83.51774597167969</v>
+        <v>83.51773071289062</v>
       </c>
       <c r="L135" t="n">
         <v>4450.3798828125</v>
@@ -5579,10 +5579,10 @@
         <v>45108</v>
       </c>
       <c r="B136" t="n">
-        <v>193.5670623779297</v>
+        <v>193.5670318603516</v>
       </c>
       <c r="C136" t="n">
-        <v>327.5388488769531</v>
+        <v>327.5387878417969</v>
       </c>
       <c r="D136" t="n">
         <v>131.4689788818359</v>
@@ -5606,7 +5606,7 @@
         <v>35.05546951293945</v>
       </c>
       <c r="K136" t="n">
-        <v>86.52366638183594</v>
+        <v>86.52365112304688</v>
       </c>
       <c r="L136" t="n">
         <v>4588.9599609375</v>
@@ -5617,22 +5617,22 @@
         <v>45139</v>
       </c>
       <c r="B137" t="n">
-        <v>185.3629455566406</v>
+        <v>185.3629608154297</v>
       </c>
       <c r="C137" t="n">
         <v>320.259033203125</v>
       </c>
       <c r="D137" t="n">
-        <v>134.8864593505859</v>
+        <v>134.886474609375</v>
       </c>
       <c r="E137" t="n">
         <v>138.0099945068359</v>
       </c>
       <c r="F137" t="n">
-        <v>49.20397567749023</v>
+        <v>49.2039794921875</v>
       </c>
       <c r="G137" t="n">
-        <v>293.0829772949219</v>
+        <v>293.0829467773438</v>
       </c>
       <c r="H137" t="n">
         <v>105.7200012207031</v>
@@ -5658,7 +5658,7 @@
         <v>168.9252777099609</v>
       </c>
       <c r="C138" t="n">
-        <v>308.5238342285156</v>
+        <v>308.5238952636719</v>
       </c>
       <c r="D138" t="n">
         <v>129.6265106201172</v>
@@ -5667,10 +5667,10 @@
         <v>127.120002746582</v>
       </c>
       <c r="F138" t="n">
-        <v>43.36948013305664</v>
+        <v>43.36947250366211</v>
       </c>
       <c r="G138" t="n">
-        <v>297.3619995117188</v>
+        <v>297.3619384765625</v>
       </c>
       <c r="H138" t="n">
         <v>102.8199996948242</v>
@@ -5679,7 +5679,7 @@
         <v>250.2200012207031</v>
       </c>
       <c r="J138" t="n">
-        <v>34.96520233154297</v>
+        <v>34.96520614624023</v>
       </c>
       <c r="K138" t="n">
         <v>80.40530395507812</v>
@@ -5693,10 +5693,10 @@
         <v>45200</v>
       </c>
       <c r="B139" t="n">
-        <v>168.4911346435547</v>
+        <v>168.4911651611328</v>
       </c>
       <c r="C139" t="n">
-        <v>330.3721313476562</v>
+        <v>330.3721923828125</v>
       </c>
       <c r="D139" t="n">
         <v>122.9104309082031</v>
@@ -5705,10 +5705,10 @@
         <v>133.0899963378906</v>
       </c>
       <c r="F139" t="n">
-        <v>40.65856552124023</v>
+        <v>40.6585693359375</v>
       </c>
       <c r="G139" t="n">
-        <v>298.4118347167969</v>
+        <v>298.411865234375</v>
       </c>
       <c r="H139" t="n">
         <v>98.5</v>
@@ -5731,13 +5731,13 @@
         <v>45231</v>
       </c>
       <c r="B140" t="n">
-        <v>187.6620941162109</v>
+        <v>187.662109375</v>
       </c>
       <c r="C140" t="n">
-        <v>370.9898986816406</v>
+        <v>370.9898681640625</v>
       </c>
       <c r="D140" t="n">
-        <v>131.2807769775391</v>
+        <v>131.2807464599609</v>
       </c>
       <c r="E140" t="n">
         <v>146.0899963378906</v>
@@ -5746,7 +5746,7 @@
         <v>46.63073348999023</v>
       </c>
       <c r="G140" t="n">
-        <v>324.0463562011719</v>
+        <v>324.04638671875</v>
       </c>
       <c r="H140" t="n">
         <v>121.1600036621094</v>
@@ -5758,7 +5758,7 @@
         <v>44.1092529296875</v>
       </c>
       <c r="K140" t="n">
-        <v>89.61640930175781</v>
+        <v>89.61639404296875</v>
       </c>
       <c r="L140" t="n">
         <v>4567.7998046875</v>
@@ -5769,22 +5769,22 @@
         <v>45261</v>
       </c>
       <c r="B141" t="n">
-        <v>190.2110443115234</v>
+        <v>190.2109985351562</v>
       </c>
       <c r="C141" t="n">
-        <v>368.1798706054688</v>
+        <v>368.1798400878906</v>
       </c>
       <c r="D141" t="n">
-        <v>138.373291015625</v>
+        <v>138.3732757568359</v>
       </c>
       <c r="E141" t="n">
         <v>151.9400024414062</v>
       </c>
       <c r="F141" t="n">
-        <v>49.37887573242188</v>
+        <v>49.37887954711914</v>
       </c>
       <c r="G141" t="n">
-        <v>350.6019897460938</v>
+        <v>350.6020812988281</v>
       </c>
       <c r="H141" t="n">
         <v>147.4100036621094</v>
@@ -5796,7 +5796,7 @@
         <v>49.58590316772461</v>
       </c>
       <c r="K141" t="n">
-        <v>108.5568084716797</v>
+        <v>108.5568161010742</v>
       </c>
       <c r="L141" t="n">
         <v>4769.830078125</v>
@@ -5807,19 +5807,19 @@
         <v>45292</v>
       </c>
       <c r="B142" t="n">
-        <v>182.178955078125</v>
+        <v>182.1789398193359</v>
       </c>
       <c r="C142" t="n">
         <v>389.2696228027344</v>
       </c>
       <c r="D142" t="n">
-        <v>138.7794342041016</v>
+        <v>138.7793884277344</v>
       </c>
       <c r="E142" t="n">
         <v>155.1999969482422</v>
       </c>
       <c r="F142" t="n">
-        <v>61.34918975830078</v>
+        <v>61.34917831420898</v>
       </c>
       <c r="G142" t="n">
         <v>386.4388427734375</v>
@@ -5834,7 +5834,7 @@
         <v>42.51066207885742</v>
       </c>
       <c r="K142" t="n">
-        <v>114.7565841674805</v>
+        <v>114.756591796875</v>
       </c>
       <c r="L142" t="n">
         <v>4845.64990234375</v>
@@ -5845,19 +5845,19 @@
         <v>45323</v>
       </c>
       <c r="B143" t="n">
-        <v>178.8007659912109</v>
+        <v>178.8008117675781</v>
       </c>
       <c r="C143" t="n">
-        <v>405.7428588867188</v>
+        <v>405.7428894042969</v>
       </c>
       <c r="D143" t="n">
-        <v>137.1548767089844</v>
+        <v>137.1548919677734</v>
       </c>
       <c r="E143" t="n">
         <v>176.7599945068359</v>
       </c>
       <c r="F143" t="n">
-        <v>78.88334655761719</v>
+        <v>78.88336944580078</v>
       </c>
       <c r="G143" t="n">
         <v>485.9953308105469</v>
@@ -5872,7 +5872,7 @@
         <v>42.60557556152344</v>
       </c>
       <c r="K143" t="n">
-        <v>126.4743957519531</v>
+        <v>126.4743728637695</v>
       </c>
       <c r="L143" t="n">
         <v>5096.27001953125</v>
@@ -5883,7 +5883,7 @@
         <v>45352</v>
       </c>
       <c r="B144" t="n">
-        <v>169.6307525634766</v>
+        <v>169.6307220458984</v>
       </c>
       <c r="C144" t="n">
         <v>412.6877136230469</v>
@@ -5898,7 +5898,7 @@
         <v>90.09910583496094</v>
       </c>
       <c r="G144" t="n">
-        <v>481.4836730957031</v>
+        <v>481.4837341308594</v>
       </c>
       <c r="H144" t="n">
         <v>180.4900054931641</v>
@@ -5910,7 +5910,7 @@
         <v>43.71401214599609</v>
       </c>
       <c r="K144" t="n">
-        <v>129.4468536376953</v>
+        <v>129.4468383789062</v>
       </c>
       <c r="L144" t="n">
         <v>5254.35009765625</v>
@@ -5921,22 +5921,22 @@
         <v>45383</v>
       </c>
       <c r="B145" t="n">
-        <v>168.4931488037109</v>
+        <v>168.4931793212891</v>
       </c>
       <c r="C145" t="n">
-        <v>381.89697265625</v>
+        <v>381.8970031738281</v>
       </c>
       <c r="D145" t="n">
-        <v>161.2456207275391</v>
+        <v>161.2456512451172</v>
       </c>
       <c r="E145" t="n">
         <v>175</v>
       </c>
       <c r="F145" t="n">
-        <v>86.15633392333984</v>
+        <v>86.15634155273438</v>
       </c>
       <c r="G145" t="n">
-        <v>426.5411682128906</v>
+        <v>426.5410766601562</v>
       </c>
       <c r="H145" t="n">
         <v>158.3800048828125</v>
@@ -5959,7 +5959,7 @@
         <v>45413</v>
       </c>
       <c r="B146" t="n">
-        <v>190.4347076416016</v>
+        <v>190.4346923828125</v>
       </c>
       <c r="C146" t="n">
         <v>407.9389343261719</v>
@@ -5971,10 +5971,10 @@
         <v>176.4400024414062</v>
       </c>
       <c r="F146" t="n">
-        <v>109.3212966918945</v>
+        <v>109.3212890625</v>
       </c>
       <c r="G146" t="n">
-        <v>462.8918151855469</v>
+        <v>462.891845703125</v>
       </c>
       <c r="H146" t="n">
         <v>166.8999938964844</v>
@@ -5986,7 +5986,7 @@
         <v>30.6555347442627</v>
       </c>
       <c r="K146" t="n">
-        <v>129.7535247802734</v>
+        <v>129.7534942626953</v>
       </c>
       <c r="L146" t="n">
         <v>5277.509765625</v>
@@ -5997,7 +5997,7 @@
         <v>45444</v>
       </c>
       <c r="B147" t="n">
-        <v>208.6312561035156</v>
+        <v>208.6312103271484</v>
       </c>
       <c r="C147" t="n">
         <v>439.2077026367188</v>
@@ -6038,19 +6038,19 @@
         <v>219.9830474853516</v>
       </c>
       <c r="C148" t="n">
-        <v>411.1031494140625</v>
+        <v>411.1031188964844</v>
       </c>
       <c r="D148" t="n">
-        <v>170.1180572509766</v>
+        <v>170.1180877685547</v>
       </c>
       <c r="E148" t="n">
         <v>186.9799957275391</v>
       </c>
       <c r="F148" t="n">
-        <v>116.6968612670898</v>
+        <v>116.6968536376953</v>
       </c>
       <c r="G148" t="n">
-        <v>471.2918395996094</v>
+        <v>471.2917785644531</v>
       </c>
       <c r="H148" t="n">
         <v>144.4799957275391</v>
@@ -6085,10 +6085,10 @@
         <v>178.5</v>
       </c>
       <c r="F149" t="n">
-        <v>119.0403823852539</v>
+        <v>119.0403747558594</v>
       </c>
       <c r="G149" t="n">
-        <v>517.4254760742188</v>
+        <v>517.425537109375</v>
       </c>
       <c r="H149" t="n">
         <v>148.5599975585938</v>
@@ -6111,22 +6111,22 @@
         <v>45536</v>
       </c>
       <c r="B150" t="n">
-        <v>231.0670471191406</v>
+        <v>231.0670928955078</v>
       </c>
       <c r="C150" t="n">
         <v>423.6082458496094</v>
       </c>
       <c r="D150" t="n">
-        <v>164.6935119628906</v>
+        <v>164.6934967041016</v>
       </c>
       <c r="E150" t="n">
         <v>186.3300018310547</v>
       </c>
       <c r="F150" t="n">
-        <v>121.1150207519531</v>
+        <v>121.1150283813477</v>
       </c>
       <c r="G150" t="n">
-        <v>568.716552734375</v>
+        <v>568.7166137695312</v>
       </c>
       <c r="H150" t="n">
         <v>164.0800018310547</v>
@@ -6138,7 +6138,7 @@
         <v>23.45999908447266</v>
       </c>
       <c r="K150" t="n">
-        <v>169.5638427734375</v>
+        <v>169.5638580322266</v>
       </c>
       <c r="L150" t="n">
         <v>5762.47998046875</v>
@@ -6152,7 +6152,7 @@
         <v>224.035888671875</v>
       </c>
       <c r="C151" t="n">
-        <v>400.0306701660156</v>
+        <v>400.0307312011719</v>
       </c>
       <c r="D151" t="n">
         <v>169.9168395996094</v>
@@ -6164,7 +6164,7 @@
         <v>132.4047241210938</v>
       </c>
       <c r="G151" t="n">
-        <v>563.88818359375</v>
+        <v>563.8881225585938</v>
       </c>
       <c r="H151" t="n">
         <v>144.0700073242188</v>
@@ -6190,7 +6190,7 @@
         <v>235.6201019287109</v>
       </c>
       <c r="C152" t="n">
-        <v>417.7091064453125</v>
+        <v>417.7090759277344</v>
       </c>
       <c r="D152" t="n">
         <v>167.7718811035156</v>
@@ -6202,7 +6202,7 @@
         <v>137.8800201416016</v>
       </c>
       <c r="G152" t="n">
-        <v>570.5842895507812</v>
+        <v>570.5843505859375</v>
       </c>
       <c r="H152" t="n">
         <v>137.1799926757812</v>
@@ -6214,7 +6214,7 @@
         <v>24.04999923706055</v>
       </c>
       <c r="K152" t="n">
-        <v>159.3212127685547</v>
+        <v>159.3211975097656</v>
       </c>
       <c r="L152" t="n">
         <v>6032.3798828125</v>
@@ -6228,7 +6228,7 @@
         <v>248.6157989501953</v>
       </c>
       <c r="C153" t="n">
-        <v>415.7757263183594</v>
+        <v>415.7756958007812</v>
       </c>
       <c r="D153" t="n">
         <v>188.1954345703125</v>
@@ -6237,10 +6237,10 @@
         <v>219.3899993896484</v>
       </c>
       <c r="F153" t="n">
-        <v>133.9398345947266</v>
+        <v>133.9398803710938</v>
       </c>
       <c r="G153" t="n">
-        <v>582.1708374023438</v>
+        <v>582.1707153320312</v>
       </c>
       <c r="H153" t="n">
         <v>120.7900009155273</v>
@@ -6263,7 +6263,7 @@
         <v>45658</v>
       </c>
       <c r="B154" t="n">
-        <v>234.2996673583984</v>
+        <v>234.2996826171875</v>
       </c>
       <c r="C154" t="n">
         <v>409.4231262207031</v>
@@ -6275,7 +6275,7 @@
         <v>237.6799926757812</v>
       </c>
       <c r="F154" t="n">
-        <v>119.7569427490234</v>
+        <v>119.7569351196289</v>
       </c>
       <c r="G154" t="n">
         <v>685.24951171875</v>
@@ -6301,13 +6301,13 @@
         <v>45689</v>
       </c>
       <c r="B155" t="n">
-        <v>240.3615875244141</v>
+        <v>240.361572265625</v>
       </c>
       <c r="C155" t="n">
         <v>392.3837585449219</v>
       </c>
       <c r="D155" t="n">
-        <v>169.2863922119141</v>
+        <v>169.2864074707031</v>
       </c>
       <c r="E155" t="n">
         <v>212.2799987792969</v>
@@ -6351,10 +6351,10 @@
         <v>190.2599945068359</v>
       </c>
       <c r="F156" t="n">
-        <v>108.1073532104492</v>
+        <v>108.1073608398438</v>
       </c>
       <c r="G156" t="n">
-        <v>573.5827026367188</v>
+        <v>573.5826416015625</v>
       </c>
       <c r="H156" t="n">
         <v>102.7399978637695</v>
@@ -6366,7 +6366,7 @@
         <v>22.70999908447266</v>
       </c>
       <c r="K156" t="n">
-        <v>165.5204467773438</v>
+        <v>165.5204315185547</v>
       </c>
       <c r="L156" t="n">
         <v>5611.85009765625</v>
@@ -6383,7 +6383,7 @@
         <v>390.673828125</v>
       </c>
       <c r="D157" t="n">
-        <v>158.0552215576172</v>
+        <v>158.0552062988281</v>
       </c>
       <c r="E157" t="n">
         <v>184.4199981689453</v>
@@ -6392,7 +6392,7 @@
         <v>108.64599609375</v>
       </c>
       <c r="G157" t="n">
-        <v>546.3546142578125</v>
+        <v>546.3545532226562</v>
       </c>
       <c r="H157" t="n">
         <v>97.34999847412109</v>
@@ -6404,7 +6404,7 @@
         <v>20.10000038146973</v>
       </c>
       <c r="K157" t="n">
-        <v>190.2748870849609</v>
+        <v>190.2748718261719</v>
       </c>
       <c r="L157" t="n">
         <v>5569.06005859375</v>
@@ -6421,16 +6421,16 @@
         <v>455.8537902832031</v>
       </c>
       <c r="D158" t="n">
-        <v>170.9345397949219</v>
+        <v>170.9345245361328</v>
       </c>
       <c r="E158" t="n">
         <v>205.0099945068359</v>
       </c>
       <c r="F158" t="n">
-        <v>134.7900695800781</v>
+        <v>134.7900848388672</v>
       </c>
       <c r="G158" t="n">
-        <v>644.3700561523438</v>
+        <v>644.3699951171875</v>
       </c>
       <c r="H158" t="n">
         <v>110.7300033569336</v>
@@ -6442,7 +6442,7 @@
         <v>19.54999923706055</v>
       </c>
       <c r="K158" t="n">
-        <v>239.3091888427734</v>
+        <v>239.3091583251953</v>
       </c>
       <c r="L158" t="n">
         <v>5911.68994140625</v>
@@ -6453,13 +6453,13 @@
         <v>45809</v>
       </c>
       <c r="B159" t="n">
-        <v>204.1831512451172</v>
+        <v>204.1831665039062</v>
       </c>
       <c r="C159" t="n">
         <v>492.5411682128906</v>
       </c>
       <c r="D159" t="n">
-        <v>175.6158142089844</v>
+        <v>175.6157989501953</v>
       </c>
       <c r="E159" t="n">
         <v>219.3899993896484</v>
@@ -6468,7 +6468,7 @@
         <v>157.6035003662109</v>
       </c>
       <c r="G159" t="n">
-        <v>735.0987548828125</v>
+        <v>735.0986938476562</v>
       </c>
       <c r="H159" t="n">
         <v>141.8999938964844</v>
@@ -6480,7 +6480,7 @@
         <v>22.39999961853027</v>
       </c>
       <c r="K159" t="n">
-        <v>273.1475830078125</v>
+        <v>273.1476135253906</v>
       </c>
       <c r="L159" t="n">
         <v>6204.9501953125</v>
@@ -6497,13 +6497,13 @@
         <v>528.2779541015625</v>
       </c>
       <c r="D160" t="n">
-        <v>191.2311859130859</v>
+        <v>191.2311706542969</v>
       </c>
       <c r="E160" t="n">
         <v>234.1100006103516</v>
       </c>
       <c r="F160" t="n">
-        <v>177.4348602294922</v>
+        <v>177.4348754882812</v>
       </c>
       <c r="G160" t="n">
         <v>770.305419921875</v>
@@ -6518,7 +6518,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="K160" t="n">
-        <v>291.0337219238281</v>
+        <v>291.0337829589844</v>
       </c>
       <c r="L160" t="n">
         <v>6339.39013671875</v>
@@ -6532,10 +6532,10 @@
         <v>231.2856292724609</v>
       </c>
       <c r="C161" t="n">
-        <v>502.5551147460938</v>
+        <v>502.5551452636719</v>
       </c>
       <c r="D161" t="n">
-        <v>212.1679840087891</v>
+        <v>212.16796875</v>
       </c>
       <c r="E161" t="n">
         <v>229</v>
@@ -6544,7 +6544,7 @@
         <v>173.7538909912109</v>
       </c>
       <c r="G161" t="n">
-        <v>735.7061767578125</v>
+        <v>735.7062377929688</v>
       </c>
       <c r="H161" t="n">
         <v>162.6300048828125</v>
@@ -6567,13 +6567,13 @@
         <v>45901</v>
       </c>
       <c r="B162" t="n">
-        <v>253.6928863525391</v>
+        <v>253.69287109375</v>
       </c>
       <c r="C162" t="n">
         <v>513.7232666015625</v>
       </c>
       <c r="D162" t="n">
-        <v>242.4694213867188</v>
+        <v>242.4694366455078</v>
       </c>
       <c r="E162" t="n">
         <v>219.5700073242188</v>
@@ -6582,7 +6582,7 @@
         <v>186.1340637207031</v>
       </c>
       <c r="G162" t="n">
-        <v>731.8973999023438</v>
+        <v>731.8973388671875</v>
       </c>
       <c r="H162" t="n">
         <v>161.7899932861328</v>
@@ -6594,7 +6594,7 @@
         <v>33.54999923706055</v>
       </c>
       <c r="K162" t="n">
-        <v>327.4751281738281</v>
+        <v>327.47509765625</v>
       </c>
       <c r="L162" t="n">
         <v>6688.4599609375</v>
@@ -6608,16 +6608,16 @@
         <v>269.3749389648438</v>
       </c>
       <c r="C163" t="n">
-        <v>513.5843505859375</v>
+        <v>513.5844116210938</v>
       </c>
       <c r="D163" t="n">
-        <v>280.4606323242188</v>
+        <v>280.4606018066406</v>
       </c>
       <c r="E163" t="n">
         <v>244.2200012207031</v>
       </c>
       <c r="F163" t="n">
-        <v>202.0060577392578</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="G163" t="n">
         <v>646.1581420898438</v>
@@ -6632,7 +6632,7 @@
         <v>39.9900016784668</v>
       </c>
       <c r="K163" t="n">
-        <v>366.9019775390625</v>
+        <v>366.9020080566406</v>
       </c>
       <c r="L163" t="n">
         <v>6840.2001953125</v>
@@ -6670,7 +6670,7 @@
         <v>40.56000137329102</v>
       </c>
       <c r="K164" t="n">
-        <v>399.9859313964844</v>
+        <v>399.9859924316406</v>
       </c>
       <c r="L164" t="n">
         <v>6849.08984375</v>
@@ -6684,7 +6684,7 @@
         <v>271.1220092773438</v>
       </c>
       <c r="C165" t="n">
-        <v>480.5711364746094</v>
+        <v>480.5711669921875</v>
       </c>
       <c r="D165" t="n">
         <v>312.3923034667969</v>
@@ -6708,7 +6708,7 @@
         <v>36.90000152587891</v>
       </c>
       <c r="K165" t="n">
-        <v>344.2030029296875</v>
+        <v>344.2029724121094</v>
       </c>
       <c r="L165" t="n">
         <v>6845.5</v>
@@ -6719,7 +6719,7 @@
         <v>46023</v>
       </c>
       <c r="B166" t="n">
-        <v>258.7756652832031</v>
+        <v>258.775634765625</v>
       </c>
       <c r="C166" t="n">
         <v>427.577392578125</v>
@@ -6746,7 +6746,7 @@
         <v>46.47000122070312</v>
       </c>
       <c r="K166" t="n">
-        <v>329.4840698242188</v>
+        <v>329.4841003417969</v>
       </c>
       <c r="L166" t="n">
         <v>6939.02978515625</v>
@@ -6769,7 +6769,7 @@
         <v>210</v>
       </c>
       <c r="F167" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="G167" t="n">
         <v>646.5156860351562</v>
@@ -6807,7 +6807,7 @@
         <v>208.2700042724609</v>
       </c>
       <c r="F168" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="G168" t="n">
         <v>571.1494750976562</v>
@@ -6822,7 +6822,7 @@
         <v>44.13000106811523</v>
       </c>
       <c r="K168" t="n">
-        <v>308.4592590332031</v>
+        <v>308.459228515625</v>
       </c>
       <c r="L168" t="n">
         <v>6528.52001953125</v>
@@ -6845,7 +6845,7 @@
         <v>265.0599975585938</v>
       </c>
       <c r="F169" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="G169" t="n">
         <v>610.8612670898438</v>
